--- a/docs/08-reports/test-reports/Report5.1_Unit_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.1_Unit_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\TrustCabinet\artifacts\test-report-build\template-edition\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9650A4B-6B1F-4E5D-962C-9C20E8C34A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F2252D0-B7A0-4940-B992-F0AA4410A05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="641" xr2:uid="{256E899A-564B-4101-9F0B-1747993D0BDA}" activeTab="0" firstSheet="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="641" xr2:uid="{FA2443BF-1D86-46F3-AD3C-B0AE21D421C2}" activeTab="0" firstSheet="0"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="sheet1"/>
@@ -1579,15 +1579,15 @@
     <cellStyle name="Linked Cell" xfId="36" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="37" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_Functional Test Case v1.0" xfId="38" xr:uid="{6E115658-514B-4FA3-9342-BD6B07B66BC3}"/>
-    <cellStyle name="Normal_Sheet1" xfId="39" xr:uid="{9D5AA2E5-B12D-4F2F-8497-F0CB75699699}"/>
-    <cellStyle name="Normal_Template_UnitTest Case_v0.9" xfId="40" xr:uid="{9DEADF66-DE7A-4603-ADC3-95FE26CD263D}"/>
+    <cellStyle name="Normal_Functional Test Case v1.0" xfId="38" xr:uid="{F9EB9215-3D9D-477A-A1BF-22152D517FEF}"/>
+    <cellStyle name="Normal_Sheet1" xfId="39" xr:uid="{72FCB13F-F807-43D6-9669-B02111FD556E}"/>
+    <cellStyle name="Normal_Template_UnitTest Case_v0.9" xfId="40" xr:uid="{01F03269-52A3-4F61-9E6B-7E59C032FE42}"/>
     <cellStyle name="Note" xfId="41" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="42" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="43" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="44" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="45" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="46" xr:uid="{0E9E65DB-E77E-4BB4-A9D8-E1A70CFD38AF}"/>
+    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="46" xr:uid="{CA668FF3-173A-46C6-AD3C-1653D27538D0}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1689,7 +1689,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-244A-4EA5-9F5C-89BCBBF25C68}"/>
+                <c16:uniqueId val="{00000000-DB6F-4C41-970D-7DD8E43D531B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1709,7 +1709,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-244A-4EA5-9F5C-89BCBBF25C68}"/>
+                <c16:uniqueId val="{00000001-DB6F-4C41-970D-7DD8E43D531B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1729,7 +1729,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-244A-4EA5-9F5C-89BCBBF25C68}"/>
+                <c16:uniqueId val="{00000002-DB6F-4C41-970D-7DD8E43D531B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1795,7 +1795,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>333</c:v>
+                  <c:v>332</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>280</c:v>
@@ -1808,7 +1808,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-244A-4EA5-9F5C-89BCBBF25C68}"/>
+              <c16:uniqueId val="{00000003-DB6F-4C41-970D-7DD8E43D531B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1999,7 +1999,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-90D1-4FBC-AF9D-1FE3A438F9B8}"/>
+                <c16:uniqueId val="{00000000-DC81-4115-964B-FE69E2331C3A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2019,7 +2019,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-90D1-4FBC-AF9D-1FE3A438F9B8}"/>
+                <c16:uniqueId val="{00000001-DC81-4115-964B-FE69E2331C3A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2039,7 +2039,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-90D1-4FBC-AF9D-1FE3A438F9B8}"/>
+                <c16:uniqueId val="{00000002-DC81-4115-964B-FE69E2331C3A}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2111,14 +2111,14 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>654</c:v>
+                  <c:v>653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-90D1-4FBC-AF9D-1FE3A438F9B8}"/>
+              <c16:uniqueId val="{00000003-DC81-4115-964B-FE69E2331C3A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2242,7 +2242,7 @@
         <xdr:cNvPr id="1143" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3C351E7-C85C-ED4F-5F46-67F8D1777DFA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C6FCD39-802E-D2D5-C6C5-F4853A93EA45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2321,7 +2321,7 @@
         <xdr:cNvPr id="2283" name="Chart 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{046F64AB-2021-52FA-B710-34174E42F0CB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB72EF16-361D-9EA3-1F14-D079139B0A18}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2359,7 +2359,7 @@
         <xdr:cNvPr id="2284" name="Chart 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43CA77E9-2A2D-67CD-EF59-60CD5B611BE4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E58536E-49FA-1571-FCCC-923179CDB73B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2668,7 +2668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6CE3CF-8F72-4660-BF53-83DBD73B54D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74039C5-26BA-4A5E-B171-3EF825B26970}">
   <dimension ref="A2:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -2736,7 +2736,7 @@
         <v>Issue Date</v>
       </c>
       <c r="F5" s="49" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
@@ -2822,7 +2822,7 @@
     </row>
     <row r="12" spans="1:6" s="18" customFormat="1" ht="21.75" customHeight="1">
       <c r="A12" s="22" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="B12" s="19" t="str">
         <v>2.0</v>
@@ -2898,7 +2898,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5216,7 +5216,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5301,8 +5301,8 @@
         <v>Number of TCs</v>
       </c>
       <c r="B3" s="78" t="n">
-        <f>COUNTIF(A12:A323,"UTC*")</f>
-        <v>207</v>
+        <f>COUNTIF(A12:A317,"UTC*")</f>
+        <v>204</v>
       </c>
       <c r="C3" s="105"/>
       <c r="D3" s="111"/>
@@ -5362,16 +5362,16 @@
         <v>Round 1</v>
       </c>
       <c r="B5" s="78" t="n">
-        <f>COUNTIF($F$12:$F$323,B$4)</f>
+        <f>COUNTIF($F$12:$F$317,B$4)</f>
         <v>0</v>
       </c>
       <c r="C5" s="78" t="n">
-        <f>COUNTIF($F$12:$F$323,C$4)</f>
+        <f>COUNTIF($F$12:$F$317,C$4)</f>
         <v>0</v>
       </c>
       <c r="D5" s="79" t="n">
-        <f>COUNTIF($F$12:$F$323,D$4)</f>
-        <v>207</v>
+        <f>COUNTIF($F$12:$F$317,D$4)</f>
+        <v>204</v>
       </c>
       <c r="E5" s="101"/>
       <c r="F5" s="101"/>
@@ -5397,16 +5397,16 @@
         <v>Round 2</v>
       </c>
       <c r="B6" s="78" t="n">
-        <f>COUNTIF($I$12:$I$323,B$4)</f>
+        <f>COUNTIF($I$12:$I$317,B$4)</f>
         <v>0</v>
       </c>
       <c r="C6" s="78" t="n">
-        <f>COUNTIF($I$12:$I$323,C$4)</f>
+        <f>COUNTIF($I$12:$I$317,C$4)</f>
         <v>0</v>
       </c>
       <c r="D6" s="79" t="n">
-        <f>COUNTIF($I$12:$I$323,D$4)</f>
-        <v>207</v>
+        <f>COUNTIF($I$12:$I$317,D$4)</f>
+        <v>204</v>
       </c>
       <c r="E6" s="101"/>
       <c r="F6" s="101"/>
@@ -5430,16 +5430,16 @@
         <v>Round 3</v>
       </c>
       <c r="B7" s="78" t="n">
-        <f>COUNTIF($L$12:$L$323,B$4)</f>
+        <f>COUNTIF($L$12:$L$317,B$4)</f>
         <v>0</v>
       </c>
       <c r="C7" s="78" t="n">
-        <f>COUNTIF($L$12:$L$323,C$4)</f>
+        <f>COUNTIF($L$12:$L$317,C$4)</f>
         <v>0</v>
       </c>
       <c r="D7" s="79" t="n">
-        <f>COUNTIF($L$12:$L$323,D$4)</f>
-        <v>207</v>
+        <f>COUNTIF($L$12:$L$317,D$4)</f>
+        <v>204</v>
       </c>
       <c r="E7" s="101"/>
       <c r="F7" s="101"/>
@@ -5495,15 +5495,15 @@
         <v>Count</v>
       </c>
       <c r="B9" s="82" t="n">
-        <f>COUNTIF($E$12:$E$323,B$8)</f>
-        <v>86</v>
+        <f>COUNTIF($E$12:$E$317,B$8)</f>
+        <v>83</v>
       </c>
       <c r="C9" s="82" t="n">
-        <f>COUNTIF($E$12:$E$323,C$8)</f>
+        <f>COUNTIF($E$12:$E$317,C$8)</f>
         <v>104</v>
       </c>
       <c r="D9" s="83" t="n">
-        <f>COUNTIF($E$12:$E$323,D$8)</f>
+        <f>COUNTIF($E$12:$E$317,D$8)</f>
         <v>17</v>
       </c>
       <c r="E9" s="101"/>
@@ -10203,7 +10203,7 @@
     </row>
     <row r="133" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A133" s="102" t="str">
-        <v>Create_captures_per_mic_unless_the_form_picks_the_room</v>
+        <v>Create_accepts_the_documented_maximum_lengths</v>
       </c>
       <c r="B133" s="102"/>
       <c r="C133" s="103"/>
@@ -10225,7 +10225,7 @@
       <c r="S133" s="90"/>
       <c r="T133"/>
     </row>
-    <row r="134" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
+    <row r="134" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
       <c r="A134" s="105" t="str">
         <v>UTC088</v>
       </c>
@@ -10233,20 +10233,15 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C134" s="107" t="str">
-        <v>ValidInput(); _actorId; [new(_actorId, "Chair")]</v>
+        <v>ValidInput( title: new string('t', 300), location: new string('l', 30…; _actorId; [new(_actorId, "Chair")]</v>
       </c>
       <c r="D134" s="108" t="str">
-        <v>Return:
-1. (NewService().CreateAsync(ValidInput(), _actorId, [new(_actorId, "Chair")])).Succeeded: true
-2. (NewService().CreateAsync(ValidInput() with { CaptureMode = "Room" }, _actorId, [new(_actorId, "Chair")])).Succeeded: true
-3. _repository.Meetings.Select(m =&gt; m.CaptureMode): [CaptureMode.PerMic, CaptureMode.Room]
-4. invalid.Outcome: MeetingOutcome.InvalidInformation
-5. invalid.Errors!["captureMode"]: "Cách ghi âm không hợp lệ."
+        <v>Return: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E134" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F134" s="105" t="str">
         <v>Pending</v>
@@ -10272,7 +10267,7 @@
     </row>
     <row r="135" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A135" s="102" t="str">
-        <v>Update_of_a_draft_changes_the_capture_mode_and_a_form_without_it_keeps_it</v>
+        <v>Create_stores_the_planned_schedule_in_utc</v>
       </c>
       <c r="B135" s="102"/>
       <c r="C135" s="103"/>
@@ -10294,22 +10289,19 @@
       <c r="S135" s="90"/>
       <c r="T135"/>
     </row>
-    <row r="136" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="136" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A136" s="105" t="str">
         <v>UTC089</v>
       </c>
       <c r="B136" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
+2. input = ValidInput() with { PlannedStartTime = "2099-03-01T09:00:00+07:00", PlannedEndTime = "209….</v>
       </c>
       <c r="C136" s="107" t="str">
-        <v>meeting.Id; ValidInput() with { CaptureMode = "Room" }; _actorId</v>
+        <v>input; _actorId; [new(_actorId, "Chair")]</v>
       </c>
       <c r="D136" s="108" t="str">
-        <v>Return:
-1. (NewService().UpdateAsync(meeting.Id, ValidInput() with { CaptureMode = "Room" }, _actorId)).Succeeded: true
-2. meeting.CaptureMode: CaptureMode.Room
-3. (NewService().UpdateAsync(meeting.Id, ValidInput(), _actorId)).Succeeded: true
-4. meeting.CaptureMode: CaptureMode.Room
+        <v>Return: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -10340,7 +10332,7 @@
     </row>
     <row r="137" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A137" s="102" t="str">
-        <v>A_published_meeting_changes_its_capture_mode_in_the_recordings_tab_not_by_rescheduling</v>
+        <v>Create_rejects_a_time_without_an_offset</v>
       </c>
       <c r="B137" s="102"/>
       <c r="C137" s="103"/>
@@ -10362,26 +10354,25 @@
       <c r="S137" s="90"/>
       <c r="T137"/>
     </row>
-    <row r="138" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="138" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A138" s="105" t="str">
         <v>UTC090</v>
       </c>
       <c r="B138" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Published).</v>
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C138" s="107" t="str">
-        <v>meeting.Id; ValidInput() with { CaptureMode = "Room" }; _actorId</v>
+        <v>start="2099-03-01 09:00"</v>
       </c>
       <c r="D138" s="108" t="str">
         <v>Return:
 1. Outcome: MeetingOutcome.InvalidInformation
-2. Errors!["captureMode"]: "Cuộc họp đã công bố, đổi cách ghi âm ở tab Bản ghi."
+2. Errors.Keys: contains "plannedStartTime"
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E138" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F138" s="105" t="str">
         <v>Pending</v>
@@ -10405,47 +10396,67 @@
       <c r="S138" s="94"/>
       <c r="T138"/>
     </row>
-    <row r="139" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A139" s="102" t="str">
-        <v>Create_accepts_the_documented_maximum_lengths</v>
-      </c>
-      <c r="B139" s="102"/>
-      <c r="C139" s="103"/>
-      <c r="D139" s="103"/>
-      <c r="E139" s="103"/>
-      <c r="F139" s="103"/>
-      <c r="G139" s="103"/>
-      <c r="H139" s="103"/>
-      <c r="I139" s="103"/>
-      <c r="J139" s="103"/>
-      <c r="K139" s="103"/>
-      <c r="L139" s="103"/>
-      <c r="M139" s="103"/>
-      <c r="N139" s="103"/>
-      <c r="O139" s="103"/>
-      <c r="P139" s="104"/>
+    <row r="139" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+      <c r="A139" s="105" t="str">
+        <v>UTC091</v>
+      </c>
+      <c r="B139" s="106" t="str">
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
+      </c>
+      <c r="C139" s="107" t="str">
+        <v>start="2099-03-01T09:00:00"</v>
+      </c>
+      <c r="D139" s="108" t="str">
+        <v>Return:
+1. Outcome: MeetingOutcome.InvalidInformation
+2. Errors.Keys: contains "plannedStartTime"
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E139" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F139" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G139" s="105" t="str"/>
+      <c r="H139" s="105" t="str"/>
+      <c r="I139" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J139" s="105"/>
+      <c r="K139" s="105"/>
+      <c r="L139" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M139" s="105"/>
+      <c r="N139" s="105"/>
+      <c r="O139" s="105" t="str"/>
+      <c r="P139" s="110" t="str"/>
       <c r="Q139"/>
       <c r="R139"/>
-      <c r="S139" s="90"/>
+      <c r="S139" s="94"/>
       <c r="T139"/>
     </row>
-    <row r="140" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="140" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A140" s="105" t="str">
-        <v>UTC091</v>
+        <v>UTC092</v>
       </c>
       <c r="B140" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C140" s="107" t="str">
-        <v>ValidInput( title: new string('t', 300), location: new string('l', 30…; _actorId; [new(_actorId, "Chair")]</v>
+        <v>start="not a time"</v>
       </c>
       <c r="D140" s="108" t="str">
-        <v>Return: true
+        <v>Return:
+1. Outcome: MeetingOutcome.InvalidInformation
+2. Errors.Keys: contains "plannedStartTime"
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E140" s="109" t="str">
-        <v>Boundary</v>
+        <v>Abnormal</v>
       </c>
       <c r="F140" s="105" t="str">
         <v>Pending</v>
@@ -10471,7 +10482,7 @@
     </row>
     <row r="141" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A141" s="102" t="str">
-        <v>Create_stores_the_planned_schedule_in_utc</v>
+        <v>Update_of_a_draft_keeps_a_start_that_has_already_passed</v>
       </c>
       <c r="B141" s="102"/>
       <c r="C141" s="103"/>
@@ -10493,19 +10504,22 @@
       <c r="S141" s="90"/>
       <c r="T141"/>
     </row>
-    <row r="142" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="142" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A142" s="105" t="str">
-        <v>UTC092</v>
+        <v>UTC093</v>
       </c>
       <c r="B142" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. input = ValidInput() with { PlannedStartTime = "2099-03-01T09:00:00+07:00", PlannedEndTime = "209….</v>
+2. meeting: prepared by GivenMeeting.
+3. past = DateTimeOffset.UtcNow.AddDays(-1).</v>
       </c>
       <c r="C142" s="107" t="str">
-        <v>input; _actorId; [new(_actorId, "Chair")]</v>
+        <v>meeting.Id; ValidInput(start: past); _actorId</v>
       </c>
       <c r="D142" s="108" t="str">
-        <v>Return: true
+        <v>Return:
+1. Succeeded: true
+2. Rescheduled: false
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -10536,7 +10550,7 @@
     </row>
     <row r="143" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A143" s="102" t="str">
-        <v>Create_rejects_a_time_without_an_offset</v>
+        <v>Create_leaves_the_approver_unassigned_until_submission</v>
       </c>
       <c r="B143" s="102"/>
       <c r="C143" s="103"/>
@@ -10558,25 +10572,24 @@
       <c r="S143" s="90"/>
       <c r="T143"/>
     </row>
-    <row r="144" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="144" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
       <c r="A144" s="105" t="str">
-        <v>UTC093</v>
+        <v>UTC094</v>
       </c>
       <c r="B144" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
+2. input: a new MeetingInput is prepared.</v>
       </c>
       <c r="C144" s="107" t="str">
-        <v>start="2099-03-01 09:00"</v>
+        <v>input; _actorId; [new(_actorId, "Chair")]</v>
       </c>
       <c r="D144" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingOutcome.InvalidInformation
-2. Errors.Keys: contains "plannedStartTime"
+        <v>Return: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E144" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F144" s="105" t="str">
         <v>Pending</v>
@@ -10600,67 +10613,48 @@
       <c r="S144" s="94"/>
       <c r="T144"/>
     </row>
-    <row r="145" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
-      <c r="A145" s="105" t="str">
-        <v>UTC094</v>
-      </c>
-      <c r="B145" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
-      </c>
-      <c r="C145" s="107" t="str">
-        <v>start="2099-03-01T09:00:00"</v>
-      </c>
-      <c r="D145" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingOutcome.InvalidInformation
-2. Errors.Keys: contains "plannedStartTime"
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E145" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F145" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G145" s="105" t="str"/>
-      <c r="H145" s="105" t="str"/>
-      <c r="I145" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J145" s="105"/>
-      <c r="K145" s="105"/>
-      <c r="L145" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M145" s="105"/>
-      <c r="N145" s="105"/>
-      <c r="O145" s="105" t="str"/>
-      <c r="P145" s="110" t="str"/>
+    <row r="145" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A145" s="102" t="str">
+        <v>Create_does_not_assign_or_validate_a_draft_approver</v>
+      </c>
+      <c r="B145" s="102"/>
+      <c r="C145" s="103"/>
+      <c r="D145" s="103"/>
+      <c r="E145" s="103"/>
+      <c r="F145" s="103"/>
+      <c r="G145" s="103"/>
+      <c r="H145" s="103"/>
+      <c r="I145" s="103"/>
+      <c r="J145" s="103"/>
+      <c r="K145" s="103"/>
+      <c r="L145" s="103"/>
+      <c r="M145" s="103"/>
+      <c r="N145" s="103"/>
+      <c r="O145" s="103"/>
+      <c r="P145" s="104"/>
       <c r="Q145"/>
       <c r="R145"/>
-      <c r="S145" s="94"/>
+      <c r="S145" s="90"/>
       <c r="T145"/>
     </row>
-    <row r="146" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="146" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A146" s="105" t="str">
         <v>UTC095</v>
       </c>
       <c r="B146" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
+2. _repository.IneligibleApproverIds.Add(approverId).</v>
       </c>
       <c r="C146" s="107" t="str">
-        <v>start="not a time"</v>
+        <v>ValidInput(); _actorId; [new(_actorId, "Chair")]</v>
       </c>
       <c r="D146" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingOutcome.InvalidInformation
-2. Errors.Keys: contains "plannedStartTime"
+        <v>Return: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E146" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F146" s="105" t="str">
         <v>Pending</v>
@@ -10686,7 +10680,7 @@
     </row>
     <row r="147" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A147" s="102" t="str">
-        <v>Update_of_a_draft_keeps_a_start_that_has_already_passed</v>
+        <v>Update_changes_draft_fields_and_preserves_assignment_without_changing_lifecycle</v>
       </c>
       <c r="B147" s="102"/>
       <c r="C147" s="103"/>
@@ -10708,22 +10702,20 @@
       <c r="S147" s="90"/>
       <c r="T147"/>
     </row>
-    <row r="148" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="148" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A148" s="105" t="str">
         <v>UTC096</v>
       </c>
       <c r="B148" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. past = DateTimeOffset.UtcNow.AddDays(-1).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Draft).
+3. meeting.AssignedApproverId = _otherActorId.</v>
       </c>
       <c r="C148" s="107" t="str">
-        <v>meeting.Id; ValidInput(start: past); _actorId</v>
+        <v>meeting.Id; ValidInput(title: " Giao ban mới ", mode: "Hybrid", sensitivity: "Sec…; _actorId</v>
       </c>
       <c r="D148" s="108" t="str">
-        <v>Return:
-1. Succeeded: true
-2. Rescheduled: false
+        <v>Return: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -10754,7 +10746,7 @@
     </row>
     <row r="149" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A149" s="102" t="str">
-        <v>Create_leaves_the_approver_unassigned_until_submission</v>
+        <v>Update_uses_form_defaults</v>
       </c>
       <c r="B149" s="102"/>
       <c r="C149" s="103"/>
@@ -10782,10 +10774,10 @@
       </c>
       <c r="B150" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. input: a new MeetingInput is prepared.</v>
+2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C150" s="107" t="str">
-        <v>input; _actorId; [new(_actorId, "Chair")]</v>
+        <v>meeting.Id; ValidInput(mode: null, sensitivity: null); _actorId</v>
       </c>
       <c r="D150" s="108" t="str">
         <v>Return: true
@@ -10819,7 +10811,7 @@
     </row>
     <row r="151" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A151" s="102" t="str">
-        <v>Create_does_not_assign_or_validate_a_draft_approver</v>
+        <v>Update_changes_rejected_information_without_changing_assignment_or_rejection_history</v>
       </c>
       <c r="B151" s="102"/>
       <c r="C151" s="103"/>
@@ -10841,24 +10833,29 @@
       <c r="S151" s="90"/>
       <c r="T151"/>
     </row>
-    <row r="152" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="152" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A152" s="105" t="str">
         <v>UTC098</v>
       </c>
       <c r="B152" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. _repository.IneligibleApproverIds.Add(approverId).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
+3. meeting.AssignedApproverId = _otherActorId.
+4. rejection: a new MeetingStatusHistory is prepared.
+5. meeting.StatusHistory.Add(rejection).</v>
       </c>
       <c r="C152" s="107" t="str">
-        <v>ValidInput(); _actorId; [new(_actorId, "Chair")]</v>
+        <v>meeting.Id; _actorId</v>
       </c>
       <c r="D152" s="108" t="str">
-        <v>Return: true
+        <v>Return:
+1. check.Succeeded: true
+2. result.Succeeded: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E152" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F152" s="105" t="str">
         <v>Pending</v>
@@ -10884,7 +10881,7 @@
     </row>
     <row r="153" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A153" s="102" t="str">
-        <v>Update_changes_draft_fields_and_preserves_assignment_without_changing_lifecycle</v>
+        <v>Update_returns_validation_errors_without_saving</v>
       </c>
       <c r="B153" s="102"/>
       <c r="C153" s="103"/>
@@ -10906,25 +10903,27 @@
       <c r="S153" s="90"/>
       <c r="T153"/>
     </row>
-    <row r="154" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="154" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A154" s="105" t="str">
         <v>UTC099</v>
       </c>
       <c r="B154" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Draft).
-3. meeting.AssignedApproverId = _otherActorId.</v>
+2. meeting: prepared by GivenMeeting (status).
+3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C154" s="107" t="str">
-        <v>meeting.Id; ValidInput(title: " Giao ban mới ", mode: "Hybrid", sensitivity: "Sec…; _actorId</v>
+        <v>status=MeetingStatus.Draft</v>
       </c>
       <c r="D154" s="108" t="str">
-        <v>Return: true
+        <v>Return:
+1. Outcome: MeetingOutcome.InvalidInformation
+2. Errors.Keys: contains "title"
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E154" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F154" s="105" t="str">
         <v>Pending</v>
@@ -10948,113 +10947,130 @@
       <c r="S154" s="94"/>
       <c r="T154"/>
     </row>
-    <row r="155" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A155" s="102" t="str">
-        <v>Update_uses_form_defaults</v>
-      </c>
-      <c r="B155" s="102"/>
-      <c r="C155" s="103"/>
-      <c r="D155" s="103"/>
-      <c r="E155" s="103"/>
-      <c r="F155" s="103"/>
-      <c r="G155" s="103"/>
-      <c r="H155" s="103"/>
-      <c r="I155" s="103"/>
-      <c r="J155" s="103"/>
-      <c r="K155" s="103"/>
-      <c r="L155" s="103"/>
-      <c r="M155" s="103"/>
-      <c r="N155" s="103"/>
-      <c r="O155" s="103"/>
-      <c r="P155" s="104"/>
+    <row r="155" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+      <c r="A155" s="105" t="str">
+        <v>UTC100</v>
+      </c>
+      <c r="B155" s="106" t="str">
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (status).
+3. oldTitle = meeting.Title.</v>
+      </c>
+      <c r="C155" s="107" t="str">
+        <v>status=MeetingStatus.Rejected</v>
+      </c>
+      <c r="D155" s="108" t="str">
+        <v>Return:
+1. Outcome: MeetingOutcome.InvalidInformation
+2. Errors.Keys: contains "title"
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E155" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F155" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G155" s="105" t="str"/>
+      <c r="H155" s="105" t="str"/>
+      <c r="I155" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J155" s="105"/>
+      <c r="K155" s="105"/>
+      <c r="L155" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M155" s="105"/>
+      <c r="N155" s="105"/>
+      <c r="O155" s="105" t="str"/>
+      <c r="P155" s="110" t="str"/>
       <c r="Q155"/>
       <c r="R155"/>
-      <c r="S155" s="90"/>
+      <c r="S155" s="94"/>
       <c r="T155"/>
     </row>
-    <row r="156" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
-      <c r="A156" s="105" t="str">
-        <v>UTC100</v>
-      </c>
-      <c r="B156" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.</v>
-      </c>
-      <c r="C156" s="107" t="str">
-        <v>meeting.Id; ValidInput(mode: null, sensitivity: null); _actorId</v>
-      </c>
-      <c r="D156" s="108" t="str">
-        <v>Return: true
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E156" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F156" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G156" s="105" t="str"/>
-      <c r="H156" s="105" t="str"/>
-      <c r="I156" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J156" s="105"/>
-      <c r="K156" s="105"/>
-      <c r="L156" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M156" s="105"/>
-      <c r="N156" s="105"/>
-      <c r="O156" s="105" t="str"/>
-      <c r="P156" s="110" t="str"/>
+    <row r="156" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A156" s="102" t="str">
+        <v>Update_rejects_a_meeting_outside_draft_rejected_or_published</v>
+      </c>
+      <c r="B156" s="102"/>
+      <c r="C156" s="103"/>
+      <c r="D156" s="103"/>
+      <c r="E156" s="103"/>
+      <c r="F156" s="103"/>
+      <c r="G156" s="103"/>
+      <c r="H156" s="103"/>
+      <c r="I156" s="103"/>
+      <c r="J156" s="103"/>
+      <c r="K156" s="103"/>
+      <c r="L156" s="103"/>
+      <c r="M156" s="103"/>
+      <c r="N156" s="103"/>
+      <c r="O156" s="103"/>
+      <c r="P156" s="104"/>
       <c r="Q156"/>
       <c r="R156"/>
-      <c r="S156" s="94"/>
+      <c r="S156" s="90"/>
       <c r="T156"/>
     </row>
-    <row r="157" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A157" s="102" t="str">
-        <v>Update_changes_rejected_information_without_changing_assignment_or_rejection_history</v>
-      </c>
-      <c r="B157" s="102"/>
-      <c r="C157" s="103"/>
-      <c r="D157" s="103"/>
-      <c r="E157" s="103"/>
-      <c r="F157" s="103"/>
-      <c r="G157" s="103"/>
-      <c r="H157" s="103"/>
-      <c r="I157" s="103"/>
-      <c r="J157" s="103"/>
-      <c r="K157" s="103"/>
-      <c r="L157" s="103"/>
-      <c r="M157" s="103"/>
-      <c r="N157" s="103"/>
-      <c r="O157" s="103"/>
-      <c r="P157" s="104"/>
+    <row r="157" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+      <c r="A157" s="105" t="str">
+        <v>UTC101</v>
+      </c>
+      <c r="B157" s="106" t="str">
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (status).
+3. oldTitle = meeting.Title.</v>
+      </c>
+      <c r="C157" s="107" t="str">
+        <v>status=MeetingStatus.WaitingApproval</v>
+      </c>
+      <c r="D157" s="108" t="str">
+        <v>Return: MeetingOutcome.NotEditable
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E157" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F157" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G157" s="105" t="str"/>
+      <c r="H157" s="105" t="str"/>
+      <c r="I157" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J157" s="105"/>
+      <c r="K157" s="105"/>
+      <c r="L157" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M157" s="105"/>
+      <c r="N157" s="105"/>
+      <c r="O157" s="105" t="str"/>
+      <c r="P157" s="110" t="str"/>
       <c r="Q157"/>
       <c r="R157"/>
-      <c r="S157" s="90"/>
+      <c r="S157" s="94"/>
       <c r="T157"/>
     </row>
-    <row r="158" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="158" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A158" s="105" t="str">
-        <v>UTC101</v>
+        <v>UTC102</v>
       </c>
       <c r="B158" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. meeting.AssignedApproverId = _otherActorId.
-4. rejection: a new MeetingStatusHistory is prepared.
-5. meeting.StatusHistory.Add(rejection).</v>
+2. meeting: prepared by GivenMeeting (status).
+3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C158" s="107" t="str">
-        <v>meeting.Id; _actorId</v>
+        <v>status=MeetingStatus.Approved</v>
       </c>
       <c r="D158" s="108" t="str">
-        <v>Return:
-1. check.Succeeded: true
-2. result.Succeeded: true
+        <v>Return: MeetingOutcome.NotEditable
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -11083,33 +11099,51 @@
       <c r="S158" s="94"/>
       <c r="T158"/>
     </row>
-    <row r="159" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A159" s="102" t="str">
-        <v>Update_returns_validation_errors_without_saving</v>
-      </c>
-      <c r="B159" s="102"/>
-      <c r="C159" s="103"/>
-      <c r="D159" s="103"/>
-      <c r="E159" s="103"/>
-      <c r="F159" s="103"/>
-      <c r="G159" s="103"/>
-      <c r="H159" s="103"/>
-      <c r="I159" s="103"/>
-      <c r="J159" s="103"/>
-      <c r="K159" s="103"/>
-      <c r="L159" s="103"/>
-      <c r="M159" s="103"/>
-      <c r="N159" s="103"/>
-      <c r="O159" s="103"/>
-      <c r="P159" s="104"/>
+    <row r="159" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+      <c r="A159" s="105" t="str">
+        <v>UTC103</v>
+      </c>
+      <c r="B159" s="106" t="str">
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (status).
+3. oldTitle = meeting.Title.</v>
+      </c>
+      <c r="C159" s="107" t="str">
+        <v>status=MeetingStatus.InProgress</v>
+      </c>
+      <c r="D159" s="108" t="str">
+        <v>Return: MeetingOutcome.NotEditable
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E159" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F159" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G159" s="105" t="str"/>
+      <c r="H159" s="105" t="str"/>
+      <c r="I159" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J159" s="105"/>
+      <c r="K159" s="105"/>
+      <c r="L159" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M159" s="105"/>
+      <c r="N159" s="105"/>
+      <c r="O159" s="105" t="str"/>
+      <c r="P159" s="110" t="str"/>
       <c r="Q159"/>
       <c r="R159"/>
-      <c r="S159" s="90"/>
+      <c r="S159" s="94"/>
       <c r="T159"/>
     </row>
     <row r="160" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A160" s="105" t="str">
-        <v>UTC102</v>
+        <v>UTC104</v>
       </c>
       <c r="B160" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
@@ -11117,12 +11151,10 @@
 3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C160" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>status=MeetingStatus.Ended</v>
       </c>
       <c r="D160" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingOutcome.InvalidInformation
-2. Errors.Keys: contains "title"
+        <v>Return: MeetingOutcome.NotEditable
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -11151,93 +11183,95 @@
       <c r="S160" s="94"/>
       <c r="T160"/>
     </row>
-    <row r="161" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
-      <c r="A161" s="105" t="str">
-        <v>UTC103</v>
-      </c>
-      <c r="B161" s="106" t="str">
+    <row r="161" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A161" s="102" t="str">
+        <v>Update_does_not_save_when_information_is_unchanged</v>
+      </c>
+      <c r="B161" s="102"/>
+      <c r="C161" s="103"/>
+      <c r="D161" s="103"/>
+      <c r="E161" s="103"/>
+      <c r="F161" s="103"/>
+      <c r="G161" s="103"/>
+      <c r="H161" s="103"/>
+      <c r="I161" s="103"/>
+      <c r="J161" s="103"/>
+      <c r="K161" s="103"/>
+      <c r="L161" s="103"/>
+      <c r="M161" s="103"/>
+      <c r="N161" s="103"/>
+      <c r="O161" s="103"/>
+      <c r="P161" s="104"/>
+      <c r="Q161"/>
+      <c r="R161"/>
+      <c r="S161" s="90"/>
+      <c r="T161"/>
+    </row>
+    <row r="162" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+      <c r="A162" s="105" t="str">
+        <v>UTC105</v>
+      </c>
+      <c r="B162" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (status).
-3. oldTitle = meeting.Title.</v>
-      </c>
-      <c r="C161" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
-      </c>
-      <c r="D161" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingOutcome.InvalidInformation
-2. Errors.Keys: contains "title"
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E161" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F161" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G161" s="105" t="str"/>
-      <c r="H161" s="105" t="str"/>
-      <c r="I161" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J161" s="105"/>
-      <c r="K161" s="105"/>
-      <c r="L161" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M161" s="105"/>
-      <c r="N161" s="105"/>
-      <c r="O161" s="105" t="str"/>
-      <c r="P161" s="110" t="str"/>
-      <c r="Q161"/>
-      <c r="R161"/>
-      <c r="S161" s="94"/>
-      <c r="T161"/>
-    </row>
-    <row r="162" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A162" s="102" t="str">
-        <v>Update_rejects_a_meeting_outside_draft_rejected_or_published</v>
-      </c>
-      <c r="B162" s="102"/>
-      <c r="C162" s="103"/>
-      <c r="D162" s="103"/>
-      <c r="E162" s="103"/>
-      <c r="F162" s="103"/>
-      <c r="G162" s="103"/>
-      <c r="H162" s="103"/>
-      <c r="I162" s="103"/>
-      <c r="J162" s="103"/>
-      <c r="K162" s="103"/>
-      <c r="L162" s="103"/>
-      <c r="M162" s="103"/>
-      <c r="N162" s="103"/>
-      <c r="O162" s="103"/>
-      <c r="P162" s="104"/>
+3. meeting.AssignedApproverId = assigned ? _otherActorId : null.
+4. meeting.UpdatedAt = new DateTimeOffset(2026, 9, 1, 0, 0, 0, TimeSpan.Zero).
+5. updatedAt = meeting.UpdatedAt.</v>
+      </c>
+      <c r="C162" s="107" t="str">
+        <v>status=MeetingStatus.Draft; assigned=false</v>
+      </c>
+      <c r="D162" s="108" t="str">
+        <v>Return: true
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E162" s="109" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F162" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G162" s="105" t="str"/>
+      <c r="H162" s="105" t="str"/>
+      <c r="I162" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J162" s="105"/>
+      <c r="K162" s="105"/>
+      <c r="L162" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M162" s="105"/>
+      <c r="N162" s="105"/>
+      <c r="O162" s="105" t="str"/>
+      <c r="P162" s="110" t="str"/>
       <c r="Q162"/>
       <c r="R162"/>
-      <c r="S162" s="90"/>
+      <c r="S162" s="94"/>
       <c r="T162"/>
     </row>
-    <row r="163" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="163" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A163" s="105" t="str">
-        <v>UTC104</v>
+        <v>UTC106</v>
       </c>
       <c r="B163" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (status).
-3. oldTitle = meeting.Title.</v>
+3. meeting.AssignedApproverId = assigned ? _otherActorId : null.
+4. meeting.UpdatedAt = new DateTimeOffset(2026, 9, 1, 0, 0, 0, TimeSpan.Zero).
+5. updatedAt = meeting.UpdatedAt.</v>
       </c>
       <c r="C163" s="107" t="str">
-        <v>status=MeetingStatus.WaitingApproval</v>
+        <v>status=MeetingStatus.Rejected; assigned=false</v>
       </c>
       <c r="D163" s="108" t="str">
-        <v>Return: MeetingOutcome.NotEditable
+        <v>Return: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E163" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F163" s="105" t="str">
         <v>Pending</v>
@@ -11261,25 +11295,27 @@
       <c r="S163" s="94"/>
       <c r="T163"/>
     </row>
-    <row r="164" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="164" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A164" s="105" t="str">
-        <v>UTC105</v>
+        <v>UTC107</v>
       </c>
       <c r="B164" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (status).
-3. oldTitle = meeting.Title.</v>
+3. meeting.AssignedApproverId = assigned ? _otherActorId : null.
+4. meeting.UpdatedAt = new DateTimeOffset(2026, 9, 1, 0, 0, 0, TimeSpan.Zero).
+5. updatedAt = meeting.UpdatedAt.</v>
       </c>
       <c r="C164" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
+        <v>status=MeetingStatus.Rejected; assigned=true</v>
       </c>
       <c r="D164" s="108" t="str">
-        <v>Return: MeetingOutcome.NotEditable
+        <v>Return: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E164" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F164" s="105" t="str">
         <v>Pending</v>
@@ -11303,67 +11339,49 @@
       <c r="S164" s="94"/>
       <c r="T164"/>
     </row>
-    <row r="165" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
-      <c r="A165" s="105" t="str">
-        <v>UTC106</v>
-      </c>
-      <c r="B165" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. oldTitle = meeting.Title.</v>
-      </c>
-      <c r="C165" s="107" t="str">
-        <v>status=MeetingStatus.InProgress</v>
-      </c>
-      <c r="D165" s="108" t="str">
-        <v>Return: MeetingOutcome.NotEditable
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E165" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F165" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G165" s="105" t="str"/>
-      <c r="H165" s="105" t="str"/>
-      <c r="I165" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J165" s="105"/>
-      <c r="K165" s="105"/>
-      <c r="L165" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M165" s="105"/>
-      <c r="N165" s="105"/>
-      <c r="O165" s="105" t="str"/>
-      <c r="P165" s="110" t="str"/>
+    <row r="165" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A165" s="102" t="str">
+        <v>Update_preserves_a_draft_assignment_when_information_is_unchanged</v>
+      </c>
+      <c r="B165" s="102"/>
+      <c r="C165" s="103"/>
+      <c r="D165" s="103"/>
+      <c r="E165" s="103"/>
+      <c r="F165" s="103"/>
+      <c r="G165" s="103"/>
+      <c r="H165" s="103"/>
+      <c r="I165" s="103"/>
+      <c r="J165" s="103"/>
+      <c r="K165" s="103"/>
+      <c r="L165" s="103"/>
+      <c r="M165" s="103"/>
+      <c r="N165" s="103"/>
+      <c r="O165" s="103"/>
+      <c r="P165" s="104"/>
       <c r="Q165"/>
       <c r="R165"/>
-      <c r="S165" s="94"/>
+      <c r="S165" s="90"/>
       <c r="T165"/>
     </row>
     <row r="166" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A166" s="105" t="str">
-        <v>UTC107</v>
+        <v>UTC108</v>
       </c>
       <c r="B166" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. oldTitle = meeting.Title.</v>
+2. meeting: prepared by GivenMeeting.
+3. meeting.AssignedApproverId = _otherActorId.</v>
       </c>
       <c r="C166" s="107" t="str">
-        <v>status=MeetingStatus.Ended</v>
+        <v>meeting.Id; ValidInput(); _actorId</v>
       </c>
       <c r="D166" s="108" t="str">
-        <v>Return: MeetingOutcome.NotEditable
+        <v>Return: true
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E166" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F166" s="105" t="str">
         <v>Pending</v>
@@ -11389,7 +11407,7 @@
     </row>
     <row r="167" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A167" s="102" t="str">
-        <v>Update_does_not_save_when_information_is_unchanged</v>
+        <v>Get_and_update_return_the_same_not_found_for_missing_or_other_owners</v>
       </c>
       <c r="B167" s="102"/>
       <c r="C167" s="103"/>
@@ -11411,27 +11429,27 @@
       <c r="S167" s="90"/>
       <c r="T167"/>
     </row>
-    <row r="168" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+    <row r="168" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A168" s="105" t="str">
-        <v>UTC108</v>
+        <v>UTC109</v>
       </c>
       <c r="B168" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. meeting.AssignedApproverId = assigned ? _otherActorId : null.
-4. meeting.UpdatedAt = new DateTimeOffset(2026, 9, 1, 0, 0, 0, TimeSpan.Zero).
-5. updatedAt = meeting.UpdatedAt.</v>
+2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C168" s="107" t="str">
-        <v>status=MeetingStatus.Draft; assigned=false</v>
+        <v>status=MeetingStatus.Draft</v>
       </c>
       <c r="D168" s="108" t="str">
-        <v>Return: true
+        <v>Return:
+1. missing.Outcome: MeetingOutcome.NotFound
+2. otherOwner: missing
+3. cannotUpdate.Outcome: MeetingOutcome.NotFound
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E168" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F168" s="105" t="str">
         <v>Pending</v>
@@ -11455,27 +11473,27 @@
       <c r="S168" s="94"/>
       <c r="T168"/>
     </row>
-    <row r="169" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+    <row r="169" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A169" s="105" t="str">
-        <v>UTC109</v>
+        <v>UTC110</v>
       </c>
       <c r="B169" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. meeting.AssignedApproverId = assigned ? _otherActorId : null.
-4. meeting.UpdatedAt = new DateTimeOffset(2026, 9, 1, 0, 0, 0, TimeSpan.Zero).
-5. updatedAt = meeting.UpdatedAt.</v>
+2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C169" s="107" t="str">
-        <v>status=MeetingStatus.Rejected; assigned=false</v>
+        <v>status=MeetingStatus.Rejected</v>
       </c>
       <c r="D169" s="108" t="str">
-        <v>Return: true
+        <v>Return:
+1. missing.Outcome: MeetingOutcome.NotFound
+2. otherOwner: missing
+3. cannotUpdate.Outcome: MeetingOutcome.NotFound
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E169" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F169" s="105" t="str">
         <v>Pending</v>
@@ -11499,205 +11517,188 @@
       <c r="S169" s="94"/>
       <c r="T169"/>
     </row>
-    <row r="170" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
-      <c r="A170" s="105" t="str">
-        <v>UTC110</v>
-      </c>
-      <c r="B170" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. meeting.AssignedApproverId = assigned ? _otherActorId : null.
-4. meeting.UpdatedAt = new DateTimeOffset(2026, 9, 1, 0, 0, 0, TimeSpan.Zero).
-5. updatedAt = meeting.UpdatedAt.</v>
-      </c>
-      <c r="C170" s="107" t="str">
-        <v>status=MeetingStatus.Rejected; assigned=true</v>
-      </c>
-      <c r="D170" s="108" t="str">
-        <v>Return: true
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E170" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F170" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G170" s="105" t="str"/>
-      <c r="H170" s="105" t="str"/>
-      <c r="I170" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J170" s="105"/>
-      <c r="K170" s="105"/>
-      <c r="L170" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M170" s="105"/>
-      <c r="N170" s="105"/>
-      <c r="O170" s="105" t="str"/>
-      <c r="P170" s="110" t="str"/>
+    <row r="170" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A170" s="102" t="str">
+        <v>Get_allows_the_assigned_approver_and_a_meeting_participant</v>
+      </c>
+      <c r="B170" s="102"/>
+      <c r="C170" s="103"/>
+      <c r="D170" s="103"/>
+      <c r="E170" s="103"/>
+      <c r="F170" s="103"/>
+      <c r="G170" s="103"/>
+      <c r="H170" s="103"/>
+      <c r="I170" s="103"/>
+      <c r="J170" s="103"/>
+      <c r="K170" s="103"/>
+      <c r="L170" s="103"/>
+      <c r="M170" s="103"/>
+      <c r="N170" s="103"/>
+      <c r="O170" s="103"/>
+      <c r="P170" s="104"/>
       <c r="Q170"/>
       <c r="R170"/>
-      <c r="S170" s="94"/>
+      <c r="S170" s="90"/>
       <c r="T170"/>
     </row>
-    <row r="171" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A171" s="102" t="str">
-        <v>Update_preserves_a_draft_assignment_when_information_is_unchanged</v>
-      </c>
-      <c r="B171" s="102"/>
-      <c r="C171" s="103"/>
-      <c r="D171" s="103"/>
-      <c r="E171" s="103"/>
-      <c r="F171" s="103"/>
-      <c r="G171" s="103"/>
-      <c r="H171" s="103"/>
-      <c r="I171" s="103"/>
-      <c r="J171" s="103"/>
-      <c r="K171" s="103"/>
-      <c r="L171" s="103"/>
-      <c r="M171" s="103"/>
-      <c r="N171" s="103"/>
-      <c r="O171" s="103"/>
-      <c r="P171" s="104"/>
+    <row r="171" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+      <c r="A171" s="105" t="str">
+        <v>UTC111</v>
+      </c>
+      <c r="B171" s="106" t="str">
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting.
+3. meeting.Status = MeetingStatus.Published.
+4. meeting.AssignedApproverId = _otherActorId.
+5. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = participantId, }).</v>
+      </c>
+      <c r="C171" s="107" t="str">
+        <v>meeting.Id; _otherActorId</v>
+      </c>
+      <c r="D171" s="108" t="str">
+        <v>Return:
+1. approverResult.Succeeded: true
+2. approverResult.Meeting.Id: meeting.Id
+3. participantResult.Succeeded: true
+4. participantResult.Meeting.Id: meeting.Id
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E171" s="109" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F171" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G171" s="105" t="str"/>
+      <c r="H171" s="105" t="str"/>
+      <c r="I171" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J171" s="105"/>
+      <c r="K171" s="105"/>
+      <c r="L171" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M171" s="105"/>
+      <c r="N171" s="105"/>
+      <c r="O171" s="105" t="str"/>
+      <c r="P171" s="110" t="str"/>
       <c r="Q171"/>
       <c r="R171"/>
-      <c r="S171" s="90"/>
+      <c r="S171" s="94"/>
       <c r="T171"/>
     </row>
-    <row r="172" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
-      <c r="A172" s="105" t="str">
-        <v>UTC111</v>
-      </c>
-      <c r="B172" s="106" t="str">
+    <row r="172" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A172" s="102" t="str">
+        <v>Get_returns_a_read_failure_when_the_repository_fails</v>
+      </c>
+      <c r="B172" s="102"/>
+      <c r="C172" s="103"/>
+      <c r="D172" s="103"/>
+      <c r="E172" s="103"/>
+      <c r="F172" s="103"/>
+      <c r="G172" s="103"/>
+      <c r="H172" s="103"/>
+      <c r="I172" s="103"/>
+      <c r="J172" s="103"/>
+      <c r="K172" s="103"/>
+      <c r="L172" s="103"/>
+      <c r="M172" s="103"/>
+      <c r="N172" s="103"/>
+      <c r="O172" s="103"/>
+      <c r="P172" s="104"/>
+      <c r="Q172"/>
+      <c r="R172"/>
+      <c r="S172" s="90"/>
+      <c r="T172"/>
+    </row>
+    <row r="173" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+      <c r="A173" s="105" t="str">
+        <v>UTC112</v>
+      </c>
+      <c r="B173" s="106" t="str">
+        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
+2. _repository.NextReadThrows = new NpgsqlException("database unavailable").</v>
+      </c>
+      <c r="C173" s="107" t="str">
+        <v>Guid.CreateVersion7(); _actorId</v>
+      </c>
+      <c r="D173" s="108" t="str">
+        <v>Return: MeetingOutcome.ReadFailed
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E173" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F173" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G173" s="105" t="str"/>
+      <c r="H173" s="105" t="str"/>
+      <c r="I173" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J173" s="105"/>
+      <c r="K173" s="105"/>
+      <c r="L173" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M173" s="105"/>
+      <c r="N173" s="105"/>
+      <c r="O173" s="105" t="str"/>
+      <c r="P173" s="110" t="str"/>
+      <c r="Q173"/>
+      <c r="R173"/>
+      <c r="S173" s="94"/>
+      <c r="T173"/>
+    </row>
+    <row r="174" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A174" s="102" t="str">
+        <v>List_forwards_criteria_and_actor_and_returns_the_page</v>
+      </c>
+      <c r="B174" s="102"/>
+      <c r="C174" s="103"/>
+      <c r="D174" s="103"/>
+      <c r="E174" s="103"/>
+      <c r="F174" s="103"/>
+      <c r="G174" s="103"/>
+      <c r="H174" s="103"/>
+      <c r="I174" s="103"/>
+      <c r="J174" s="103"/>
+      <c r="K174" s="103"/>
+      <c r="L174" s="103"/>
+      <c r="M174" s="103"/>
+      <c r="N174" s="103"/>
+      <c r="O174" s="103"/>
+      <c r="P174" s="104"/>
+      <c r="Q174"/>
+      <c r="R174"/>
+      <c r="S174" s="90"/>
+      <c r="T174"/>
+    </row>
+    <row r="175" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+      <c r="A175" s="105" t="str">
+        <v>UTC113</v>
+      </c>
+      <c r="B175" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting.
-3. meeting.AssignedApproverId = _otherActorId.</v>
-      </c>
-      <c r="C172" s="107" t="str">
-        <v>meeting.Id; ValidInput(); _actorId</v>
-      </c>
-      <c r="D172" s="108" t="str">
-        <v>Return: true
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E172" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F172" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G172" s="105" t="str"/>
-      <c r="H172" s="105" t="str"/>
-      <c r="I172" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J172" s="105"/>
-      <c r="K172" s="105"/>
-      <c r="L172" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M172" s="105"/>
-      <c r="N172" s="105"/>
-      <c r="O172" s="105" t="str"/>
-      <c r="P172" s="110" t="str"/>
-      <c r="Q172"/>
-      <c r="R172"/>
-      <c r="S172" s="94"/>
-      <c r="T172"/>
-    </row>
-    <row r="173" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A173" s="102" t="str">
-        <v>Get_and_update_return_the_same_not_found_for_missing_or_other_owners</v>
-      </c>
-      <c r="B173" s="102"/>
-      <c r="C173" s="103"/>
-      <c r="D173" s="103"/>
-      <c r="E173" s="103"/>
-      <c r="F173" s="103"/>
-      <c r="G173" s="103"/>
-      <c r="H173" s="103"/>
-      <c r="I173" s="103"/>
-      <c r="J173" s="103"/>
-      <c r="K173" s="103"/>
-      <c r="L173" s="103"/>
-      <c r="M173" s="103"/>
-      <c r="N173" s="103"/>
-      <c r="O173" s="103"/>
-      <c r="P173" s="104"/>
-      <c r="Q173"/>
-      <c r="R173"/>
-      <c r="S173" s="90"/>
-      <c r="T173"/>
-    </row>
-    <row r="174" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
-      <c r="A174" s="105" t="str">
-        <v>UTC112</v>
-      </c>
-      <c r="B174" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).</v>
-      </c>
-      <c r="C174" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
-      </c>
-      <c r="D174" s="108" t="str">
-        <v>Return:
-1. missing.Outcome: MeetingOutcome.NotFound
-2. otherOwner: missing
-3. cannotUpdate.Outcome: MeetingOutcome.NotFound
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E174" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F174" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G174" s="105" t="str"/>
-      <c r="H174" s="105" t="str"/>
-      <c r="I174" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J174" s="105"/>
-      <c r="K174" s="105"/>
-      <c r="L174" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M174" s="105"/>
-      <c r="N174" s="105"/>
-      <c r="O174" s="105" t="str"/>
-      <c r="P174" s="110" t="str"/>
-      <c r="Q174"/>
-      <c r="R174"/>
-      <c r="S174" s="94"/>
-      <c r="T174"/>
-    </row>
-    <row r="175" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
-      <c r="A175" s="105" t="str">
-        <v>UTC113</v>
-      </c>
-      <c r="B175" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).</v>
+3. query: a new MeetingListQuery is prepared.</v>
       </c>
       <c r="C175" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>query; _actorId</v>
       </c>
       <c r="D175" s="108" t="str">
         <v>Return:
-1. missing.Outcome: MeetingOutcome.NotFound
-2. otherOwner: missing
-3. cannotUpdate.Outcome: MeetingOutcome.NotFound
+1. Outcome: MeetingOutcome.Success
+2. Page.TotalCount: 1
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E175" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F175" s="105" t="str">
         <v>Pending</v>
@@ -11723,7 +11724,7 @@
     </row>
     <row r="176" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A176" s="102" t="str">
-        <v>Get_allows_the_assigned_approver_and_a_meeting_participant</v>
+        <v>List_with_timing_compares_against_the_service_clock</v>
       </c>
       <c r="B176" s="102"/>
       <c r="C176" s="103"/>
@@ -11745,26 +11746,24 @@
       <c r="S176" s="90"/>
       <c r="T176"/>
     </row>
-    <row r="177" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+    <row r="177" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A177" s="105" t="str">
         <v>UTC114</v>
       </c>
       <c r="B177" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. meeting.Status = MeetingStatus.Published.
-4. meeting.AssignedApproverId = _otherActorId.
-5. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = participantId, }).</v>
+2. query: a new MeetingListQuery is prepared.
+3. before = DateTimeOffset.UtcNow.
+4. now = _repository.LastListQuery.Now.</v>
       </c>
       <c r="C177" s="107" t="str">
-        <v>meeting.Id; _otherActorId</v>
+        <v>query; _actorId</v>
       </c>
       <c r="D177" s="108" t="str">
         <v>Return:
-1. approverResult.Succeeded: true
-2. approverResult.Meeting.Id: meeting.Id
-3. participantResult.Succeeded: true
-4. participantResult.Meeting.Id: meeting.Id
+1. now: not null
+2. now.Value: between before and DateTimeOffset.UtcNow
+3. _repository.LastListQuery: query with { Now = now }
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -11795,7 +11794,7 @@
     </row>
     <row r="178" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A178" s="102" t="str">
-        <v>Get_returns_a_read_failure_when_the_repository_fails</v>
+        <v>List_maps_a_database_failure_to_read_failed</v>
       </c>
       <c r="B178" s="102"/>
       <c r="C178" s="103"/>
@@ -11817,21 +11816,28 @@
       <c r="S178" s="90"/>
       <c r="T178"/>
     </row>
-    <row r="179" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="179" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A179" s="105" t="str">
         <v>UTC115</v>
       </c>
       <c r="B179" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. _repository.NextReadThrows = new NpgsqlException("database unavailable").</v>
+2. failure = new NpgsqlException("database unavailable").
+3. _repository.NextReadThrows = failure.
+4. logger = new CaptureLogger().
+5. query: a new MeetingListQuery is prepared.</v>
       </c>
       <c r="C179" s="107" t="str">
-        <v>Guid.CreateVersion7(); _actorId</v>
+        <v>query; _actorId</v>
       </c>
       <c r="D179" s="108" t="str">
-        <v>Return: MeetingOutcome.ReadFailed
-Exception: N/A
-Log Message: N/A</v>
+        <v>Return:
+1. Outcome: MeetingOutcome.ReadFailed
+2. Page: null
+Exception: N/A
+Log Message:
+1. LogLevel.Error
+2. failure</v>
       </c>
       <c r="E179" s="109" t="str">
         <v>Abnormal</v>
@@ -11860,7 +11866,7 @@
     </row>
     <row r="180" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A180" s="102" t="str">
-        <v>List_forwards_criteria_and_actor_and_returns_the_page</v>
+        <v>List_propagates_request_cancellation</v>
       </c>
       <c r="B180" s="102"/>
       <c r="C180" s="103"/>
@@ -11882,23 +11888,22 @@
       <c r="S180" s="90"/>
       <c r="T180"/>
     </row>
-    <row r="181" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="181" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A181" s="105" t="str">
         <v>UTC116</v>
       </c>
       <c r="B181" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. query: a new MeetingListQuery is prepared.</v>
+2. source = new CancellationTokenSource().
+3. _repository.NextReadThrows = new OperationCanceledException(source.Token).
+4. query: a new MeetingListQuery is prepared.</v>
       </c>
       <c r="C181" s="107" t="str">
-        <v>query; _actorId</v>
+        <v>N/A</v>
       </c>
       <c r="D181" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingOutcome.Success
-2. Page.TotalCount: 1
-Exception: N/A
+        <v>Return: N/A
+Exception: OperationCanceledException
 Log Message: N/A</v>
       </c>
       <c r="E181" s="109" t="str">
@@ -11928,7 +11933,7 @@
     </row>
     <row r="182" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A182" s="102" t="str">
-        <v>List_with_timing_compares_against_the_service_clock</v>
+        <v>List_eligible_approvers_returns_the_repository_options</v>
       </c>
       <c r="B182" s="102"/>
       <c r="C182" s="103"/>
@@ -11950,24 +11955,22 @@
       <c r="S182" s="90"/>
       <c r="T182"/>
     </row>
-    <row r="183" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="183" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A183" s="105" t="str">
         <v>UTC117</v>
       </c>
       <c r="B183" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. query: a new MeetingListQuery is prepared.
-3. before = DateTimeOffset.UtcNow.
-4. now = _repository.LastListQuery.Now.</v>
+2. expected = new[] { new MeetingApproverOption(Guid.CreateVersion7(), "An Nguyễn"), new MeetingApprove….
+3. _repository.EligibleApprovers.AddRange(expected).</v>
       </c>
       <c r="C183" s="107" t="str">
-        <v>query; _actorId</v>
+        <v>N/A</v>
       </c>
       <c r="D183" s="108" t="str">
         <v>Return:
-1. now: not null
-2. now.Value: between before and DateTimeOffset.UtcNow
-3. _repository.LastListQuery: query with { Now = now }
+1. Outcome: MeetingOutcome.Success
+2. Approvers: expected
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -11998,7 +12001,7 @@
     </row>
     <row r="184" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A184" s="102" t="str">
-        <v>List_maps_a_database_failure_to_read_failed</v>
+        <v>List_eligible_approvers_maps_database_failure_to_read_failed</v>
       </c>
       <c r="B184" s="102"/>
       <c r="C184" s="103"/>
@@ -12020,28 +12023,23 @@
       <c r="S184" s="90"/>
       <c r="T184"/>
     </row>
-    <row r="185" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="185" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A185" s="105" t="str">
         <v>UTC118</v>
       </c>
       <c r="B185" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. failure = new NpgsqlException("database unavailable").
-3. _repository.NextReadThrows = failure.
-4. logger = new CaptureLogger().
-5. query: a new MeetingListQuery is prepared.</v>
+2. _repository.NextApproverReadThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C185" s="107" t="str">
-        <v>query; _actorId</v>
+        <v>N/A</v>
       </c>
       <c r="D185" s="108" t="str">
         <v>Return:
 1. Outcome: MeetingOutcome.ReadFailed
-2. Page: null
-Exception: N/A
-Log Message:
-1. LogLevel.Error
-2. failure</v>
+2. Approvers: null
+Exception: N/A
+Log Message: N/A</v>
       </c>
       <c r="E185" s="109" t="str">
         <v>Abnormal</v>
@@ -12070,7 +12068,7 @@
     </row>
     <row r="186" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A186" s="102" t="str">
-        <v>List_propagates_request_cancellation</v>
+        <v>Save_failure_is_returned_as_a_service_failure</v>
       </c>
       <c r="B186" s="102"/>
       <c r="C186" s="103"/>
@@ -12092,26 +12090,24 @@
       <c r="S186" s="90"/>
       <c r="T186"/>
     </row>
-    <row r="187" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="187" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A187" s="105" t="str">
         <v>UTC119</v>
       </c>
       <c r="B187" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. source = new CancellationTokenSource().
-3. _repository.NextReadThrows = new OperationCanceledException(source.Token).
-4. query: a new MeetingListQuery is prepared.</v>
+2. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C187" s="107" t="str">
-        <v>N/A</v>
+        <v>ValidInput(); _actorId; [new(_actorId, "Chair")]</v>
       </c>
       <c r="D187" s="108" t="str">
-        <v>Return: N/A
-Exception: OperationCanceledException
+        <v>Return: MeetingOutcome.SaveFailed
+Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E187" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F187" s="105" t="str">
         <v>Pending</v>
@@ -12137,7 +12133,7 @@
     </row>
     <row r="188" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A188" s="102" t="str">
-        <v>List_eligible_approvers_returns_the_repository_options</v>
+        <v>Update_save_failure_is_returned_and_does_not_keep_mutated_values</v>
       </c>
       <c r="B188" s="102"/>
       <c r="C188" s="103"/>
@@ -12159,27 +12155,25 @@
       <c r="S188" s="90"/>
       <c r="T188"/>
     </row>
-    <row r="189" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="189" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A189" s="105" t="str">
         <v>UTC120</v>
       </c>
       <c r="B189" s="106" t="str">
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. expected = new[] { new MeetingApproverOption(Guid.CreateVersion7(), "An Nguyễn"), new MeetingApprove….
-3. _repository.EligibleApprovers.AddRange(expected).</v>
+2. meeting: prepared by GivenMeeting.
+3. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C189" s="107" t="str">
-        <v>N/A</v>
+        <v>meeting.Id; ValidInput(title: "Không được lưu"); _actorId</v>
       </c>
       <c r="D189" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingOutcome.Success
-2. Approvers: expected
+        <v>Return: MeetingOutcome.SaveFailed
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E189" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F189" s="105" t="str">
         <v>Pending</v>
@@ -12205,7 +12199,7 @@
     </row>
     <row r="190" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A190" s="102" t="str">
-        <v>List_eligible_approvers_maps_database_failure_to_read_failed</v>
+        <v>Submission_readiness_does_not_depend_on_agenda_content</v>
       </c>
       <c r="B190" s="102"/>
       <c r="C190" s="103"/>
@@ -12232,21 +12226,20 @@
         <v>UTC121</v>
       </c>
       <c r="B191" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. _repository.NextApproverReadThrows = new NpgsqlException("database unavailable").</v>
+        <v>1. MeetingSubmissionReadiness runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C191" s="107" t="str">
         <v>N/A</v>
       </c>
       <c r="D191" s="108" t="str">
         <v>Return:
-1. Outcome: MeetingOutcome.ReadFailed
-2. Approvers: null
+1. MeetingSubmissionReadinessRules.Validate(meeting): empty
+2. MeetingSubmissionReadinessRules.Validate(meeting): empty
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E191" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F191" s="105" t="str">
         <v>Pending</v>
@@ -12272,7 +12265,7 @@
     </row>
     <row r="192" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A192" s="102" t="str">
-        <v>Save_failure_is_returned_as_a_service_failure</v>
+        <v>Submission_readiness_requires_a_valid_planned_schedule</v>
       </c>
       <c r="B192" s="102"/>
       <c r="C192" s="103"/>
@@ -12294,24 +12287,26 @@
       <c r="S192" s="90"/>
       <c r="T192"/>
     </row>
-    <row r="193" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="193" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A193" s="105" t="str">
         <v>UTC122</v>
       </c>
       <c r="B193" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
+        <v>1. MeetingSubmissionReadiness runs in process; its dependencies are fakes or stubs.
+2. meeting: a new Meeting is prepared.</v>
       </c>
       <c r="C193" s="107" t="str">
-        <v>ValidInput(); _actorId; [new(_actorId, "Chair")]</v>
+        <v>meeting</v>
       </c>
       <c r="D193" s="108" t="str">
-        <v>Return: MeetingOutcome.SaveFailed
+        <v>Return:
+1. Keys: contains "plannedStartTime"
+2. Keys: contains "plannedEndTime"
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E193" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F193" s="105" t="str">
         <v>Pending</v>
@@ -12337,7 +12332,7 @@
     </row>
     <row r="194" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A194" s="102" t="str">
-        <v>Update_save_failure_is_returned_and_does_not_keep_mutated_values</v>
+        <v>Meeting_readiness_reuses_information_rules_and_keeps_optional_fields_optional</v>
       </c>
       <c r="B194" s="102"/>
       <c r="C194" s="103"/>
@@ -12364,20 +12359,23 @@
         <v>UTC123</v>
       </c>
       <c r="B195" s="106" t="str">
-        <v>1. MeetingService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
+        <v>1. MeetingSubmissionReadiness runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C195" s="107" t="str">
-        <v>meeting.Id; ValidInput(title: "Không được lưu"); _actorId</v>
+        <v>N/A</v>
       </c>
       <c r="D195" s="108" t="str">
-        <v>Return: MeetingOutcome.SaveFailed
+        <v>Return:
+1. MeetingSubmissionReadinessRules.Validate(meeting): empty
+2. invalid.Keys: contains "title"
+3. invalid.Keys: contains "sensitivity"
+4. invalid.Keys: contains "description"
+5. invalid.Keys: contains "onlineLink"
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E195" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F195" s="105" t="str">
         <v>Pending</v>
@@ -12403,7 +12401,7 @@
     </row>
     <row r="196" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A196" s="102" t="str">
-        <v>Submission_readiness_does_not_depend_on_agenda_content</v>
+        <v>Submit_records_assignment_history_and_approver_notification</v>
       </c>
       <c r="B196" s="102"/>
       <c r="C196" s="103"/>
@@ -12425,20 +12423,20 @@
       <c r="S196" s="90"/>
       <c r="T196"/>
     </row>
-    <row r="197" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="197" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A197" s="105" t="str">
         <v>UTC124</v>
       </c>
       <c r="B197" s="106" t="str">
-        <v>1. MeetingSubmissionReadiness runs in process; its dependencies are fakes or stubs.</v>
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting.
+3. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C197" s="107" t="str">
-        <v>N/A</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.SubmitForApprova…; _organizerId</v>
       </c>
       <c r="D197" s="108" t="str">
-        <v>Return:
-1. MeetingSubmissionReadinessRules.Validate(meeting): empty
-2. MeetingSubmissionReadinessRules.Validate(meeting): empty
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -12469,7 +12467,7 @@
     </row>
     <row r="198" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A198" s="102" t="str">
-        <v>Submission_readiness_requires_a_valid_planned_schedule</v>
+        <v>Approve_notifies_the_organizer</v>
       </c>
       <c r="B198" s="102"/>
       <c r="C198" s="103"/>
@@ -12491,21 +12489,19 @@
       <c r="S198" s="90"/>
       <c r="T198"/>
     </row>
-    <row r="199" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="199" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A199" s="105" t="str">
         <v>UTC125</v>
       </c>
       <c r="B199" s="106" t="str">
-        <v>1. MeetingSubmissionReadiness runs in process; its dependencies are fakes or stubs.
-2. meeting: a new Meeting is prepared.</v>
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C199" s="107" t="str">
-        <v>meeting</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); _approverId</v>
       </c>
       <c r="D199" s="108" t="str">
-        <v>Return:
-1. Keys: contains "plannedStartTime"
-2. Keys: contains "plannedEndTime"
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -12536,7 +12532,7 @@
     </row>
     <row r="200" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A200" s="102" t="str">
-        <v>Meeting_readiness_reuses_information_rules_and_keeps_optional_fields_optional</v>
+        <v>Reject_notifies_the_organizer_with_the_reason</v>
       </c>
       <c r="B200" s="102"/>
       <c r="C200" s="103"/>
@@ -12558,28 +12554,24 @@
       <c r="S200" s="90"/>
       <c r="T200"/>
     </row>
-    <row r="201" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="201" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A201" s="105" t="str">
         <v>UTC126</v>
       </c>
       <c r="B201" s="106" t="str">
-        <v>1. MeetingSubmissionReadiness runs in process; its dependencies are fakes or stubs.</v>
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C201" s="107" t="str">
-        <v>N/A</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Reject, Reason:…; _approverId</v>
       </c>
       <c r="D201" s="108" t="str">
-        <v>Return:
-1. MeetingSubmissionReadinessRules.Validate(meeting): empty
-2. invalid.Keys: contains "title"
-3. invalid.Keys: contains "sensitivity"
-4. invalid.Keys: contains "description"
-5. invalid.Keys: contains "onlineLink"
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E201" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F201" s="105" t="str">
         <v>Pending</v>
@@ -12605,7 +12597,7 @@
     </row>
     <row r="202" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A202" s="102" t="str">
-        <v>Submit_records_assignment_history_and_approver_notification</v>
+        <v>Rejected_meeting_returns_to_draft_with_a_new_history_without_losing_reason</v>
       </c>
       <c r="B202" s="102"/>
       <c r="C202" s="103"/>
@@ -12627,17 +12619,17 @@
       <c r="S202" s="90"/>
       <c r="T202"/>
     </row>
-    <row r="203" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="203" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A203" s="105" t="str">
         <v>UTC127</v>
       </c>
       <c r="B203" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
+3. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, FromStatus = MeetingStatus.WaitingApproval, ToStatus = Meeting….</v>
       </c>
       <c r="C203" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.SubmitForApprova…; _organizerId</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.ReturnToDraft); _organizerId</v>
       </c>
       <c r="D203" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -12645,7 +12637,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E203" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F203" s="105" t="str">
         <v>Pending</v>
@@ -12671,7 +12663,7 @@
     </row>
     <row r="204" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A204" s="102" t="str">
-        <v>Approve_notifies_the_organizer</v>
+        <v>Draft_approver_selected_by_legacy_data_cannot_read_detail_or_history</v>
       </c>
       <c r="B204" s="102"/>
       <c r="C204" s="103"/>
@@ -12693,24 +12685,29 @@
       <c r="S204" s="90"/>
       <c r="T204"/>
     </row>
-    <row r="205" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="205" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A205" s="105" t="str">
         <v>UTC128</v>
       </c>
       <c r="B205" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
+2. meeting: prepared by GivenMeeting.
+3. meeting.AssignedApproverId = _approverId.</v>
       </c>
       <c r="C205" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); _approverId</v>
+        <v>meeting.Id; _approverId</v>
       </c>
       <c r="D205" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return:
+1. detail.Outcome: MeetingOutcome.NotFound
+2. organizerDetail.Meeting.AssignedApproverId: null
+3. history.Outcome: MeetingWorkflowOutcome.NotFound
+4. action.Outcome: MeetingWorkflowOutcome.NotFound
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E205" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F205" s="105" t="str">
         <v>Pending</v>
@@ -12736,7 +12733,7 @@
     </row>
     <row r="206" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A206" s="102" t="str">
-        <v>Reject_notifies_the_organizer_with_the_reason</v>
+        <v>Assigned_approver_with_capability_can_approve_but_an_unassigned_approver_cannot</v>
       </c>
       <c r="B206" s="102"/>
       <c r="C206" s="103"/>
@@ -12767,10 +12764,12 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C207" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Reject, Reason:…; _approverId</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); otherApprover</v>
       </c>
       <c r="D207" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return:
+1. denied.Outcome: MeetingWorkflowOutcome.NotFound
+2. approved.Outcome: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -12801,7 +12800,7 @@
     </row>
     <row r="208" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A208" s="102" t="str">
-        <v>Rejected_meeting_returns_to_draft_with_a_new_history_without_losing_reason</v>
+        <v>Assigned_approver_without_current_capability_is_forbidden</v>
       </c>
       <c r="B208" s="102"/>
       <c r="C208" s="103"/>
@@ -12823,20 +12822,19 @@
       <c r="S208" s="90"/>
       <c r="T208"/>
     </row>
-    <row r="209" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="209" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A209" s="105" t="str">
         <v>UTC130</v>
       </c>
       <c r="B209" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, FromStatus = MeetingStatus.WaitingApproval, ToStatus = Meeting….</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C209" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.ReturnToDraft); _organizerId</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); _approverId</v>
       </c>
       <c r="D209" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.Forbidden
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -12867,7 +12865,7 @@
     </row>
     <row r="210" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A210" s="102" t="str">
-        <v>Draft_approver_selected_by_legacy_data_cannot_read_detail_or_history</v>
+        <v>Readiness_get_and_submit_use_the_same_meeting_information_validation</v>
       </c>
       <c r="B210" s="102"/>
       <c r="C210" s="103"/>
@@ -12889,29 +12887,29 @@
       <c r="S210" s="90"/>
       <c r="T210"/>
     </row>
-    <row r="211" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="211" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A211" s="105" t="str">
         <v>UTC131</v>
       </c>
       <c r="B211" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting.
-3. meeting.AssignedApproverId = _approverId.</v>
+3. meeting.Title = " ".</v>
       </c>
       <c r="C211" s="107" t="str">
-        <v>meeting.Id; _approverId</v>
+        <v>meeting.Id; _organizerId</v>
       </c>
       <c r="D211" s="108" t="str">
         <v>Return:
-1. detail.Outcome: MeetingOutcome.NotFound
-2. organizerDetail.Meeting.AssignedApproverId: null
-3. history.Outcome: MeetingWorkflowOutcome.NotFound
-4. action.Outcome: MeetingWorkflowOutcome.NotFound
+1. readiness.Ready: false
+2. readiness.Errors.Keys: contains "title"
+3. submit.Outcome: MeetingWorkflowOutcome.SubmissionNotReady
+4. submit.Errors: readiness.Errors
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E211" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F211" s="105" t="str">
         <v>Pending</v>
@@ -12937,7 +12935,7 @@
     </row>
     <row r="212" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A212" s="102" t="str">
-        <v>Assigned_approver_with_capability_can_approve_but_an_unassigned_approver_cannot</v>
+        <v>Reject_requires_nonblank_reason_and_stores_trimmed_value</v>
       </c>
       <c r="B212" s="102"/>
       <c r="C212" s="103"/>
@@ -12968,12 +12966,10 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C213" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); otherApprover</v>
+        <v>reason=null; expected=MeetingWorkflowOutcome.RejectionReasonRequired</v>
       </c>
       <c r="D213" s="108" t="str">
-        <v>Return:
-1. denied.Outcome: MeetingWorkflowOutcome.NotFound
-2. approved.Outcome: MeetingWorkflowOutcome.Success
+        <v>Return: expected
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -13002,43 +12998,60 @@
       <c r="S213" s="94"/>
       <c r="T213"/>
     </row>
-    <row r="214" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A214" s="102" t="str">
-        <v>Assigned_approver_without_current_capability_is_forbidden</v>
-      </c>
-      <c r="B214" s="102"/>
-      <c r="C214" s="103"/>
-      <c r="D214" s="103"/>
-      <c r="E214" s="103"/>
-      <c r="F214" s="103"/>
-      <c r="G214" s="103"/>
-      <c r="H214" s="103"/>
-      <c r="I214" s="103"/>
-      <c r="J214" s="103"/>
-      <c r="K214" s="103"/>
-      <c r="L214" s="103"/>
-      <c r="M214" s="103"/>
-      <c r="N214" s="103"/>
-      <c r="O214" s="103"/>
-      <c r="P214" s="104"/>
+    <row r="214" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+      <c r="A214" s="105" t="str">
+        <v>UTC133</v>
+      </c>
+      <c r="B214" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
+      </c>
+      <c r="C214" s="107" t="str">
+        <v>reason="   "; expected=MeetingWorkflowOutcome.RejectionReasonRequired</v>
+      </c>
+      <c r="D214" s="108" t="str">
+        <v>Return: expected
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E214" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F214" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G214" s="105" t="str"/>
+      <c r="H214" s="105" t="str"/>
+      <c r="I214" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J214" s="105"/>
+      <c r="K214" s="105"/>
+      <c r="L214" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M214" s="105"/>
+      <c r="N214" s="105"/>
+      <c r="O214" s="105" t="str"/>
+      <c r="P214" s="110" t="str"/>
       <c r="Q214"/>
       <c r="R214"/>
-      <c r="S214" s="90"/>
+      <c r="S214" s="94"/>
       <c r="T214"/>
     </row>
     <row r="215" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A215" s="105" t="str">
-        <v>UTC133</v>
+        <v>UTC134</v>
       </c>
       <c r="B215" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C215" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); _approverId</v>
+        <v>reason="valid"; expected=MeetingWorkflowOutcome.Success</v>
       </c>
       <c r="D215" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Forbidden
+        <v>Return: expected
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -13069,7 +13082,7 @@
     </row>
     <row r="216" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A216" s="102" t="str">
-        <v>Readiness_get_and_submit_use_the_same_meeting_information_validation</v>
+        <v>Reject_accepts_exactly_1000_characters_and_rejects_1001</v>
       </c>
       <c r="B216" s="102"/>
       <c r="C216" s="103"/>
@@ -13091,29 +13104,27 @@
       <c r="S216" s="90"/>
       <c r="T216"/>
     </row>
-    <row r="217" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="217" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A217" s="105" t="str">
-        <v>UTC134</v>
+        <v>UTC135</v>
       </c>
       <c r="B217" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. meeting.Title = " ".</v>
+2. acceptedMeeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
+3. rejectedMeeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C217" s="107" t="str">
-        <v>meeting.Id; _organizerId</v>
+        <v>acceptedMeeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Reject, Reason:…; _approverId</v>
       </c>
       <c r="D217" s="108" t="str">
         <v>Return:
-1. readiness.Ready: false
-2. readiness.Errors.Keys: contains "title"
-3. submit.Outcome: MeetingWorkflowOutcome.SubmissionNotReady
-4. submit.Errors: readiness.Errors
+1. accepted.Outcome: MeetingWorkflowOutcome.Success
+2. rejected.Outcome: MeetingWorkflowOutcome.RejectionReasonTooLong
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E217" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F217" s="105" t="str">
         <v>Pending</v>
@@ -13139,7 +13150,7 @@
     </row>
     <row r="218" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A218" s="102" t="str">
-        <v>Reject_requires_nonblank_reason_and_stores_trimmed_value</v>
+        <v>Publish_notifies_active_non_delegated_participants_and_passes_meeting_id_to_the_email_owner</v>
       </c>
       <c r="B218" s="102"/>
       <c r="C218" s="103"/>
@@ -13161,24 +13172,27 @@
       <c r="S218" s="90"/>
       <c r="T218"/>
     </row>
-    <row r="219" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="219" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A219" s="105" t="str">
-        <v>UTC135</v>
+        <v>UTC136</v>
       </c>
       <c r="B219" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. meeting.Participants.Add(active).
+4. meeting.Participants.Add(inactive).
+5. meeting.Participants.Add(delegated).</v>
       </c>
       <c r="C219" s="107" t="str">
-        <v>reason=null; expected=MeetingWorkflowOutcome.RejectionReasonRequired</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
       </c>
       <c r="D219" s="108" t="str">
-        <v>Return: expected
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E219" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F219" s="105" t="str">
         <v>Pending</v>
@@ -13202,65 +13216,52 @@
       <c r="S219" s="94"/>
       <c r="T219"/>
     </row>
-    <row r="220" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
-      <c r="A220" s="105" t="str">
-        <v>UTC136</v>
-      </c>
-      <c r="B220" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
-      </c>
-      <c r="C220" s="107" t="str">
-        <v>reason="   "; expected=MeetingWorkflowOutcome.RejectionReasonRequired</v>
-      </c>
-      <c r="D220" s="108" t="str">
-        <v>Return: expected
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E220" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F220" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G220" s="105" t="str"/>
-      <c r="H220" s="105" t="str"/>
-      <c r="I220" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J220" s="105"/>
-      <c r="K220" s="105"/>
-      <c r="L220" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M220" s="105"/>
-      <c r="N220" s="105"/>
-      <c r="O220" s="105" t="str"/>
-      <c r="P220" s="110" t="str"/>
+    <row r="220" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A220" s="102" t="str">
+        <v>Publish_does_not_notify_the_publisher_in_app_even_when_they_are_a_participant</v>
+      </c>
+      <c r="B220" s="102"/>
+      <c r="C220" s="103"/>
+      <c r="D220" s="103"/>
+      <c r="E220" s="103"/>
+      <c r="F220" s="103"/>
+      <c r="G220" s="103"/>
+      <c r="H220" s="103"/>
+      <c r="I220" s="103"/>
+      <c r="J220" s="103"/>
+      <c r="K220" s="103"/>
+      <c r="L220" s="103"/>
+      <c r="M220" s="103"/>
+      <c r="N220" s="103"/>
+      <c r="O220" s="103"/>
+      <c r="P220" s="104"/>
       <c r="Q220"/>
       <c r="R220"/>
-      <c r="S220" s="94"/>
+      <c r="S220" s="90"/>
       <c r="T220"/>
     </row>
-    <row r="221" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="221" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A221" s="105" t="str">
         <v>UTC137</v>
       </c>
       <c r="B221" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. publisher.User.Id = _organizerId.
+4. publisher.UserId = _organizerId.
+5. meeting.Participants.Add(publisher).
+6. Further arrangement is in the test source.</v>
       </c>
       <c r="C221" s="107" t="str">
-        <v>reason="valid"; expected=MeetingWorkflowOutcome.Success</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
       </c>
       <c r="D221" s="108" t="str">
-        <v>Return: expected
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E221" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F221" s="105" t="str">
         <v>Pending</v>
@@ -13286,7 +13287,7 @@
     </row>
     <row r="222" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A222" s="102" t="str">
-        <v>Reject_accepts_exactly_1000_characters_and_rejects_1001</v>
+        <v>Publish_keeps_the_full_unicode_title_available_to_the_email_owner</v>
       </c>
       <c r="B222" s="102"/>
       <c r="C222" s="103"/>
@@ -13308,27 +13309,28 @@
       <c r="S222" s="90"/>
       <c r="T222"/>
     </row>
-    <row r="223" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="223" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A223" s="105" t="str">
         <v>UTC138</v>
       </c>
       <c r="B223" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. acceptedMeeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
-3. rejectedMeeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).</v>
       </c>
       <c r="C223" s="107" t="str">
-        <v>acceptedMeeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Reject, Reason:…; _approverId</v>
+        <v>N/A</v>
       </c>
       <c r="D223" s="108" t="str">
         <v>Return:
-1. accepted.Outcome: MeetingWorkflowOutcome.Success
-2. rejected.Outcome: MeetingWorkflowOutcome.RejectionReasonTooLong
+1. meeting.Title.Length: 300
+2. result.Outcome: MeetingWorkflowOutcome.Success
+3. Assert.Single(_repository.StagedPublicationIds): meeting.Id
+4. _repository.Meetings.Single().Title: new string('a', 290) + string.Concat(Enumerable.Repeat("📋", 5))
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E223" s="109" t="str">
-        <v>Boundary</v>
+        <v>Normal</v>
       </c>
       <c r="F223" s="105" t="str">
         <v>Pending</v>
@@ -13354,7 +13356,7 @@
     </row>
     <row r="224" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A224" s="102" t="str">
-        <v>Publish_notifies_active_non_delegated_participants_and_passes_meeting_id_to_the_email_owner</v>
+        <v>Organizer_cannot_submit_to_self_even_with_both_capabilities</v>
       </c>
       <c r="B224" s="102"/>
       <c r="C224" s="103"/>
@@ -13376,27 +13378,27 @@
       <c r="S224" s="90"/>
       <c r="T224"/>
     </row>
-    <row r="225" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="225" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A225" s="105" t="str">
         <v>UTC139</v>
       </c>
       <c r="B225" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. meeting.Participants.Add(active).
-4. meeting.Participants.Add(inactive).
-5. meeting.Participants.Add(delegated).</v>
+2. meeting: prepared by GivenMeeting.
+3. meeting.Sensitivity = sensitivity.
+4. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = _organizerId, Role = MeetingRole.Chair }).
+5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C225" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
+        <v>sensitivity=Sensitivity.Normal</v>
       </c>
       <c r="D225" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.InvalidApprover
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E225" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F225" s="105" t="str">
         <v>Pending</v>
@@ -13420,52 +13422,71 @@
       <c r="S225" s="94"/>
       <c r="T225"/>
     </row>
-    <row r="226" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A226" s="102" t="str">
-        <v>Publish_does_not_notify_the_publisher_in_app_even_when_they_are_a_participant</v>
-      </c>
-      <c r="B226" s="102"/>
-      <c r="C226" s="103"/>
-      <c r="D226" s="103"/>
-      <c r="E226" s="103"/>
-      <c r="F226" s="103"/>
-      <c r="G226" s="103"/>
-      <c r="H226" s="103"/>
-      <c r="I226" s="103"/>
-      <c r="J226" s="103"/>
-      <c r="K226" s="103"/>
-      <c r="L226" s="103"/>
-      <c r="M226" s="103"/>
-      <c r="N226" s="103"/>
-      <c r="O226" s="103"/>
-      <c r="P226" s="104"/>
+    <row r="226" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+      <c r="A226" s="105" t="str">
+        <v>UTC140</v>
+      </c>
+      <c r="B226" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting.
+3. meeting.Sensitivity = sensitivity.
+4. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = _organizerId, Role = MeetingRole.Chair }).
+5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
+      </c>
+      <c r="C226" s="107" t="str">
+        <v>sensitivity=Sensitivity.Internal</v>
+      </c>
+      <c r="D226" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.InvalidApprover
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E226" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F226" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G226" s="105" t="str"/>
+      <c r="H226" s="105" t="str"/>
+      <c r="I226" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J226" s="105"/>
+      <c r="K226" s="105"/>
+      <c r="L226" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M226" s="105"/>
+      <c r="N226" s="105"/>
+      <c r="O226" s="105" t="str"/>
+      <c r="P226" s="110" t="str"/>
       <c r="Q226"/>
       <c r="R226"/>
-      <c r="S226" s="90"/>
+      <c r="S226" s="94"/>
       <c r="T226"/>
     </row>
-    <row r="227" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
+    <row r="227" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A227" s="105" t="str">
-        <v>UTC140</v>
+        <v>UTC141</v>
       </c>
       <c r="B227" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. publisher.User.Id = _organizerId.
-4. publisher.UserId = _organizerId.
-5. meeting.Participants.Add(publisher).
-6. Further arrangement is in the test source.</v>
+2. meeting: prepared by GivenMeeting.
+3. meeting.Sensitivity = sensitivity.
+4. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = _organizerId, Role = MeetingRole.Chair }).
+5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C227" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
+        <v>sensitivity=Sensitivity.Confidential</v>
       </c>
       <c r="D227" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.InvalidApprover
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E227" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F227" s="105" t="str">
         <v>Pending</v>
@@ -13489,115 +13510,130 @@
       <c r="S227" s="94"/>
       <c r="T227"/>
     </row>
-    <row r="228" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A228" s="102" t="str">
-        <v>Publish_keeps_the_full_unicode_title_available_to_the_email_owner</v>
-      </c>
-      <c r="B228" s="102"/>
-      <c r="C228" s="103"/>
-      <c r="D228" s="103"/>
-      <c r="E228" s="103"/>
-      <c r="F228" s="103"/>
-      <c r="G228" s="103"/>
-      <c r="H228" s="103"/>
-      <c r="I228" s="103"/>
-      <c r="J228" s="103"/>
-      <c r="K228" s="103"/>
-      <c r="L228" s="103"/>
-      <c r="M228" s="103"/>
-      <c r="N228" s="103"/>
-      <c r="O228" s="103"/>
-      <c r="P228" s="104"/>
-      <c r="Q228"/>
-      <c r="R228"/>
-      <c r="S228" s="90"/>
-      <c r="T228"/>
-    </row>
-    <row r="229" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
-      <c r="A229" s="105" t="str">
-        <v>UTC141</v>
-      </c>
-      <c r="B229" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).</v>
-      </c>
-      <c r="C229" s="107" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="D229" s="108" t="str">
-        <v>Return:
-1. meeting.Title.Length: 300
-2. result.Outcome: MeetingWorkflowOutcome.Success
-3. Assert.Single(_repository.StagedPublicationIds): meeting.Id
-4. _repository.Meetings.Single().Title: new string('a', 290) + string.Concat(Enumerable.Repeat("📋", 5))
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E229" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F229" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G229" s="105" t="str"/>
-      <c r="H229" s="105" t="str"/>
-      <c r="I229" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J229" s="105"/>
-      <c r="K229" s="105"/>
-      <c r="L229" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M229" s="105"/>
-      <c r="N229" s="105"/>
-      <c r="O229" s="105" t="str"/>
-      <c r="P229" s="110" t="str"/>
-      <c r="Q229"/>
-      <c r="R229"/>
-      <c r="S229" s="94"/>
-      <c r="T229"/>
-    </row>
-    <row r="230" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A230" s="102" t="str">
-        <v>Organizer_cannot_submit_to_self_even_with_both_capabilities</v>
-      </c>
-      <c r="B230" s="102"/>
-      <c r="C230" s="103"/>
-      <c r="D230" s="103"/>
-      <c r="E230" s="103"/>
-      <c r="F230" s="103"/>
-      <c r="G230" s="103"/>
-      <c r="H230" s="103"/>
-      <c r="I230" s="103"/>
-      <c r="J230" s="103"/>
-      <c r="K230" s="103"/>
-      <c r="L230" s="103"/>
-      <c r="M230" s="103"/>
-      <c r="N230" s="103"/>
-      <c r="O230" s="103"/>
-      <c r="P230" s="104"/>
-      <c r="Q230"/>
-      <c r="R230"/>
-      <c r="S230" s="90"/>
-      <c r="T230"/>
-    </row>
-    <row r="231" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
-      <c r="A231" s="105" t="str">
+    <row r="228" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+      <c r="A228" s="105" t="str">
         <v>UTC142</v>
       </c>
-      <c r="B231" s="106" t="str">
+      <c r="B228" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting.
 3. meeting.Sensitivity = sensitivity.
 4. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = _organizerId, Role = MeetingRole.Chair }).
 5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
+      <c r="C228" s="107" t="str">
+        <v>sensitivity=Sensitivity.Secret</v>
+      </c>
+      <c r="D228" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.InvalidApprover
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E228" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F228" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G228" s="105" t="str"/>
+      <c r="H228" s="105" t="str"/>
+      <c r="I228" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J228" s="105"/>
+      <c r="K228" s="105"/>
+      <c r="L228" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M228" s="105"/>
+      <c r="N228" s="105"/>
+      <c r="O228" s="105" t="str"/>
+      <c r="P228" s="110" t="str"/>
+      <c r="Q228"/>
+      <c r="R228"/>
+      <c r="S228" s="94"/>
+      <c r="T228"/>
+    </row>
+    <row r="229" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A229" s="102" t="str">
+        <v>Legacy_self_assignment_cannot_approve_or_reject</v>
+      </c>
+      <c r="B229" s="102"/>
+      <c r="C229" s="103"/>
+      <c r="D229" s="103"/>
+      <c r="E229" s="103"/>
+      <c r="F229" s="103"/>
+      <c r="G229" s="103"/>
+      <c r="H229" s="103"/>
+      <c r="I229" s="103"/>
+      <c r="J229" s="103"/>
+      <c r="K229" s="103"/>
+      <c r="L229" s="103"/>
+      <c r="M229" s="103"/>
+      <c r="N229" s="103"/>
+      <c r="O229" s="103"/>
+      <c r="P229" s="104"/>
+      <c r="Q229"/>
+      <c r="R229"/>
+      <c r="S229" s="90"/>
+      <c r="T229"/>
+    </row>
+    <row r="230" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+      <c r="A230" s="105" t="str">
+        <v>UTC143</v>
+      </c>
+      <c r="B230" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
+3. meeting.AssignedApproverId = _organizerId.</v>
+      </c>
+      <c r="C230" s="107" t="str">
+        <v>action=MeetingTransitionAction.Approve</v>
+      </c>
+      <c r="D230" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.Forbidden
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E230" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F230" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G230" s="105" t="str"/>
+      <c r="H230" s="105" t="str"/>
+      <c r="I230" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J230" s="105"/>
+      <c r="K230" s="105"/>
+      <c r="L230" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M230" s="105"/>
+      <c r="N230" s="105"/>
+      <c r="O230" s="105" t="str"/>
+      <c r="P230" s="110" t="str"/>
+      <c r="Q230"/>
+      <c r="R230"/>
+      <c r="S230" s="94"/>
+      <c r="T230"/>
+    </row>
+    <row r="231" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+      <c r="A231" s="105" t="str">
+        <v>UTC144</v>
+      </c>
+      <c r="B231" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
+3. meeting.AssignedApproverId = _organizerId.</v>
+      </c>
       <c r="C231" s="107" t="str">
-        <v>sensitivity=Sensitivity.Normal</v>
+        <v>action=MeetingTransitionAction.Reject</v>
       </c>
       <c r="D231" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidApprover
+        <v>Return: MeetingWorkflowOutcome.Forbidden
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -13626,71 +13662,48 @@
       <c r="S231" s="94"/>
       <c r="T231"/>
     </row>
-    <row r="232" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
-      <c r="A232" s="105" t="str">
-        <v>UTC143</v>
-      </c>
-      <c r="B232" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. meeting.Sensitivity = sensitivity.
-4. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = _organizerId, Role = MeetingRole.Chair }).
-5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
-      </c>
-      <c r="C232" s="107" t="str">
-        <v>sensitivity=Sensitivity.Internal</v>
-      </c>
-      <c r="D232" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidApprover
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E232" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F232" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G232" s="105" t="str"/>
-      <c r="H232" s="105" t="str"/>
-      <c r="I232" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J232" s="105"/>
-      <c r="K232" s="105"/>
-      <c r="L232" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M232" s="105"/>
-      <c r="N232" s="105"/>
-      <c r="O232" s="105" t="str"/>
-      <c r="P232" s="110" t="str"/>
+    <row r="232" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A232" s="102" t="str">
+        <v>Waiting_approval_can_be_withdrawn_only_when_approver_is_ineligible</v>
+      </c>
+      <c r="B232" s="102"/>
+      <c r="C232" s="103"/>
+      <c r="D232" s="103"/>
+      <c r="E232" s="103"/>
+      <c r="F232" s="103"/>
+      <c r="G232" s="103"/>
+      <c r="H232" s="103"/>
+      <c r="I232" s="103"/>
+      <c r="J232" s="103"/>
+      <c r="K232" s="103"/>
+      <c r="L232" s="103"/>
+      <c r="M232" s="103"/>
+      <c r="N232" s="103"/>
+      <c r="O232" s="103"/>
+      <c r="P232" s="104"/>
       <c r="Q232"/>
       <c r="R232"/>
-      <c r="S232" s="94"/>
+      <c r="S232" s="90"/>
       <c r="T232"/>
     </row>
-    <row r="233" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+    <row r="233" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A233" s="105" t="str">
-        <v>UTC144</v>
+        <v>UTC145</v>
       </c>
       <c r="B233" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. meeting.Sensitivity = sensitivity.
-4. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = _organizerId, Role = MeetingRole.Chair }).
-5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C233" s="107" t="str">
-        <v>sensitivity=Sensitivity.Confidential</v>
+        <v>approverEligible=true</v>
       </c>
       <c r="D233" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidApprover
+        <v>Return: approverEligible ? MeetingWorkflowOutcome.StatusConflict : MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E233" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F233" s="105" t="str">
         <v>Pending</v>
@@ -13714,27 +13727,24 @@
       <c r="S233" s="94"/>
       <c r="T233"/>
     </row>
-    <row r="234" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+    <row r="234" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A234" s="105" t="str">
-        <v>UTC145</v>
+        <v>UTC146</v>
       </c>
       <c r="B234" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.
-3. meeting.Sensitivity = sensitivity.
-4. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = _organizerId, Role = MeetingRole.Chair }).
-5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C234" s="107" t="str">
-        <v>sensitivity=Sensitivity.Secret</v>
+        <v>approverEligible=false</v>
       </c>
       <c r="D234" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidApprover
+        <v>Return: approverEligible ? MeetingWorkflowOutcome.StatusConflict : MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E234" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F234" s="105" t="str">
         <v>Pending</v>
@@ -13760,7 +13770,7 @@
     </row>
     <row r="235" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A235" s="102" t="str">
-        <v>Legacy_self_assignment_cannot_approve_or_reject</v>
+        <v>Legacy_missing_or_self_assignment_can_be_withdrawn_and_resubmitted</v>
       </c>
       <c r="B235" s="102"/>
       <c r="C235" s="103"/>
@@ -13782,20 +13792,21 @@
       <c r="S235" s="90"/>
       <c r="T235"/>
     </row>
-    <row r="236" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="236" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A236" s="105" t="str">
-        <v>UTC146</v>
+        <v>UTC147</v>
       </c>
       <c r="B236" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
-3. meeting.AssignedApproverId = _organizerId.</v>
+3. meeting.AssignedApproverId = selfAssignment ? _organizerId : null.
+4. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C236" s="107" t="str">
-        <v>action=MeetingTransitionAction.Approve</v>
+        <v>selfAssignment=true</v>
       </c>
       <c r="D236" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Forbidden
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -13824,20 +13835,21 @@
       <c r="S236" s="94"/>
       <c r="T236"/>
     </row>
-    <row r="237" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="237" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A237" s="105" t="str">
-        <v>UTC147</v>
+        <v>UTC148</v>
       </c>
       <c r="B237" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
-3. meeting.AssignedApproverId = _organizerId.</v>
+3. meeting.AssignedApproverId = selfAssignment ? _organizerId : null.
+4. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C237" s="107" t="str">
-        <v>action=MeetingTransitionAction.Reject</v>
+        <v>selfAssignment=false</v>
       </c>
       <c r="D237" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Forbidden
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -13868,7 +13880,7 @@
     </row>
     <row r="238" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A238" s="102" t="str">
-        <v>Waiting_approval_can_be_withdrawn_only_when_approver_is_ineligible</v>
+        <v>Withdrawal_save_failure_rolls_back_the_blocked_approval_cycle</v>
       </c>
       <c r="B238" s="102"/>
       <c r="C238" s="103"/>
@@ -13890,24 +13902,25 @@
       <c r="S238" s="90"/>
       <c r="T238"/>
     </row>
-    <row r="239" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="239" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A239" s="105" t="str">
-        <v>UTC148</v>
+        <v>UTC149</v>
       </c>
       <c r="B239" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
+3. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C239" s="107" t="str">
-        <v>approverEligible=true</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.ReturnToDraft); _organizerId</v>
       </c>
       <c r="D239" s="108" t="str">
-        <v>Return: approverEligible ? MeetingWorkflowOutcome.StatusConflict : MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.SaveFailed
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E239" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F239" s="105" t="str">
         <v>Pending</v>
@@ -13931,91 +13944,89 @@
       <c r="S239" s="94"/>
       <c r="T239"/>
     </row>
-    <row r="240" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
-      <c r="A240" s="105" t="str">
-        <v>UTC149</v>
-      </c>
-      <c r="B240" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
-      </c>
-      <c r="C240" s="107" t="str">
-        <v>approverEligible=false</v>
-      </c>
-      <c r="D240" s="108" t="str">
-        <v>Return: approverEligible ? MeetingWorkflowOutcome.StatusConflict : MeetingWorkflowOutcome.Success
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E240" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F240" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G240" s="105" t="str"/>
-      <c r="H240" s="105" t="str"/>
-      <c r="I240" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J240" s="105"/>
-      <c r="K240" s="105"/>
-      <c r="L240" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M240" s="105"/>
-      <c r="N240" s="105"/>
-      <c r="O240" s="105" t="str"/>
-      <c r="P240" s="110" t="str"/>
+    <row r="240" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A240" s="102" t="str">
+        <v>Ineligible_approver_does_not_allow_withdrawal_from_other_states</v>
+      </c>
+      <c r="B240" s="102"/>
+      <c r="C240" s="103"/>
+      <c r="D240" s="103"/>
+      <c r="E240" s="103"/>
+      <c r="F240" s="103"/>
+      <c r="G240" s="103"/>
+      <c r="H240" s="103"/>
+      <c r="I240" s="103"/>
+      <c r="J240" s="103"/>
+      <c r="K240" s="103"/>
+      <c r="L240" s="103"/>
+      <c r="M240" s="103"/>
+      <c r="N240" s="103"/>
+      <c r="O240" s="103"/>
+      <c r="P240" s="104"/>
       <c r="Q240"/>
       <c r="R240"/>
-      <c r="S240" s="94"/>
+      <c r="S240" s="90"/>
       <c r="T240"/>
     </row>
-    <row r="241" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A241" s="102" t="str">
-        <v>Legacy_missing_or_self_assignment_can_be_withdrawn_and_resubmitted</v>
-      </c>
-      <c r="B241" s="102"/>
-      <c r="C241" s="103"/>
-      <c r="D241" s="103"/>
-      <c r="E241" s="103"/>
-      <c r="F241" s="103"/>
-      <c r="G241" s="103"/>
-      <c r="H241" s="103"/>
-      <c r="I241" s="103"/>
-      <c r="J241" s="103"/>
-      <c r="K241" s="103"/>
-      <c r="L241" s="103"/>
-      <c r="M241" s="103"/>
-      <c r="N241" s="103"/>
-      <c r="O241" s="103"/>
-      <c r="P241" s="104"/>
+    <row r="241" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+      <c r="A241" s="105" t="str">
+        <v>UTC150</v>
+      </c>
+      <c r="B241" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (status).</v>
+      </c>
+      <c r="C241" s="107" t="str">
+        <v>status=MeetingStatus.Draft</v>
+      </c>
+      <c r="D241" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E241" s="109" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F241" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G241" s="105" t="str"/>
+      <c r="H241" s="105" t="str"/>
+      <c r="I241" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J241" s="105"/>
+      <c r="K241" s="105"/>
+      <c r="L241" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M241" s="105"/>
+      <c r="N241" s="105"/>
+      <c r="O241" s="105" t="str"/>
+      <c r="P241" s="110" t="str"/>
       <c r="Q241"/>
       <c r="R241"/>
-      <c r="S241" s="90"/>
+      <c r="S241" s="94"/>
       <c r="T241"/>
     </row>
-    <row r="242" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="242" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A242" s="105" t="str">
-        <v>UTC150</v>
+        <v>UTC151</v>
       </c>
       <c r="B242" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
-3. meeting.AssignedApproverId = selfAssignment ? _organizerId : null.
-4. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
+2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C242" s="107" t="str">
-        <v>selfAssignment=true</v>
+        <v>status=MeetingStatus.Approved</v>
       </c>
       <c r="D242" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E242" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F242" s="105" t="str">
         <v>Pending</v>
@@ -14039,26 +14050,24 @@
       <c r="S242" s="94"/>
       <c r="T242"/>
     </row>
-    <row r="243" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="243" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A243" s="105" t="str">
-        <v>UTC151</v>
+        <v>UTC152</v>
       </c>
       <c r="B243" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
-3. meeting.AssignedApproverId = selfAssignment ? _organizerId : null.
-4. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
+2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C243" s="107" t="str">
-        <v>selfAssignment=false</v>
+        <v>status=MeetingStatus.Published</v>
       </c>
       <c r="D243" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E243" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F243" s="105" t="str">
         <v>Pending</v>
@@ -14084,7 +14093,7 @@
     </row>
     <row r="244" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A244" s="102" t="str">
-        <v>Withdrawal_save_failure_rolls_back_the_blocked_approval_cycle</v>
+        <v>Publish_persistence_failure_rolls_back_status_history_notifications_and_jobs</v>
       </c>
       <c r="B244" s="102"/>
       <c r="C244" s="103"/>
@@ -14106,17 +14115,18 @@
       <c r="S244" s="90"/>
       <c r="T244"/>
     </row>
-    <row r="245" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="245" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A245" s="105" t="str">
-        <v>UTC152</v>
+        <v>UTC153</v>
       </c>
       <c r="B245" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).
-3. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. meeting.Participants.Add(Participant(meeting, active: true, InvitationResponse.Pending)).
+4. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C245" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.ReturnToDraft); _organizerId</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
       </c>
       <c r="D245" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.SaveFailed
@@ -14150,7 +14160,7 @@
     </row>
     <row r="246" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A246" s="102" t="str">
-        <v>Ineligible_approver_does_not_allow_withdrawal_from_other_states</v>
+        <v>Organizer_and_current_approver_get_reasons_and_published_participant_gets_redacted_timeline</v>
       </c>
       <c r="B246" s="102"/>
       <c r="C246" s="103"/>
@@ -14172,19 +14182,27 @@
       <c r="S246" s="90"/>
       <c r="T246"/>
     </row>
-    <row r="247" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="247" spans="1:20" s="93" customFormat="1" ht="283.5" outlineLevel="1" customHeight="1">
       <c r="A247" s="105" t="str">
-        <v>UTC153</v>
+        <v>UTC154</v>
       </c>
       <c r="B247" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Draft).
+3. meeting.AssignedApproverId = currentApprover.
+4. meeting.Status = MeetingStatus.Published.
+5. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = publishedParticipant, Response = InvitationResponse.Acce….
+6. Further arrangement is in the test source.</v>
       </c>
       <c r="C247" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>meeting.Id; currentApprover; 1; 20</v>
       </c>
       <c r="D247" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
+        <v>Return:
+1. current.Outcome: MeetingWorkflowOutcome.Success
+2. organizer.Outcome: MeetingWorkflowOutcome.Success
+3. former.Outcome: MeetingWorkflowOutcome.NotFound
+4. participant.Outcome: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -14213,60 +14231,50 @@
       <c r="S247" s="94"/>
       <c r="T247"/>
     </row>
-    <row r="248" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
-      <c r="A248" s="105" t="str">
-        <v>UTC154</v>
-      </c>
-      <c r="B248" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).</v>
-      </c>
-      <c r="C248" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
-      </c>
-      <c r="D248" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E248" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F248" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G248" s="105" t="str"/>
-      <c r="H248" s="105" t="str"/>
-      <c r="I248" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J248" s="105"/>
-      <c r="K248" s="105"/>
-      <c r="L248" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M248" s="105"/>
-      <c r="N248" s="105"/>
-      <c r="O248" s="105" t="str"/>
-      <c r="P248" s="110" t="str"/>
+    <row r="248" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A248" s="102" t="str">
+        <v>Administrative_transfer_recovers_an_approved_meeting_and_records_typed_organizer_ids</v>
+      </c>
+      <c r="B248" s="102"/>
+      <c r="C248" s="103"/>
+      <c r="D248" s="103"/>
+      <c r="E248" s="103"/>
+      <c r="F248" s="103"/>
+      <c r="G248" s="103"/>
+      <c r="H248" s="103"/>
+      <c r="I248" s="103"/>
+      <c r="J248" s="103"/>
+      <c r="K248" s="103"/>
+      <c r="L248" s="103"/>
+      <c r="M248" s="103"/>
+      <c r="N248" s="103"/>
+      <c r="O248" s="103"/>
+      <c r="P248" s="104"/>
       <c r="Q248"/>
       <c r="R248"/>
-      <c r="S248" s="94"/>
+      <c r="S248" s="90"/>
       <c r="T248"/>
     </row>
-    <row r="249" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="249" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A249" s="105" t="str">
         <v>UTC155</v>
       </c>
       <c r="B249" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. _repository.InactiveUserIds.Add(_organizerId).
+4. approval: a new MeetingStatusHistory is prepared.
+5. meeting.StatusHistory.Add(approval).</v>
       </c>
       <c r="C249" s="107" t="str">
-        <v>status=MeetingStatus.Published</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
       </c>
       <c r="D249" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
+        <v>Return:
+1. Outcome: MeetingWorkflowOutcome.Success
+2. Meeting: null
+3. History.PreviousOrganizerId: _organizerId
+4. History.NewOrganizerId: replacement
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -14297,7 +14305,7 @@
     </row>
     <row r="250" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A250" s="102" t="str">
-        <v>Publish_persistence_failure_rolls_back_status_history_notifications_and_jobs</v>
+        <v>Transfer_requires_current_active_administrator_before_reading_the_meeting</v>
       </c>
       <c r="B250" s="102"/>
       <c r="C250" s="103"/>
@@ -14319,26 +14327,27 @@
       <c r="S250" s="90"/>
       <c r="T250"/>
     </row>
-    <row r="251" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
+    <row r="251" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A251" s="105" t="str">
         <v>UTC156</v>
       </c>
       <c r="B251" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. meeting.Participants.Add(Participant(meeting, active: true, InvitationResponse.Pending)).
-4. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
+3. if (inactive) _repository.InactiveUserIds.Add(administrator).
+4. _repository.InactiveUserIds.Add(_organizerId).
+5. _repository.NextWorkflowReadThrows = new InvalidOperationException("Resource must not be loaded").</v>
       </c>
       <c r="C251" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
+        <v>inactive=false</v>
       </c>
       <c r="D251" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.SaveFailed
+        <v>Return: MeetingWorkflowOutcome.NotFound
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E251" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F251" s="105" t="str">
         <v>Pending</v>
@@ -14362,196 +14371,202 @@
       <c r="S251" s="94"/>
       <c r="T251"/>
     </row>
-    <row r="252" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A252" s="102" t="str">
-        <v>Organizer_and_current_approver_get_reasons_and_published_participant_gets_redacted_timeline</v>
-      </c>
-      <c r="B252" s="102"/>
-      <c r="C252" s="103"/>
-      <c r="D252" s="103"/>
-      <c r="E252" s="103"/>
-      <c r="F252" s="103"/>
-      <c r="G252" s="103"/>
-      <c r="H252" s="103"/>
-      <c r="I252" s="103"/>
-      <c r="J252" s="103"/>
-      <c r="K252" s="103"/>
-      <c r="L252" s="103"/>
-      <c r="M252" s="103"/>
-      <c r="N252" s="103"/>
-      <c r="O252" s="103"/>
-      <c r="P252" s="104"/>
-      <c r="Q252"/>
-      <c r="R252"/>
-      <c r="S252" s="90"/>
-      <c r="T252"/>
-    </row>
-    <row r="253" spans="1:20" s="93" customFormat="1" ht="283.5" outlineLevel="1" customHeight="1">
-      <c r="A253" s="105" t="str">
+    <row r="252" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
+      <c r="A252" s="105" t="str">
         <v>UTC157</v>
       </c>
-      <c r="B253" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Draft).
-3. meeting.AssignedApproverId = currentApprover.
-4. meeting.Status = MeetingStatus.Published.
-5. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = publishedParticipant, Response = InvitationResponse.Acce….
-6. Further arrangement is in the test source.</v>
-      </c>
-      <c r="C253" s="107" t="str">
-        <v>meeting.Id; currentApprover; 1; 20</v>
-      </c>
-      <c r="D253" s="108" t="str">
-        <v>Return:
-1. current.Outcome: MeetingWorkflowOutcome.Success
-2. organizer.Outcome: MeetingWorkflowOutcome.Success
-3. former.Outcome: MeetingWorkflowOutcome.NotFound
-4. participant.Outcome: MeetingWorkflowOutcome.Success
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E253" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F253" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G253" s="105" t="str"/>
-      <c r="H253" s="105" t="str"/>
-      <c r="I253" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J253" s="105"/>
-      <c r="K253" s="105"/>
-      <c r="L253" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M253" s="105"/>
-      <c r="N253" s="105"/>
-      <c r="O253" s="105" t="str"/>
-      <c r="P253" s="110" t="str"/>
-      <c r="Q253"/>
-      <c r="R253"/>
-      <c r="S253" s="94"/>
-      <c r="T253"/>
-    </row>
-    <row r="254" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A254" s="102" t="str">
-        <v>Administrative_transfer_recovers_an_approved_meeting_and_records_typed_organizer_ids</v>
-      </c>
-      <c r="B254" s="102"/>
-      <c r="C254" s="103"/>
-      <c r="D254" s="103"/>
-      <c r="E254" s="103"/>
-      <c r="F254" s="103"/>
-      <c r="G254" s="103"/>
-      <c r="H254" s="103"/>
-      <c r="I254" s="103"/>
-      <c r="J254" s="103"/>
-      <c r="K254" s="103"/>
-      <c r="L254" s="103"/>
-      <c r="M254" s="103"/>
-      <c r="N254" s="103"/>
-      <c r="O254" s="103"/>
-      <c r="P254" s="104"/>
-      <c r="Q254"/>
-      <c r="R254"/>
-      <c r="S254" s="90"/>
-      <c r="T254"/>
-    </row>
-    <row r="255" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
-      <c r="A255" s="105" t="str">
-        <v>UTC158</v>
-      </c>
-      <c r="B255" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. _repository.InactiveUserIds.Add(_organizerId).
-4. approval: a new MeetingStatusHistory is prepared.
-5. meeting.StatusHistory.Add(approval).</v>
-      </c>
-      <c r="C255" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
-      </c>
-      <c r="D255" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingWorkflowOutcome.Success
-2. Meeting: null
-3. History.PreviousOrganizerId: _organizerId
-4. History.NewOrganizerId: replacement
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E255" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F255" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G255" s="105" t="str"/>
-      <c r="H255" s="105" t="str"/>
-      <c r="I255" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J255" s="105"/>
-      <c r="K255" s="105"/>
-      <c r="L255" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M255" s="105"/>
-      <c r="N255" s="105"/>
-      <c r="O255" s="105" t="str"/>
-      <c r="P255" s="110" t="str"/>
-      <c r="Q255"/>
-      <c r="R255"/>
-      <c r="S255" s="94"/>
-      <c r="T255"/>
-    </row>
-    <row r="256" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A256" s="102" t="str">
-        <v>Transfer_requires_current_active_administrator_before_reading_the_meeting</v>
-      </c>
-      <c r="B256" s="102"/>
-      <c r="C256" s="103"/>
-      <c r="D256" s="103"/>
-      <c r="E256" s="103"/>
-      <c r="F256" s="103"/>
-      <c r="G256" s="103"/>
-      <c r="H256" s="103"/>
-      <c r="I256" s="103"/>
-      <c r="J256" s="103"/>
-      <c r="K256" s="103"/>
-      <c r="L256" s="103"/>
-      <c r="M256" s="103"/>
-      <c r="N256" s="103"/>
-      <c r="O256" s="103"/>
-      <c r="P256" s="104"/>
-      <c r="Q256"/>
-      <c r="R256"/>
-      <c r="S256" s="90"/>
-      <c r="T256"/>
-    </row>
-    <row r="257" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
-      <c r="A257" s="105" t="str">
-        <v>UTC159</v>
-      </c>
-      <c r="B257" s="106" t="str">
+      <c r="B252" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
 3. if (inactive) _repository.InactiveUserIds.Add(administrator).
 4. _repository.InactiveUserIds.Add(_organizerId).
 5. _repository.NextWorkflowReadThrows = new InvalidOperationException("Resource must not be loaded").</v>
       </c>
+      <c r="C252" s="107" t="str">
+        <v>inactive=true</v>
+      </c>
+      <c r="D252" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.NotFound
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E252" s="109" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F252" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G252" s="105" t="str"/>
+      <c r="H252" s="105" t="str"/>
+      <c r="I252" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J252" s="105"/>
+      <c r="K252" s="105"/>
+      <c r="L252" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M252" s="105"/>
+      <c r="N252" s="105"/>
+      <c r="O252" s="105" t="str"/>
+      <c r="P252" s="110" t="str"/>
+      <c r="Q252"/>
+      <c r="R252"/>
+      <c r="S252" s="94"/>
+      <c r="T252"/>
+    </row>
+    <row r="253" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A253" s="102" t="str">
+        <v>Transfer_cannot_replace_an_active_organizer_even_if_their_creator_capability_was_removed</v>
+      </c>
+      <c r="B253" s="102"/>
+      <c r="C253" s="103"/>
+      <c r="D253" s="103"/>
+      <c r="E253" s="103"/>
+      <c r="F253" s="103"/>
+      <c r="G253" s="103"/>
+      <c r="H253" s="103"/>
+      <c r="I253" s="103"/>
+      <c r="J253" s="103"/>
+      <c r="K253" s="103"/>
+      <c r="L253" s="103"/>
+      <c r="M253" s="103"/>
+      <c r="N253" s="103"/>
+      <c r="O253" s="103"/>
+      <c r="P253" s="104"/>
+      <c r="Q253"/>
+      <c r="R253"/>
+      <c r="S253" s="90"/>
+      <c r="T253"/>
+    </row>
+    <row r="254" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+      <c r="A254" s="105" t="str">
+        <v>UTC158</v>
+      </c>
+      <c r="B254" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).</v>
+      </c>
+      <c r="C254" s="107" t="str">
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
+      </c>
+      <c r="D254" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E254" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F254" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G254" s="105" t="str"/>
+      <c r="H254" s="105" t="str"/>
+      <c r="I254" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J254" s="105"/>
+      <c r="K254" s="105"/>
+      <c r="L254" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M254" s="105"/>
+      <c r="N254" s="105"/>
+      <c r="O254" s="105" t="str"/>
+      <c r="P254" s="110" t="str"/>
+      <c r="Q254"/>
+      <c r="R254"/>
+      <c r="S254" s="94"/>
+      <c r="T254"/>
+    </row>
+    <row r="255" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A255" s="102" t="str">
+        <v>Transfer_rejects_an_invalid_organizer_without_recording_history</v>
+      </c>
+      <c r="B255" s="102"/>
+      <c r="C255" s="103"/>
+      <c r="D255" s="103"/>
+      <c r="E255" s="103"/>
+      <c r="F255" s="103"/>
+      <c r="G255" s="103"/>
+      <c r="H255" s="103"/>
+      <c r="I255" s="103"/>
+      <c r="J255" s="103"/>
+      <c r="K255" s="103"/>
+      <c r="L255" s="103"/>
+      <c r="M255" s="103"/>
+      <c r="N255" s="103"/>
+      <c r="O255" s="103"/>
+      <c r="P255" s="104"/>
+      <c r="Q255"/>
+      <c r="R255"/>
+      <c r="S255" s="90"/>
+      <c r="T255"/>
+    </row>
+    <row r="256" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+      <c r="A256" s="105" t="str">
+        <v>UTC159</v>
+      </c>
+      <c r="B256" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. _repository.InactiveUserIds.Add(_organizerId).
+4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
+      </c>
+      <c r="C256" s="107" t="str">
+        <v>target="missing"</v>
+      </c>
+      <c r="D256" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E256" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F256" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G256" s="105" t="str"/>
+      <c r="H256" s="105" t="str"/>
+      <c r="I256" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J256" s="105"/>
+      <c r="K256" s="105"/>
+      <c r="L256" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M256" s="105"/>
+      <c r="N256" s="105"/>
+      <c r="O256" s="105" t="str"/>
+      <c r="P256" s="110" t="str"/>
+      <c r="Q256"/>
+      <c r="R256"/>
+      <c r="S256" s="94"/>
+      <c r="T256"/>
+    </row>
+    <row r="257" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+      <c r="A257" s="105" t="str">
+        <v>UTC160</v>
+      </c>
+      <c r="B257" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. _repository.InactiveUserIds.Add(_organizerId).
+4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
+      </c>
       <c r="C257" s="107" t="str">
-        <v>inactive=false</v>
+        <v>target="inactive"</v>
       </c>
       <c r="D257" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.NotFound
+        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E257" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F257" s="105" t="str">
         <v>Pending</v>
@@ -14575,27 +14590,26 @@
       <c r="S257" s="94"/>
       <c r="T257"/>
     </row>
-    <row r="258" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
+    <row r="258" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A258" s="105" t="str">
-        <v>UTC160</v>
+        <v>UTC161</v>
       </c>
       <c r="B258" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. if (inactive) _repository.InactiveUserIds.Add(administrator).
-4. _repository.InactiveUserIds.Add(_organizerId).
-5. _repository.NextWorkflowReadThrows = new InvalidOperationException("Resource must not be loaded").</v>
+3. _repository.InactiveUserIds.Add(_organizerId).
+4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
       </c>
       <c r="C258" s="107" t="str">
-        <v>inactive=true</v>
+        <v>target="withoutCapability"</v>
       </c>
       <c r="D258" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.NotFound
+        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E258" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F258" s="105" t="str">
         <v>Pending</v>
@@ -14619,43 +14633,64 @@
       <c r="S258" s="94"/>
       <c r="T258"/>
     </row>
-    <row r="259" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A259" s="102" t="str">
-        <v>Transfer_cannot_replace_an_active_organizer_even_if_their_creator_capability_was_removed</v>
-      </c>
-      <c r="B259" s="102"/>
-      <c r="C259" s="103"/>
-      <c r="D259" s="103"/>
-      <c r="E259" s="103"/>
-      <c r="F259" s="103"/>
-      <c r="G259" s="103"/>
-      <c r="H259" s="103"/>
-      <c r="I259" s="103"/>
-      <c r="J259" s="103"/>
-      <c r="K259" s="103"/>
-      <c r="L259" s="103"/>
-      <c r="M259" s="103"/>
-      <c r="N259" s="103"/>
-      <c r="O259" s="103"/>
-      <c r="P259" s="104"/>
+    <row r="259" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+      <c r="A259" s="105" t="str">
+        <v>UTC162</v>
+      </c>
+      <c r="B259" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. _repository.InactiveUserIds.Add(_organizerId).
+4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
+      </c>
+      <c r="C259" s="107" t="str">
+        <v>target="previousOrganizer"</v>
+      </c>
+      <c r="D259" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E259" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F259" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G259" s="105" t="str"/>
+      <c r="H259" s="105" t="str"/>
+      <c r="I259" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J259" s="105"/>
+      <c r="K259" s="105"/>
+      <c r="L259" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M259" s="105"/>
+      <c r="N259" s="105"/>
+      <c r="O259" s="105" t="str"/>
+      <c r="P259" s="110" t="str"/>
       <c r="Q259"/>
       <c r="R259"/>
-      <c r="S259" s="90"/>
+      <c r="S259" s="94"/>
       <c r="T259"/>
     </row>
-    <row r="260" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="260" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A260" s="105" t="str">
-        <v>UTC161</v>
+        <v>UTC163</v>
       </c>
       <c r="B260" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. _repository.InactiveUserIds.Add(_organizerId).
+4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
       </c>
       <c r="C260" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
+        <v>target="assignedApprover"</v>
       </c>
       <c r="D260" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
+        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -14686,7 +14721,7 @@
     </row>
     <row r="261" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A261" s="102" t="str">
-        <v>Transfer_rejects_an_invalid_organizer_without_recording_history</v>
+        <v>Transfer_requires_an_approved_meeting</v>
       </c>
       <c r="B261" s="102"/>
       <c r="C261" s="103"/>
@@ -14708,26 +14743,25 @@
       <c r="S261" s="90"/>
       <c r="T261"/>
     </row>
-    <row r="262" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="262" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A262" s="105" t="str">
-        <v>UTC162</v>
+        <v>UTC164</v>
       </c>
       <c r="B262" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. _repository.InactiveUserIds.Add(_organizerId).
-4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
+2. meeting: prepared by GivenMeeting (status).
+3. _repository.InactiveUserIds.Add(_organizerId).</v>
       </c>
       <c r="C262" s="107" t="str">
-        <v>target="missing"</v>
+        <v>status=MeetingStatus.Draft</v>
       </c>
       <c r="D262" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E262" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F262" s="105" t="str">
         <v>Pending</v>
@@ -14751,26 +14785,25 @@
       <c r="S262" s="94"/>
       <c r="T262"/>
     </row>
-    <row r="263" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="263" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A263" s="105" t="str">
-        <v>UTC163</v>
+        <v>UTC165</v>
       </c>
       <c r="B263" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. _repository.InactiveUserIds.Add(_organizerId).
-4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
+2. meeting: prepared by GivenMeeting (status).
+3. _repository.InactiveUserIds.Add(_organizerId).</v>
       </c>
       <c r="C263" s="107" t="str">
-        <v>target="inactive"</v>
+        <v>status=MeetingStatus.WaitingApproval</v>
       </c>
       <c r="D263" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E263" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F263" s="105" t="str">
         <v>Pending</v>
@@ -14794,26 +14827,25 @@
       <c r="S263" s="94"/>
       <c r="T263"/>
     </row>
-    <row r="264" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="264" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A264" s="105" t="str">
-        <v>UTC164</v>
+        <v>UTC166</v>
       </c>
       <c r="B264" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. _repository.InactiveUserIds.Add(_organizerId).
-4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
+2. meeting: prepared by GivenMeeting (status).
+3. _repository.InactiveUserIds.Add(_organizerId).</v>
       </c>
       <c r="C264" s="107" t="str">
-        <v>target="withoutCapability"</v>
+        <v>status=MeetingStatus.Rejected</v>
       </c>
       <c r="D264" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E264" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F264" s="105" t="str">
         <v>Pending</v>
@@ -14837,26 +14869,25 @@
       <c r="S264" s="94"/>
       <c r="T264"/>
     </row>
-    <row r="265" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="265" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A265" s="105" t="str">
-        <v>UTC165</v>
+        <v>UTC167</v>
       </c>
       <c r="B265" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. _repository.InactiveUserIds.Add(_organizerId).
-4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
+2. meeting: prepared by GivenMeeting (status).
+3. _repository.InactiveUserIds.Add(_organizerId).</v>
       </c>
       <c r="C265" s="107" t="str">
-        <v>target="previousOrganizer"</v>
+        <v>status=MeetingStatus.Published</v>
       </c>
       <c r="D265" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E265" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F265" s="105" t="str">
         <v>Pending</v>
@@ -14880,129 +14911,115 @@
       <c r="S265" s="94"/>
       <c r="T265"/>
     </row>
-    <row r="266" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
-      <c r="A266" s="105" t="str">
-        <v>UTC166</v>
-      </c>
-      <c r="B266" s="106" t="str">
+    <row r="266" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A266" s="102" t="str">
+        <v>Transfer_save_failure_rolls_back_the_organizer_and_history</v>
+      </c>
+      <c r="B266" s="102"/>
+      <c r="C266" s="103"/>
+      <c r="D266" s="103"/>
+      <c r="E266" s="103"/>
+      <c r="F266" s="103"/>
+      <c r="G266" s="103"/>
+      <c r="H266" s="103"/>
+      <c r="I266" s="103"/>
+      <c r="J266" s="103"/>
+      <c r="K266" s="103"/>
+      <c r="L266" s="103"/>
+      <c r="M266" s="103"/>
+      <c r="N266" s="103"/>
+      <c r="O266" s="103"/>
+      <c r="P266" s="104"/>
+      <c r="Q266"/>
+      <c r="R266"/>
+      <c r="S266" s="90"/>
+      <c r="T266"/>
+    </row>
+    <row r="267" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+      <c r="A267" s="105" t="str">
+        <v>UTC168</v>
+      </c>
+      <c r="B267" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
 3. _repository.InactiveUserIds.Add(_organizerId).
-4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
-      </c>
-      <c r="C266" s="107" t="str">
-        <v>target="assignedApprover"</v>
-      </c>
-      <c r="D266" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E266" s="109" t="str">
+4. _repository.NextSaveThrows = new TimeoutException("Persistence unavailable").</v>
+      </c>
+      <c r="C267" s="107" t="str">
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
+      </c>
+      <c r="D267" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.SaveFailed
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E267" s="109" t="str">
         <v>Abnormal</v>
       </c>
-      <c r="F266" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G266" s="105" t="str"/>
-      <c r="H266" s="105" t="str"/>
-      <c r="I266" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J266" s="105"/>
-      <c r="K266" s="105"/>
-      <c r="L266" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M266" s="105"/>
-      <c r="N266" s="105"/>
-      <c r="O266" s="105" t="str"/>
-      <c r="P266" s="110" t="str"/>
-      <c r="Q266"/>
-      <c r="R266"/>
-      <c r="S266" s="94"/>
-      <c r="T266"/>
-    </row>
-    <row r="267" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A267" s="102" t="str">
-        <v>Transfer_requires_an_approved_meeting</v>
-      </c>
-      <c r="B267" s="102"/>
-      <c r="C267" s="103"/>
-      <c r="D267" s="103"/>
-      <c r="E267" s="103"/>
-      <c r="F267" s="103"/>
-      <c r="G267" s="103"/>
-      <c r="H267" s="103"/>
-      <c r="I267" s="103"/>
-      <c r="J267" s="103"/>
-      <c r="K267" s="103"/>
-      <c r="L267" s="103"/>
-      <c r="M267" s="103"/>
-      <c r="N267" s="103"/>
-      <c r="O267" s="103"/>
-      <c r="P267" s="104"/>
+      <c r="F267" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G267" s="105" t="str"/>
+      <c r="H267" s="105" t="str"/>
+      <c r="I267" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J267" s="105"/>
+      <c r="K267" s="105"/>
+      <c r="L267" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M267" s="105"/>
+      <c r="N267" s="105"/>
+      <c r="O267" s="105" t="str"/>
+      <c r="P267" s="110" t="str"/>
       <c r="Q267"/>
       <c r="R267"/>
-      <c r="S267" s="90"/>
+      <c r="S267" s="94"/>
       <c r="T267"/>
     </row>
-    <row r="268" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
-      <c r="A268" s="105" t="str">
-        <v>UTC167</v>
-      </c>
-      <c r="B268" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. _repository.InactiveUserIds.Add(_organizerId).</v>
-      </c>
-      <c r="C268" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
-      </c>
-      <c r="D268" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E268" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F268" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G268" s="105" t="str"/>
-      <c r="H268" s="105" t="str"/>
-      <c r="I268" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J268" s="105"/>
-      <c r="K268" s="105"/>
-      <c r="L268" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M268" s="105"/>
-      <c r="N268" s="105"/>
-      <c r="O268" s="105" t="str"/>
-      <c r="P268" s="110" t="str"/>
+    <row r="268" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A268" s="102" t="str">
+        <v>Transfer_organizer_ids_are_visible_only_in_full_history</v>
+      </c>
+      <c r="B268" s="102"/>
+      <c r="C268" s="103"/>
+      <c r="D268" s="103"/>
+      <c r="E268" s="103"/>
+      <c r="F268" s="103"/>
+      <c r="G268" s="103"/>
+      <c r="H268" s="103"/>
+      <c r="I268" s="103"/>
+      <c r="J268" s="103"/>
+      <c r="K268" s="103"/>
+      <c r="L268" s="103"/>
+      <c r="M268" s="103"/>
+      <c r="N268" s="103"/>
+      <c r="O268" s="103"/>
+      <c r="P268" s="104"/>
       <c r="Q268"/>
       <c r="R268"/>
-      <c r="S268" s="94"/>
+      <c r="S268" s="90"/>
       <c r="T268"/>
     </row>
-    <row r="269" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="269" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A269" s="105" t="str">
-        <v>UTC168</v>
+        <v>UTC169</v>
       </c>
       <c r="B269" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. _repository.InactiveUserIds.Add(_organizerId).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Published).
+3. meeting.Participants.Add(member).
+4. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, FromStatus = MeetingStatus.Approved, ToStatus = MeetingStatus.….</v>
       </c>
       <c r="C269" s="107" t="str">
-        <v>status=MeetingStatus.WaitingApproval</v>
+        <v>meeting.Id; _organizerId; 1; 20</v>
       </c>
       <c r="D269" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
+        <v>Return:
+1. full.Page.Items.Single().NewOrganizerId: _organizerId
+2. limited.Page.Items.Single().NewOrganizerId: null
+3. limited.Page.Items.Single().Action: MeetingHistoryAction.TransferOrganizer
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -15031,67 +15048,54 @@
       <c r="S269" s="94"/>
       <c r="T269"/>
     </row>
-    <row r="270" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
-      <c r="A270" s="105" t="str">
-        <v>UTC169</v>
-      </c>
-      <c r="B270" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. _repository.InactiveUserIds.Add(_organizerId).</v>
-      </c>
-      <c r="C270" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
-      </c>
-      <c r="D270" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E270" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F270" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G270" s="105" t="str"/>
-      <c r="H270" s="105" t="str"/>
-      <c r="I270" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J270" s="105"/>
-      <c r="K270" s="105"/>
-      <c r="L270" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M270" s="105"/>
-      <c r="N270" s="105"/>
-      <c r="O270" s="105" t="str"/>
-      <c r="P270" s="110" t="str"/>
+    <row r="270" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A270" s="102" t="str">
+        <v>Submit_accepts_draft_or_rejected_without_agenda_or_sessions</v>
+      </c>
+      <c r="B270" s="102"/>
+      <c r="C270" s="103"/>
+      <c r="D270" s="103"/>
+      <c r="E270" s="103"/>
+      <c r="F270" s="103"/>
+      <c r="G270" s="103"/>
+      <c r="H270" s="103"/>
+      <c r="I270" s="103"/>
+      <c r="J270" s="103"/>
+      <c r="K270" s="103"/>
+      <c r="L270" s="103"/>
+      <c r="M270" s="103"/>
+      <c r="N270" s="103"/>
+      <c r="O270" s="103"/>
+      <c r="P270" s="104"/>
       <c r="Q270"/>
       <c r="R270"/>
-      <c r="S270" s="94"/>
+      <c r="S270" s="90"/>
       <c r="T270"/>
     </row>
-    <row r="271" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="271" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A271" s="105" t="str">
         <v>UTC170</v>
       </c>
       <c r="B271" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (status).
-3. _repository.InactiveUserIds.Add(_organizerId).</v>
+3. previousApproverId = _approverId.
+4. MeetingStatusHistory? rejection = null.
+5. if (status == MeetingStatus.Rejected) { rejection = new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject….</v>
       </c>
       <c r="C271" s="107" t="str">
-        <v>status=MeetingStatus.Published</v>
+        <v>status=MeetingStatus.Draft</v>
       </c>
       <c r="D271" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
+        <v>Return:
+1. readiness.Ready: true
+2. readiness.Status: status
+3. result.Outcome: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E271" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F271" s="105" t="str">
         <v>Pending</v>
@@ -15115,120 +15119,142 @@
       <c r="S271" s="94"/>
       <c r="T271"/>
     </row>
-    <row r="272" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A272" s="102" t="str">
-        <v>Transfer_save_failure_rolls_back_the_organizer_and_history</v>
-      </c>
-      <c r="B272" s="102"/>
-      <c r="C272" s="103"/>
-      <c r="D272" s="103"/>
-      <c r="E272" s="103"/>
-      <c r="F272" s="103"/>
-      <c r="G272" s="103"/>
-      <c r="H272" s="103"/>
-      <c r="I272" s="103"/>
-      <c r="J272" s="103"/>
-      <c r="K272" s="103"/>
-      <c r="L272" s="103"/>
-      <c r="M272" s="103"/>
-      <c r="N272" s="103"/>
-      <c r="O272" s="103"/>
-      <c r="P272" s="104"/>
+    <row r="272" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+      <c r="A272" s="105" t="str">
+        <v>UTC171</v>
+      </c>
+      <c r="B272" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (status).
+3. previousApproverId = _approverId.
+4. MeetingStatusHistory? rejection = null.
+5. if (status == MeetingStatus.Rejected) { rejection = new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject….</v>
+      </c>
+      <c r="C272" s="107" t="str">
+        <v>status=MeetingStatus.Rejected</v>
+      </c>
+      <c r="D272" s="108" t="str">
+        <v>Return:
+1. readiness.Ready: true
+2. readiness.Status: status
+3. result.Outcome: MeetingWorkflowOutcome.Success
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E272" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F272" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G272" s="105" t="str"/>
+      <c r="H272" s="105" t="str"/>
+      <c r="I272" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J272" s="105"/>
+      <c r="K272" s="105"/>
+      <c r="L272" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M272" s="105"/>
+      <c r="N272" s="105"/>
+      <c r="O272" s="105" t="str"/>
+      <c r="P272" s="110" t="str"/>
       <c r="Q272"/>
       <c r="R272"/>
-      <c r="S272" s="90"/>
+      <c r="S272" s="94"/>
       <c r="T272"/>
     </row>
-    <row r="273" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
-      <c r="A273" s="105" t="str">
-        <v>UTC171</v>
-      </c>
-      <c r="B273" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. _repository.InactiveUserIds.Add(_organizerId).
-4. _repository.NextSaveThrows = new TimeoutException("Persistence unavailable").</v>
-      </c>
-      <c r="C273" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
-      </c>
-      <c r="D273" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.SaveFailed
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E273" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F273" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G273" s="105" t="str"/>
-      <c r="H273" s="105" t="str"/>
-      <c r="I273" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J273" s="105"/>
-      <c r="K273" s="105"/>
-      <c r="L273" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M273" s="105"/>
-      <c r="N273" s="105"/>
-      <c r="O273" s="105" t="str"/>
-      <c r="P273" s="110" t="str"/>
+    <row r="273" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A273" s="102" t="str">
+        <v>Failed_rejected_resubmission_keeps_assignment_and_rejection_evidence</v>
+      </c>
+      <c r="B273" s="102"/>
+      <c r="C273" s="103"/>
+      <c r="D273" s="103"/>
+      <c r="E273" s="103"/>
+      <c r="F273" s="103"/>
+      <c r="G273" s="103"/>
+      <c r="H273" s="103"/>
+      <c r="I273" s="103"/>
+      <c r="J273" s="103"/>
+      <c r="K273" s="103"/>
+      <c r="L273" s="103"/>
+      <c r="M273" s="103"/>
+      <c r="N273" s="103"/>
+      <c r="O273" s="103"/>
+      <c r="P273" s="104"/>
       <c r="Q273"/>
       <c r="R273"/>
-      <c r="S273" s="94"/>
+      <c r="S273" s="90"/>
       <c r="T273"/>
     </row>
-    <row r="274" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A274" s="102" t="str">
-        <v>Transfer_organizer_ids_are_visible_only_in_full_history</v>
-      </c>
-      <c r="B274" s="102"/>
-      <c r="C274" s="103"/>
-      <c r="D274" s="103"/>
-      <c r="E274" s="103"/>
-      <c r="F274" s="103"/>
-      <c r="G274" s="103"/>
-      <c r="H274" s="103"/>
-      <c r="I274" s="103"/>
-      <c r="J274" s="103"/>
-      <c r="K274" s="103"/>
-      <c r="L274" s="103"/>
-      <c r="M274" s="103"/>
-      <c r="N274" s="103"/>
-      <c r="O274" s="103"/>
-      <c r="P274" s="104"/>
+    <row r="274" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+      <c r="A274" s="105" t="str">
+        <v>UTC172</v>
+      </c>
+      <c r="B274" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
+3. rejection: a new MeetingStatusHistory is prepared.
+4. meeting.StatusHistory.Add(rejection).
+5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
+      </c>
+      <c r="C274" s="107" t="str">
+        <v>failure="invalidApprover"; expected=MeetingWorkflowOutcome.InvalidApprover</v>
+      </c>
+      <c r="D274" s="108" t="str">
+        <v>Return: expected
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E274" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F274" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G274" s="105" t="str"/>
+      <c r="H274" s="105" t="str"/>
+      <c r="I274" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J274" s="105"/>
+      <c r="K274" s="105"/>
+      <c r="L274" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M274" s="105"/>
+      <c r="N274" s="105"/>
+      <c r="O274" s="105" t="str"/>
+      <c r="P274" s="110" t="str"/>
       <c r="Q274"/>
       <c r="R274"/>
-      <c r="S274" s="90"/>
+      <c r="S274" s="94"/>
       <c r="T274"/>
     </row>
-    <row r="275" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
+    <row r="275" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
       <c r="A275" s="105" t="str">
-        <v>UTC172</v>
+        <v>UTC173</v>
       </c>
       <c r="B275" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Published).
-3. meeting.Participants.Add(member).
-4. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, FromStatus = MeetingStatus.Approved, ToStatus = MeetingStatus.….</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
+3. rejection: a new MeetingStatusHistory is prepared.
+4. meeting.StatusHistory.Add(rejection).
+5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
       </c>
       <c r="C275" s="107" t="str">
-        <v>meeting.Id; _organizerId; 1; 20</v>
+        <v>failure="invalidInformation"; expected=MeetingWorkflowOutcome.SubmissionNotReady</v>
       </c>
       <c r="D275" s="108" t="str">
-        <v>Return:
-1. full.Page.Items.Single().NewOrganizerId: _organizerId
-2. limited.Page.Items.Single().NewOrganizerId: null
-3. limited.Page.Items.Single().Action: MeetingHistoryAction.TransferOrganizer
+        <v>Return: expected
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E275" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F275" s="105" t="str">
         <v>Pending</v>
@@ -15252,101 +15278,93 @@
       <c r="S275" s="94"/>
       <c r="T275"/>
     </row>
-    <row r="276" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A276" s="102" t="str">
-        <v>Submit_accepts_draft_or_rejected_without_agenda_or_sessions</v>
-      </c>
-      <c r="B276" s="102"/>
-      <c r="C276" s="103"/>
-      <c r="D276" s="103"/>
-      <c r="E276" s="103"/>
-      <c r="F276" s="103"/>
-      <c r="G276" s="103"/>
-      <c r="H276" s="103"/>
-      <c r="I276" s="103"/>
-      <c r="J276" s="103"/>
-      <c r="K276" s="103"/>
-      <c r="L276" s="103"/>
-      <c r="M276" s="103"/>
-      <c r="N276" s="103"/>
-      <c r="O276" s="103"/>
-      <c r="P276" s="104"/>
+    <row r="276" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+      <c r="A276" s="105" t="str">
+        <v>UTC174</v>
+      </c>
+      <c r="B276" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
+3. rejection: a new MeetingStatusHistory is prepared.
+4. meeting.StatusHistory.Add(rejection).
+5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
+      </c>
+      <c r="C276" s="107" t="str">
+        <v>failure="saveFailure"; expected=MeetingWorkflowOutcome.SaveFailed</v>
+      </c>
+      <c r="D276" s="108" t="str">
+        <v>Return: expected
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E276" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F276" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G276" s="105" t="str"/>
+      <c r="H276" s="105" t="str"/>
+      <c r="I276" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J276" s="105"/>
+      <c r="K276" s="105"/>
+      <c r="L276" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M276" s="105"/>
+      <c r="N276" s="105"/>
+      <c r="O276" s="105" t="str"/>
+      <c r="P276" s="110" t="str"/>
       <c r="Q276"/>
       <c r="R276"/>
-      <c r="S276" s="90"/>
+      <c r="S276" s="94"/>
       <c r="T276"/>
     </row>
-    <row r="277" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
-      <c r="A277" s="105" t="str">
-        <v>UTC173</v>
-      </c>
-      <c r="B277" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. previousApproverId = _approverId.
-4. MeetingStatusHistory? rejection = null.
-5. if (status == MeetingStatus.Rejected) { rejection = new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject….</v>
-      </c>
-      <c r="C277" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
-      </c>
-      <c r="D277" s="108" t="str">
-        <v>Return:
-1. readiness.Ready: true
-2. readiness.Status: status
-3. result.Outcome: MeetingWorkflowOutcome.Success
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E277" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F277" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G277" s="105" t="str"/>
-      <c r="H277" s="105" t="str"/>
-      <c r="I277" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J277" s="105"/>
-      <c r="K277" s="105"/>
-      <c r="L277" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M277" s="105"/>
-      <c r="N277" s="105"/>
-      <c r="O277" s="105" t="str"/>
-      <c r="P277" s="110" t="str"/>
+    <row r="277" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A277" s="102" t="str">
+        <v>Publish_succeeds_with_the_meeting_level_schedule</v>
+      </c>
+      <c r="B277" s="102"/>
+      <c r="C277" s="103"/>
+      <c r="D277" s="103"/>
+      <c r="E277" s="103"/>
+      <c r="F277" s="103"/>
+      <c r="G277" s="103"/>
+      <c r="H277" s="103"/>
+      <c r="I277" s="103"/>
+      <c r="J277" s="103"/>
+      <c r="K277" s="103"/>
+      <c r="L277" s="103"/>
+      <c r="M277" s="103"/>
+      <c r="N277" s="103"/>
+      <c r="O277" s="103"/>
+      <c r="P277" s="104"/>
       <c r="Q277"/>
       <c r="R277"/>
-      <c r="S277" s="94"/>
+      <c r="S277" s="90"/>
       <c r="T277"/>
     </row>
-    <row r="278" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+    <row r="278" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A278" s="105" t="str">
-        <v>UTC174</v>
+        <v>UTC175</v>
       </c>
       <c r="B278" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
-3. previousApproverId = _approverId.
-4. MeetingStatusHistory? rejection = null.
-5. if (status == MeetingStatus.Rejected) { rejection = new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject….</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. meeting.Participants.Add(Participant(meeting, active: true, InvitationResponse.Accepted)).</v>
       </c>
       <c r="C278" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
       </c>
       <c r="D278" s="108" t="str">
-        <v>Return:
-1. readiness.Ready: true
-2. readiness.Status: status
-3. result.Outcome: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E278" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F278" s="105" t="str">
         <v>Pending</v>
@@ -15372,7 +15390,7 @@
     </row>
     <row r="279" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A279" s="102" t="str">
-        <v>Failed_rejected_resubmission_keeps_assignment_and_rejection_evidence</v>
+        <v>Publish_requires_exactly_one_active_chair_and_an_active_secretary</v>
       </c>
       <c r="B279" s="102"/>
       <c r="C279" s="103"/>
@@ -15394,27 +15412,25 @@
       <c r="S279" s="90"/>
       <c r="T279"/>
     </row>
-    <row r="280" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+    <row r="280" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A280" s="105" t="str">
-        <v>UTC175</v>
+        <v>UTC176</v>
       </c>
       <c r="B280" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. rejection: a new MeetingStatusHistory is prepared.
-4. meeting.StatusHistory.Add(rejection).
-5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C280" s="107" t="str">
-        <v>failure="invalidApprover"; expected=MeetingWorkflowOutcome.InvalidApprover</v>
+        <v>scenario="no-participants"</v>
       </c>
       <c r="D280" s="108" t="str">
-        <v>Return: expected
+        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E280" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Boundary</v>
       </c>
       <c r="F280" s="105" t="str">
         <v>Pending</v>
@@ -15438,27 +15454,25 @@
       <c r="S280" s="94"/>
       <c r="T280"/>
     </row>
-    <row r="281" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+    <row r="281" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A281" s="105" t="str">
-        <v>UTC176</v>
+        <v>UTC177</v>
       </c>
       <c r="B281" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. rejection: a new MeetingStatusHistory is prepared.
-4. meeting.StatusHistory.Add(rejection).
-5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C281" s="107" t="str">
-        <v>failure="invalidInformation"; expected=MeetingWorkflowOutcome.SubmissionNotReady</v>
+        <v>scenario="no-chair"</v>
       </c>
       <c r="D281" s="108" t="str">
-        <v>Return: expected
+        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E281" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Boundary</v>
       </c>
       <c r="F281" s="105" t="str">
         <v>Pending</v>
@@ -15482,27 +15496,25 @@
       <c r="S281" s="94"/>
       <c r="T281"/>
     </row>
-    <row r="282" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+    <row r="282" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A282" s="105" t="str">
-        <v>UTC177</v>
+        <v>UTC178</v>
       </c>
       <c r="B282" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. rejection: a new MeetingStatusHistory is prepared.
-4. meeting.StatusHistory.Add(rejection).
-5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C282" s="107" t="str">
-        <v>failure="saveFailure"; expected=MeetingWorkflowOutcome.SaveFailed</v>
+        <v>scenario="multiple-chairs"</v>
       </c>
       <c r="D282" s="108" t="str">
-        <v>Return: expected
+        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E282" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Boundary</v>
       </c>
       <c r="F282" s="105" t="str">
         <v>Pending</v>
@@ -15526,49 +15538,67 @@
       <c r="S282" s="94"/>
       <c r="T282"/>
     </row>
-    <row r="283" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A283" s="102" t="str">
-        <v>Publish_succeeds_with_the_meeting_level_schedule</v>
-      </c>
-      <c r="B283" s="102"/>
-      <c r="C283" s="103"/>
-      <c r="D283" s="103"/>
-      <c r="E283" s="103"/>
-      <c r="F283" s="103"/>
-      <c r="G283" s="103"/>
-      <c r="H283" s="103"/>
-      <c r="I283" s="103"/>
-      <c r="J283" s="103"/>
-      <c r="K283" s="103"/>
-      <c r="L283" s="103"/>
-      <c r="M283" s="103"/>
-      <c r="N283" s="103"/>
-      <c r="O283" s="103"/>
-      <c r="P283" s="104"/>
+    <row r="283" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+      <c r="A283" s="105" t="str">
+        <v>UTC179</v>
+      </c>
+      <c r="B283" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
+      </c>
+      <c r="C283" s="107" t="str">
+        <v>scenario="inactive-chair"</v>
+      </c>
+      <c r="D283" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E283" s="109" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="F283" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G283" s="105" t="str"/>
+      <c r="H283" s="105" t="str"/>
+      <c r="I283" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J283" s="105"/>
+      <c r="K283" s="105"/>
+      <c r="L283" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M283" s="105"/>
+      <c r="N283" s="105"/>
+      <c r="O283" s="105" t="str"/>
+      <c r="P283" s="110" t="str"/>
       <c r="Q283"/>
       <c r="R283"/>
-      <c r="S283" s="90"/>
+      <c r="S283" s="94"/>
       <c r="T283"/>
     </row>
-    <row r="284" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="284" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A284" s="105" t="str">
-        <v>UTC178</v>
+        <v>UTC180</v>
       </c>
       <c r="B284" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. meeting.Participants.Add(Participant(meeting, active: true, InvitationResponse.Accepted)).</v>
+3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C284" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
+        <v>scenario="no-secretary"</v>
       </c>
       <c r="D284" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E284" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F284" s="105" t="str">
         <v>Pending</v>
@@ -15592,91 +15622,97 @@
       <c r="S284" s="94"/>
       <c r="T284"/>
     </row>
-    <row r="285" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A285" s="102" t="str">
-        <v>Publish_requires_exactly_one_active_chair_and_an_active_secretary</v>
-      </c>
-      <c r="B285" s="102"/>
-      <c r="C285" s="103"/>
-      <c r="D285" s="103"/>
-      <c r="E285" s="103"/>
-      <c r="F285" s="103"/>
-      <c r="G285" s="103"/>
-      <c r="H285" s="103"/>
-      <c r="I285" s="103"/>
-      <c r="J285" s="103"/>
-      <c r="K285" s="103"/>
-      <c r="L285" s="103"/>
-      <c r="M285" s="103"/>
-      <c r="N285" s="103"/>
-      <c r="O285" s="103"/>
-      <c r="P285" s="104"/>
-      <c r="Q285"/>
-      <c r="R285"/>
-      <c r="S285" s="90"/>
-      <c r="T285"/>
-    </row>
-    <row r="286" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
-      <c r="A286" s="105" t="str">
-        <v>UTC179</v>
-      </c>
-      <c r="B286" s="106" t="str">
+    <row r="285" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+      <c r="A285" s="105" t="str">
+        <v>UTC181</v>
+      </c>
+      <c r="B285" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
 2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
 3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
-      <c r="C286" s="107" t="str">
-        <v>scenario="no-participants"</v>
-      </c>
-      <c r="D286" s="108" t="str">
+      <c r="C285" s="107" t="str">
+        <v>scenario="inactive-secretaries"</v>
+      </c>
+      <c r="D285" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
 Exception: N/A
 Log Message: N/A</v>
       </c>
-      <c r="E286" s="109" t="str">
+      <c r="E285" s="109" t="str">
         <v>Boundary</v>
       </c>
-      <c r="F286" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G286" s="105" t="str"/>
-      <c r="H286" s="105" t="str"/>
-      <c r="I286" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J286" s="105"/>
-      <c r="K286" s="105"/>
-      <c r="L286" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M286" s="105"/>
-      <c r="N286" s="105"/>
-      <c r="O286" s="105" t="str"/>
-      <c r="P286" s="110" t="str"/>
+      <c r="F285" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G285" s="105" t="str"/>
+      <c r="H285" s="105" t="str"/>
+      <c r="I285" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J285" s="105"/>
+      <c r="K285" s="105"/>
+      <c r="L285" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M285" s="105"/>
+      <c r="N285" s="105"/>
+      <c r="O285" s="105" t="str"/>
+      <c r="P285" s="110" t="str"/>
+      <c r="Q285"/>
+      <c r="R285"/>
+      <c r="S285" s="94"/>
+      <c r="T285"/>
+    </row>
+    <row r="286" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A286" s="102" t="str">
+        <v>Assigned_secretary_reads_detail_and_rejection_reason_without_transfer_ids</v>
+      </c>
+      <c r="B286" s="102"/>
+      <c r="C286" s="103"/>
+      <c r="D286" s="103"/>
+      <c r="E286" s="103"/>
+      <c r="F286" s="103"/>
+      <c r="G286" s="103"/>
+      <c r="H286" s="103"/>
+      <c r="I286" s="103"/>
+      <c r="J286" s="103"/>
+      <c r="K286" s="103"/>
+      <c r="L286" s="103"/>
+      <c r="M286" s="103"/>
+      <c r="N286" s="103"/>
+      <c r="O286" s="103"/>
+      <c r="P286" s="104"/>
       <c r="Q286"/>
       <c r="R286"/>
-      <c r="S286" s="94"/>
+      <c r="S286" s="90"/>
       <c r="T286"/>
     </row>
-    <row r="287" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="287" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
       <c r="A287" s="105" t="str">
-        <v>UTC180</v>
+        <v>UTC182</v>
       </c>
       <c r="B287" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
+2. meeting: prepared by GivenMeeting (status).
+3. secretary.Role = MeetingRole.Secretary.
+4. meeting.Participants.Add(secretary).
+5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
+6. Further arrangement is in the test source.</v>
       </c>
       <c r="C287" s="107" t="str">
-        <v>scenario="no-chair"</v>
+        <v>status=MeetingStatus.Draft</v>
       </c>
       <c r="D287" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
+        <v>Return:
+1. history.Outcome: MeetingWorkflowOutcome.Success
+2. history.Page.Items: every item passes the check
+3. details.Outcome: MeetingOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E287" s="109" t="str">
-        <v>Boundary</v>
+        <v>Abnormal</v>
       </c>
       <c r="F287" s="105" t="str">
         <v>Pending</v>
@@ -15700,25 +15736,31 @@
       <c r="S287" s="94"/>
       <c r="T287"/>
     </row>
-    <row r="288" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="288" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
       <c r="A288" s="105" t="str">
-        <v>UTC181</v>
+        <v>UTC183</v>
       </c>
       <c r="B288" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
+2. meeting: prepared by GivenMeeting (status).
+3. secretary.Role = MeetingRole.Secretary.
+4. meeting.Participants.Add(secretary).
+5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
+6. Further arrangement is in the test source.</v>
       </c>
       <c r="C288" s="107" t="str">
-        <v>scenario="multiple-chairs"</v>
+        <v>status=MeetingStatus.WaitingApproval</v>
       </c>
       <c r="D288" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
+        <v>Return:
+1. history.Outcome: MeetingWorkflowOutcome.Success
+2. history.Page.Items: every item passes the check
+3. details.Outcome: MeetingOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E288" s="109" t="str">
-        <v>Boundary</v>
+        <v>Abnormal</v>
       </c>
       <c r="F288" s="105" t="str">
         <v>Pending</v>
@@ -15742,25 +15784,31 @@
       <c r="S288" s="94"/>
       <c r="T288"/>
     </row>
-    <row r="289" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="289" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
       <c r="A289" s="105" t="str">
-        <v>UTC182</v>
+        <v>UTC184</v>
       </c>
       <c r="B289" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
+2. meeting: prepared by GivenMeeting (status).
+3. secretary.Role = MeetingRole.Secretary.
+4. meeting.Participants.Add(secretary).
+5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
+6. Further arrangement is in the test source.</v>
       </c>
       <c r="C289" s="107" t="str">
-        <v>scenario="inactive-chair"</v>
+        <v>status=MeetingStatus.Rejected</v>
       </c>
       <c r="D289" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
+        <v>Return:
+1. history.Outcome: MeetingWorkflowOutcome.Success
+2. history.Page.Items: every item passes the check
+3. details.Outcome: MeetingOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E289" s="109" t="str">
-        <v>Boundary</v>
+        <v>Abnormal</v>
       </c>
       <c r="F289" s="105" t="str">
         <v>Pending</v>
@@ -15784,25 +15832,31 @@
       <c r="S289" s="94"/>
       <c r="T289"/>
     </row>
-    <row r="290" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="290" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
       <c r="A290" s="105" t="str">
-        <v>UTC183</v>
+        <v>UTC185</v>
       </c>
       <c r="B290" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
+2. meeting: prepared by GivenMeeting (status).
+3. secretary.Role = MeetingRole.Secretary.
+4. meeting.Participants.Add(secretary).
+5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
+6. Further arrangement is in the test source.</v>
       </c>
       <c r="C290" s="107" t="str">
-        <v>scenario="no-secretary"</v>
+        <v>status=MeetingStatus.Approved</v>
       </c>
       <c r="D290" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
+        <v>Return:
+1. history.Outcome: MeetingWorkflowOutcome.Success
+2. history.Page.Items: every item passes the check
+3. details.Outcome: MeetingOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E290" s="109" t="str">
-        <v>Boundary</v>
+        <v>Abnormal</v>
       </c>
       <c r="F290" s="105" t="str">
         <v>Pending</v>
@@ -15826,25 +15880,31 @@
       <c r="S290" s="94"/>
       <c r="T290"/>
     </row>
-    <row r="291" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="291" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
       <c r="A291" s="105" t="str">
-        <v>UTC184</v>
+        <v>UTC186</v>
       </c>
       <c r="B291" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
+2. meeting: prepared by GivenMeeting (status).
+3. secretary.Role = MeetingRole.Secretary.
+4. meeting.Participants.Add(secretary).
+5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
+6. Further arrangement is in the test source.</v>
       </c>
       <c r="C291" s="107" t="str">
-        <v>scenario="inactive-secretaries"</v>
+        <v>status=MeetingStatus.Published</v>
       </c>
       <c r="D291" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
+        <v>Return:
+1. history.Outcome: MeetingWorkflowOutcome.Success
+2. history.Page.Items: every item passes the check
+3. details.Outcome: MeetingOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E291" s="109" t="str">
-        <v>Boundary</v>
+        <v>Abnormal</v>
       </c>
       <c r="F291" s="105" t="str">
         <v>Pending</v>
@@ -15870,7 +15930,7 @@
     </row>
     <row r="292" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A292" s="102" t="str">
-        <v>Assigned_secretary_reads_detail_and_rejection_reason_without_transfer_ids</v>
+        <v>Invalid_secretary_relationship_does_not_grant_prepublication_history</v>
       </c>
       <c r="B292" s="102"/>
       <c r="C292" s="103"/>
@@ -15892,26 +15952,23 @@
       <c r="S292" s="90"/>
       <c r="T292"/>
     </row>
-    <row r="293" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+    <row r="293" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A293" s="105" t="str">
-        <v>UTC185</v>
+        <v>UTC187</v>
       </c>
       <c r="B293" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
 3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).
-5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
-6. Further arrangement is in the test source.</v>
+4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C293" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>invalid="member"</v>
       </c>
       <c r="D293" s="108" t="str">
         <v>Return:
-1. history.Outcome: MeetingWorkflowOutcome.Success
-2. history.Page.Items: every item passes the check
-3. details.Outcome: MeetingOutcome.Success
+1. result.Outcome: MeetingWorkflowOutcome.NotFound
+2. result.Page: null
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -15940,26 +15997,23 @@
       <c r="S293" s="94"/>
       <c r="T293"/>
     </row>
-    <row r="294" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+    <row r="294" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A294" s="105" t="str">
-        <v>UTC186</v>
+        <v>UTC188</v>
       </c>
       <c r="B294" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
 3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).
-5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
-6. Further arrangement is in the test source.</v>
+4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C294" s="107" t="str">
-        <v>status=MeetingStatus.WaitingApproval</v>
+        <v>invalid="globalSecretary"</v>
       </c>
       <c r="D294" s="108" t="str">
         <v>Return:
-1. history.Outcome: MeetingWorkflowOutcome.Success
-2. history.Page.Items: every item passes the check
-3. details.Outcome: MeetingOutcome.Success
+1. result.Outcome: MeetingWorkflowOutcome.NotFound
+2. result.Page: null
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -15988,26 +16042,23 @@
       <c r="S294" s="94"/>
       <c r="T294"/>
     </row>
-    <row r="295" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+    <row r="295" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A295" s="105" t="str">
-        <v>UTC187</v>
+        <v>UTC189</v>
       </c>
       <c r="B295" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
 3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).
-5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
-6. Further arrangement is in the test source.</v>
+4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C295" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>invalid="otherMeeting"</v>
       </c>
       <c r="D295" s="108" t="str">
         <v>Return:
-1. history.Outcome: MeetingWorkflowOutcome.Success
-2. history.Page.Items: every item passes the check
-3. details.Outcome: MeetingOutcome.Success
+1. result.Outcome: MeetingWorkflowOutcome.NotFound
+2. result.Page: null
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -16036,26 +16087,23 @@
       <c r="S295" s="94"/>
       <c r="T295"/>
     </row>
-    <row r="296" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+    <row r="296" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A296" s="105" t="str">
-        <v>UTC188</v>
+        <v>UTC190</v>
       </c>
       <c r="B296" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
 3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).
-5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
-6. Further arrangement is in the test source.</v>
+4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C296" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
+        <v>invalid="delegated"</v>
       </c>
       <c r="D296" s="108" t="str">
         <v>Return:
-1. history.Outcome: MeetingWorkflowOutcome.Success
-2. history.Page.Items: every item passes the check
-3. details.Outcome: MeetingOutcome.Success
+1. result.Outcome: MeetingWorkflowOutcome.NotFound
+2. result.Page: null
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -16084,26 +16132,23 @@
       <c r="S296" s="94"/>
       <c r="T296"/>
     </row>
-    <row r="297" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
+    <row r="297" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A297" s="105" t="str">
-        <v>UTC189</v>
+        <v>UTC191</v>
       </c>
       <c r="B297" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).
+2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
 3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).
-5. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject, FromStatus = MeetingStat….
-6. Further arrangement is in the test source.</v>
+4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C297" s="107" t="str">
-        <v>status=MeetingStatus.Published</v>
+        <v>invalid="delegationTarget"</v>
       </c>
       <c r="D297" s="108" t="str">
         <v>Return:
-1. history.Outcome: MeetingWorkflowOutcome.Success
-2. history.Page.Items: every item passes the check
-3. details.Outcome: MeetingOutcome.Success
+1. result.Outcome: MeetingWorkflowOutcome.NotFound
+2. result.Page: null
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -16134,7 +16179,7 @@
     </row>
     <row r="298" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A298" s="102" t="str">
-        <v>Invalid_secretary_relationship_does_not_grant_prepublication_history</v>
+        <v>Cancel_after_publication_records_who_why_and_when_and_tells_the_invitees</v>
       </c>
       <c r="B298" s="102"/>
       <c r="C298" s="103"/>
@@ -16156,28 +16201,28 @@
       <c r="S298" s="90"/>
       <c r="T298"/>
     </row>
-    <row r="299" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="299" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A299" s="105" t="str">
-        <v>UTC190</v>
+        <v>UTC192</v>
       </c>
       <c r="B299" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. meeting.Status = MeetingStatus.Published.</v>
       </c>
       <c r="C299" s="107" t="str">
-        <v>invalid="member"</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
       </c>
       <c r="D299" s="108" t="str">
         <v>Return:
-1. result.Outcome: MeetingWorkflowOutcome.NotFound
-2. result.Page: null
+1. Outcome: MeetingWorkflowOutcome.Success
+2. History.CancellationReason: "Lãnh đạo đi công tác"
+3. Meeting.Cancellation.Reason: "Lãnh đạo đi công tác"
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E299" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F299" s="105" t="str">
         <v>Pending</v>
@@ -16201,73 +16246,48 @@
       <c r="S299" s="94"/>
       <c r="T299"/>
     </row>
-    <row r="300" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
-      <c r="A300" s="105" t="str">
-        <v>UTC191</v>
-      </c>
-      <c r="B300" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).</v>
-      </c>
-      <c r="C300" s="107" t="str">
-        <v>invalid="globalSecretary"</v>
-      </c>
-      <c r="D300" s="108" t="str">
-        <v>Return:
-1. result.Outcome: MeetingWorkflowOutcome.NotFound
-2. result.Page: null
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E300" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F300" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G300" s="105" t="str"/>
-      <c r="H300" s="105" t="str"/>
-      <c r="I300" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J300" s="105"/>
-      <c r="K300" s="105"/>
-      <c r="L300" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M300" s="105"/>
-      <c r="N300" s="105"/>
-      <c r="O300" s="105" t="str"/>
-      <c r="P300" s="110" t="str"/>
+    <row r="300" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A300" s="102" t="str">
+        <v>Cancel_while_waiting_for_approval_closes_the_request_and_tells_the_approver</v>
+      </c>
+      <c r="B300" s="102"/>
+      <c r="C300" s="103"/>
+      <c r="D300" s="103"/>
+      <c r="E300" s="103"/>
+      <c r="F300" s="103"/>
+      <c r="G300" s="103"/>
+      <c r="H300" s="103"/>
+      <c r="I300" s="103"/>
+      <c r="J300" s="103"/>
+      <c r="K300" s="103"/>
+      <c r="L300" s="103"/>
+      <c r="M300" s="103"/>
+      <c r="N300" s="103"/>
+      <c r="O300" s="103"/>
+      <c r="P300" s="104"/>
       <c r="Q300"/>
       <c r="R300"/>
-      <c r="S300" s="94"/>
+      <c r="S300" s="90"/>
       <c r="T300"/>
     </row>
-    <row r="301" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="301" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A301" s="105" t="str">
-        <v>UTC192</v>
+        <v>UTC193</v>
       </c>
       <c r="B301" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C301" s="107" t="str">
-        <v>invalid="otherMeeting"</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
       </c>
       <c r="D301" s="108" t="str">
-        <v>Return:
-1. result.Outcome: MeetingWorkflowOutcome.NotFound
-2. result.Page: null
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E301" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F301" s="105" t="str">
         <v>Pending</v>
@@ -16291,73 +16311,48 @@
       <c r="S301" s="94"/>
       <c r="T301"/>
     </row>
-    <row r="302" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
-      <c r="A302" s="105" t="str">
-        <v>UTC193</v>
-      </c>
-      <c r="B302" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).</v>
-      </c>
-      <c r="C302" s="107" t="str">
-        <v>invalid="delegated"</v>
-      </c>
-      <c r="D302" s="108" t="str">
-        <v>Return:
-1. result.Outcome: MeetingWorkflowOutcome.NotFound
-2. result.Page: null
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E302" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F302" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G302" s="105" t="str"/>
-      <c r="H302" s="105" t="str"/>
-      <c r="I302" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J302" s="105"/>
-      <c r="K302" s="105"/>
-      <c r="L302" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M302" s="105"/>
-      <c r="N302" s="105"/>
-      <c r="O302" s="105" t="str"/>
-      <c r="P302" s="110" t="str"/>
+    <row r="302" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A302" s="102" t="str">
+        <v>Cancel_before_publication_tells_nobody</v>
+      </c>
+      <c r="B302" s="102"/>
+      <c r="C302" s="103"/>
+      <c r="D302" s="103"/>
+      <c r="E302" s="103"/>
+      <c r="F302" s="103"/>
+      <c r="G302" s="103"/>
+      <c r="H302" s="103"/>
+      <c r="I302" s="103"/>
+      <c r="J302" s="103"/>
+      <c r="K302" s="103"/>
+      <c r="L302" s="103"/>
+      <c r="M302" s="103"/>
+      <c r="N302" s="103"/>
+      <c r="O302" s="103"/>
+      <c r="P302" s="104"/>
       <c r="Q302"/>
       <c r="R302"/>
-      <c r="S302" s="94"/>
+      <c r="S302" s="90"/>
       <c r="T302"/>
     </row>
-    <row r="303" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="303" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A303" s="105" t="str">
         <v>UTC194</v>
       </c>
       <c r="B303" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Rejected).
-3. secretary.Role = MeetingRole.Secretary.
-4. meeting.Participants.Add(secretary).</v>
+2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C303" s="107" t="str">
-        <v>invalid="delegationTarget"</v>
+        <v>status=MeetingStatus.Draft</v>
       </c>
       <c r="D303" s="108" t="str">
-        <v>Return:
-1. result.Outcome: MeetingWorkflowOutcome.NotFound
-2. result.Page: null
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E303" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Normal</v>
       </c>
       <c r="F303" s="105" t="str">
         <v>Pending</v>
@@ -16381,47 +16376,60 @@
       <c r="S303" s="94"/>
       <c r="T303"/>
     </row>
-    <row r="304" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A304" s="102" t="str">
-        <v>Cancel_after_publication_records_who_why_and_when_and_tells_the_invitees</v>
-      </c>
-      <c r="B304" s="102"/>
-      <c r="C304" s="103"/>
-      <c r="D304" s="103"/>
-      <c r="E304" s="103"/>
-      <c r="F304" s="103"/>
-      <c r="G304" s="103"/>
-      <c r="H304" s="103"/>
-      <c r="I304" s="103"/>
-      <c r="J304" s="103"/>
-      <c r="K304" s="103"/>
-      <c r="L304" s="103"/>
-      <c r="M304" s="103"/>
-      <c r="N304" s="103"/>
-      <c r="O304" s="103"/>
-      <c r="P304" s="104"/>
+    <row r="304" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+      <c r="A304" s="105" t="str">
+        <v>UTC195</v>
+      </c>
+      <c r="B304" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (status).</v>
+      </c>
+      <c r="C304" s="107" t="str">
+        <v>status=MeetingStatus.Rejected</v>
+      </c>
+      <c r="D304" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.Success
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E304" s="109" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F304" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G304" s="105" t="str"/>
+      <c r="H304" s="105" t="str"/>
+      <c r="I304" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J304" s="105"/>
+      <c r="K304" s="105"/>
+      <c r="L304" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M304" s="105"/>
+      <c r="N304" s="105"/>
+      <c r="O304" s="105" t="str"/>
+      <c r="P304" s="110" t="str"/>
       <c r="Q304"/>
       <c r="R304"/>
-      <c r="S304" s="90"/>
+      <c r="S304" s="94"/>
       <c r="T304"/>
     </row>
-    <row r="305" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="305" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A305" s="105" t="str">
-        <v>UTC195</v>
+        <v>UTC196</v>
       </c>
       <c r="B305" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. meeting.Status = MeetingStatus.Published.</v>
+2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C305" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
+        <v>status=MeetingStatus.Approved</v>
       </c>
       <c r="D305" s="108" t="str">
-        <v>Return:
-1. Outcome: MeetingWorkflowOutcome.Success
-2. History.CancellationReason: "Lãnh đạo đi công tác"
-3. Meeting.Cancellation.Reason: "Lãnh đạo đi công tác"
+        <v>Return: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -16452,7 +16460,7 @@
     </row>
     <row r="306" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A306" s="102" t="str">
-        <v>Cancel_while_waiting_for_approval_closes_the_request_and_tells_the_approver</v>
+        <v>A_started_ended_or_cancelled_meeting_cannot_be_cancelled</v>
       </c>
       <c r="B306" s="102"/>
       <c r="C306" s="103"/>
@@ -16474,24 +16482,25 @@
       <c r="S306" s="90"/>
       <c r="T306"/>
     </row>
-    <row r="307" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="307" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A307" s="105" t="str">
-        <v>UTC196</v>
+        <v>UTC197</v>
       </c>
       <c r="B307" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. meeting.Status = status.</v>
       </c>
       <c r="C307" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
+        <v>status=MeetingStatus.InProgress</v>
       </c>
       <c r="D307" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E307" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F307" s="105" t="str">
         <v>Pending</v>
@@ -16515,48 +16524,67 @@
       <c r="S307" s="94"/>
       <c r="T307"/>
     </row>
-    <row r="308" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A308" s="102" t="str">
-        <v>Cancel_before_publication_tells_nobody</v>
-      </c>
-      <c r="B308" s="102"/>
-      <c r="C308" s="103"/>
-      <c r="D308" s="103"/>
-      <c r="E308" s="103"/>
-      <c r="F308" s="103"/>
-      <c r="G308" s="103"/>
-      <c r="H308" s="103"/>
-      <c r="I308" s="103"/>
-      <c r="J308" s="103"/>
-      <c r="K308" s="103"/>
-      <c r="L308" s="103"/>
-      <c r="M308" s="103"/>
-      <c r="N308" s="103"/>
-      <c r="O308" s="103"/>
-      <c r="P308" s="104"/>
+    <row r="308" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+      <c r="A308" s="105" t="str">
+        <v>UTC198</v>
+      </c>
+      <c r="B308" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. meeting.Status = status.</v>
+      </c>
+      <c r="C308" s="107" t="str">
+        <v>status=MeetingStatus.Ended</v>
+      </c>
+      <c r="D308" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E308" s="109" t="str">
+        <v>Abnormal</v>
+      </c>
+      <c r="F308" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G308" s="105" t="str"/>
+      <c r="H308" s="105" t="str"/>
+      <c r="I308" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J308" s="105"/>
+      <c r="K308" s="105"/>
+      <c r="L308" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M308" s="105"/>
+      <c r="N308" s="105"/>
+      <c r="O308" s="105" t="str"/>
+      <c r="P308" s="110" t="str"/>
       <c r="Q308"/>
       <c r="R308"/>
-      <c r="S308" s="90"/>
+      <c r="S308" s="94"/>
       <c r="T308"/>
     </row>
-    <row r="309" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="309" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A309" s="105" t="str">
-        <v>UTC197</v>
+        <v>UTC199</v>
       </c>
       <c r="B309" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
+3. meeting.Status = status.</v>
       </c>
       <c r="C309" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>status=MeetingStatus.Cancelled</v>
       </c>
       <c r="D309" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.StatusConflict
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E309" s="109" t="str">
-        <v>Normal</v>
+        <v>Abnormal</v>
       </c>
       <c r="F309" s="105" t="str">
         <v>Pending</v>
@@ -16580,65 +16608,48 @@
       <c r="S309" s="94"/>
       <c r="T309"/>
     </row>
-    <row r="310" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
-      <c r="A310" s="105" t="str">
-        <v>UTC198</v>
-      </c>
-      <c r="B310" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).</v>
-      </c>
-      <c r="C310" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
-      </c>
-      <c r="D310" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E310" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F310" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G310" s="105" t="str"/>
-      <c r="H310" s="105" t="str"/>
-      <c r="I310" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J310" s="105"/>
-      <c r="K310" s="105"/>
-      <c r="L310" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M310" s="105"/>
-      <c r="N310" s="105"/>
-      <c r="O310" s="105" t="str"/>
-      <c r="P310" s="110" t="str"/>
+    <row r="310" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A310" s="102" t="str">
+        <v>Cancel_requires_a_reason</v>
+      </c>
+      <c r="B310" s="102"/>
+      <c r="C310" s="103"/>
+      <c r="D310" s="103"/>
+      <c r="E310" s="103"/>
+      <c r="F310" s="103"/>
+      <c r="G310" s="103"/>
+      <c r="H310" s="103"/>
+      <c r="I310" s="103"/>
+      <c r="J310" s="103"/>
+      <c r="K310" s="103"/>
+      <c r="L310" s="103"/>
+      <c r="M310" s="103"/>
+      <c r="N310" s="103"/>
+      <c r="O310" s="103"/>
+      <c r="P310" s="104"/>
       <c r="Q310"/>
       <c r="R310"/>
-      <c r="S310" s="94"/>
+      <c r="S310" s="90"/>
       <c r="T310"/>
     </row>
     <row r="311" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A311" s="105" t="str">
-        <v>UTC199</v>
+        <v>UTC200</v>
       </c>
       <c r="B311" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (status).</v>
+2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C311" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
+        <v>reason=null</v>
       </c>
       <c r="D311" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Success
+        <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E311" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F311" s="105" t="str">
         <v>Pending</v>
@@ -16662,49 +16673,65 @@
       <c r="S311" s="94"/>
       <c r="T311"/>
     </row>
-    <row r="312" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A312" s="102" t="str">
-        <v>A_started_ended_or_cancelled_meeting_cannot_be_cancelled</v>
-      </c>
-      <c r="B312" s="102"/>
-      <c r="C312" s="103"/>
-      <c r="D312" s="103"/>
-      <c r="E312" s="103"/>
-      <c r="F312" s="103"/>
-      <c r="G312" s="103"/>
-      <c r="H312" s="103"/>
-      <c r="I312" s="103"/>
-      <c r="J312" s="103"/>
-      <c r="K312" s="103"/>
-      <c r="L312" s="103"/>
-      <c r="M312" s="103"/>
-      <c r="N312" s="103"/>
-      <c r="O312" s="103"/>
-      <c r="P312" s="104"/>
+    <row r="312" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+      <c r="A312" s="105" t="str">
+        <v>UTC201</v>
+      </c>
+      <c r="B312" s="106" t="str">
+        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
+2. meeting: prepared by GivenMeeting.</v>
+      </c>
+      <c r="C312" s="107" t="str">
+        <v>reason=""</v>
+      </c>
+      <c r="D312" s="108" t="str">
+        <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E312" s="109" t="str">
+        <v>Boundary</v>
+      </c>
+      <c r="F312" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G312" s="105" t="str"/>
+      <c r="H312" s="105" t="str"/>
+      <c r="I312" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J312" s="105"/>
+      <c r="K312" s="105"/>
+      <c r="L312" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M312" s="105"/>
+      <c r="N312" s="105"/>
+      <c r="O312" s="105" t="str"/>
+      <c r="P312" s="110" t="str"/>
       <c r="Q312"/>
       <c r="R312"/>
-      <c r="S312" s="90"/>
+      <c r="S312" s="94"/>
       <c r="T312"/>
     </row>
-    <row r="313" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="313" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A313" s="105" t="str">
-        <v>UTC200</v>
+        <v>UTC202</v>
       </c>
       <c r="B313" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. meeting.Status = status.</v>
+2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C313" s="107" t="str">
-        <v>status=MeetingStatus.InProgress</v>
+        <v>reason="   "</v>
       </c>
       <c r="D313" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
+        <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E313" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Boundary</v>
       </c>
       <c r="F313" s="105" t="str">
         <v>Pending</v>
@@ -16728,67 +16755,50 @@
       <c r="S313" s="94"/>
       <c r="T313"/>
     </row>
-    <row r="314" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
-      <c r="A314" s="105" t="str">
-        <v>UTC201</v>
-      </c>
-      <c r="B314" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. meeting.Status = status.</v>
-      </c>
-      <c r="C314" s="107" t="str">
-        <v>status=MeetingStatus.Ended</v>
-      </c>
-      <c r="D314" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E314" s="109" t="str">
-        <v>Abnormal</v>
-      </c>
-      <c r="F314" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G314" s="105" t="str"/>
-      <c r="H314" s="105" t="str"/>
-      <c r="I314" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J314" s="105"/>
-      <c r="K314" s="105"/>
-      <c r="L314" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M314" s="105"/>
-      <c r="N314" s="105"/>
-      <c r="O314" s="105" t="str"/>
-      <c r="P314" s="110" t="str"/>
+    <row r="314" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A314" s="102" t="str">
+        <v>Cancel_accepts_exactly_1000_characters_and_rejects_1001</v>
+      </c>
+      <c r="B314" s="102"/>
+      <c r="C314" s="103"/>
+      <c r="D314" s="103"/>
+      <c r="E314" s="103"/>
+      <c r="F314" s="103"/>
+      <c r="G314" s="103"/>
+      <c r="H314" s="103"/>
+      <c r="I314" s="103"/>
+      <c r="J314" s="103"/>
+      <c r="K314" s="103"/>
+      <c r="L314" s="103"/>
+      <c r="M314" s="103"/>
+      <c r="N314" s="103"/>
+      <c r="O314" s="103"/>
+      <c r="P314" s="104"/>
       <c r="Q314"/>
       <c r="R314"/>
-      <c r="S314" s="94"/>
+      <c r="S314" s="90"/>
       <c r="T314"/>
     </row>
-    <row r="315" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="315" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A315" s="105" t="str">
-        <v>UTC202</v>
+        <v>UTC203</v>
       </c>
       <c r="B315" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).
-3. meeting.Status = status.</v>
+2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C315" s="107" t="str">
-        <v>status=MeetingStatus.Cancelled</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
       </c>
       <c r="D315" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.StatusConflict
+        <v>Return:
+1. tooLong.Outcome: MeetingWorkflowOutcome.CancellationReasonTooLong
+2. exact.Outcome: MeetingWorkflowOutcome.Success
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E315" s="109" t="str">
-        <v>Abnormal</v>
+        <v>Boundary</v>
       </c>
       <c r="F315" s="105" t="str">
         <v>Pending</v>
@@ -16814,7 +16824,7 @@
     </row>
     <row r="316" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A316" s="102" t="str">
-        <v>Cancel_requires_a_reason</v>
+        <v>Only_the_organizer_may_cancel</v>
       </c>
       <c r="B316" s="102"/>
       <c r="C316" s="103"/>
@@ -16836,24 +16846,24 @@
       <c r="S316" s="90"/>
       <c r="T316"/>
     </row>
-    <row r="317" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="317" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A317" s="105" t="str">
-        <v>UTC203</v>
+        <v>UTC204</v>
       </c>
       <c r="B317" s="106" t="str">
         <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.</v>
+2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C317" s="107" t="str">
-        <v>reason=null</v>
+        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _approverId</v>
       </c>
       <c r="D317" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
+        <v>Return: MeetingWorkflowOutcome.Forbidden
 Exception: N/A
 Log Message: N/A</v>
       </c>
       <c r="E317" s="109" t="str">
-        <v>Boundary</v>
+        <v>Normal</v>
       </c>
       <c r="F317" s="105" t="str">
         <v>Pending</v>
@@ -16877,229 +16887,15 @@
       <c r="S317" s="94"/>
       <c r="T317"/>
     </row>
-    <row r="318" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
-      <c r="A318" s="105" t="str">
-        <v>UTC204</v>
-      </c>
-      <c r="B318" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.</v>
-      </c>
-      <c r="C318" s="107" t="str">
-        <v>reason=""</v>
-      </c>
-      <c r="D318" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E318" s="109" t="str">
-        <v>Boundary</v>
-      </c>
-      <c r="F318" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G318" s="105" t="str"/>
-      <c r="H318" s="105" t="str"/>
-      <c r="I318" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J318" s="105"/>
-      <c r="K318" s="105"/>
-      <c r="L318" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M318" s="105"/>
-      <c r="N318" s="105"/>
-      <c r="O318" s="105" t="str"/>
-      <c r="P318" s="110" t="str"/>
-      <c r="Q318"/>
-      <c r="R318"/>
-      <c r="S318" s="94"/>
-      <c r="T318"/>
-    </row>
-    <row r="319" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
-      <c r="A319" s="105" t="str">
-        <v>UTC205</v>
-      </c>
-      <c r="B319" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.</v>
-      </c>
-      <c r="C319" s="107" t="str">
-        <v>reason="   "</v>
-      </c>
-      <c r="D319" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E319" s="109" t="str">
-        <v>Boundary</v>
-      </c>
-      <c r="F319" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G319" s="105" t="str"/>
-      <c r="H319" s="105" t="str"/>
-      <c r="I319" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J319" s="105"/>
-      <c r="K319" s="105"/>
-      <c r="L319" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M319" s="105"/>
-      <c r="N319" s="105"/>
-      <c r="O319" s="105" t="str"/>
-      <c r="P319" s="110" t="str"/>
-      <c r="Q319"/>
-      <c r="R319"/>
-      <c r="S319" s="94"/>
-      <c r="T319"/>
-    </row>
-    <row r="320" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A320" s="102" t="str">
-        <v>Cancel_accepts_exactly_1000_characters_and_rejects_1001</v>
-      </c>
-      <c r="B320" s="102"/>
-      <c r="C320" s="103"/>
-      <c r="D320" s="103"/>
-      <c r="E320" s="103"/>
-      <c r="F320" s="103"/>
-      <c r="G320" s="103"/>
-      <c r="H320" s="103"/>
-      <c r="I320" s="103"/>
-      <c r="J320" s="103"/>
-      <c r="K320" s="103"/>
-      <c r="L320" s="103"/>
-      <c r="M320" s="103"/>
-      <c r="N320" s="103"/>
-      <c r="O320" s="103"/>
-      <c r="P320" s="104"/>
-      <c r="Q320"/>
-      <c r="R320"/>
-      <c r="S320" s="90"/>
-      <c r="T320"/>
-    </row>
-    <row r="321" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
-      <c r="A321" s="105" t="str">
-        <v>UTC206</v>
-      </c>
-      <c r="B321" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting.</v>
-      </c>
-      <c r="C321" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
-      </c>
-      <c r="D321" s="108" t="str">
-        <v>Return:
-1. tooLong.Outcome: MeetingWorkflowOutcome.CancellationReasonTooLong
-2. exact.Outcome: MeetingWorkflowOutcome.Success
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E321" s="109" t="str">
-        <v>Boundary</v>
-      </c>
-      <c r="F321" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G321" s="105" t="str"/>
-      <c r="H321" s="105" t="str"/>
-      <c r="I321" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J321" s="105"/>
-      <c r="K321" s="105"/>
-      <c r="L321" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M321" s="105"/>
-      <c r="N321" s="105"/>
-      <c r="O321" s="105" t="str"/>
-      <c r="P321" s="110" t="str"/>
-      <c r="Q321"/>
-      <c r="R321"/>
-      <c r="S321" s="94"/>
-      <c r="T321"/>
-    </row>
-    <row r="322" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A322" s="102" t="str">
-        <v>Only_the_organizer_may_cancel</v>
-      </c>
-      <c r="B322" s="102"/>
-      <c r="C322" s="103"/>
-      <c r="D322" s="103"/>
-      <c r="E322" s="103"/>
-      <c r="F322" s="103"/>
-      <c r="G322" s="103"/>
-      <c r="H322" s="103"/>
-      <c r="I322" s="103"/>
-      <c r="J322" s="103"/>
-      <c r="K322" s="103"/>
-      <c r="L322" s="103"/>
-      <c r="M322" s="103"/>
-      <c r="N322" s="103"/>
-      <c r="O322" s="103"/>
-      <c r="P322" s="104"/>
-      <c r="Q322"/>
-      <c r="R322"/>
-      <c r="S322" s="90"/>
-      <c r="T322"/>
-    </row>
-    <row r="323" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
-      <c r="A323" s="105" t="str">
-        <v>UTC207</v>
-      </c>
-      <c r="B323" s="106" t="str">
-        <v>1. MeetingWorkflowService runs in process; its dependencies are fakes or stubs.
-2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
-      </c>
-      <c r="C323" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _approverId</v>
-      </c>
-      <c r="D323" s="108" t="str">
-        <v>Return: MeetingWorkflowOutcome.Forbidden
-Exception: N/A
-Log Message: N/A</v>
-      </c>
-      <c r="E323" s="109" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F323" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="G323" s="105" t="str"/>
-      <c r="H323" s="105" t="str"/>
-      <c r="I323" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="J323" s="105"/>
-      <c r="K323" s="105"/>
-      <c r="L323" s="105" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="M323" s="105"/>
-      <c r="N323" s="105"/>
-      <c r="O323" s="105" t="str"/>
-      <c r="P323" s="110" t="str"/>
-      <c r="Q323"/>
-      <c r="R323"/>
-      <c r="S323" s="94"/>
-      <c r="T323"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F12:F323 I12:I323 L12:L323">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F12:F317 I12:I317 L12:L317">
       <formula1>$T$2:$T$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E12:E323">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E12:E317">
       <formula1>"Normal,Abnormal,Boundary"</formula1>
     </dataValidation>
   </dataValidations>
@@ -17109,7 +16905,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17574,7 +17370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -21902,7 +21698,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -21987,8 +21783,8 @@
         <v>Number of TCs</v>
       </c>
       <c r="B3" s="78" t="n">
-        <f>COUNTIF(A12:A19,"UTC*")</f>
-        <v>4</v>
+        <f>COUNTIF(A12:A23,"UTC*")</f>
+        <v>6</v>
       </c>
       <c r="C3" s="105"/>
       <c r="D3" s="111"/>
@@ -22048,16 +21844,16 @@
         <v>Round 1</v>
       </c>
       <c r="B5" s="78" t="n">
-        <f>COUNTIF($F$12:$F$19,B$4)</f>
+        <f>COUNTIF($F$12:$F$23,B$4)</f>
         <v>0</v>
       </c>
       <c r="C5" s="78" t="n">
-        <f>COUNTIF($F$12:$F$19,C$4)</f>
+        <f>COUNTIF($F$12:$F$23,C$4)</f>
         <v>0</v>
       </c>
       <c r="D5" s="79" t="n">
-        <f>COUNTIF($F$12:$F$19,D$4)</f>
-        <v>4</v>
+        <f>COUNTIF($F$12:$F$23,D$4)</f>
+        <v>6</v>
       </c>
       <c r="E5" s="101"/>
       <c r="F5" s="101"/>
@@ -22083,16 +21879,16 @@
         <v>Round 2</v>
       </c>
       <c r="B6" s="78" t="n">
-        <f>COUNTIF($I$12:$I$19,B$4)</f>
+        <f>COUNTIF($I$12:$I$23,B$4)</f>
         <v>0</v>
       </c>
       <c r="C6" s="78" t="n">
-        <f>COUNTIF($I$12:$I$19,C$4)</f>
+        <f>COUNTIF($I$12:$I$23,C$4)</f>
         <v>0</v>
       </c>
       <c r="D6" s="79" t="n">
-        <f>COUNTIF($I$12:$I$19,D$4)</f>
-        <v>4</v>
+        <f>COUNTIF($I$12:$I$23,D$4)</f>
+        <v>6</v>
       </c>
       <c r="E6" s="101"/>
       <c r="F6" s="101"/>
@@ -22116,16 +21912,16 @@
         <v>Round 3</v>
       </c>
       <c r="B7" s="78" t="n">
-        <f>COUNTIF($L$12:$L$19,B$4)</f>
+        <f>COUNTIF($L$12:$L$23,B$4)</f>
         <v>0</v>
       </c>
       <c r="C7" s="78" t="n">
-        <f>COUNTIF($L$12:$L$19,C$4)</f>
+        <f>COUNTIF($L$12:$L$23,C$4)</f>
         <v>0</v>
       </c>
       <c r="D7" s="79" t="n">
-        <f>COUNTIF($L$12:$L$19,D$4)</f>
-        <v>4</v>
+        <f>COUNTIF($L$12:$L$23,D$4)</f>
+        <v>6</v>
       </c>
       <c r="E7" s="101"/>
       <c r="F7" s="101"/>
@@ -22181,15 +21977,15 @@
         <v>Count</v>
       </c>
       <c r="B9" s="82" t="n">
-        <f>COUNTIF($E$12:$E$19,B$8)</f>
-        <v>2</v>
+        <f>COUNTIF($E$12:$E$23,B$8)</f>
+        <v>4</v>
       </c>
       <c r="C9" s="82" t="n">
-        <f>COUNTIF($E$12:$E$19,C$8)</f>
+        <f>COUNTIF($E$12:$E$23,C$8)</f>
         <v>0</v>
       </c>
       <c r="D9" s="83" t="n">
-        <f>COUNTIF($E$12:$E$19,D$8)</f>
+        <f>COUNTIF($E$12:$E$23,D$8)</f>
         <v>2</v>
       </c>
       <c r="E9" s="101"/>
@@ -22483,7 +22279,7 @@
     </row>
     <row r="18" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="102" t="str">
-        <v>The_best_sample_counts_and_a_person_is_suggested_for_one_voice_only</v>
+        <v>The_best_sample_counts_and_one_person_split_in_two_is_suggested_for_both_voices</v>
       </c>
       <c r="B18" s="102"/>
       <c r="C18" s="103"/>
@@ -22519,7 +22315,7 @@
         <v>Return:
 1. result["SPEAKER_00"].UserId: Lan
 2. result["SPEAKER_02"].UserId: Minh
-3. ContainsKey("SPEAKER_01"): false
+3. result["SPEAKER_01"].UserId: Lan
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -22548,15 +22344,147 @@
       <c r="S19" s="94"/>
       <c r="T19"/>
     </row>
+    <row r="20" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A20" s="102" t="str">
+        <v>A_second_voice_that_does_not_sound_like_the_first_is_not_given_the_same_name</v>
+      </c>
+      <c r="B20" s="102"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="103"/>
+      <c r="M20" s="103"/>
+      <c r="N20" s="103"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="104"/>
+      <c r="Q20"/>
+      <c r="R20"/>
+      <c r="S20" s="90"/>
+      <c r="T20"/>
+    </row>
+    <row r="21" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+      <c r="A21" s="105" t="str">
+        <v>UTC005</v>
+      </c>
+      <c r="B21" s="106" t="str">
+        <v>1. SpeakerMatcher runs in process; its dependencies are fakes or stubs.</v>
+      </c>
+      <c r="C21" s="107" t="str">
+        <v>[new("SPEAKER_00", 1000, [1f, 0f]), new("SPEAKER_01", 1000, [0.6f, 0.…; C(Lan, [1f, 0f]); C(Lan, [0.6f, 0.8f])</v>
+      </c>
+      <c r="D21" s="108" t="str">
+        <v>Return:
+1. result["SPEAKER_00"].UserId: Lan
+2. ContainsKey("SPEAKER_01"): false
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E21" s="109" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F21" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G21" s="105" t="str"/>
+      <c r="H21" s="105" t="str"/>
+      <c r="I21" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M21" s="105"/>
+      <c r="N21" s="105"/>
+      <c r="O21" s="105" t="str"/>
+      <c r="P21" s="110" t="str"/>
+      <c r="Q21"/>
+      <c r="R21"/>
+      <c r="S21" s="94"/>
+      <c r="T21"/>
+    </row>
+    <row r="22" spans="1:20" s="70" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A22" s="102" t="str">
+        <v>The_weaker_voice_of_a_person_points_at_the_surer_one_until_the_secretary_decides</v>
+      </c>
+      <c r="B22" s="102"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="103"/>
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="103"/>
+      <c r="J22" s="103"/>
+      <c r="K22" s="103"/>
+      <c r="L22" s="103"/>
+      <c r="M22" s="103"/>
+      <c r="N22" s="103"/>
+      <c r="O22" s="103"/>
+      <c r="P22" s="104"/>
+      <c r="Q22"/>
+      <c r="R22"/>
+      <c r="S22" s="90"/>
+      <c r="T22"/>
+    </row>
+    <row r="23" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+      <c r="A23" s="105" t="str">
+        <v>UTC006</v>
+      </c>
+      <c r="B23" s="106" t="str">
+        <v>1. SpeakerMatcher runs in process; its dependencies are fakes or stubs.</v>
+      </c>
+      <c r="C23" s="107" t="str">
+        <v>[("SPEAKER_00", Lan, 0.70, null), ("SPEAKER_01", Lan, 0.82, null), ("…</v>
+      </c>
+      <c r="D23" s="108" t="str">
+        <v>Return:
+1. same["SPEAKER_00"]: "SPEAKER_01"
+2. same: exactly one item
+Exception: N/A
+Log Message: N/A</v>
+      </c>
+      <c r="E23" s="109" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F23" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="G23" s="105" t="str"/>
+      <c r="H23" s="105" t="str"/>
+      <c r="I23" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="105" t="str"/>
+      <c r="P23" s="110" t="str"/>
+      <c r="Q23"/>
+      <c r="R23"/>
+      <c r="S23" s="94"/>
+      <c r="T23"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F12:F19 I12:I19 L12:L19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F12:F23 I12:I23 L12:L23">
       <formula1>$T$2:$T$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E12:E19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E12:E23">
       <formula1>"Normal,Abnormal,Boundary"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22566,7 +22494,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -28578,7 +28506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E825D98C-77AF-4456-AB2E-63255F4500ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3578CB4C-E828-4B28-945C-3E0FCA1FE4AE}">
   <dimension ref="B1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -28822,7 +28750,7 @@
         <v>Meetings</v>
       </c>
       <c r="E16" s="129" t="str">
-        <v>105 methods, 207 cases</v>
+        <v>102 methods, 204 cases</v>
       </c>
       <c r="F16" s="130" t="str">
         <v>None (in-process fakes)</v>
@@ -28876,7 +28804,7 @@
         <v>Recordings</v>
       </c>
       <c r="E19" s="129" t="str">
-        <v>4 methods, 4 cases</v>
+        <v>6 methods, 6 cases</v>
       </c>
       <c r="F19" s="130" t="str">
         <v>None (in-process fakes)</v>
@@ -28928,7 +28856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F870BF-256D-480A-BD7B-226C08E2E9CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822EAD2B-75B1-41DD-B57A-CC25CC6C5230}">
   <dimension ref="A2:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -29032,7 +28960,7 @@
       </c>
       <c r="E6" s="148"/>
       <c r="F6" s="152" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
       <c r="G6" s="153"/>
       <c r="H6" s="153"/>
@@ -29382,11 +29310,11 @@
       </c>
       <c r="E19" s="41" t="n">
         <f>'Meetings'!B3-'Meetings'!B5-'Meetings'!C5</f>
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F19" s="42" t="n">
         <f>'Meetings'!B9</f>
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G19" s="41" t="n">
         <f>'Meetings'!C9</f>
@@ -29398,7 +29326,7 @@
       </c>
       <c r="I19" s="41" t="n">
         <f>'Meetings'!B3</f>
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20" customHeight="1">
@@ -29490,11 +29418,11 @@
       </c>
       <c r="E22" s="41" t="n">
         <f>'Recordings'!B3-'Recordings'!B5-'Recordings'!C5</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" s="42" t="n">
         <f>'Recordings'!B9</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="41" t="n">
         <f>'Recordings'!C9</f>
@@ -29506,7 +29434,7 @@
       </c>
       <c r="I22" s="41" t="n">
         <f>'Recordings'!B3</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20" customHeight="1">
@@ -29582,11 +29510,11 @@
       </c>
       <c r="E26" s="44" t="n">
         <f>SUM(E12:E25)</f>
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F26" s="44" t="n">
         <f>SUM(F12:F25)</f>
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G26" s="44" t="n">
         <f>SUM(G12:G25)</f>
@@ -29598,7 +29526,7 @@
       </c>
       <c r="I26" s="44" t="n">
         <f>SUM(I12:I25)</f>
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27">
@@ -29656,7 +29584,7 @@
       <c r="C30" s="34"/>
       <c r="D30" s="61" t="n">
         <f>IFERROR(F26*100/I26,0)</f>
-        <v>50.92</v>
+        <v>50.84</v>
       </c>
       <c r="E30" s="34" t="str">
         <v>%</v>
@@ -29674,7 +29602,7 @@
       <c r="C31"/>
       <c r="D31" s="61" t="n">
         <f>IFERROR(G26*100/I26,0)</f>
-        <v>42.81</v>
+        <v>42.88</v>
       </c>
       <c r="E31" s="34" t="str">
         <v>%</v>
@@ -29692,7 +29620,7 @@
       <c r="C32"/>
       <c r="D32" s="61" t="n">
         <f>IFERROR(H26*100/I26,0)</f>
-        <v>6.27</v>
+        <v>6.28</v>
       </c>
       <c r="E32" s="34" t="str">
         <v>%</v>
@@ -29741,7 +29669,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -35209,7 +35137,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -35962,7 +35890,7 @@
         <v>Return:
 1. Title: "X"
 2. Description: "A\nB"
-3. DocumentIds: empty
+3. DocumentIds: null
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -36009,7 +35937,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -37997,7 +37925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -44010,7 +43938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -46160,7 +46088,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A37E2BC-2104-444C-9B5A-1C7429FD6C21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>

--- a/docs/08-reports/test-reports/Report5.1_Unit_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.1_Unit_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\TrustCabinet\artifacts\test-report-build\template-edition\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F2252D0-B7A0-4940-B992-F0AA4410A05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18EDBB6E-31EF-438D-9DB4-7DFD237EED1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="641" xr2:uid="{FA2443BF-1D86-46F3-AD3C-B0AE21D421C2}" activeTab="0" firstSheet="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="641" xr2:uid="{F2F39266-E81B-480E-9EC2-6124A2D61A65}" activeTab="0" firstSheet="0"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="sheet1"/>
@@ -1579,15 +1579,15 @@
     <cellStyle name="Linked Cell" xfId="36" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="37" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_Functional Test Case v1.0" xfId="38" xr:uid="{F9EB9215-3D9D-477A-A1BF-22152D517FEF}"/>
-    <cellStyle name="Normal_Sheet1" xfId="39" xr:uid="{72FCB13F-F807-43D6-9669-B02111FD556E}"/>
-    <cellStyle name="Normal_Template_UnitTest Case_v0.9" xfId="40" xr:uid="{01F03269-52A3-4F61-9E6B-7E59C032FE42}"/>
+    <cellStyle name="Normal_Functional Test Case v1.0" xfId="38" xr:uid="{0849A3DE-A885-4038-9296-9ECD047E5C24}"/>
+    <cellStyle name="Normal_Sheet1" xfId="39" xr:uid="{7D176B20-EBBC-4670-AF06-B407D855B490}"/>
+    <cellStyle name="Normal_Template_UnitTest Case_v0.9" xfId="40" xr:uid="{9D6BCDA0-0344-403C-8DCF-85EC4131754A}"/>
     <cellStyle name="Note" xfId="41" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="42" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="43" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="44" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="45" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="46" xr:uid="{CA668FF3-173A-46C6-AD3C-1653D27538D0}"/>
+    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="46" xr:uid="{60842961-AA5C-4BD0-8437-AF46D55B8D6C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1689,7 +1689,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-DB6F-4C41-970D-7DD8E43D531B}"/>
+                <c16:uniqueId val="{00000000-8817-445C-9A95-6D9F73656B3C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1709,7 +1709,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-DB6F-4C41-970D-7DD8E43D531B}"/>
+                <c16:uniqueId val="{00000001-8817-445C-9A95-6D9F73656B3C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1729,7 +1729,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-DB6F-4C41-970D-7DD8E43D531B}"/>
+                <c16:uniqueId val="{00000002-8817-445C-9A95-6D9F73656B3C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1795,20 +1795,20 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>332</c:v>
+                  <c:v>311</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>280</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-DB6F-4C41-970D-7DD8E43D531B}"/>
+              <c16:uniqueId val="{00000003-8817-445C-9A95-6D9F73656B3C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1999,7 +1999,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-DC81-4115-964B-FE69E2331C3A}"/>
+                <c16:uniqueId val="{00000000-10F8-41BB-A90B-FBED645AB6CB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2019,7 +2019,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-DC81-4115-964B-FE69E2331C3A}"/>
+                <c16:uniqueId val="{00000001-10F8-41BB-A90B-FBED645AB6CB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2039,7 +2039,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-DC81-4115-964B-FE69E2331C3A}"/>
+                <c16:uniqueId val="{00000002-10F8-41BB-A90B-FBED645AB6CB}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2118,7 +2118,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-DC81-4115-964B-FE69E2331C3A}"/>
+              <c16:uniqueId val="{00000003-10F8-41BB-A90B-FBED645AB6CB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2242,7 +2242,7 @@
         <xdr:cNvPr id="1143" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C6FCD39-802E-D2D5-C6C5-F4853A93EA45}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF795424-E923-7B34-A3A1-2D35F6424194}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2321,7 +2321,7 @@
         <xdr:cNvPr id="2283" name="Chart 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB72EF16-361D-9EA3-1F14-D079139B0A18}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{211708ED-54E1-C89E-95AE-8C77B31176D8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2359,7 +2359,7 @@
         <xdr:cNvPr id="2284" name="Chart 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E58536E-49FA-1571-FCCC-923179CDB73B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB5D027F-9D77-14D6-346B-0BA80D7FC922}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2668,7 +2668,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A74039C5-26BA-4A5E-B171-3EF825B26970}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEEBDD-2240-420E-9655-FD684C8C98FC}">
   <dimension ref="A2:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -2898,7 +2898,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -3314,7 +3314,7 @@
 2. probe = new WorkerProbe().</v>
       </c>
       <c r="C13" s="107" t="str">
-        <v>CancellationToken.None</v>
+        <v>N/A</v>
       </c>
       <c r="D13" s="108" t="str">
         <v>Return:
@@ -3448,7 +3448,7 @@
 3. dispatchScopes = new List&lt;object&gt;().</v>
       </c>
       <c r="C17" s="107" t="str">
-        <v>default</v>
+        <v>N/A</v>
       </c>
       <c r="D17" s="108" t="str">
         <v>Return:
@@ -3573,7 +3573,7 @@
       <c r="S20" s="90"/>
       <c r="T20"/>
     </row>
-    <row r="21" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="21" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A21" s="105" t="str">
         <v>UTC005</v>
       </c>
@@ -3581,7 +3581,10 @@
         <v>1. PasswordResetEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C21" s="107" t="str">
-        <v>"thanhvien@trustcabinet.local"; "Lê Thành Viên"; Token; TimeSpan.FromMinutes(60)</v>
+        <v>toAddress = "thanhvien@trustcabinet.local"
+fullName = "Lê Thành Viên"
+resetToken = "AbCdEf0123456789_-AbCdEf0123456789_-AbCdEfG"
+validFor = TimeSpan.FromMinutes(60)</v>
       </c>
       <c r="D21" s="108" t="str">
         <v>Return: true
@@ -3645,7 +3648,8 @@
         <v>1. PasswordResetEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>"https://trustcabinet.example"; Token</v>
+        <v>applicationBaseUrl = "https://trustcabinet.example"
+resetToken = "AbCdEf0123456789_-AbCdEf0123456789_-AbCdEfG"</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return:
@@ -3703,7 +3707,7 @@
       <c r="S24" s="90"/>
       <c r="T24"/>
     </row>
-    <row r="25" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="25" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A25" s="105" t="str">
         <v>UTC007</v>
       </c>
@@ -3711,7 +3715,10 @@
         <v>1. PasswordResetEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C25" s="107" t="str">
-        <v>"thanhvien@trustcabinet.local"; "Lê Thành Viên"; Token; TimeSpan.FromMinutes(60)</v>
+        <v>toAddress = "thanhvien@trustcabinet.local"
+fullName = "Lê Thành Viên"
+resetToken = "AbCdEf0123456789_-AbCdEf0123456789_-AbCdEfG"
+validFor = TimeSpan.FromMinutes(60)</v>
       </c>
       <c r="D25" s="108" t="str">
         <v>Return: false
@@ -3767,7 +3774,7 @@
       <c r="S26" s="90"/>
       <c r="T26"/>
     </row>
-    <row r="27" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="27" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A27" s="105" t="str">
         <v>UTC008</v>
       </c>
@@ -3775,7 +3782,10 @@
         <v>1. PasswordResetEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C27" s="107" t="str">
-        <v>"thanhvien@trustcabinet.local"; "Lê Thành Viên"; Token; TimeSpan.FromMinutes(60)</v>
+        <v>toAddress = "thanhvien@trustcabinet.local"
+fullName = "Lê Thành Viên"
+resetToken = "AbCdEf0123456789_-AbCdEf0123456789_-AbCdEfG"
+validFor = TimeSpan.FromMinutes(60)</v>
       </c>
       <c r="D27" s="108" t="str">
         <v>Return: false
@@ -3831,7 +3841,7 @@
       <c r="S28" s="90"/>
       <c r="T28"/>
     </row>
-    <row r="29" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="29" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A29" s="105" t="str">
         <v>UTC009</v>
       </c>
@@ -3840,7 +3850,10 @@
 2. _smtp.Throws = new IOException("Connection refused").</v>
       </c>
       <c r="C29" s="107" t="str">
-        <v>"thanhvien@trustcabinet.local"; "Lê Thành Viên"; Token; TimeSpan.FromMinutes(60)</v>
+        <v>toAddress = "thanhvien@trustcabinet.local"
+fullName = "Lê Thành Viên"
+resetToken = "AbCdEf0123456789_-AbCdEf0123456789_-AbCdEfG"
+validFor = TimeSpan.FromMinutes(60)</v>
       </c>
       <c r="D29" s="108" t="str">
         <v>Return: false
@@ -3896,7 +3909,7 @@
       <c r="S30" s="90"/>
       <c r="T30"/>
     </row>
-    <row r="31" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="31" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A31" s="105" t="str">
         <v>UTC010</v>
       </c>
@@ -3905,7 +3918,10 @@
 2. _smtp.Hangs = true.</v>
       </c>
       <c r="C31" s="107" t="str">
-        <v>"thanhvien@trustcabinet.local"; "Lê Thành Viên"; Token; TimeSpan.FromMinutes(60)</v>
+        <v>toAddress = "thanhvien@trustcabinet.local"
+fullName = "Lê Thành Viên"
+resetToken = "AbCdEf0123456789_-AbCdEf0123456789_-AbCdEfG"
+validFor = TimeSpan.FromMinutes(60)</v>
       </c>
       <c r="D31" s="108" t="str">
         <v>Return: false
@@ -4027,7 +4043,7 @@
       <c r="S34" s="90"/>
       <c r="T34"/>
     </row>
-    <row r="35" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="35" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A35" s="105" t="str">
         <v>UTC012</v>
       </c>
@@ -4035,7 +4051,7 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C35" s="107" t="str">
-        <v>message</v>
+        <v>message = EmailMessage { DeduplicationKey = "test", ToAddress = "thanhvien@example.com", Subject = "Thư mời họp", Body = "Nội dung", CalendarAttachment = "BEGIN:VCALENDAR\r\nEND:VCALENDAR" }</v>
       </c>
       <c r="D35" s="108" t="str">
         <v>Return: "4ef9a417-02e9-4d39-ad75-9611e0fcc33c"
@@ -4091,7 +4107,7 @@
       <c r="S36" s="90"/>
       <c r="T36"/>
     </row>
-    <row r="37" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="37" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A37" s="105" t="str">
         <v>UTC013</v>
       </c>
@@ -4099,7 +4115,7 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C37" s="107" t="str">
-        <v>Invitation()</v>
+        <v>message = EmailMessage { DeduplicationKey = "test", ToAddress = "thanhvien@example.com", Subject = "Thư mời họp", Body = "Nội dung", CalendarAttachment = null }</v>
       </c>
       <c r="D37" s="108" t="str">
         <v>Return:
@@ -4157,7 +4173,7 @@
       <c r="S38" s="90"/>
       <c r="T38"/>
     </row>
-    <row r="39" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="39" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A39" s="105" t="str">
         <v>UTC014</v>
       </c>
@@ -4165,7 +4181,9 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C39" s="107" t="str">
-        <v>status=HttpStatusCode.BadRequest</v>
+        <v>status = HTTP 400 Bad Request
+body = """{"statusCode":422,"name":"validation_error","message":"Invalid `to` field."}"""
+status = HttpStatusCode.BadRequest</v>
       </c>
       <c r="D39" s="108" t="str">
         <v>Return: contains "validation_error"
@@ -4197,7 +4215,7 @@
       <c r="S39" s="94"/>
       <c r="T39"/>
     </row>
-    <row r="40" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="40" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A40" s="105" t="str">
         <v>UTC015</v>
       </c>
@@ -4205,7 +4223,9 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C40" s="107" t="str">
-        <v>status=HttpStatusCode.UnprocessableEntity</v>
+        <v>status = HTTP 422 Unprocessable Entity
+body = """{"statusCode":422,"name":"validation_error","message":"Invalid `to` field."}"""
+status = HttpStatusCode.UnprocessableEntity</v>
       </c>
       <c r="D40" s="108" t="str">
         <v>Return: contains "validation_error"
@@ -4261,7 +4281,7 @@
       <c r="S41" s="90"/>
       <c r="T41"/>
     </row>
-    <row r="42" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="42" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A42" s="105" t="str">
         <v>UTC016</v>
       </c>
@@ -4269,7 +4289,9 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C42" s="107" t="str">
-        <v>status=HttpStatusCode.Unauthorized</v>
+        <v>status = HTTP 401 Unauthorized
+body = "&lt;html&gt;gateway&lt;/html&gt;"
+status = HttpStatusCode.Unauthorized</v>
       </c>
       <c r="D42" s="108" t="str">
         <v>Return: status
@@ -4301,7 +4323,7 @@
       <c r="S42" s="94"/>
       <c r="T42"/>
     </row>
-    <row r="43" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="43" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A43" s="105" t="str">
         <v>UTC017</v>
       </c>
@@ -4309,7 +4331,9 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C43" s="107" t="str">
-        <v>status=HttpStatusCode.Forbidden</v>
+        <v>status = HTTP 403 Forbidden
+body = "&lt;html&gt;gateway&lt;/html&gt;"
+status = HttpStatusCode.Forbidden</v>
       </c>
       <c r="D43" s="108" t="str">
         <v>Return: status
@@ -4341,7 +4365,7 @@
       <c r="S43" s="94"/>
       <c r="T43"/>
     </row>
-    <row r="44" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="44" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A44" s="105" t="str">
         <v>UTC018</v>
       </c>
@@ -4349,7 +4373,9 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C44" s="107" t="str">
-        <v>status=HttpStatusCode.Conflict</v>
+        <v>status = HTTP 409 Conflict
+body = "&lt;html&gt;gateway&lt;/html&gt;"
+status = HttpStatusCode.Conflict</v>
       </c>
       <c r="D44" s="108" t="str">
         <v>Return: status
@@ -4381,7 +4407,7 @@
       <c r="S44" s="94"/>
       <c r="T44"/>
     </row>
-    <row r="45" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="45" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A45" s="105" t="str">
         <v>UTC019</v>
       </c>
@@ -4389,7 +4415,9 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C45" s="107" t="str">
-        <v>status=HttpStatusCode.TooManyRequests</v>
+        <v>status = HTTP 429 Too Many Requests
+body = "&lt;html&gt;gateway&lt;/html&gt;"
+status = HttpStatusCode.TooManyRequests</v>
       </c>
       <c r="D45" s="108" t="str">
         <v>Return: status
@@ -4421,7 +4449,7 @@
       <c r="S45" s="94"/>
       <c r="T45"/>
     </row>
-    <row r="46" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="46" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A46" s="105" t="str">
         <v>UTC020</v>
       </c>
@@ -4429,7 +4457,9 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C46" s="107" t="str">
-        <v>status=HttpStatusCode.InternalServerError</v>
+        <v>status = HTTP 500 Internal Server Error
+body = "&lt;html&gt;gateway&lt;/html&gt;"
+status = HttpStatusCode.InternalServerError</v>
       </c>
       <c r="D46" s="108" t="str">
         <v>Return: status
@@ -4461,7 +4491,7 @@
       <c r="S46" s="94"/>
       <c r="T46"/>
     </row>
-    <row r="47" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="47" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A47" s="105" t="str">
         <v>UTC021</v>
       </c>
@@ -4469,7 +4499,9 @@
         <v>1. ResendEmailSender runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C47" s="107" t="str">
-        <v>status=HttpStatusCode.ServiceUnavailable</v>
+        <v>status = HTTP 503 Service Unavailable
+body = "&lt;html&gt;gateway&lt;/html&gt;"
+status = HttpStatusCode.ServiceUnavailable</v>
       </c>
       <c r="D47" s="108" t="str">
         <v>Return: status
@@ -4589,7 +4621,7 @@
       <c r="S50" s="90"/>
       <c r="T50"/>
     </row>
-    <row r="51" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="51" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A51" s="105" t="str">
         <v>UTC023</v>
       </c>
@@ -4597,7 +4629,10 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C51" s="107" t="str">
-        <v>Secret; "msg_1"; timestamp; Body</v>
+        <v>secret = "whsec_" + Convert.ToBase64String(Encoding.UTF8.GetBytes("trustcabinet-test-secret-32-bytes"))
+id = "msg_1"
+timestamp = 2026-10-27T08:00:00Z.ToUnixTimeSeconds()
+body = Encoding.UTF8.GetBytes("""{"type":"email.delivered"}""")</v>
       </c>
       <c r="D51" s="108" t="str">
         <v>Return: true
@@ -4720,7 +4755,7 @@
       <c r="S54" s="90"/>
       <c r="T54"/>
     </row>
-    <row r="55" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="55" spans="1:20" s="93" customFormat="1" ht="356.0" outlineLevel="1" customHeight="1">
       <c r="A55" s="105" t="str">
         <v>UTC025</v>
       </c>
@@ -4728,7 +4763,12 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C55" s="107" t="str">
-        <v>Secret; "msg_1"; stale; Sign(Secret, "msg_1", stale, Body); Body; Now</v>
+        <v>secret = "whsec_" + Convert.ToBase64String(Encoding.UTF8.GetBytes("trustcabinet-test-secret-32-bytes"))
+id = "msg_1"
+timestamp = 2026-10-27T07:54:00Z.ToUnixTimeSeconds()
+signature = Sign("whsec_" + Convert.ToBase64String(Encoding.UTF8.GetBytes("trustcabinet-test-secret-32-bytes")), "msg_1", 2026-10-27T07:54:00Z.ToUnixTimeSeconds(), Encoding.UTF8.GetBytes("""{"type":"email.delive…
+body = Encoding.UTF8.GetBytes("""{"type":"email.delivered"}""")
+now = 2026-10-27T08:00:00Z</v>
       </c>
       <c r="D55" s="108" t="str">
         <v>Return: false
@@ -4784,7 +4824,7 @@
       <c r="S56" s="90"/>
       <c r="T56"/>
     </row>
-    <row r="57" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="57" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A57" s="105" t="str">
         <v>UTC026</v>
       </c>
@@ -4792,7 +4832,12 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C57" s="107" t="str">
-        <v>id=null; timestamp="1"; signature="v1,abc"</v>
+        <v>secret = "whsec_" + Convert.ToBase64String(Encoding.UTF8.GetBytes("trustcabinet-test-secret-32-bytes"))
+id = null
+timestamp = "1"
+signature = "v1,abc"
+body = Encoding.UTF8.GetBytes("""{"type":"email.delivered"}""")
+now = 2026-10-27T08:00:00Z</v>
       </c>
       <c r="D57" s="108" t="str">
         <v>Return: false
@@ -4824,7 +4869,7 @@
       <c r="S57" s="94"/>
       <c r="T57"/>
     </row>
-    <row r="58" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="58" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A58" s="105" t="str">
         <v>UTC027</v>
       </c>
@@ -4832,7 +4877,12 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C58" s="107" t="str">
-        <v>id="msg_1"; timestamp="not-a-number"; signature="v1,abc"</v>
+        <v>secret = "whsec_" + Convert.ToBase64String(Encoding.UTF8.GetBytes("trustcabinet-test-secret-32-bytes"))
+id = "msg_1"
+timestamp = "not-a-number"
+signature = "v1,abc"
+body = Encoding.UTF8.GetBytes("""{"type":"email.delivered"}""")
+now = 2026-10-27T08:00:00Z</v>
       </c>
       <c r="D58" s="108" t="str">
         <v>Return: false
@@ -4864,7 +4914,7 @@
       <c r="S58" s="94"/>
       <c r="T58"/>
     </row>
-    <row r="59" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="59" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A59" s="105" t="str">
         <v>UTC028</v>
       </c>
@@ -4872,7 +4922,12 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C59" s="107" t="str">
-        <v>id="msg_1"; timestamp="1"; signature=null</v>
+        <v>secret = "whsec_" + Convert.ToBase64String(Encoding.UTF8.GetBytes("trustcabinet-test-secret-32-bytes"))
+id = "msg_1"
+timestamp = "1"
+signature = null
+body = Encoding.UTF8.GetBytes("""{"type":"email.delivered"}""")
+now = 2026-10-27T08:00:00Z</v>
       </c>
       <c r="D59" s="108" t="str">
         <v>Return: false
@@ -4904,7 +4959,7 @@
       <c r="S59" s="94"/>
       <c r="T59"/>
     </row>
-    <row r="60" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="60" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A60" s="105" t="str">
         <v>UTC029</v>
       </c>
@@ -4912,7 +4967,12 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C60" s="107" t="str">
-        <v>id="msg_1"; timestamp="1"; signature="v1,***not-base64***"</v>
+        <v>secret = "whsec_" + Convert.ToBase64String(Encoding.UTF8.GetBytes("trustcabinet-test-secret-32-bytes"))
+id = "msg_1"
+timestamp = "1"
+signature = "v1,***not-base64***"
+body = Encoding.UTF8.GetBytes("""{"type":"email.delivered"}""")
+now = 2026-10-27T08:00:00Z</v>
       </c>
       <c r="D60" s="108" t="str">
         <v>Return: false
@@ -4976,7 +5036,7 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C62" s="107" t="str">
-        <v>Encoding.UTF8.GetBytes($$""" { "type": "email.bounced", "created_at":…</v>
+        <v>body = Encoding.UTF8.GetBytes($$""" { "type": "email.bounced", "created_at": "2026-10-27T08:00:05.000Z", "data": { "email_id": "4ef9a417-02e9-4d39-ad75-9611e0fcc33c", "to": ["nobody@example.com"], "bounce":…</v>
       </c>
       <c r="D62" s="108" t="str">
         <v>Return:
@@ -5038,7 +5098,7 @@
       <c r="S63" s="90"/>
       <c r="T63"/>
     </row>
-    <row r="64" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="64" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A64" s="105" t="str">
         <v>UTC031</v>
       </c>
@@ -5046,7 +5106,8 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C64" s="107" t="str">
-        <v>type="email.sent"</v>
+        <v>body = Encoding.UTF8.GetBytes( $$$"""{"type":"{{{type}}}","created_at":"2026-10-27T08:00:00Z","data":{"email_id":"x"}}""")
+type = "email.sent"</v>
       </c>
       <c r="D64" s="108" t="str">
         <v>Return: null
@@ -5078,7 +5139,7 @@
       <c r="S64" s="94"/>
       <c r="T64"/>
     </row>
-    <row r="65" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="65" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A65" s="105" t="str">
         <v>UTC032</v>
       </c>
@@ -5086,7 +5147,8 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C65" s="107" t="str">
-        <v>type="email.opened"</v>
+        <v>body = Encoding.UTF8.GetBytes( $$$"""{"type":"{{{type}}}","created_at":"2026-10-27T08:00:00Z","data":{"email_id":"x"}}""")
+type = "email.opened"</v>
       </c>
       <c r="D65" s="108" t="str">
         <v>Return: null
@@ -5118,7 +5180,7 @@
       <c r="S65" s="94"/>
       <c r="T65"/>
     </row>
-    <row r="66" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="66" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A66" s="105" t="str">
         <v>UTC033</v>
       </c>
@@ -5126,7 +5188,8 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C66" s="107" t="str">
-        <v>type="email.clicked"</v>
+        <v>body = Encoding.UTF8.GetBytes( $$$"""{"type":"{{{type}}}","created_at":"2026-10-27T08:00:00Z","data":{"email_id":"x"}}""")
+type = "email.clicked"</v>
       </c>
       <c r="D66" s="108" t="str">
         <v>Return: null
@@ -5158,7 +5221,7 @@
       <c r="S66" s="94"/>
       <c r="T66"/>
     </row>
-    <row r="67" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="67" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A67" s="105" t="str">
         <v>UTC034</v>
       </c>
@@ -5166,7 +5229,8 @@
         <v>1. ResendWebhookReceiver runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C67" s="107" t="str">
-        <v>type="domain.updated"</v>
+        <v>body = Encoding.UTF8.GetBytes( $$$"""{"type":"{{{type}}}","created_at":"2026-10-27T08:00:00Z","data":{"email_id":"x"}}""")
+type = "domain.updated"</v>
       </c>
       <c r="D67" s="108" t="str">
         <v>Return: null
@@ -5216,7 +5280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5496,7 +5560,7 @@
       </c>
       <c r="B9" s="82" t="n">
         <f>COUNTIF($E$12:$E$317,B$8)</f>
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="C9" s="82" t="n">
         <f>COUNTIF($E$12:$E$317,C$8)</f>
@@ -5504,7 +5568,7 @@
       </c>
       <c r="D9" s="83" t="n">
         <f>COUNTIF($E$12:$E$317,D$8)</f>
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E9" s="101"/>
       <c r="F9" s="101"/>
@@ -5634,7 +5698,7 @@
 4. sourceParticipant.DelegatedToUserId = delegateUser.Id.</v>
       </c>
       <c r="C13" s="107" t="str">
-        <v>participants</v>
+        <v>participants = List&lt;MeetingParticipant&gt; { MeetingParticipant { MeetingId = 01924ec9-7fcf-793a-a5d0-8cd949ef8633 (generated), UserId = 0191e7a0-541d-7d9c-9f83-10e510e4b987 (generated), User = User { FullName = "sour…</v>
       </c>
       <c r="D13" s="108" t="str">
         <v>Return:
@@ -5692,7 +5756,7 @@
       <c r="S14" s="90"/>
       <c r="T14"/>
     </row>
-    <row r="15" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="15" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A15" s="105" t="str">
         <v>UTC002</v>
       </c>
@@ -5702,7 +5766,7 @@
 3. active = NewUser("active@trustcabinet.local").</v>
       </c>
       <c r="C15" s="107" t="str">
-        <v>participants</v>
+        <v>participants = [MeetingParticipant { MeetingId = 0190ee43-1c2e-7e1b-9214-e1f8bb7eef9a (generated), UserId = 019aeca1-0fb4-7e77-a116-8fab698334ac (generated), User = User { FullName = "inactive@trustcabinet.local",…</v>
       </c>
       <c r="D15" s="108" t="str">
         <v>Return: active.Id
@@ -5770,7 +5834,7 @@
 5. Test data is seeded (Domain.Enums.MeetingStatus.InProgress, count: 0).</v>
       </c>
       <c r="C17" s="107" t="str">
-        <v>var action in new[] { "Start", "End" }</v>
+        <v>} = var action in new[] { "Start", "End" }</v>
       </c>
       <c r="D17" s="108" t="str">
         <v>Return: completes without error
@@ -5838,7 +5902,7 @@
 5. confirmedAt = meetingEndedAt.AddSeconds(2).</v>
       </c>
       <c r="C19" s="107" t="str">
-        <v>existingSession=false</v>
+        <v>meetingId = fixture.Seed(MeetingStatus.InProgress).MeetingId</v>
       </c>
       <c r="D19" s="108" t="str">
         <v>Return:
@@ -5889,7 +5953,7 @@
 5. confirmedAt = meetingEndedAt.AddSeconds(2).</v>
       </c>
       <c r="C20" s="107" t="str">
-        <v>existingSession=true</v>
+        <v>meetingId = fixture.Seed(MeetingStatus.InProgress).MeetingId</v>
       </c>
       <c r="D20" s="108" t="str">
         <v>Return:
@@ -5962,7 +6026,7 @@
 3. if (action == "End") { var item = (locked.AgendaItems.FindAsync(s.Items[0])); item.Status = AgendaItemStatus.InProgress; item.ActualStarted….</v>
       </c>
       <c r="C22" s="107" t="str">
-        <v>action="Start"; count=2</v>
+        <v>action = "Start"</v>
       </c>
       <c r="D22" s="108" t="str">
         <v>Return:
@@ -6006,7 +6070,7 @@
 3. if (action == "End") { var item = (locked.AgendaItems.FindAsync(s.Items[0])); item.Status = AgendaItemStatus.InProgress; item.ActualStarted….</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>action="End"; count=2</v>
+        <v>action = "End"</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return:
@@ -6050,7 +6114,7 @@
 3. if (action == "End") { var item = (locked.AgendaItems.FindAsync(s.Items[0])); item.Status = AgendaItemStatus.InProgress; item.ActualStarted….</v>
       </c>
       <c r="C24" s="107" t="str">
-        <v>action="Start"; count=20</v>
+        <v>action = "Start"</v>
       </c>
       <c r="D24" s="108" t="str">
         <v>Return:
@@ -6094,7 +6158,7 @@
 3. if (action == "End") { var item = (locked.AgendaItems.FindAsync(s.Items[0])); item.Status = AgendaItemStatus.InProgress; item.ActualStarted….</v>
       </c>
       <c r="C25" s="107" t="str">
-        <v>action="End"; count=20</v>
+        <v>action = "End"</v>
       </c>
       <c r="D25" s="108" t="str">
         <v>Return:
@@ -6162,7 +6226,7 @@
 3. received = Channel.CreateUnbounded&lt;AgendaChange&gt;().</v>
       </c>
       <c r="C27" s="107" t="str">
-        <v>hasCurrent=false</v>
+        <v>actor = fixture.Seed(MeetingStatus.InProgress).Member</v>
       </c>
       <c r="D27" s="108" t="str">
         <v>Return:
@@ -6207,7 +6271,7 @@
 3. received = Channel.CreateUnbounded&lt;AgendaChange&gt;().</v>
       </c>
       <c r="C28" s="107" t="str">
-        <v>hasCurrent=true</v>
+        <v>actor = fixture.Seed(MeetingStatus.InProgress).Member</v>
       </c>
       <c r="D28" s="108" t="str">
         <v>Return:
@@ -6277,7 +6341,8 @@
 4. excludedEvents = Channel.CreateUnbounded&lt;AgendaChange&gt;().</v>
       </c>
       <c r="C30" s="107" t="str">
-        <v>reason="inactive"</v>
+        <v>actor = fixture.Seed(MeetingStatus.InProgress).Member
+reason = "inactive"</v>
       </c>
       <c r="D30" s="108" t="str">
         <v>Return: "MeetingEnded"
@@ -6320,7 +6385,8 @@
 4. excludedEvents = Channel.CreateUnbounded&lt;AgendaChange&gt;().</v>
       </c>
       <c r="C31" s="107" t="str">
-        <v>reason="removed"</v>
+        <v>actor = fixture.Seed(MeetingStatus.InProgress).Member
+reason = "removed"</v>
       </c>
       <c r="D31" s="108" t="str">
         <v>Return: "MeetingEnded"
@@ -6363,7 +6429,8 @@
 4. excludedEvents = Channel.CreateUnbounded&lt;AgendaChange&gt;().</v>
       </c>
       <c r="C32" s="107" t="str">
-        <v>reason="otherMeeting"</v>
+        <v>actor = fixture.Seed(MeetingStatus.InProgress).Member
+reason = "otherMeeting"</v>
       </c>
       <c r="D32" s="108" t="str">
         <v>Return: "MeetingEnded"
@@ -6430,7 +6497,7 @@
 4. next.Role = MeetingRole.Chair.</v>
       </c>
       <c r="C34" s="107" t="str">
-        <v>action="Start"</v>
+        <v>action = "Start"</v>
       </c>
       <c r="D34" s="108" t="str">
         <v>Return: s.Member
@@ -6473,7 +6540,7 @@
 4. next.Role = MeetingRole.Chair.</v>
       </c>
       <c r="C35" s="107" t="str">
-        <v>action="End"</v>
+        <v>action = "End"</v>
       </c>
       <c r="D35" s="108" t="str">
         <v>Return: s.Member
@@ -6541,7 +6608,7 @@
 5. Guid sessionId.</v>
       </c>
       <c r="C37" s="107" t="str">
-        <v>latestEvidence="start"</v>
+        <v>latestEvidence = "start"</v>
       </c>
       <c r="D37" s="108" t="str">
         <v>Return:
@@ -6588,7 +6655,7 @@
 5. Guid sessionId.</v>
       </c>
       <c r="C38" s="107" t="str">
-        <v>latestEvidence="join"</v>
+        <v>latestEvidence = "join"</v>
       </c>
       <c r="D38" s="108" t="str">
         <v>Return:
@@ -6635,7 +6702,7 @@
 5. Guid sessionId.</v>
       </c>
       <c r="C39" s="107" t="str">
-        <v>latestEvidence="leave"</v>
+        <v>latestEvidence = "leave"</v>
       </c>
       <c r="D39" s="108" t="str">
         <v>Return:
@@ -6760,7 +6827,7 @@
       <c r="S42" s="90"/>
       <c r="T42"/>
     </row>
-    <row r="43" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="43" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A43" s="105" t="str">
         <v>UTC021</v>
       </c>
@@ -6769,7 +6836,10 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C43" s="107" t="str">
-        <v>reason="inactive"</v>
+        <v>response = fixture.Client(fixture.Seed().Chair).PostAsJsonAsync($"/api/meetings/{id}/transitions", { "Start" })
+status = 200
+code = "MSG110"
+reason = "inactive"</v>
       </c>
       <c r="D43" s="108" t="str">
         <v>Return: new[] { s.Secretary }
@@ -6801,7 +6871,7 @@
       <c r="S43" s="94"/>
       <c r="T43"/>
     </row>
-    <row r="44" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="44" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A44" s="105" t="str">
         <v>UTC022</v>
       </c>
@@ -6810,7 +6880,10 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C44" s="107" t="str">
-        <v>reason="removed"</v>
+        <v>response = fixture.Client(fixture.Seed().Chair).PostAsJsonAsync($"/api/meetings/{id}/transitions", { "Start" })
+status = 200
+code = "MSG110"
+reason = "removed"</v>
       </c>
       <c r="D44" s="108" t="str">
         <v>Return: new[] { s.Secretary }
@@ -6842,7 +6915,7 @@
       <c r="S44" s="94"/>
       <c r="T44"/>
     </row>
-    <row r="45" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="45" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A45" s="105" t="str">
         <v>UTC023</v>
       </c>
@@ -6851,7 +6924,10 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C45" s="107" t="str">
-        <v>reason="delegated"</v>
+        <v>response = fixture.Client(fixture.Seed().Chair).PostAsJsonAsync($"/api/meetings/{id}/transitions", { "Start" })
+status = 200
+code = "MSG110"
+reason = "delegated"</v>
       </c>
       <c r="D45" s="108" t="str">
         <v>Return: new[] { s.Secretary }
@@ -6883,7 +6959,7 @@
       <c r="S45" s="94"/>
       <c r="T45"/>
     </row>
-    <row r="46" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="46" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A46" s="105" t="str">
         <v>UTC024</v>
       </c>
@@ -6892,7 +6968,10 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C46" s="107" t="str">
-        <v>reason="guest"</v>
+        <v>response = fixture.Client(fixture.Seed().Chair).PostAsJsonAsync($"/api/meetings/{id}/transitions", { "Start" })
+status = 200
+code = "MSG110"
+reason = "guest"</v>
       </c>
       <c r="D46" s="108" t="str">
         <v>Return: new[] { s.Secretary }
@@ -7026,7 +7105,8 @@
         <v>1. MeetingLifecycle runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C50" s="107" t="str">
-        <v>operation="current"</v>
+        <v>fixture.Seed(MeetingStatus.InProgress).Url + $"/{s.Items[0]}/current"
+null</v>
       </c>
       <c r="D50" s="108" t="str">
         <v>Return:
@@ -7069,7 +7149,8 @@
         <v>1. MeetingLifecycle runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C51" s="107" t="str">
-        <v>operation="complete"</v>
+        <v>fixture.Seed(MeetingStatus.InProgress).Url + $"/{s.Items[0]}/current"
+null</v>
       </c>
       <c r="D51" s="108" t="str">
         <v>Return:
@@ -7138,7 +7219,8 @@
 3. abort = new CancellationTokenSource().</v>
       </c>
       <c r="C53" s="107" t="str">
-        <v>action="Start"</v>
+        <v>n =&gt; n.MeetingId == s.MeetingId
+action = "Start"</v>
       </c>
       <c r="D53" s="108" t="str">
         <v>Return:
@@ -7184,7 +7266,8 @@
 3. abort = new CancellationTokenSource().</v>
       </c>
       <c r="C54" s="107" t="str">
-        <v>action="End"</v>
+        <v>n =&gt; n.MeetingId == s.MeetingId
+action = "End"</v>
       </c>
       <c r="D54" s="108" t="str">
         <v>Return:
@@ -7252,7 +7335,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C56" s="107" t="str">
-        <v>input=""</v>
+        <v>body = ""</v>
       </c>
       <c r="D56" s="108" t="str">
         <v>Return:
@@ -7299,7 +7382,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C57" s="107" t="str">
-        <v>input="?status=&amp;sensitivity=&amp;q=&amp;from=&amp;to=&amp;page=&amp;pageSize=&amp;sortBy=&amp;sortDir="</v>
+        <v>body = "?status=&amp;sensitivity=&amp;q=&amp;from=&amp;to=&amp;page=&amp;pageSize=&amp;sortBy=&amp;sortDir="</v>
       </c>
       <c r="D57" s="108" t="str">
         <v>Return:
@@ -7370,7 +7453,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C59" s="107" t="str">
-        <v>"?status=Published&amp;sensitivity=Secret&amp;q=%20Giao%20ban%20" + "&amp;from=20…</v>
+        <v>body = "?status=Published&amp;sensitivity=Secret&amp;q=%20Giao%20ban%20" + "&amp;from=2026-10-01T09%3A00%3A00%2B07%3A00&amp;to=2026-10-02T09%3A00%3A00%2B07%3A00" + "&amp;page=2&amp;pageSize=100&amp;sortBy=title&amp;sortDir=desc"</v>
       </c>
       <c r="D59" s="108" t="str">
         <v>Return:
@@ -7433,7 +7516,7 @@
       <c r="S60" s="90"/>
       <c r="T60"/>
     </row>
-    <row r="61" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="61" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A61" s="105" t="str">
         <v>UTC033</v>
       </c>
@@ -7441,7 +7524,9 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C61" s="107" t="str">
-        <v>field="from"; timestamp="2026-10-01T09:00+07:00"; expectedUtc="2026-10-01T02:00:00Z"</v>
+        <v>body = $"?{field}={Uri.EscapeDataString(timestamp)}"
+field = "from"
+timestamp = "2026-10-01T09:00+07:00"</v>
       </c>
       <c r="D61" s="108" t="str">
         <v>Return:
@@ -7475,7 +7560,7 @@
       <c r="S61" s="94"/>
       <c r="T61"/>
     </row>
-    <row r="62" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="62" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A62" s="105" t="str">
         <v>UTC034</v>
       </c>
@@ -7483,7 +7568,9 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C62" s="107" t="str">
-        <v>field="to"; timestamp="2026-10-01T09:00+07:00"; expectedUtc="2026-10-01T02:00:00Z"</v>
+        <v>body = $"?{field}={Uri.EscapeDataString(timestamp)}"
+field = "to"
+timestamp = "2026-10-01T09:00+07:00"</v>
       </c>
       <c r="D62" s="108" t="str">
         <v>Return:
@@ -7517,7 +7604,7 @@
       <c r="S62" s="94"/>
       <c r="T62"/>
     </row>
-    <row r="63" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="63" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A63" s="105" t="str">
         <v>UTC035</v>
       </c>
@@ -7525,7 +7612,9 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C63" s="107" t="str">
-        <v>field="from"; timestamp="2026-10-01T02:00Z"; expectedUtc="2026-10-01T02:00:00Z"</v>
+        <v>body = $"?{field}={Uri.EscapeDataString(timestamp)}"
+field = "from"
+timestamp = "2026-10-01T02:00Z"</v>
       </c>
       <c r="D63" s="108" t="str">
         <v>Return:
@@ -7559,7 +7648,7 @@
       <c r="S63" s="94"/>
       <c r="T63"/>
     </row>
-    <row r="64" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="64" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A64" s="105" t="str">
         <v>UTC036</v>
       </c>
@@ -7567,7 +7656,9 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C64" s="107" t="str">
-        <v>field="to"; timestamp="2026-10-01T09:00-07:00"; expectedUtc="2026-10-01T16:00:00Z"</v>
+        <v>body = $"?{field}={Uri.EscapeDataString(timestamp)}"
+field = "to"
+timestamp = "2026-10-01T09:00-07:00"</v>
       </c>
       <c r="D64" s="108" t="str">
         <v>Return:
@@ -7601,7 +7692,7 @@
       <c r="S64" s="94"/>
       <c r="T64"/>
     </row>
-    <row r="65" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="65" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A65" s="105" t="str">
         <v>UTC037</v>
       </c>
@@ -7609,7 +7700,9 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C65" s="107" t="str">
-        <v>field="from"; timestamp="2026-10-01T09:00:15.1234567+07:00"; expectedUtc="2026-10-01T02:00:15.1234567Z"</v>
+        <v>body = $"?{field}={Uri.EscapeDataString(timestamp)}"
+field = "from"
+timestamp = "2026-10-01T09:00:15.1234567+07:00"</v>
       </c>
       <c r="D65" s="108" t="str">
         <v>Return:
@@ -7675,7 +7768,8 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C67" s="107" t="str">
-        <v>raw="title"; expectedBy=MeetingSortBy.Title; expectedDirection=MeetingSortDirection.Asc</v>
+        <v>body = $"?sortBy={raw}"
+raw = "title"</v>
       </c>
       <c r="D67" s="108" t="str">
         <v>Return:
@@ -7718,7 +7812,8 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C68" s="107" t="str">
-        <v>raw="createdAt"; expectedBy=MeetingSortBy.CreatedAt; expectedDirection=MeetingSortDirection.Desc</v>
+        <v>body = $"?sortBy={raw}"
+raw = "createdAt"</v>
       </c>
       <c r="D68" s="108" t="str">
         <v>Return:
@@ -7761,7 +7856,8 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C69" s="107" t="str">
-        <v>raw="plannedStartTime"; expectedBy=MeetingSortBy.PlannedStartTime; expectedDirection=MeetingSortDirection.Desc</v>
+        <v>body = $"?sortBy={raw}"
+raw = "plannedStartTime"</v>
       </c>
       <c r="D69" s="108" t="str">
         <v>Return:
@@ -7828,7 +7924,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C71" s="107" t="str">
-        <v>"?sortDir=asc"</v>
+        <v>body = "?sortDir=asc"</v>
       </c>
       <c r="D71" s="108" t="str">
         <v>Return:
@@ -7895,7 +7991,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C73" s="107" t="str">
-        <v>input="?timing=upcoming"; expected=MeetingTiming.Upcoming</v>
+        <v>body = "?timing=upcoming"</v>
       </c>
       <c r="D73" s="108" t="str">
         <v>Return:
@@ -7938,7 +8034,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C74" s="107" t="str">
-        <v>input="?timing=past"; expected=MeetingTiming.Past</v>
+        <v>body = "?timing=past"</v>
       </c>
       <c r="D74" s="108" t="str">
         <v>Return:
@@ -7981,7 +8077,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C75" s="107" t="str">
-        <v>input=""; expected=null</v>
+        <v>body = ""</v>
       </c>
       <c r="D75" s="108" t="str">
         <v>Return:
@@ -8048,7 +8144,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C77" s="107" t="str">
-        <v>input="?status=published"; field="status"</v>
+        <v>body = "?status=published"</v>
       </c>
       <c r="D77" s="108" t="str">
         <v>Return:
@@ -8090,7 +8186,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C78" s="107" t="str">
-        <v>input="?sensitivity=Unknown"; field="sensitivity"</v>
+        <v>body = "?sensitivity=Unknown"</v>
       </c>
       <c r="D78" s="108" t="str">
         <v>Return:
@@ -8132,7 +8228,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C79" s="107" t="str">
-        <v>input="?from=2026-10-01"; field="from"</v>
+        <v>body = "?from=2026-10-01"</v>
       </c>
       <c r="D79" s="108" t="str">
         <v>Return:
@@ -8174,7 +8270,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C80" s="107" t="str">
-        <v>input="?to=2026-10-01T09:00:00"; field="to"</v>
+        <v>body = "?to=2026-10-01T09:00:00"</v>
       </c>
       <c r="D80" s="108" t="str">
         <v>Return:
@@ -8216,7 +8312,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C81" s="107" t="str">
-        <v>input="?from=2026-10-01T09:00"; field="from"</v>
+        <v>body = "?from=2026-10-01T09:00"</v>
       </c>
       <c r="D81" s="108" t="str">
         <v>Return:
@@ -8258,7 +8354,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C82" s="107" t="str">
-        <v>input="?to=2026-10-01T09:00.5Z"; field="to"</v>
+        <v>body = "?to=2026-10-01T09:00.5Z"</v>
       </c>
       <c r="D82" s="108" t="str">
         <v>Return:
@@ -8300,7 +8396,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C83" s="107" t="str">
-        <v>input="?from=2026-09-31T09:00Z"; field="from"</v>
+        <v>body = "?from=2026-09-31T09:00Z"</v>
       </c>
       <c r="D83" s="108" t="str">
         <v>Return:
@@ -8342,7 +8438,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C84" s="107" t="str">
-        <v>input="?to=2026-10-01T25:00Z"; field="to"</v>
+        <v>body = "?to=2026-10-01T25:00Z"</v>
       </c>
       <c r="D84" s="108" t="str">
         <v>Return:
@@ -8384,7 +8480,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C85" s="107" t="str">
-        <v>input="?page=0"; field="page"</v>
+        <v>body = "?page=0"</v>
       </c>
       <c r="D85" s="108" t="str">
         <v>Return:
@@ -8426,7 +8522,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C86" s="107" t="str">
-        <v>input="?page=abc"; field="page"</v>
+        <v>body = "?page=abc"</v>
       </c>
       <c r="D86" s="108" t="str">
         <v>Return:
@@ -8468,7 +8564,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C87" s="107" t="str">
-        <v>input="?pageSize=101"; field="pageSize"</v>
+        <v>body = "?pageSize=101"</v>
       </c>
       <c r="D87" s="108" t="str">
         <v>Return:
@@ -8510,7 +8606,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C88" s="107" t="str">
-        <v>input="?pageSize=-1"; field="pageSize"</v>
+        <v>body = "?pageSize=-1"</v>
       </c>
       <c r="D88" s="108" t="str">
         <v>Return:
@@ -8552,7 +8648,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C89" s="107" t="str">
-        <v>input="?sortBy=location"; field="sortBy"</v>
+        <v>body = "?sortBy=location"</v>
       </c>
       <c r="D89" s="108" t="str">
         <v>Return:
@@ -8594,7 +8690,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C90" s="107" t="str">
-        <v>input="?sortBy=startsAt"; field="sortBy"</v>
+        <v>body = "?sortBy=startsAt"</v>
       </c>
       <c r="D90" s="108" t="str">
         <v>Return:
@@ -8636,7 +8732,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C91" s="107" t="str">
-        <v>input="?sortDir=up"; field="sortDir"</v>
+        <v>body = "?sortDir=up"</v>
       </c>
       <c r="D91" s="108" t="str">
         <v>Return:
@@ -8678,7 +8774,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C92" s="107" t="str">
-        <v>input="?status=Draft&amp;status=Published"; field="status"</v>
+        <v>body = "?status=Draft&amp;status=Published"</v>
       </c>
       <c r="D92" s="108" t="str">
         <v>Return:
@@ -8720,7 +8816,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C93" s="107" t="str">
-        <v>input="?timing=today"; field="timing"</v>
+        <v>body = "?timing=today"</v>
       </c>
       <c r="D93" s="108" t="str">
         <v>Return:
@@ -8762,7 +8858,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C94" s="107" t="str">
-        <v>input="?timing=Upcoming"; field="timing"</v>
+        <v>body = "?timing=Upcoming"</v>
       </c>
       <c r="D94" s="108" t="str">
         <v>Return:
@@ -8828,7 +8924,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C96" s="107" t="str">
-        <v>"?from=2026-10-02T00%3A00%3A00Z&amp;to=2026-10-01T00%3A00%3A00Z"</v>
+        <v>body = "?from=2026-10-02T00%3A00%3A00Z&amp;to=2026-10-01T00%3A00%3A00Z"</v>
       </c>
       <c r="D96" s="108" t="str">
         <v>Return:
@@ -8894,7 +8990,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C98" s="107" t="str">
-        <v>"?page=2147483647&amp;pageSize=100"</v>
+        <v>body = "?page=2147483647&amp;pageSize=100"</v>
       </c>
       <c r="D98" s="108" t="str">
         <v>Return:
@@ -8961,7 +9057,7 @@
         <v>1. MeetingListQueryParser runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C100" s="107" t="str">
-        <v>"?status=Wrong&amp;page=0&amp;sortDir=wrong"</v>
+        <v>body = "?status=Wrong&amp;page=0&amp;sortDir=wrong"</v>
       </c>
       <c r="D100" s="108" t="str">
         <v>Return:
@@ -9307,7 +9403,7 @@
 5. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C110" s="107" t="str">
-        <v>scenario="member"</v>
+        <v>actorId) = "member"</v>
       </c>
       <c r="D110" s="108" t="str">
         <v>Return:
@@ -9353,7 +9449,7 @@
 5. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C111" s="107" t="str">
-        <v>scenario="delegated"</v>
+        <v>actorId) = "delegated"</v>
       </c>
       <c r="D111" s="108" t="str">
         <v>Return:
@@ -9399,7 +9495,7 @@
 5. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C112" s="107" t="str">
-        <v>scenario="delegateReference"</v>
+        <v>actorId) = "delegateReference"</v>
       </c>
       <c r="D112" s="108" t="str">
         <v>Return:
@@ -9445,7 +9541,7 @@
 5. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C113" s="107" t="str">
-        <v>scenario="otherMeeting"</v>
+        <v>actorId) = "otherMeeting"</v>
       </c>
       <c r="D113" s="108" t="str">
         <v>Return:
@@ -9491,7 +9587,7 @@
 5. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C114" s="107" t="str">
-        <v>scenario="otherUser"</v>
+        <v>actorId) = "otherUser"</v>
       </c>
       <c r="D114" s="108" t="str">
         <v>Return:
@@ -9560,7 +9656,8 @@
 4. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C116" s="107" t="str">
-        <v>role=MeetingRole.Chair; scenario="delegated"</v>
+        <v>actorId) = "delegated"
+role = MeetingRole.Chair</v>
       </c>
       <c r="D116" s="108" t="str">
         <v>Return:
@@ -9605,7 +9702,8 @@
 4. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C117" s="107" t="str">
-        <v>role=MeetingRole.Secretary; scenario="delegateReference"</v>
+        <v>actorId) = "delegateReference"
+role = MeetingRole.Secretary</v>
       </c>
       <c r="D117" s="108" t="str">
         <v>Return:
@@ -9650,7 +9748,8 @@
 4. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C118" s="107" t="str">
-        <v>role=MeetingRole.Member; scenario="otherMeeting"</v>
+        <v>actorId) = "otherMeeting"
+role = MeetingRole.Member</v>
       </c>
       <c r="D118" s="108" t="str">
         <v>Return:
@@ -9695,7 +9794,8 @@
 4. meeting.Participants.Add(participant).</v>
       </c>
       <c r="C119" s="107" t="str">
-        <v>role=MeetingRole.Member; scenario="otherUser"</v>
+        <v>actorId) = "otherUser"
+role = MeetingRole.Member</v>
       </c>
       <c r="D119" s="108" t="str">
         <v>Return:
@@ -9753,7 +9853,7 @@
       <c r="S120" s="90"/>
       <c r="T120"/>
     </row>
-    <row r="121" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="121" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A121" s="105" t="str">
         <v>UTC079</v>
       </c>
@@ -9762,7 +9862,10 @@
 2. input = ValidInput(title: title).</v>
       </c>
       <c r="C121" s="107" t="str">
-        <v>title=null</v>
+        <v>input = MeetingInput { Title = null, PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Interna…
+actorId = 0199fb77-7481-77ef-b77b-790118cfa525 (generated)
+participants = [{ 0199fb77-7481-77ef-b77b-790118cfa525 (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D121" s="108" t="str">
         <v>Return:
@@ -9796,7 +9899,7 @@
       <c r="S121" s="94"/>
       <c r="T121"/>
     </row>
-    <row r="122" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="122" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A122" s="105" t="str">
         <v>UTC080</v>
       </c>
@@ -9805,7 +9908,10 @@
 2. input = ValidInput(title: title).</v>
       </c>
       <c r="C122" s="107" t="str">
-        <v>title=""</v>
+        <v>input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
+actorId = 019cea92-687d-73ba-a726-f6593c7179a0 (generated)
+participants = [{ 019cea92-687d-73ba-a726-f6593c7179a0 (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D122" s="108" t="str">
         <v>Return:
@@ -9839,7 +9945,7 @@
       <c r="S122" s="94"/>
       <c r="T122"/>
     </row>
-    <row r="123" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="123" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A123" s="105" t="str">
         <v>UTC081</v>
       </c>
@@ -9848,7 +9954,10 @@
 2. input = ValidInput(title: title).</v>
       </c>
       <c r="C123" s="107" t="str">
-        <v>title="   "</v>
+        <v>input = MeetingInput { Title = "   ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Intern…
+actorId = 01976757-af95-7799-8365-077991d5fc68 (generated)
+participants = [{ 01976757-af95-7799-8365-077991d5fc68 (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D123" s="108" t="str">
         <v>Return:
@@ -9906,7 +10015,7 @@
       <c r="S124" s="90"/>
       <c r="T124"/>
     </row>
-    <row r="125" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="125" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A125" s="105" t="str">
         <v>UTC082</v>
       </c>
@@ -9914,7 +10023,10 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C125" s="107" t="str">
-        <v>ValidInput( title: new string('a', 301), mode: "0", location: new str…; _actorId; [new(_actorId, "Chair")]</v>
+        <v>input = MeetingInput { Title = 'a' × 301, PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "0", Location = 'b' × 301, OnlineLink = null, Sensitivity = "not-a-sensiti…
+actorId = 019049de-1aca-7bbf-a58c-305fab06f061 (generated)
+participants = [{ 019049de-1aca-7bbf-a58c-305fab06f061 (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D125" s="108" t="str">
         <v>Return:
@@ -9977,7 +10089,7 @@
       <c r="S126" s="90"/>
       <c r="T126"/>
     </row>
-    <row r="127" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="127" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A127" s="105" t="str">
         <v>UTC083</v>
       </c>
@@ -9985,7 +10097,11 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C127" s="107" t="str">
-        <v>mode="InPerson"; sensitivity="Normal"</v>
+        <v>input = MeetingInput { Title = "  Giao ban  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "  Phòng A  ", OnlineLink = null, Sensitivity…
+actorId = 0197b94d-22a4-7d7b-b9ad-d75c8b202db9 (generated)
+participants = [{ 0197b94d-22a4-7d7b-b9ad-d75c8b202db9 (generated), "Chair" }]
+sensitivity = "Normal"
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D127" s="108" t="str">
         <v>Return: true
@@ -9993,7 +10109,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E127" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F127" s="105" t="str">
         <v>Pending</v>
@@ -10017,7 +10133,7 @@
       <c r="S127" s="94"/>
       <c r="T127"/>
     </row>
-    <row r="128" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="128" spans="1:20" s="93" customFormat="1" ht="327.0" outlineLevel="1" customHeight="1">
       <c r="A128" s="105" t="str">
         <v>UTC084</v>
       </c>
@@ -10025,7 +10141,11 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C128" s="107" t="str">
-        <v>mode="Online"; sensitivity="Internal"</v>
+        <v>input = MeetingInput { Title = "  Giao ban  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "Online", Location = "  Phòng A  ", OnlineLink = null, Sensitivity =…
+actorId = 01929d09-b91b-7157-8ebd-2632ac549172 (generated)
+participants = [{ 01929d09-b91b-7157-8ebd-2632ac549172 (generated), "Chair" }]
+sensitivity = "Internal"
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D128" s="108" t="str">
         <v>Return: true
@@ -10033,7 +10153,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E128" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F128" s="105" t="str">
         <v>Pending</v>
@@ -10057,7 +10177,7 @@
       <c r="S128" s="94"/>
       <c r="T128"/>
     </row>
-    <row r="129" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="129" spans="1:20" s="93" customFormat="1" ht="327.0" outlineLevel="1" customHeight="1">
       <c r="A129" s="105" t="str">
         <v>UTC085</v>
       </c>
@@ -10065,7 +10185,11 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C129" s="107" t="str">
-        <v>mode="Hybrid"; sensitivity="Confidential"</v>
+        <v>input = MeetingInput { Title = "  Giao ban  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "Hybrid", Location = "  Phòng A  ", OnlineLink = null, Sensitivity =…
+actorId = 019e0e26-f60e-7773-9116-2114e62e252f (generated)
+participants = [{ 019e0e26-f60e-7773-9116-2114e62e252f (generated), "Chair" }]
+sensitivity = "Confidential"
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D129" s="108" t="str">
         <v>Return: true
@@ -10073,7 +10197,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E129" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F129" s="105" t="str">
         <v>Pending</v>
@@ -10097,7 +10221,7 @@
       <c r="S129" s="94"/>
       <c r="T129"/>
     </row>
-    <row r="130" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="130" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A130" s="105" t="str">
         <v>UTC086</v>
       </c>
@@ -10105,7 +10229,11 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C130" s="107" t="str">
-        <v>mode="InPerson"; sensitivity="Secret"</v>
+        <v>input = MeetingInput { Title = "  Giao ban  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "  Phòng A  ", OnlineLink = null, Sensitivity…
+actorId = 019bbcf5-c494-7324-9ee1-8ad955624709 (generated)
+participants = [{ 019bbcf5-c494-7324-9ee1-8ad955624709 (generated), "Chair" }]
+sensitivity = "Secret"
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D130" s="108" t="str">
         <v>Return: true
@@ -10113,7 +10241,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E130" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F130" s="105" t="str">
         <v>Pending</v>
@@ -10161,7 +10289,7 @@
       <c r="S131" s="90"/>
       <c r="T131"/>
     </row>
-    <row r="132" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="132" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A132" s="105" t="str">
         <v>UTC087</v>
       </c>
@@ -10169,7 +10297,10 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C132" s="107" t="str">
-        <v>ValidInput(mode: null, sensitivity: null); _actorId; [new(_actorId, "Chair")]</v>
+        <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = null, Location = "Phòng họp A", OnlineLink = null, Sensitivity = nul…
+actorId = 019b13dd-1bc1-75ab-8534-8e1db8f99bbb (generated)
+participants = [{ 019b13dd-1bc1-75ab-8534-8e1db8f99bbb (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D132" s="108" t="str">
         <v>Return: true
@@ -10225,7 +10356,7 @@
       <c r="S133" s="90"/>
       <c r="T133"/>
     </row>
-    <row r="134" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="134" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A134" s="105" t="str">
         <v>UTC088</v>
       </c>
@@ -10233,7 +10364,10 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C134" s="107" t="str">
-        <v>ValidInput( title: new string('t', 300), location: new string('l', 30…; _actorId; [new(_actorId, "Chair")]</v>
+        <v>input = MeetingInput { Title = 't' × 300, PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = 'l' × 300, OnlineLink = null, Sensitivity = "Intern…
+actorId = 0195f162-780f-71d1-abd2-1f366d7dcc10 (generated)
+participants = [{ 0195f162-780f-71d1-abd2-1f366d7dcc10 (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D134" s="108" t="str">
         <v>Return: true
@@ -10289,7 +10423,7 @@
       <c r="S135" s="90"/>
       <c r="T135"/>
     </row>
-    <row r="136" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="136" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A136" s="105" t="str">
         <v>UTC089</v>
       </c>
@@ -10298,7 +10432,10 @@
 2. input = ValidInput() with { PlannedStartTime = "2099-03-01T09:00:00+07:00", PlannedEndTime = "209….</v>
       </c>
       <c r="C136" s="107" t="str">
-        <v>input; _actorId; [new(_actorId, "Chair")]</v>
+        <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+actorId = 0194eb83-f9fd-7a63-bc92-785e67769e15 (generated)
+participants = [{ 0194eb83-f9fd-7a63-bc92-785e67769e15 (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D136" s="108" t="str">
         <v>Return: true
@@ -10354,7 +10491,7 @@
       <c r="S137" s="90"/>
       <c r="T137"/>
     </row>
-    <row r="138" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="138" spans="1:20" s="93" customFormat="1" ht="327.0" outlineLevel="1" customHeight="1">
       <c r="A138" s="105" t="str">
         <v>UTC090</v>
       </c>
@@ -10362,7 +10499,11 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C138" s="107" t="str">
-        <v>start="2099-03-01 09:00"</v>
+        <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+actorId = 0193bf77-06e0-712f-8b39-a2d01ebc9412 (generated)
+participants = [{ 0193bf77-06e0-712f-8b39-a2d01ebc9412 (generated), "Chair" }]
+start = "2099-03-01 09:00"
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D138" s="108" t="str">
         <v>Return:
@@ -10396,7 +10537,7 @@
       <c r="S138" s="94"/>
       <c r="T138"/>
     </row>
-    <row r="139" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="139" spans="1:20" s="93" customFormat="1" ht="327.0" outlineLevel="1" customHeight="1">
       <c r="A139" s="105" t="str">
         <v>UTC091</v>
       </c>
@@ -10404,7 +10545,11 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C139" s="107" t="str">
-        <v>start="2099-03-01T09:00:00"</v>
+        <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+actorId = 0196214b-4db7-7293-8741-96108c4565ea (generated)
+participants = [{ 0196214b-4db7-7293-8741-96108c4565ea (generated), "Chair" }]
+start = "2099-03-01T09:00:00"
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D139" s="108" t="str">
         <v>Return:
@@ -10438,7 +10583,7 @@
       <c r="S139" s="94"/>
       <c r="T139"/>
     </row>
-    <row r="140" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="140" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A140" s="105" t="str">
         <v>UTC092</v>
       </c>
@@ -10446,7 +10591,11 @@
         <v>1. MeetingService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C140" s="107" t="str">
-        <v>start="not a time"</v>
+        <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+actorId = 019698e2-7ee3-72b5-8897-ad9e4a27a9d2 (generated)
+participants = [{ 019698e2-7ee3-72b5-8897-ad9e4a27a9d2 (generated), "Chair" }]
+start = "not a time"
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D140" s="108" t="str">
         <v>Return:
@@ -10504,7 +10653,7 @@
       <c r="S141" s="90"/>
       <c r="T141"/>
     </row>
-    <row r="142" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="142" spans="1:20" s="93" customFormat="1" ht="283.5" outlineLevel="1" customHeight="1">
       <c r="A142" s="105" t="str">
         <v>UTC093</v>
       </c>
@@ -10514,7 +10663,10 @@
 3. past = DateTimeOffset.UtcNow.AddDays(-1).</v>
       </c>
       <c r="C142" s="107" t="str">
-        <v>meeting.Id; ValidInput(start: past); _actorId</v>
+        <v>id = 0192a02c-63da-75da-89f1-db0df08a10a7 (generated)
+input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-10-29T10:36:00Z", PlannedEndTime = "2026-10-29T11:36:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+actorId = 01949f21-1e1c-7f93-8304-f75982c46284 (generated)
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D142" s="108" t="str">
         <v>Return:
@@ -10572,7 +10724,7 @@
       <c r="S143" s="90"/>
       <c r="T143"/>
     </row>
-    <row r="144" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="144" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A144" s="105" t="str">
         <v>UTC094</v>
       </c>
@@ -10581,7 +10733,10 @@
 2. input: a new MeetingInput is prepared.</v>
       </c>
       <c r="C144" s="107" t="str">
-        <v>input; _actorId; [new(_actorId, "Chair")]</v>
+        <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = null, Location = null, OnlineLink = null, Sensitivity = null, Descri…
+actorId = 019790b3-0863-75a5-a3f4-ef6e0cd6798d (generated)
+participants = [{ 019790b3-0863-75a5-a3f4-ef6e0cd6798d (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D144" s="108" t="str">
         <v>Return: true
@@ -10637,7 +10792,7 @@
       <c r="S145" s="90"/>
       <c r="T145"/>
     </row>
-    <row r="146" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="146" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A146" s="105" t="str">
         <v>UTC095</v>
       </c>
@@ -10646,7 +10801,10 @@
 2. _repository.IneligibleApproverIds.Add(approverId).</v>
       </c>
       <c r="C146" s="107" t="str">
-        <v>ValidInput(); _actorId; [new(_actorId, "Chair")]</v>
+        <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+actorId = 019b6f85-c758-702f-84b5-1216ab8bebc2 (generated)
+participants = [{ 019b6f85-c758-702f-84b5-1216ab8bebc2 (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D146" s="108" t="str">
         <v>Return: true
@@ -10702,7 +10860,7 @@
       <c r="S147" s="90"/>
       <c r="T147"/>
     </row>
-    <row r="148" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="148" spans="1:20" s="93" customFormat="1" ht="283.5" outlineLevel="1" customHeight="1">
       <c r="A148" s="105" t="str">
         <v>UTC096</v>
       </c>
@@ -10712,7 +10870,10 @@
 3. meeting.AssignedApproverId = _otherActorId.</v>
       </c>
       <c r="C148" s="107" t="str">
-        <v>meeting.Id; ValidInput(title: " Giao ban mới ", mode: "Hybrid", sensitivity: "Sec…; _actorId</v>
+        <v>id = 0199af92-7f91-736d-ad5a-e0f3232c883e (generated)
+input = MeetingInput { Title = "  Giao ban mới  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "Hybrid", Location = "Phòng họp A", OnlineLink = null, Sensitivit…
+actorId = 01979603-74ea-72ae-aae3-5bee674a3ccd (generated)
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D148" s="108" t="str">
         <v>Return: true
@@ -10768,7 +10929,7 @@
       <c r="S149" s="90"/>
       <c r="T149"/>
     </row>
-    <row r="150" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="150" spans="1:20" s="93" customFormat="1" ht="283.5" outlineLevel="1" customHeight="1">
       <c r="A150" s="105" t="str">
         <v>UTC097</v>
       </c>
@@ -10777,7 +10938,10 @@
 2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C150" s="107" t="str">
-        <v>meeting.Id; ValidInput(mode: null, sensitivity: null); _actorId</v>
+        <v>id = 019a87bf-4b02-772c-a349-acb8bd59b26c (generated)
+input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = null, Location = "Phòng họp A", OnlineLink = null, Sensitivity = nul…
+actorId = 0196d460-b2cb-70cc-99cc-61405816c2b8 (generated)
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D150" s="108" t="str">
         <v>Return: true
@@ -10845,7 +11009,8 @@
 5. meeting.StatusHistory.Add(rejection).</v>
       </c>
       <c r="C152" s="107" t="str">
-        <v>meeting.Id; _actorId</v>
+        <v>id = 019a6e0f-89c0-7fdc-8a37-204d1a041898 (generated)
+actorId = 019876e0-a33c-7989-9825-fe32ebc327b3 (generated)</v>
       </c>
       <c r="D152" s="108" t="str">
         <v>Return:
@@ -10903,7 +11068,7 @@
       <c r="S153" s="90"/>
       <c r="T153"/>
     </row>
-    <row r="154" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="154" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A154" s="105" t="str">
         <v>UTC099</v>
       </c>
@@ -10913,7 +11078,11 @@
 3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C154" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>id = 019290c3-0562-7aaf-82b3-a492b1651f44 (generated)
+input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
+actorId = 0197b236-4cfc-7391-a435-4f25fc0b4a5e (generated)
+status = MeetingStatus.Draft
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D154" s="108" t="str">
         <v>Return:
@@ -10947,7 +11116,7 @@
       <c r="S154" s="94"/>
       <c r="T154"/>
     </row>
-    <row r="155" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="155" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A155" s="105" t="str">
         <v>UTC100</v>
       </c>
@@ -10957,7 +11126,11 @@
 3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C155" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>id = 01990f26-3aea-700d-861b-46a81b019887 (generated)
+input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
+actorId = 01971dce-2360-7688-8843-bbf68bef3bee (generated)
+status = MeetingStatus.Rejected
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D155" s="108" t="str">
         <v>Return:
@@ -11015,7 +11188,7 @@
       <c r="S156" s="90"/>
       <c r="T156"/>
     </row>
-    <row r="157" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="157" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A157" s="105" t="str">
         <v>UTC101</v>
       </c>
@@ -11025,7 +11198,11 @@
 3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C157" s="107" t="str">
-        <v>status=MeetingStatus.WaitingApproval</v>
+        <v>id = 01937f14-819e-7d1d-9b58-66fba588ae88 (generated)
+input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
+actorId = 019f9591-9920-7285-89f6-56ccbdeee38d (generated)
+status = MeetingStatus.WaitingApproval
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D157" s="108" t="str">
         <v>Return: MeetingOutcome.NotEditable
@@ -11057,7 +11234,7 @@
       <c r="S157" s="94"/>
       <c r="T157"/>
     </row>
-    <row r="158" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="158" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A158" s="105" t="str">
         <v>UTC102</v>
       </c>
@@ -11067,7 +11244,11 @@
 3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C158" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
+        <v>id = 01954785-0277-70e6-a2c8-99f0dbf65553 (generated)
+input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
+actorId = 0197b73c-cf30-7079-b7f7-dcfb49e98a2f (generated)
+status = MeetingStatus.Approved
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D158" s="108" t="str">
         <v>Return: MeetingOutcome.NotEditable
@@ -11099,7 +11280,7 @@
       <c r="S158" s="94"/>
       <c r="T158"/>
     </row>
-    <row r="159" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="159" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A159" s="105" t="str">
         <v>UTC103</v>
       </c>
@@ -11109,7 +11290,11 @@
 3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C159" s="107" t="str">
-        <v>status=MeetingStatus.InProgress</v>
+        <v>id = 019c719d-75c5-727c-8e50-384ade04b34a (generated)
+input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
+actorId = 019408ef-c78b-7fed-b50c-a34eb3c586d3 (generated)
+status = MeetingStatus.InProgress
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D159" s="108" t="str">
         <v>Return: MeetingOutcome.NotEditable
@@ -11141,7 +11326,7 @@
       <c r="S159" s="94"/>
       <c r="T159"/>
     </row>
-    <row r="160" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="160" spans="1:20" s="93" customFormat="1" ht="312.5" outlineLevel="1" customHeight="1">
       <c r="A160" s="105" t="str">
         <v>UTC104</v>
       </c>
@@ -11151,7 +11336,11 @@
 3. oldTitle = meeting.Title.</v>
       </c>
       <c r="C160" s="107" t="str">
-        <v>status=MeetingStatus.Ended</v>
+        <v>id = 019e350b-0f49-7f8a-a915-f6970b745aa2 (generated)
+input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
+actorId = 019fb61b-b24f-7fce-8747-79c00bb8f589 (generated)
+status = MeetingStatus.Ended
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D160" s="108" t="str">
         <v>Return: MeetingOutcome.NotEditable
@@ -11207,7 +11396,7 @@
       <c r="S161" s="90"/>
       <c r="T161"/>
     </row>
-    <row r="162" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+    <row r="162" spans="1:20" s="93" customFormat="1" ht="327.0" outlineLevel="1" customHeight="1">
       <c r="A162" s="105" t="str">
         <v>UTC105</v>
       </c>
@@ -11219,7 +11408,12 @@
 5. updatedAt = meeting.UpdatedAt.</v>
       </c>
       <c r="C162" s="107" t="str">
-        <v>status=MeetingStatus.Draft; assigned=false</v>
+        <v>id = 019b235c-600d-7e0a-9dfe-71a95e03f7cb (generated)
+input = MeetingInput { Title = "  Giao ban tuần  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "  Phòng họp A  ", OnlineLink = null, Sen…
+actorId = 01962d9f-cbf2-7092-a9b4-0194c3d2cb8a (generated)
+status = MeetingStatus.Draft
+assigned = false
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D162" s="108" t="str">
         <v>Return: true
@@ -11227,7 +11421,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E162" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F162" s="105" t="str">
         <v>Pending</v>
@@ -11251,7 +11445,7 @@
       <c r="S162" s="94"/>
       <c r="T162"/>
     </row>
-    <row r="163" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+    <row r="163" spans="1:20" s="93" customFormat="1" ht="327.0" outlineLevel="1" customHeight="1">
       <c r="A163" s="105" t="str">
         <v>UTC106</v>
       </c>
@@ -11263,7 +11457,12 @@
 5. updatedAt = meeting.UpdatedAt.</v>
       </c>
       <c r="C163" s="107" t="str">
-        <v>status=MeetingStatus.Rejected; assigned=false</v>
+        <v>id = 0195033e-b3dd-757d-a2c0-2fb5cecbd9ed (generated)
+input = MeetingInput { Title = "  Giao ban tuần  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "  Phòng họp A  ", OnlineLink = null, Sen…
+actorId = 01963e47-2edc-7642-bad3-14a361d5a7a8 (generated)
+status = MeetingStatus.Rejected
+assigned = false
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D163" s="108" t="str">
         <v>Return: true
@@ -11271,7 +11470,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E163" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F163" s="105" t="str">
         <v>Pending</v>
@@ -11295,7 +11494,7 @@
       <c r="S163" s="94"/>
       <c r="T163"/>
     </row>
-    <row r="164" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+    <row r="164" spans="1:20" s="93" customFormat="1" ht="327.0" outlineLevel="1" customHeight="1">
       <c r="A164" s="105" t="str">
         <v>UTC107</v>
       </c>
@@ -11307,7 +11506,12 @@
 5. updatedAt = meeting.UpdatedAt.</v>
       </c>
       <c r="C164" s="107" t="str">
-        <v>status=MeetingStatus.Rejected; assigned=true</v>
+        <v>id = 019059d9-06a8-7aac-9832-12a32ae84e80 (generated)
+input = MeetingInput { Title = "  Giao ban tuần  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "  Phòng họp A  ", OnlineLink = null, Sen…
+actorId = 0190fe14-7826-7f0b-9eeb-4ca5ecc59e15 (generated)
+status = MeetingStatus.Rejected
+assigned = true
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D164" s="108" t="str">
         <v>Return: true
@@ -11315,7 +11519,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E164" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F164" s="105" t="str">
         <v>Pending</v>
@@ -11363,7 +11567,7 @@
       <c r="S165" s="90"/>
       <c r="T165"/>
     </row>
-    <row r="166" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="166" spans="1:20" s="93" customFormat="1" ht="283.5" outlineLevel="1" customHeight="1">
       <c r="A166" s="105" t="str">
         <v>UTC108</v>
       </c>
@@ -11373,7 +11577,10 @@
 3. meeting.AssignedApproverId = _otherActorId.</v>
       </c>
       <c r="C166" s="107" t="str">
-        <v>meeting.Id; ValidInput(); _actorId</v>
+        <v>id = 01934659-304b-76d9-95e9-5fad5915d2ee (generated)
+input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+actorId = 019c7d63-bdda-72f9-867e-061f32104143 (generated)
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D166" s="108" t="str">
         <v>Return: true
@@ -11438,7 +11645,9 @@
 2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C168" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>id = 0198014d-bacd-7ccb-8aea-93b05ba8ad45 (generated)
+actorId = 01974292-4d51-747f-bc8a-adcaf836a8cd (generated)
+status = MeetingStatus.Draft</v>
       </c>
       <c r="D168" s="108" t="str">
         <v>Return:
@@ -11482,7 +11691,9 @@
 2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C169" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>id = 01952e81-a54d-77bc-9f6b-a370ac8e9f2b (generated)
+actorId = 0193cd69-eb1d-7587-960c-fd278b296dd4 (generated)
+status = MeetingStatus.Rejected</v>
       </c>
       <c r="D169" s="108" t="str">
         <v>Return:
@@ -11553,7 +11764,8 @@
 5. meeting.Participants.Add(new MeetingParticipant { MeetingId = meeting.Id, UserId = participantId, }).</v>
       </c>
       <c r="C171" s="107" t="str">
-        <v>meeting.Id; _otherActorId</v>
+        <v>id = 019c217e-7677-7436-abe4-7934bfdc214d (generated)
+actorId = 019d885f-7053-7236-84bc-50c2e94eb3cd (generated)</v>
       </c>
       <c r="D171" s="108" t="str">
         <v>Return:
@@ -11622,7 +11834,8 @@
 2. _repository.NextReadThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C173" s="107" t="str">
-        <v>Guid.CreateVersion7(); _actorId</v>
+        <v>id = 019beda1-1b59-7fba-b483-c7d0bc25955f (generated)
+actorId = 01975004-6d02-7622-a94e-74680fc18bc3 (generated)</v>
       </c>
       <c r="D173" s="108" t="str">
         <v>Return: MeetingOutcome.ReadFailed
@@ -11678,7 +11891,7 @@
       <c r="S174" s="90"/>
       <c r="T174"/>
     </row>
-    <row r="175" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="175" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A175" s="105" t="str">
         <v>UTC113</v>
       </c>
@@ -11688,7 +11901,8 @@
 3. query: a new MeetingListQuery is prepared.</v>
       </c>
       <c r="C175" s="107" t="str">
-        <v>query; _actorId</v>
+        <v>query = MeetingListQuery { Status = MeetingStatus.Draft, Sensitivity = Sensitivity.Internal, Query = "Giao ban", From = null, To = null, Page = 1, PageSize = 20, SortBy = MeetingSortBy.Title, SortDirection =…
+actorId = 0190d964-9710-78ac-ad16-4701739a23d8 (generated)</v>
       </c>
       <c r="D175" s="108" t="str">
         <v>Return:
@@ -11746,7 +11960,7 @@
       <c r="S176" s="90"/>
       <c r="T176"/>
     </row>
-    <row r="177" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="177" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A177" s="105" t="str">
         <v>UTC114</v>
       </c>
@@ -11757,7 +11971,8 @@
 4. now = _repository.LastListQuery.Now.</v>
       </c>
       <c r="C177" s="107" t="str">
-        <v>query; _actorId</v>
+        <v>query = MeetingListQuery { Status = null, Sensitivity = null, Query = null, From = null, To = null, Page = 1, PageSize = 20, SortBy = MeetingSortBy.PlannedStartTime, SortDirection = MeetingSortDirection.Desc…
+actorId = 01928a89-0529-7ed0-8ec2-f79bfd9bb3a6 (generated)</v>
       </c>
       <c r="D177" s="108" t="str">
         <v>Return:
@@ -11816,7 +12031,7 @@
       <c r="S178" s="90"/>
       <c r="T178"/>
     </row>
-    <row r="179" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="179" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A179" s="105" t="str">
         <v>UTC115</v>
       </c>
@@ -11828,7 +12043,8 @@
 5. query: a new MeetingListQuery is prepared.</v>
       </c>
       <c r="C179" s="107" t="str">
-        <v>query; _actorId</v>
+        <v>query = MeetingListQuery { Status = null, Sensitivity = null, Query = null, From = null, To = null, Page = 1, PageSize = 20, SortBy = MeetingSortBy.CreatedAt, SortDirection = MeetingSortDirection.Desc, Exclu…
+actorId = 019b91c4-8d91-759f-bf8e-ec6bca220a11 (generated)</v>
       </c>
       <c r="D179" s="108" t="str">
         <v>Return:
@@ -12090,7 +12306,7 @@
       <c r="S186" s="90"/>
       <c r="T186"/>
     </row>
-    <row r="187" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="187" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A187" s="105" t="str">
         <v>UTC119</v>
       </c>
@@ -12099,7 +12315,10 @@
 2. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C187" s="107" t="str">
-        <v>ValidInput(); _actorId; [new(_actorId, "Chair")]</v>
+        <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+actorId = 01986f74-094e-7e5e-9cae-749fb93b0257 (generated)
+participants = [{ 01986f74-094e-7e5e-9cae-749fb93b0257 (generated), "Chair" }]
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D187" s="108" t="str">
         <v>Return: MeetingOutcome.SaveFailed
@@ -12155,7 +12374,7 @@
       <c r="S188" s="90"/>
       <c r="T188"/>
     </row>
-    <row r="189" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="189" spans="1:20" s="93" customFormat="1" ht="283.5" outlineLevel="1" customHeight="1">
       <c r="A189" s="105" t="str">
         <v>UTC120</v>
       </c>
@@ -12165,7 +12384,10 @@
 3. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C189" s="107" t="str">
-        <v>meeting.Id; ValidInput(title: "Không được lưu"); _actorId</v>
+        <v>id = 01953d41-8f50-7d90-9c36-58985e7b34cb (generated)
+input = MeetingInput { Title = "Không được lưu", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivit…
+actorId = 0196513e-dd0f-7203-9cd6-70022cd14f5d (generated)
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D189" s="108" t="str">
         <v>Return: MeetingOutcome.SaveFailed
@@ -12287,7 +12509,7 @@
       <c r="S192" s="90"/>
       <c r="T192"/>
     </row>
-    <row r="193" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="193" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A193" s="105" t="str">
         <v>UTC122</v>
       </c>
@@ -12296,7 +12518,7 @@
 2. meeting: a new Meeting is prepared.</v>
       </c>
       <c r="C193" s="107" t="str">
-        <v>meeting</v>
+        <v>input = Meeting { Title = "Giao ban tuần", Status = MeetingStatus.Draft, Sensitivity = Sensitivity.Normal, Mode = MeetingMode.InPerson, CreatedById = 0199f7a3-168b-7fdb-a8c5-f4af971175f4 (generated) }</v>
       </c>
       <c r="D193" s="108" t="str">
         <v>Return:
@@ -12423,7 +12645,7 @@
       <c r="S196" s="90"/>
       <c r="T196"/>
     </row>
-    <row r="197" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="197" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A197" s="105" t="str">
         <v>UTC124</v>
       </c>
@@ -12433,7 +12655,9 @@
 3. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C197" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.SubmitForApprova…; _organizerId</v>
+        <v>meetingId = 019952c2-26cb-7aa4-8be7-5c09f3615fb5 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.SubmitForApproval, AssignedApproverId = 0190c4df-6c10-7596-85e2-83ff85754a26 (generated), Reason = null, OrganizerId = null }
+actorId = 01909c1d-f950-7c7e-9b6a-4ffeda4b437b (generated)</v>
       </c>
       <c r="D197" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -12489,7 +12713,7 @@
       <c r="S198" s="90"/>
       <c r="T198"/>
     </row>
-    <row r="199" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="199" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A199" s="105" t="str">
         <v>UTC125</v>
       </c>
@@ -12498,7 +12722,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C199" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); _approverId</v>
+        <v>meetingId = 019e6bea-685d-7b38-a337-379567e64768 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Approve, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 0194bc64-a1aa-7319-a308-e20047a9b14b (generated)</v>
       </c>
       <c r="D199" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -12554,7 +12780,7 @@
       <c r="S200" s="90"/>
       <c r="T200"/>
     </row>
-    <row r="201" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="201" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A201" s="105" t="str">
         <v>UTC126</v>
       </c>
@@ -12563,7 +12789,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C201" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Reject, Reason:…; _approverId</v>
+        <v>meetingId = 019db216-f1a4-756e-b961-9102d51099f7 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Reject, Reason = "Thiếu số liệu quý 3", AssignedApproverId = null, OrganizerId = null }
+actorId = 01967bdb-b063-7f32-b825-058daad7fa5b (generated)</v>
       </c>
       <c r="D201" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -12629,7 +12857,9 @@
 3. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, FromStatus = MeetingStatus.WaitingApproval, ToStatus = Meeting….</v>
       </c>
       <c r="C203" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.ReturnToDraft); _organizerId</v>
+        <v>meetingId = 0195e927-f498-7e59-a5ef-d04bd6141fc5 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019d57be-322d-7a85-a2a9-1c22f72ad2c7 (generated)</v>
       </c>
       <c r="D203" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -12695,7 +12925,8 @@
 3. meeting.AssignedApproverId = _approverId.</v>
       </c>
       <c r="C205" s="107" t="str">
-        <v>meeting.Id; _approverId</v>
+        <v>meetingId = 01983bee-f4c5-7e2b-b70d-6543cd801bb5 (generated)
+actorId = 0198e4ba-3acf-7db0-876f-a1f96d580b27 (generated)</v>
       </c>
       <c r="D205" s="108" t="str">
         <v>Return:
@@ -12755,7 +12986,7 @@
       <c r="S206" s="90"/>
       <c r="T206"/>
     </row>
-    <row r="207" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="207" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A207" s="105" t="str">
         <v>UTC129</v>
       </c>
@@ -12764,7 +12995,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C207" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); otherApprover</v>
+        <v>meetingId = 019fa515-b1de-7a9e-ad35-4c4259d8d86d (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Approve, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 0190f254-8f95-7ab2-9b29-055beb090a15 (generated)</v>
       </c>
       <c r="D207" s="108" t="str">
         <v>Return:
@@ -12822,7 +13055,7 @@
       <c r="S208" s="90"/>
       <c r="T208"/>
     </row>
-    <row r="209" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="209" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A209" s="105" t="str">
         <v>UTC130</v>
       </c>
@@ -12831,7 +13064,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C209" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Approve); _approverId</v>
+        <v>meetingId = 019c87fb-58e2-750a-bb70-1ffa9b5a2eba (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Approve, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 01913be7-47dc-782a-995e-14202a58bc2c (generated)</v>
       </c>
       <c r="D209" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Forbidden
@@ -12897,7 +13132,8 @@
 3. meeting.Title = " ".</v>
       </c>
       <c r="C211" s="107" t="str">
-        <v>meeting.Id; _organizerId</v>
+        <v>id = 019a264e-1ba9-724d-93e7-351f792a525b (generated)
+actorId = 019d5f04-b853-70e2-b6d2-897f6fcf07b6 (generated)</v>
       </c>
       <c r="D211" s="108" t="str">
         <v>Return:
@@ -12957,7 +13193,7 @@
       <c r="S212" s="90"/>
       <c r="T212"/>
     </row>
-    <row r="213" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="213" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A213" s="105" t="str">
         <v>UTC132</v>
       </c>
@@ -12966,7 +13202,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C213" s="107" t="str">
-        <v>reason=null; expected=MeetingWorkflowOutcome.RejectionReasonRequired</v>
+        <v>meetingId = 019b19e0-a99d-78ed-9d31-3581d4faeca1 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Reject, Reason = null, AssignedApproverId = null, OrganizerId = null }
+actorId = 019d2fe5-4583-710d-9d6e-f082da2b9b48 (generated)</v>
       </c>
       <c r="D213" s="108" t="str">
         <v>Return: expected
@@ -12998,7 +13236,7 @@
       <c r="S213" s="94"/>
       <c r="T213"/>
     </row>
-    <row r="214" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="214" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A214" s="105" t="str">
         <v>UTC133</v>
       </c>
@@ -13007,7 +13245,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C214" s="107" t="str">
-        <v>reason="   "; expected=MeetingWorkflowOutcome.RejectionReasonRequired</v>
+        <v>meetingId = 019b0e96-3397-7267-beea-18b29c284b49 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Reject, Reason = "   ", AssignedApproverId = null, OrganizerId = null }
+actorId = 01956e7c-a426-72c7-bb0d-a9c681b21e58 (generated)</v>
       </c>
       <c r="D214" s="108" t="str">
         <v>Return: expected
@@ -13039,7 +13279,7 @@
       <c r="S214" s="94"/>
       <c r="T214"/>
     </row>
-    <row r="215" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="215" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A215" s="105" t="str">
         <v>UTC134</v>
       </c>
@@ -13048,7 +13288,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C215" s="107" t="str">
-        <v>reason="valid"; expected=MeetingWorkflowOutcome.Success</v>
+        <v>meetingId = 019490a6-c54b-7838-8fb5-8e6123787e37 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Reject, Reason = "valid", AssignedApproverId = null, OrganizerId = null }
+actorId = 01997569-b388-7459-baca-4fff4cabcc91 (generated)</v>
       </c>
       <c r="D215" s="108" t="str">
         <v>Return: expected
@@ -13104,7 +13346,7 @@
       <c r="S216" s="90"/>
       <c r="T216"/>
     </row>
-    <row r="217" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="217" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A217" s="105" t="str">
         <v>UTC135</v>
       </c>
@@ -13114,7 +13356,9 @@
 3. rejectedMeeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C217" s="107" t="str">
-        <v>acceptedMeeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Reject, Reason:…; _approverId</v>
+        <v>meetingId = 019b5812-c731-7997-9286-7c026d0d8215 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Reject, Reason = 'x' × 1000, AssignedApproverId = null, OrganizerId = null }
+actorId = 019c99cd-42bd-7dba-bc84-60bbdf8bec67 (generated)</v>
       </c>
       <c r="D217" s="108" t="str">
         <v>Return:
@@ -13184,7 +13428,9 @@
 5. meeting.Participants.Add(delegated).</v>
       </c>
       <c r="C219" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
+        <v>meetingId = 0191640d-2126-7b89-831c-6e3941070811 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 0199a18c-8557-709f-ab0a-e4f3e1ad2f83 (generated)</v>
       </c>
       <c r="D219" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -13253,7 +13499,9 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C221" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
+        <v>meetingId = 019fb45f-5376-7423-8c2d-14c31c044fcb (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 0198da32-773e-7547-8bfa-29050ce6eb12 (generated)</v>
       </c>
       <c r="D221" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -13378,7 +13626,7 @@
       <c r="S224" s="90"/>
       <c r="T224"/>
     </row>
-    <row r="225" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+    <row r="225" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A225" s="105" t="str">
         <v>UTC139</v>
       </c>
@@ -13390,7 +13638,10 @@
 5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C225" s="107" t="str">
-        <v>sensitivity=Sensitivity.Normal</v>
+        <v>meetingId = 019b4b7b-af53-7498-a0d3-5c1ce04b981c (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.SubmitForApproval, AssignedApproverId = 019e8eef-bb48-78d7-8303-7f8aefaac9a6 (generated), Reason = null, OrganizerId = null }
+actorId = 019e8eef-bb48-78d7-8303-7f8aefaac9a6 (generated)
+sensitivity = Sensitivity.Normal</v>
       </c>
       <c r="D225" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidApprover
@@ -13422,7 +13673,7 @@
       <c r="S225" s="94"/>
       <c r="T225"/>
     </row>
-    <row r="226" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+    <row r="226" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A226" s="105" t="str">
         <v>UTC140</v>
       </c>
@@ -13434,7 +13685,10 @@
 5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C226" s="107" t="str">
-        <v>sensitivity=Sensitivity.Internal</v>
+        <v>meetingId = 019e708b-91b7-736d-b78f-2769660058b1 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.SubmitForApproval, AssignedApproverId = 019d571f-da48-75b6-9d67-614424c6f2e7 (generated), Reason = null, OrganizerId = null }
+actorId = 019d571f-da48-75b6-9d67-614424c6f2e7 (generated)
+sensitivity = Sensitivity.Internal</v>
       </c>
       <c r="D226" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidApprover
@@ -13466,7 +13720,7 @@
       <c r="S226" s="94"/>
       <c r="T226"/>
     </row>
-    <row r="227" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+    <row r="227" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A227" s="105" t="str">
         <v>UTC141</v>
       </c>
@@ -13478,7 +13732,10 @@
 5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C227" s="107" t="str">
-        <v>sensitivity=Sensitivity.Confidential</v>
+        <v>meetingId = 0194daa8-310b-740c-9473-e95c6c28cc6a (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.SubmitForApproval, AssignedApproverId = 0194538f-630c-77fc-a16d-0086e99a3ca3 (generated), Reason = null, OrganizerId = null }
+actorId = 0194538f-630c-77fc-a16d-0086e99a3ca3 (generated)
+sensitivity = Sensitivity.Confidential</v>
       </c>
       <c r="D227" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidApprover
@@ -13510,7 +13767,7 @@
       <c r="S227" s="94"/>
       <c r="T227"/>
     </row>
-    <row r="228" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
+    <row r="228" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A228" s="105" t="str">
         <v>UTC142</v>
       </c>
@@ -13522,7 +13779,10 @@
 5. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C228" s="107" t="str">
-        <v>sensitivity=Sensitivity.Secret</v>
+        <v>meetingId = 01970967-9b57-7c85-93b3-ec66d5c659d2 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.SubmitForApproval, AssignedApproverId = 0199222e-f098-71bc-96a6-705333bc0bf7 (generated), Reason = null, OrganizerId = null }
+actorId = 0199222e-f098-71bc-96a6-705333bc0bf7 (generated)
+sensitivity = Sensitivity.Secret</v>
       </c>
       <c r="D228" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidApprover
@@ -13578,7 +13838,7 @@
       <c r="S229" s="90"/>
       <c r="T229"/>
     </row>
-    <row r="230" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="230" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A230" s="105" t="str">
         <v>UTC143</v>
       </c>
@@ -13588,7 +13848,9 @@
 3. meeting.AssignedApproverId = _organizerId.</v>
       </c>
       <c r="C230" s="107" t="str">
-        <v>action=MeetingTransitionAction.Approve</v>
+        <v>meetingId = 019e5c7e-681f-7894-86ba-3e2ecfacd356 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Approve, Reason = action == MeetingTransitionAction.Reject ? "Lý do" : null, AssignedApproverId = null, OrganizerId = null }
+actorId = 0190206d-80b3-7319-9fd8-9c971216105d (generated)</v>
       </c>
       <c r="D230" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Forbidden
@@ -13620,7 +13882,7 @@
       <c r="S230" s="94"/>
       <c r="T230"/>
     </row>
-    <row r="231" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="231" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A231" s="105" t="str">
         <v>UTC144</v>
       </c>
@@ -13630,7 +13892,9 @@
 3. meeting.AssignedApproverId = _organizerId.</v>
       </c>
       <c r="C231" s="107" t="str">
-        <v>action=MeetingTransitionAction.Reject</v>
+        <v>meetingId = 01993fe4-f88c-73bb-bb0f-c0498036b9e0 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Reject, Reason = action == MeetingTransitionAction.Reject ? "Lý do" : null, AssignedApproverId = null, OrganizerId = null }
+actorId = 019d93c7-9840-7ef5-aab3-1df46d8c4197 (generated)</v>
       </c>
       <c r="D231" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Forbidden
@@ -13686,7 +13950,7 @@
       <c r="S232" s="90"/>
       <c r="T232"/>
     </row>
-    <row r="233" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="233" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A233" s="105" t="str">
         <v>UTC145</v>
       </c>
@@ -13695,7 +13959,10 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C233" s="107" t="str">
-        <v>approverEligible=true</v>
+        <v>meetingId = 019e349e-9910-7432-9c31-f3edbd301b8a (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 0192bb26-d6f3-7df3-8c42-e45a85ec61a6 (generated)
+approverEligible = true</v>
       </c>
       <c r="D233" s="108" t="str">
         <v>Return: approverEligible ? MeetingWorkflowOutcome.StatusConflict : MeetingWorkflowOutcome.Success
@@ -13703,7 +13970,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E233" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F233" s="105" t="str">
         <v>Pending</v>
@@ -13727,7 +13994,7 @@
       <c r="S233" s="94"/>
       <c r="T233"/>
     </row>
-    <row r="234" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="234" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A234" s="105" t="str">
         <v>UTC146</v>
       </c>
@@ -13736,7 +14003,10 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C234" s="107" t="str">
-        <v>approverEligible=false</v>
+        <v>meetingId = 019adad9-1cb7-7206-b708-e0aa0644b659 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019285fb-a239-7977-9189-87200a466874 (generated)
+approverEligible = false</v>
       </c>
       <c r="D234" s="108" t="str">
         <v>Return: approverEligible ? MeetingWorkflowOutcome.StatusConflict : MeetingWorkflowOutcome.Success
@@ -13744,7 +14014,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E234" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F234" s="105" t="str">
         <v>Pending</v>
@@ -13792,7 +14062,7 @@
       <c r="S235" s="90"/>
       <c r="T235"/>
     </row>
-    <row r="236" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="236" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A236" s="105" t="str">
         <v>UTC147</v>
       </c>
@@ -13803,7 +14073,10 @@
 4. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C236" s="107" t="str">
-        <v>selfAssignment=true</v>
+        <v>meetingId = 019dec9a-4ac2-794a-a616-cee9d06bfe6f (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019cbec4-37b4-7b7a-9610-ecec1a1901fa (generated)
+selfAssignment = true</v>
       </c>
       <c r="D236" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -13835,7 +14108,7 @@
       <c r="S236" s="94"/>
       <c r="T236"/>
     </row>
-    <row r="237" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="237" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A237" s="105" t="str">
         <v>UTC148</v>
       </c>
@@ -13846,7 +14119,10 @@
 4. meeting.AgendaItems.Add(Agenda(meeting.Id)).</v>
       </c>
       <c r="C237" s="107" t="str">
-        <v>selfAssignment=false</v>
+        <v>meetingId = 01924f65-df32-711a-b48a-ea891d0d9cbc (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 01992fbb-e67d-79f5-9796-994818317f8c (generated)
+selfAssignment = false</v>
       </c>
       <c r="D237" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -13902,7 +14178,7 @@
       <c r="S238" s="90"/>
       <c r="T238"/>
     </row>
-    <row r="239" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="239" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A239" s="105" t="str">
         <v>UTC149</v>
       </c>
@@ -13912,7 +14188,9 @@
 3. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C239" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.ReturnToDraft); _organizerId</v>
+        <v>meetingId = 0194f56e-6ee2-74fe-911f-107c9b1b58a3 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 01996554-8a8f-7409-b549-5c083656978e (generated)</v>
       </c>
       <c r="D239" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.SaveFailed
@@ -13968,7 +14246,7 @@
       <c r="S240" s="90"/>
       <c r="T240"/>
     </row>
-    <row r="241" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="241" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A241" s="105" t="str">
         <v>UTC150</v>
       </c>
@@ -13977,7 +14255,10 @@
 2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C241" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>meetingId = 019f613a-bc74-7034-ab46-d38a0bac5cdd (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019b1299-15ee-76a8-94f9-84f4514e628d (generated)
+status = MeetingStatus.Draft</v>
       </c>
       <c r="D241" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -13985,7 +14266,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E241" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F241" s="105" t="str">
         <v>Pending</v>
@@ -14009,7 +14290,7 @@
       <c r="S241" s="94"/>
       <c r="T241"/>
     </row>
-    <row r="242" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="242" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A242" s="105" t="str">
         <v>UTC151</v>
       </c>
@@ -14018,7 +14299,10 @@
 2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C242" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
+        <v>meetingId = 0199a57b-10f0-7177-9165-d3dab9023948 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 01998ea5-656a-7a67-810d-25276168644d (generated)
+status = MeetingStatus.Approved</v>
       </c>
       <c r="D242" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -14026,7 +14310,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E242" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F242" s="105" t="str">
         <v>Pending</v>
@@ -14050,7 +14334,7 @@
       <c r="S242" s="94"/>
       <c r="T242"/>
     </row>
-    <row r="243" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="243" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A243" s="105" t="str">
         <v>UTC152</v>
       </c>
@@ -14059,7 +14343,10 @@
 2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C243" s="107" t="str">
-        <v>status=MeetingStatus.Published</v>
+        <v>meetingId = 0198146e-f8c6-7817-9a57-7c5254702136 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.ReturnToDraft, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 01989299-2520-7657-af2b-7da27155d1fe (generated)
+status = MeetingStatus.Published</v>
       </c>
       <c r="D243" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -14067,7 +14354,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E243" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F243" s="105" t="str">
         <v>Pending</v>
@@ -14126,7 +14413,9 @@
 4. _repository.NextSaveThrows = new NpgsqlException("database unavailable").</v>
       </c>
       <c r="C245" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
+        <v>meetingId = 0191e255-ae43-70b5-86e2-603329c2a9ba (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019b38fa-b968-7e80-a990-ea8bbb72ab2f (generated)</v>
       </c>
       <c r="D245" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.SaveFailed
@@ -14195,7 +14484,10 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C247" s="107" t="str">
-        <v>meeting.Id; currentApprover; 1; 20</v>
+        <v>id = 019567a1-4f3d-7522-964f-8e2852399f3a (generated)
+actorId = 019d5686-5d33-7394-8509-6612af99958a (generated)
+page = 1
+pageSize = 20</v>
       </c>
       <c r="D247" s="108" t="str">
         <v>Return:
@@ -14255,7 +14547,7 @@
       <c r="S248" s="90"/>
       <c r="T248"/>
     </row>
-    <row r="249" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
+    <row r="249" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A249" s="105" t="str">
         <v>UTC155</v>
       </c>
@@ -14267,7 +14559,9 @@
 5. meeting.StatusHistory.Add(approval).</v>
       </c>
       <c r="C249" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
+        <v>meetingId = 01931377-a411-7c30-a2a2-d64dceb93b46 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 0196cf0b-df06-7f54-a8ea-495c41e3f045 (generated), AssignedApproverId = null, Reason = null }
+actorId = 0190f66d-2ea5-7cd5-b204-53d9a14b09a8 (generated)</v>
       </c>
       <c r="D249" s="108" t="str">
         <v>Return:
@@ -14339,7 +14633,10 @@
 5. _repository.NextWorkflowReadThrows = new InvalidOperationException("Resource must not be loaded").</v>
       </c>
       <c r="C251" s="107" t="str">
-        <v>inactive=false</v>
+        <v>meetingId = 0198cc2a-14c8-7af1-ad10-dd07be79102d (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 01999886-0aa6-76f6-b10a-478a052fc5fb (generated), AssignedApproverId = null, Reason = null }
+actorId = 019c10fa-9715-7ec5-95bf-2417ecc9e3be (generated)
+inactive = false</v>
       </c>
       <c r="D251" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.NotFound
@@ -14347,7 +14644,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E251" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F251" s="105" t="str">
         <v>Pending</v>
@@ -14383,7 +14680,10 @@
 5. _repository.NextWorkflowReadThrows = new InvalidOperationException("Resource must not be loaded").</v>
       </c>
       <c r="C252" s="107" t="str">
-        <v>inactive=true</v>
+        <v>meetingId = 0195b11a-9ec3-7474-8ab3-ce2102a21894 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 0198b62c-d2da-7b71-a62f-91bff72b48c5 (generated), AssignedApproverId = null, Reason = null }
+actorId = 019c006e-a0bb-79cf-b14f-d9bec8a451a4 (generated)
+inactive = true</v>
       </c>
       <c r="D252" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.NotFound
@@ -14391,7 +14691,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E252" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F252" s="105" t="str">
         <v>Pending</v>
@@ -14439,7 +14739,7 @@
       <c r="S253" s="90"/>
       <c r="T253"/>
     </row>
-    <row r="254" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="254" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A254" s="105" t="str">
         <v>UTC158</v>
       </c>
@@ -14448,7 +14748,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.Approved).</v>
       </c>
       <c r="C254" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
+        <v>meetingId = 019c11df-84e5-7aa5-bade-2a6e07b61cda (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 019e605f-7b71-7520-9b97-9a2fa1f7ad95 (generated), AssignedApproverId = null, Reason = null }
+actorId = 01904c11-5405-7611-80e7-e80c9e105126 (generated)</v>
       </c>
       <c r="D254" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -14504,7 +14806,7 @@
       <c r="S255" s="90"/>
       <c r="T255"/>
     </row>
-    <row r="256" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="256" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A256" s="105" t="str">
         <v>UTC159</v>
       </c>
@@ -14515,7 +14817,10 @@
 4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
       </c>
       <c r="C256" s="107" t="str">
-        <v>target="missing"</v>
+        <v>meetingId = 0195592d-dcf1-784f-88c3-3495f0ed214f (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 019cd7fc-8539-7ddc-b97b-456a07038580 (generated), AssignedApproverId = null, Reason = null }
+actorId = 019a84d7-2b4a-731b-9369-06e908a6ae55 (generated)
+target = "missing"</v>
       </c>
       <c r="D256" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
@@ -14547,7 +14852,7 @@
       <c r="S256" s="94"/>
       <c r="T256"/>
     </row>
-    <row r="257" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="257" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A257" s="105" t="str">
         <v>UTC160</v>
       </c>
@@ -14558,7 +14863,10 @@
 4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
       </c>
       <c r="C257" s="107" t="str">
-        <v>target="inactive"</v>
+        <v>meetingId = 019b5859-8589-7dc7-90c6-3aa85cec5cfb (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 019d3ad6-5da9-7d6b-96b6-c25f8b0d0c23 (generated), AssignedApproverId = null, Reason = null }
+actorId = 0198817c-87f5-7ec8-b293-9c1eb6d26121 (generated)
+target = "inactive"</v>
       </c>
       <c r="D257" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
@@ -14590,7 +14898,7 @@
       <c r="S257" s="94"/>
       <c r="T257"/>
     </row>
-    <row r="258" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="258" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A258" s="105" t="str">
         <v>UTC161</v>
       </c>
@@ -14601,7 +14909,10 @@
 4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
       </c>
       <c r="C258" s="107" t="str">
-        <v>target="withoutCapability"</v>
+        <v>meetingId = 019eb558-5b61-7ca0-ab6c-76955c297b12 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 019c8951-842b-7187-bb87-8e93f4e49ca0 (generated), AssignedApproverId = null, Reason = null }
+actorId = 019fe102-5dcf-7938-93b9-d32fce403a48 (generated)
+target = "withoutCapability"</v>
       </c>
       <c r="D258" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
@@ -14633,7 +14944,7 @@
       <c r="S258" s="94"/>
       <c r="T258"/>
     </row>
-    <row r="259" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="259" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A259" s="105" t="str">
         <v>UTC162</v>
       </c>
@@ -14644,7 +14955,10 @@
 4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
       </c>
       <c r="C259" s="107" t="str">
-        <v>target="previousOrganizer"</v>
+        <v>meetingId = 01934571-276d-7113-a66d-aca96ea2face (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 019f59c2-d8b0-72ae-bdec-535077db2f2e (generated), AssignedApproverId = null, Reason = null }
+actorId = 0194a542-0a0b-7daf-bc14-9d6782bd17e9 (generated)
+target = "previousOrganizer"</v>
       </c>
       <c r="D259" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
@@ -14676,7 +14990,7 @@
       <c r="S259" s="94"/>
       <c r="T259"/>
     </row>
-    <row r="260" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="260" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A260" s="105" t="str">
         <v>UTC163</v>
       </c>
@@ -14687,7 +15001,10 @@
 4. if (target == "inactive") _repository.InactiveUserIds.Add(replacement).</v>
       </c>
       <c r="C260" s="107" t="str">
-        <v>target="assignedApprover"</v>
+        <v>meetingId = 0194c0b9-6082-7e64-8cfa-02affa466514 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 01905c7e-b213-7438-8831-274716708872 (generated), AssignedApproverId = null, Reason = null }
+actorId = 019d2281-95fe-78ba-902e-d5d5cdde32e0 (generated)
+target = "assignedApprover"</v>
       </c>
       <c r="D260" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.InvalidOrganizer
@@ -14743,7 +15060,7 @@
       <c r="S261" s="90"/>
       <c r="T261"/>
     </row>
-    <row r="262" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="262" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A262" s="105" t="str">
         <v>UTC164</v>
       </c>
@@ -14753,7 +15070,10 @@
 3. _repository.InactiveUserIds.Add(_organizerId).</v>
       </c>
       <c r="C262" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>meetingId = 019a40a8-9a2c-74d7-adc3-440d3506ed69 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 0199578d-167e-7c0c-bc19-8fa22612d2df (generated), AssignedApproverId = null, Reason = null }
+actorId = 019899a3-f24e-7f21-84cc-786622a2aab0 (generated)
+status = MeetingStatus.Draft</v>
       </c>
       <c r="D262" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -14761,7 +15081,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E262" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F262" s="105" t="str">
         <v>Pending</v>
@@ -14785,7 +15105,7 @@
       <c r="S262" s="94"/>
       <c r="T262"/>
     </row>
-    <row r="263" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="263" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A263" s="105" t="str">
         <v>UTC165</v>
       </c>
@@ -14795,7 +15115,10 @@
 3. _repository.InactiveUserIds.Add(_organizerId).</v>
       </c>
       <c r="C263" s="107" t="str">
-        <v>status=MeetingStatus.WaitingApproval</v>
+        <v>meetingId = 019feb8a-06e7-75cf-ab96-a1e02c79e53b (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 019fa759-3885-7ecf-8dfa-e735dfcb66a5 (generated), AssignedApproverId = null, Reason = null }
+actorId = 019b403f-2a1f-7076-a4f6-a1a637c4b567 (generated)
+status = MeetingStatus.WaitingApproval</v>
       </c>
       <c r="D263" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -14803,7 +15126,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E263" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F263" s="105" t="str">
         <v>Pending</v>
@@ -14827,7 +15150,7 @@
       <c r="S263" s="94"/>
       <c r="T263"/>
     </row>
-    <row r="264" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="264" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A264" s="105" t="str">
         <v>UTC166</v>
       </c>
@@ -14837,7 +15160,10 @@
 3. _repository.InactiveUserIds.Add(_organizerId).</v>
       </c>
       <c r="C264" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>meetingId = 01965997-afd5-7e41-9df4-41247459ced1 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 0198ec87-806f-7d04-94a0-589554678041 (generated), AssignedApproverId = null, Reason = null }
+actorId = 01941b66-31ba-7e9e-b25c-a7a623d1b075 (generated)
+status = MeetingStatus.Rejected</v>
       </c>
       <c r="D264" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -14845,7 +15171,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E264" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F264" s="105" t="str">
         <v>Pending</v>
@@ -14869,7 +15195,7 @@
       <c r="S264" s="94"/>
       <c r="T264"/>
     </row>
-    <row r="265" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="265" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A265" s="105" t="str">
         <v>UTC167</v>
       </c>
@@ -14879,7 +15205,10 @@
 3. _repository.InactiveUserIds.Add(_organizerId).</v>
       </c>
       <c r="C265" s="107" t="str">
-        <v>status=MeetingStatus.Published</v>
+        <v>meetingId = 019889b2-86be-7c37-9c2c-a4c539c7ee4e (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 01915820-038f-7e5b-be3b-96dded3a12b3 (generated), AssignedApproverId = null, Reason = null }
+actorId = 01965c52-a02d-7b37-a11a-6e659ee81a3d (generated)
+status = MeetingStatus.Published</v>
       </c>
       <c r="D265" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -14887,7 +15216,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E265" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F265" s="105" t="str">
         <v>Pending</v>
@@ -14935,7 +15264,7 @@
       <c r="S266" s="90"/>
       <c r="T266"/>
     </row>
-    <row r="267" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="267" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A267" s="105" t="str">
         <v>UTC168</v>
       </c>
@@ -14946,7 +15275,9 @@
 4. _repository.NextSaveThrows = new TimeoutException("Persistence unavailable").</v>
       </c>
       <c r="C267" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.TransferOrganize…; administrator</v>
+        <v>meetingId = 0193cea5-6cbe-7403-be4c-7aaa5ebd5c8d (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.TransferOrganizer, OrganizerId = 019712e3-24b5-7131-add7-4f58e4aa32d3 (generated), AssignedApproverId = null, Reason = null }
+actorId = 0192c278-4efd-7f4c-b208-585ec35a9b62 (generated)</v>
       </c>
       <c r="D267" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.SaveFailed
@@ -15013,7 +15344,10 @@
 4. meeting.StatusHistory.Add(new MeetingStatusHistory { MeetingId = meeting.Id, FromStatus = MeetingStatus.Approved, ToStatus = MeetingStatus.….</v>
       </c>
       <c r="C269" s="107" t="str">
-        <v>meeting.Id; _organizerId; 1; 20</v>
+        <v>id = 019fc4f6-62dd-7976-a734-a6b1e46fc1e5 (generated)
+actorId = 019ca83b-1d3a-7b89-9f3f-cb0ede8a364c (generated)
+page = 1
+pageSize = 20</v>
       </c>
       <c r="D269" s="108" t="str">
         <v>Return:
@@ -15084,7 +15418,9 @@
 5. if (status == MeetingStatus.Rejected) { rejection = new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject….</v>
       </c>
       <c r="C271" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>id = 0198f73a-5084-7950-9f55-7b90a8c896dd (generated)
+actorId = 01971861-882b-7fc6-9cde-0653273b1105 (generated)
+status = MeetingStatus.Draft</v>
       </c>
       <c r="D271" s="108" t="str">
         <v>Return:
@@ -15131,7 +15467,9 @@
 5. if (status == MeetingStatus.Rejected) { rejection = new MeetingStatusHistory { MeetingId = meeting.Id, Action = MeetingHistoryAction.Reject….</v>
       </c>
       <c r="C272" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>id = 019594a6-b2ba-78b2-af3b-9d8aa6aa483c (generated)
+actorId = 01910773-83bd-70ae-b1f6-a8033862b844 (generated)
+status = MeetingStatus.Rejected</v>
       </c>
       <c r="D272" s="108" t="str">
         <v>Return:
@@ -15202,7 +15540,10 @@
 5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
       </c>
       <c r="C274" s="107" t="str">
-        <v>failure="invalidApprover"; expected=MeetingWorkflowOutcome.InvalidApprover</v>
+        <v>meetingId = 01901352-f3b8-7891-ae43-f08052041c62 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.SubmitForApproval, AssignedApproverId = 019cdf7a-fb03-7d97-8a1d-78d9929b38a1 (generated), Reason = null, OrganizerId = null }
+actorId = 0198272f-8555-73aa-a8cc-2ffa363893b7 (generated)
+failure = "invalidApprover"</v>
       </c>
       <c r="D274" s="108" t="str">
         <v>Return: expected
@@ -15246,7 +15587,10 @@
 5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
       </c>
       <c r="C275" s="107" t="str">
-        <v>failure="invalidInformation"; expected=MeetingWorkflowOutcome.SubmissionNotReady</v>
+        <v>meetingId = 01976ff1-9e0c-7fc6-a434-da9da9c6f796 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.SubmitForApproval, AssignedApproverId = 019924ca-8f8f-78e1-ad82-ce61a8709251 (generated), Reason = null, OrganizerId = null }
+actorId = 019d4438-e694-75a9-bf00-cb8ac4d85f7a (generated)
+failure = "invalidInformation"</v>
       </c>
       <c r="D275" s="108" t="str">
         <v>Return: expected
@@ -15290,7 +15634,10 @@
 5. switch (failure) { case "invalidApprover": _repository.IneligibleApproverIds.Add(replacement); break; case "invalidInformation": meeting.Ti….</v>
       </c>
       <c r="C276" s="107" t="str">
-        <v>failure="saveFailure"; expected=MeetingWorkflowOutcome.SaveFailed</v>
+        <v>meetingId = 01946c32-c3d3-7128-ab23-e9c21a01c049 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.SubmitForApproval, AssignedApproverId = 01964168-43c8-7bb2-ad70-85e7e00d2b34 (generated), Reason = null, OrganizerId = null }
+actorId = 0195ee9a-5560-7a49-86bb-996f4d0b8183 (generated)
+failure = "saveFailure"</v>
       </c>
       <c r="D276" s="108" t="str">
         <v>Return: expected
@@ -15346,7 +15693,7 @@
       <c r="S277" s="90"/>
       <c r="T277"/>
     </row>
-    <row r="278" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="278" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A278" s="105" t="str">
         <v>UTC175</v>
       </c>
@@ -15356,7 +15703,9 @@
 3. meeting.Participants.Add(Participant(meeting, active: true, InvitationResponse.Accepted)).</v>
       </c>
       <c r="C278" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Publish); _organizerId</v>
+        <v>meetingId = 0197c1b5-c856-74ce-8609-27f065de2e0c (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 0198519c-639e-756e-8f59-34ffeee5e377 (generated)</v>
       </c>
       <c r="D278" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -15412,7 +15761,7 @@
       <c r="S279" s="90"/>
       <c r="T279"/>
     </row>
-    <row r="280" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="280" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A280" s="105" t="str">
         <v>UTC176</v>
       </c>
@@ -15422,7 +15771,10 @@
 3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C280" s="107" t="str">
-        <v>scenario="no-participants"</v>
+        <v>meetingId = 01992b19-15b8-7fab-9cac-e58dc29449cc (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019d81b3-4d4f-7101-9513-de3aae8fae7c (generated)
+scenario = "no-participants"</v>
       </c>
       <c r="D280" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
@@ -15454,7 +15806,7 @@
       <c r="S280" s="94"/>
       <c r="T280"/>
     </row>
-    <row r="281" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="281" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A281" s="105" t="str">
         <v>UTC177</v>
       </c>
@@ -15464,7 +15816,10 @@
 3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C281" s="107" t="str">
-        <v>scenario="no-chair"</v>
+        <v>meetingId = 019d3f1c-36f1-7155-9e6f-a411a8655897 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019203ec-5cfa-7c3a-91d1-a1aea3859e62 (generated)
+scenario = "no-chair"</v>
       </c>
       <c r="D281" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
@@ -15496,7 +15851,7 @@
       <c r="S281" s="94"/>
       <c r="T281"/>
     </row>
-    <row r="282" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="282" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A282" s="105" t="str">
         <v>UTC178</v>
       </c>
@@ -15506,7 +15861,10 @@
 3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C282" s="107" t="str">
-        <v>scenario="multiple-chairs"</v>
+        <v>meetingId = 0198224d-6531-7a69-8c09-ca7735eef330 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019b894a-4128-74cc-a192-dc27efda9810 (generated)
+scenario = "multiple-chairs"</v>
       </c>
       <c r="D282" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
@@ -15538,7 +15896,7 @@
       <c r="S282" s="94"/>
       <c r="T282"/>
     </row>
-    <row r="283" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="283" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A283" s="105" t="str">
         <v>UTC179</v>
       </c>
@@ -15548,7 +15906,10 @@
 3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C283" s="107" t="str">
-        <v>scenario="inactive-chair"</v>
+        <v>meetingId = 01946293-d954-7099-9e72-09fff0370277 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 0191ccc5-c4bb-7dfb-939c-2e16c6566d68 (generated)
+scenario = "inactive-chair"</v>
       </c>
       <c r="D283" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
@@ -15580,7 +15941,7 @@
       <c r="S283" s="94"/>
       <c r="T283"/>
     </row>
-    <row r="284" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="284" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A284" s="105" t="str">
         <v>UTC180</v>
       </c>
@@ -15590,7 +15951,10 @@
 3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C284" s="107" t="str">
-        <v>scenario="no-secretary"</v>
+        <v>meetingId = 019cc508-0a73-79ec-95d3-3ced329dd4af (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 019530f4-d143-7e90-90fd-8c453d95c6e4 (generated)
+scenario = "no-secretary"</v>
       </c>
       <c r="D284" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
@@ -15622,7 +15986,7 @@
       <c r="S284" s="94"/>
       <c r="T284"/>
     </row>
-    <row r="285" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="285" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A285" s="105" t="str">
         <v>UTC181</v>
       </c>
@@ -15632,7 +15996,10 @@
 3. switch (scenario) { case "no-participants": meeting.Participants.Clear(); break; case "no-chair": meeting.Participants.Remove(meeting.Parti….</v>
       </c>
       <c r="C285" s="107" t="str">
-        <v>scenario="inactive-secretaries"</v>
+        <v>meetingId = 01984806-3ccb-7b48-95eb-c26e547697b5 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Publish, AssignedApproverId = null, Reason = null, OrganizerId = null }
+actorId = 0197914c-e60d-77e0-93c3-d3739051afa5 (generated)
+scenario = "inactive-secretaries"</v>
       </c>
       <c r="D285" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.PublicationRosterNotReady
@@ -15701,7 +16068,10 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C287" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>id = 019f995b-2ba1-7bba-9e4d-dba048617281 (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Draft), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20</v>
       </c>
       <c r="D287" s="108" t="str">
         <v>Return:
@@ -15749,7 +16119,10 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C288" s="107" t="str">
-        <v>status=MeetingStatus.WaitingApproval</v>
+        <v>id = 0196df9c-8970-79ea-9530-3f656b4482c9 (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.WaitingApproval), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20</v>
       </c>
       <c r="D288" s="108" t="str">
         <v>Return:
@@ -15797,7 +16170,10 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C289" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>id = 01995cda-a96e-77f0-8b61-e52600debc2d (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Rejected), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20</v>
       </c>
       <c r="D289" s="108" t="str">
         <v>Return:
@@ -15845,7 +16221,10 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C290" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
+        <v>id = 019b41bd-d63a-7880-8a19-321edcb12d22 (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Approved), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20</v>
       </c>
       <c r="D290" s="108" t="str">
         <v>Return:
@@ -15893,7 +16272,10 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C291" s="107" t="str">
-        <v>status=MeetingStatus.Published</v>
+        <v>id = 0195a7ae-0b25-7ff1-8490-ae18df6e6661 (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Published), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20</v>
       </c>
       <c r="D291" s="108" t="str">
         <v>Return:
@@ -15963,7 +16345,11 @@
 4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C293" s="107" t="str">
-        <v>invalid="member"</v>
+        <v>id = 0198e32b-42ca-7e66-908d-fec0bfabdde9 (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Rejected), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20
+invalid = "member"</v>
       </c>
       <c r="D293" s="108" t="str">
         <v>Return:
@@ -15997,7 +16383,7 @@
       <c r="S293" s="94"/>
       <c r="T293"/>
     </row>
-    <row r="294" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="294" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A294" s="105" t="str">
         <v>UTC188</v>
       </c>
@@ -16008,7 +16394,11 @@
 4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C294" s="107" t="str">
-        <v>invalid="globalSecretary"</v>
+        <v>id = 0198d22f-4981-731f-a616-ef90891cf210 (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Rejected), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20
+invalid = "globalSecretary"</v>
       </c>
       <c r="D294" s="108" t="str">
         <v>Return:
@@ -16042,7 +16432,7 @@
       <c r="S294" s="94"/>
       <c r="T294"/>
     </row>
-    <row r="295" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="295" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A295" s="105" t="str">
         <v>UTC189</v>
       </c>
@@ -16053,7 +16443,11 @@
 4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C295" s="107" t="str">
-        <v>invalid="otherMeeting"</v>
+        <v>id = 01947747-e111-7ecf-bc2d-300a45d3ed6b (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Rejected), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20
+invalid = "otherMeeting"</v>
       </c>
       <c r="D295" s="108" t="str">
         <v>Return:
@@ -16098,7 +16492,11 @@
 4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C296" s="107" t="str">
-        <v>invalid="delegated"</v>
+        <v>id = 019d55af-1f6c-701e-816f-021fe500a65c (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Rejected), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20
+invalid = "delegated"</v>
       </c>
       <c r="D296" s="108" t="str">
         <v>Return:
@@ -16132,7 +16530,7 @@
       <c r="S296" s="94"/>
       <c r="T296"/>
     </row>
-    <row r="297" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="297" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A297" s="105" t="str">
         <v>UTC191</v>
       </c>
@@ -16143,7 +16541,11 @@
 4. meeting.Participants.Add(secretary).</v>
       </c>
       <c r="C297" s="107" t="str">
-        <v>invalid="delegationTarget"</v>
+        <v>id = 0198fcb5-0ecb-7cde-a6df-8d76d4e9785e (generated)
+actorId = Participant(GivenMeeting(MeetingStatus.Rejected), active: true, InvitationResponse.Accepted).UserId
+page = 1
+pageSize = 20
+invalid = "delegationTarget"</v>
       </c>
       <c r="D297" s="108" t="str">
         <v>Return:
@@ -16201,7 +16603,7 @@
       <c r="S298" s="90"/>
       <c r="T298"/>
     </row>
-    <row r="299" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="299" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A299" s="105" t="str">
         <v>UTC192</v>
       </c>
@@ -16211,7 +16613,9 @@
 3. meeting.Status = MeetingStatus.Published.</v>
       </c>
       <c r="C299" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
+        <v>meetingId = 019cc531-ad2a-7ad6-b271-b2da2cfc80be (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "  Lãnh đạo đi công tác  ", AssignedApproverId = null, OrganizerId = null }
+actorId = 0195f8f2-2c2f-7c28-a81a-cd826892a37d (generated)</v>
       </c>
       <c r="D299" s="108" t="str">
         <v>Return:
@@ -16270,7 +16674,7 @@
       <c r="S300" s="90"/>
       <c r="T300"/>
     </row>
-    <row r="301" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="301" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A301" s="105" t="str">
         <v>UTC193</v>
       </c>
@@ -16279,7 +16683,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C301" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
+        <v>meetingId = 01933f06-a574-7cb7-a8d1-5b391d8df1bb (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "Gộp vào họp tháng", AssignedApproverId = null, OrganizerId = null }
+actorId = 01974ba8-6f2c-753f-a55e-a676388833af (generated)</v>
       </c>
       <c r="D301" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -16335,7 +16741,7 @@
       <c r="S302" s="90"/>
       <c r="T302"/>
     </row>
-    <row r="303" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="303" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A303" s="105" t="str">
         <v>UTC194</v>
       </c>
@@ -16344,7 +16750,10 @@
 2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C303" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>meetingId = 01930d66-fed5-7aaf-81b1-6de19eee8399 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "Không cần nữa", AssignedApproverId = null, OrganizerId = null }
+actorId = 019dda72-a8f0-7881-932f-8b9934e604e3 (generated)
+status = MeetingStatus.Draft</v>
       </c>
       <c r="D303" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -16352,7 +16761,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E303" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F303" s="105" t="str">
         <v>Pending</v>
@@ -16376,7 +16785,7 @@
       <c r="S303" s="94"/>
       <c r="T303"/>
     </row>
-    <row r="304" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="304" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A304" s="105" t="str">
         <v>UTC195</v>
       </c>
@@ -16385,7 +16794,10 @@
 2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C304" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>meetingId = 019f8172-b18c-7f3a-bd77-d352661a583a (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "Không cần nữa", AssignedApproverId = null, OrganizerId = null }
+actorId = 019b935c-869d-7191-8b04-a23c30c74416 (generated)
+status = MeetingStatus.Rejected</v>
       </c>
       <c r="D304" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -16393,7 +16805,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E304" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F304" s="105" t="str">
         <v>Pending</v>
@@ -16417,7 +16829,7 @@
       <c r="S304" s="94"/>
       <c r="T304"/>
     </row>
-    <row r="305" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="305" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A305" s="105" t="str">
         <v>UTC196</v>
       </c>
@@ -16426,7 +16838,10 @@
 2. meeting: prepared by GivenMeeting (status).</v>
       </c>
       <c r="C305" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
+        <v>meetingId = 019b38c7-e485-773b-ab08-6c43f7006316 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "Không cần nữa", AssignedApproverId = null, OrganizerId = null }
+actorId = 0199cbdf-7c4b-7c2e-84fb-3beeb11a39e9 (generated)
+status = MeetingStatus.Approved</v>
       </c>
       <c r="D305" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Success
@@ -16434,7 +16849,7 @@
 Log Message: N/A</v>
       </c>
       <c r="E305" s="109" t="str">
-        <v>Normal</v>
+        <v>Boundary</v>
       </c>
       <c r="F305" s="105" t="str">
         <v>Pending</v>
@@ -16482,7 +16897,7 @@
       <c r="S306" s="90"/>
       <c r="T306"/>
     </row>
-    <row r="307" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="307" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A307" s="105" t="str">
         <v>UTC197</v>
       </c>
@@ -16492,7 +16907,10 @@
 3. meeting.Status = status.</v>
       </c>
       <c r="C307" s="107" t="str">
-        <v>status=MeetingStatus.InProgress</v>
+        <v>meetingId = 0192bfe9-d1cf-79db-81a3-09ee689a8318 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "Muộn rồi", AssignedApproverId = null, OrganizerId = null }
+actorId = 0192a4fe-a2e3-72a1-ba73-3c2a3bf8464e (generated)
+status = MeetingStatus.InProgress</v>
       </c>
       <c r="D307" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -16524,7 +16942,7 @@
       <c r="S307" s="94"/>
       <c r="T307"/>
     </row>
-    <row r="308" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="308" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A308" s="105" t="str">
         <v>UTC198</v>
       </c>
@@ -16534,7 +16952,10 @@
 3. meeting.Status = status.</v>
       </c>
       <c r="C308" s="107" t="str">
-        <v>status=MeetingStatus.Ended</v>
+        <v>meetingId = 01978efa-b6d2-77f8-8ab0-0d0fab242232 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "Muộn rồi", AssignedApproverId = null, OrganizerId = null }
+actorId = 0194d2f3-4c3f-7d41-8de7-6b72e9c6c92b (generated)
+status = MeetingStatus.Ended</v>
       </c>
       <c r="D308" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -16566,7 +16987,7 @@
       <c r="S308" s="94"/>
       <c r="T308"/>
     </row>
-    <row r="309" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="309" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A309" s="105" t="str">
         <v>UTC199</v>
       </c>
@@ -16576,7 +16997,10 @@
 3. meeting.Status = status.</v>
       </c>
       <c r="C309" s="107" t="str">
-        <v>status=MeetingStatus.Cancelled</v>
+        <v>meetingId = 01923817-2516-77d6-9a6a-098d305ade3c (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "Muộn rồi", AssignedApproverId = null, OrganizerId = null }
+actorId = 0194b851-6fea-7aab-b809-e9b50619f6b6 (generated)
+status = MeetingStatus.Cancelled</v>
       </c>
       <c r="D309" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.StatusConflict
@@ -16632,7 +17056,7 @@
       <c r="S310" s="90"/>
       <c r="T310"/>
     </row>
-    <row r="311" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="311" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A311" s="105" t="str">
         <v>UTC200</v>
       </c>
@@ -16641,7 +17065,9 @@
 2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C311" s="107" t="str">
-        <v>reason=null</v>
+        <v>meetingId = 019f6b71-2470-7b04-b99a-819777a95e4a (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = null, AssignedApproverId = null, OrganizerId = null }
+actorId = 019b5110-ec87-78b0-b693-acf7d5a488c2 (generated)</v>
       </c>
       <c r="D311" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
@@ -16673,7 +17099,7 @@
       <c r="S311" s="94"/>
       <c r="T311"/>
     </row>
-    <row r="312" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="312" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A312" s="105" t="str">
         <v>UTC201</v>
       </c>
@@ -16682,7 +17108,9 @@
 2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C312" s="107" t="str">
-        <v>reason=""</v>
+        <v>meetingId = 0197320e-615e-7106-9aab-feb57ab3cff0 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "", AssignedApproverId = null, OrganizerId = null }
+actorId = 0195ffe9-5973-79a7-9364-36e578d70d1b (generated)</v>
       </c>
       <c r="D312" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
@@ -16714,7 +17142,7 @@
       <c r="S312" s="94"/>
       <c r="T312"/>
     </row>
-    <row r="313" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="313" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A313" s="105" t="str">
         <v>UTC202</v>
       </c>
@@ -16723,7 +17151,9 @@
 2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C313" s="107" t="str">
-        <v>reason="   "</v>
+        <v>meetingId = 019eda0b-c198-7f17-84fd-7ce1818a8133 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "   ", AssignedApproverId = null, OrganizerId = null }
+actorId = 019a910b-5825-7914-abc5-d70f9f579129 (generated)</v>
       </c>
       <c r="D313" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.CancellationReasonRequired
@@ -16779,7 +17209,7 @@
       <c r="S314" s="90"/>
       <c r="T314"/>
     </row>
-    <row r="315" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="315" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A315" s="105" t="str">
         <v>UTC203</v>
       </c>
@@ -16788,7 +17218,9 @@
 2. meeting: prepared by GivenMeeting.</v>
       </c>
       <c r="C315" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _organizerId</v>
+        <v>meetingId = 01997025-68b9-755b-ba9a-9f6367494bfe (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = 'a' × 1001, AssignedApproverId = null, OrganizerId = null }
+actorId = 019d4892-bf29-75fb-b27f-c8b937f9ec30 (generated)</v>
       </c>
       <c r="D315" s="108" t="str">
         <v>Return:
@@ -16846,7 +17278,7 @@
       <c r="S316" s="90"/>
       <c r="T316"/>
     </row>
-    <row r="317" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="317" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A317" s="105" t="str">
         <v>UTC204</v>
       </c>
@@ -16855,7 +17287,9 @@
 2. meeting: prepared by GivenMeeting (MeetingStatus.WaitingApproval).</v>
       </c>
       <c r="C317" s="107" t="str">
-        <v>meeting.Id; new MeetingTransitionCommand(MeetingTransitionAction.Cancel, Reason:…; _approverId</v>
+        <v>meetingId = 019c3868-75cf-7122-8744-fd5e6fdb8796 (generated)
+command = MeetingTransitionCommand { Action = MeetingTransitionAction.Cancel, Reason = "Không phải việc của tôi", AssignedApproverId = null, OrganizerId = null }
+actorId = 019dbb00-8ced-7df6-95db-67a6b741366c (generated)</v>
       </c>
       <c r="D317" s="108" t="str">
         <v>Return: MeetingWorkflowOutcome.Forbidden
@@ -16905,7 +17339,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17312,7 +17746,7 @@
       <c r="S12" s="90"/>
       <c r="T12"/>
     </row>
-    <row r="13" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="13" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A13" s="105" t="str">
         <v>UTC001</v>
       </c>
@@ -17323,7 +17757,10 @@
         <v>N/A</v>
       </c>
       <c r="D13" s="108" t="str">
-        <v>Return: exactly one item
+        <v>Return:
+1. migration.UpOperations.OfType&lt;SqlOperation&gt;(): exactly one item
+2. sql: contains "SET pushed_at = created_at"
+3. operation =&gt; operation.Name == "action_url": does not contain migration.UpOperations.OfType&lt;AddColumnOperation&gt;()
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -17370,7 +17807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17790,7 +18227,7 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C13" s="107" t="str">
-        <v>s</v>
+        <v>s = f.Seed()</v>
       </c>
       <c r="D13" s="108" t="str">
         <v>Return: completes without error
@@ -17855,7 +18292,7 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C15" s="107" t="str">
-        <v>change="removed"; expected="MSG259"</v>
+        <v>id = f.Seed().Url + "/participants/chair-handover-candidates"</v>
       </c>
       <c r="D15" s="108" t="str">
         <v>Return: "\"participants-0\""
@@ -17896,7 +18333,7 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C16" s="107" t="str">
-        <v>change="secretary"; expected="MSG259"</v>
+        <v>id = f.Seed().Url + "/participants/chair-handover-candidates"</v>
       </c>
       <c r="D16" s="108" t="str">
         <v>Return: "\"participants-0\""
@@ -17937,7 +18374,7 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C17" s="107" t="str">
-        <v>change="unrelated"; expected="MSG275"</v>
+        <v>id = f.Seed().Url + "/participants/chair-handover-candidates"</v>
       </c>
       <c r="D17" s="108" t="str">
         <v>Return: "\"participants-0\""
@@ -17978,7 +18415,7 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C18" s="107" t="str">
-        <v>change="ended"; expected="MSG260"</v>
+        <v>id = f.Seed().Url + "/participants/chair-handover-candidates"</v>
       </c>
       <c r="D18" s="108" t="str">
         <v>Return: "\"participants-0\""
@@ -18044,7 +18481,7 @@
 3. f.Queries.RejectUserUpdates = true.</v>
       </c>
       <c r="C20" s="107" t="str">
-        <v>s.Chair</v>
+        <v>id = f.Seed().Chair</v>
       </c>
       <c r="D20" s="108" t="str">
         <v>Return:
@@ -18117,7 +18554,8 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C22" s="107" t="str">
-        <v>postFirst=true</v>
+        <v>s = f.Seed()
+postFirst = true</v>
       </c>
       <c r="D22" s="108" t="str">
         <v>Return: completes without error
@@ -18162,7 +18600,8 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>postFirst=false</v>
+        <v>s = f.Seed()
+postFirst = false</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return: completes without error
@@ -18294,7 +18733,7 @@
 3. f.Queries.RejectUserUpdates = true.</v>
       </c>
       <c r="C27" s="107" t="str">
-        <v>s.Secretary</v>
+        <v>id = f.Seed().Secretary</v>
       </c>
       <c r="D27" s="108" t="str">
         <v>Return:
@@ -18352,7 +18791,7 @@
       <c r="S28" s="90"/>
       <c r="T28"/>
     </row>
-    <row r="29" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="29" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A29" s="105" t="str">
         <v>UTC011</v>
       </c>
@@ -18362,7 +18801,8 @@
 3. body = new { changes = new[] { new { participantId = s.ChairAssignment, role = "Member" }, new {….</v>
       </c>
       <c r="C29" s="107" t="str">
-        <v>Write(secretary, s.Url + "/participants/assignments", HttpMethod.Put,…; Write(secretary, s.Url + "/participants/assignments", HttpMethod.Put,…</v>
+        <v>Write(f.Client(f.Seed(MeetingStatus.Approved).Secretary), f.Seed(MeetingStatus.Approved).Url + "/participants/assignments", HttpMethod.Put, { changes = [{ participantId = f.Seed(MeetingStatus.Approve…
+Write(f.Client(f.Seed(MeetingStatus.Approved).Secretary), f.Seed(MeetingStatus.Approved).Url + "/participants/assignments", HttpMethod.Put, { changes = [{ participantId = f.Seed(MeetingStatus.Approve…</v>
       </c>
       <c r="D29" s="108" t="str">
         <v>Return:
@@ -18420,7 +18860,7 @@
       <c r="S30" s="90"/>
       <c r="T30"/>
     </row>
-    <row r="31" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="31" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A31" s="105" t="str">
         <v>UTC012</v>
       </c>
@@ -18429,7 +18869,8 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C31" s="107" t="str">
-        <v>Write(member, s.Url + "/invitation-response", HttpMethod.Put, new { r…; Write(secretary, s.Url + $"/participants/{s.MemberAssignment}", HttpM…</v>
+        <v>Write(f.Client(f.Seed().Member), f.Seed().Url + "/invitation-response", HttpMethod.Put, { response = "Accepted" })
+Write(f.Client(f.Seed().Secretary), f.Seed().Url + $"/participants/{s.MemberAssignment}", HttpMethod.Delete)</v>
       </c>
       <c r="D31" s="108" t="str">
         <v>Return: HTTP 200 OK
@@ -18494,7 +18935,9 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C33" s="107" t="str">
-        <v>Write(secretary, s.Url + "/participants", HttpMethod.Post, new { user…; 201; "MSG96"</v>
+        <v>response = Write(f.Client(f.Seed().Secretary), f.Seed().Url + "/participants", HttpMethod.Post, { userIds = [f.Seed().Organizer], role = "Member" })
+status = 201
+code = "MSG96"</v>
       </c>
       <c r="D33" s="108" t="str">
         <v>Return:
@@ -18695,7 +19138,7 @@
       <c r="S38" s="90"/>
       <c r="T38"/>
     </row>
-    <row r="39" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="39" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A39" s="105" t="str">
         <v>UTC016</v>
       </c>
@@ -18704,7 +19147,9 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C39" s="107" t="str">
-        <v>Write(chair, s.Url + "/participants/chair-handover", HttpMethod.Post,…; 200; "MSG257"</v>
+        <v>response = Write(f.Client(f.Seed().Chair), f.Seed().Url + "/participants/chair-handover", HttpMethod.Post, { newChairParticipantId = f.Seed().MemberAssignment, confirmed = true })
+status = 200
+code = "MSG257"</v>
       </c>
       <c r="D39" s="108" t="str">
         <v>Return: 2
@@ -18770,7 +19215,9 @@
 3. Guid invitationId.</v>
       </c>
       <c r="C41" s="107" t="str">
-        <v>Write(secretary, s.Url + "/participants", HttpMethod.Post, new { user…; 201; "MSG96"</v>
+        <v>response = Write(f.Client(f.Seed().Secretary), f.Seed().Url + "/participants", HttpMethod.Post, { userIds = [f.Seed().Outsider], role = "Member" })
+status = 201
+code = "MSG96"</v>
       </c>
       <c r="D41" s="108" t="str">
         <v>Return:
@@ -18842,7 +19289,9 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C43" s="107" t="str">
-        <v>Write(secretary, s.Url + "/participants", HttpMethod.Post, new { user…; 201; "MSG96"</v>
+        <v>response = Write(f.Client(f.Seed().Secretary), f.Seed().Url + "/participants", HttpMethod.Post, { userIds = [f.Seed().Outsider], role = "Member" })
+status = 201
+code = "MSG96"</v>
       </c>
       <c r="D43" s="108" t="str">
         <v>Return:
@@ -18901,7 +19350,7 @@
       <c r="S44" s="90"/>
       <c r="T44"/>
     </row>
-    <row r="45" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="45" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A45" s="105" t="str">
         <v>UTC019</v>
       </c>
@@ -18910,7 +19359,9 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C45" s="107" t="str">
-        <v>Write(secretary, s.Url + "/participants", HttpMethod.Post, new { user…; 201; "MSG96"</v>
+        <v>response = Write(f.Client(f.Seed().Secretary), f.Seed().Url + "/participants", HttpMethod.Post, { userIds = [f.Seed().Outsider], role = "Member" }, Tag(f.Client(f.Seed().Secretary), f.Seed().Url))
+status = 201
+code = "MSG96"</v>
       </c>
       <c r="D45" s="108" t="str">
         <v>Return: "Phòng họp trực tuyến TrustCabinet"
@@ -19047,7 +19498,9 @@
 3. _options.Smtp.Enabled = false.</v>
       </c>
       <c r="C49" s="107" t="str">
-        <v>Write(secretary, s.Url + "/participants", HttpMethod.Post, new { user…; 201; "MSG96"</v>
+        <v>response = Write(f.Client(f.Seed().Secretary), f.Seed().Url + "/participants", HttpMethod.Post, { userIds = [f.Seed().Outsider], role = "Member" })
+status = 201
+code = "MSG96"</v>
       </c>
       <c r="D49" s="108" t="str">
         <v>Return:
@@ -19194,7 +19647,7 @@
 4. Guid ownerId.</v>
       </c>
       <c r="C53" s="107" t="str">
-        <v>guest=false</v>
+        <v>id = f.Seed().Secretary</v>
       </c>
       <c r="D53" s="108" t="str">
         <v>Return:
@@ -19241,7 +19694,7 @@
 4. Guid ownerId.</v>
       </c>
       <c r="C54" s="107" t="str">
-        <v>guest=true</v>
+        <v>id = f.Seed().Secretary</v>
       </c>
       <c r="D54" s="108" t="str">
         <v>Return:
@@ -19310,7 +19763,7 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C56" s="107" t="str">
-        <v>legacyEmailOnly=false</v>
+        <v>legacyEmailOnly = false</v>
       </c>
       <c r="D56" s="108" t="str">
         <v>Return:
@@ -19355,7 +19808,7 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C57" s="107" t="str">
-        <v>legacyEmailOnly=true</v>
+        <v>legacyEmailOnly = true</v>
       </c>
       <c r="D57" s="108" t="str">
         <v>Return:
@@ -19426,7 +19879,8 @@
 4. links: a new Links is prepared.</v>
       </c>
       <c r="C59" s="107" t="str">
-        <v>probe=true; cancellationException=false</v>
+        <v>probe = true
+cancellationException = false</v>
       </c>
       <c r="D59" s="108" t="str">
         <v>Return:
@@ -19474,7 +19928,8 @@
 4. links: a new Links is prepared.</v>
       </c>
       <c r="C60" s="107" t="str">
-        <v>probe=false; cancellationException=false</v>
+        <v>probe = false
+cancellationException = false</v>
       </c>
       <c r="D60" s="108" t="str">
         <v>Return:
@@ -19522,7 +19977,8 @@
 4. links: a new Links is prepared.</v>
       </c>
       <c r="C61" s="107" t="str">
-        <v>probe=true; cancellationException=true</v>
+        <v>probe = true
+cancellationException = true</v>
       </c>
       <c r="D61" s="108" t="str">
         <v>Return:
@@ -19570,7 +20026,8 @@
 4. links: a new Links is prepared.</v>
       </c>
       <c r="C62" s="107" t="str">
-        <v>probe=false; cancellationException=true</v>
+        <v>probe = false
+cancellationException = true</v>
       </c>
       <c r="D62" s="108" t="str">
         <v>Return:
@@ -19642,7 +20099,9 @@
 4. processor: a new MeetingInvitationDispatchProcessor is prepared.</v>
       </c>
       <c r="C64" s="107" t="str">
-        <v>Write(secretary, s.Url + "/participants", HttpMethod.Post, new { user…; 201; "MSG96"</v>
+        <v>response = Write(f.Client(f.Seed().Secretary), f.Seed().Url + "/participants", HttpMethod.Post, { userIds = [f.Seed().Outsider], role = "Member" }, Tag(f.Client(f.Seed().Secretary), f.Seed().Url))
+status = 201
+code = "MSG96"</v>
       </c>
       <c r="D64" s="108" t="str">
         <v>Return:
@@ -19781,7 +20240,9 @@
 2. Test data is seeded (MeetingStatus.Approved).</v>
       </c>
       <c r="C68" s="107" t="str">
-        <v>Write(secretary, s.Url + "/guest-invitations", HttpMethod.Post, new {…; 201; "MSG96"</v>
+        <v>response = Write(f.Client(f.Seed(MeetingStatus.Approved).Secretary), f.Seed(MeetingStatus.Approved).Url + "/guest-invitations", HttpMethod.Post, { invitedName = "Guest", email = $"{Guid.NewGuid():N}@guests.test…
+status = 201
+code = "MSG96"</v>
       </c>
       <c r="D68" s="108" t="str">
         <v>Return:
@@ -19923,7 +20384,7 @@
         <v>1. ParticipantDelivery runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C72" s="107" t="str">
-        <v>new(Guid.NewGuid(), Guid.NewGuid(), Guid.NewGuid()); default</v>
+        <v>identity = MeetingGuestSession { MeetingId = 0195b6a7-4a16-7786-938c-5212ee711f60 (generated), InvitationId = 01930d07-213c-7d6a-8a9f-4a04d407c2be (generated), SessionId = 019be89e-7c20-7d9e-9ab9-3f6cb7a9ef37 (…</v>
       </c>
       <c r="D72" s="108" t="str">
         <v>Return:
@@ -19994,7 +20455,7 @@
 6. Further arrangement is in the test source.</v>
       </c>
       <c r="C74" s="107" t="str">
-        <v>chair</v>
+        <v>client = f.Client(f.Seed().Chair)</v>
       </c>
       <c r="D74" s="108" t="str">
         <v>Return:
@@ -20066,7 +20527,7 @@
 3. events = Channel.CreateUnbounded&lt;ParticipantsChange&gt;().</v>
       </c>
       <c r="C76" s="107" t="str">
-        <v>member</v>
+        <v>client = f.Client(f.Seed().Member)</v>
       </c>
       <c r="D76" s="108" t="str">
         <v>Return:
@@ -20139,7 +20600,8 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C78" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>} = var actor in new[] { s.Chair, s.Secretary }
+status = MeetingStatus.Draft</v>
       </c>
       <c r="D78" s="108" t="str">
         <v>Return: completes without error
@@ -20180,7 +20642,8 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C79" s="107" t="str">
-        <v>status=MeetingStatus.Rejected</v>
+        <v>} = var actor in new[] { s.Chair, s.Secretary }
+status = MeetingStatus.Rejected</v>
       </c>
       <c r="D79" s="108" t="str">
         <v>Return: completes without error
@@ -20221,7 +20684,8 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C80" s="107" t="str">
-        <v>status=MeetingStatus.Approved</v>
+        <v>} = var actor in new[] { s.Chair, s.Secretary }
+status = MeetingStatus.Approved</v>
       </c>
       <c r="D80" s="108" t="str">
         <v>Return: completes without error
@@ -20262,7 +20726,8 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C81" s="107" t="str">
-        <v>status=MeetingStatus.Published</v>
+        <v>} = var actor in new[] { s.Chair, s.Secretary }
+status = MeetingStatus.Published</v>
       </c>
       <c r="D81" s="108" t="str">
         <v>Return: completes without error
@@ -20303,7 +20768,8 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C82" s="107" t="str">
-        <v>status=MeetingStatus.InProgress</v>
+        <v>} = var actor in new[] { s.Chair, s.Secretary }
+status = MeetingStatus.InProgress</v>
       </c>
       <c r="D82" s="108" t="str">
         <v>Return: completes without error
@@ -20368,7 +20834,9 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C84" s="107" t="str">
-        <v>status=MeetingStatus.Published</v>
+        <v>response = Write(f.Client(f.Seed(MeetingStatus.Published).Secretary), f.Seed(MeetingStatus.Published).Url + "/participants/assignments", HttpMethod.Put, object { changes = [{ participantId = f.Seed(MeetingStatu…
+status = 409
+code = "MSG256"</v>
       </c>
       <c r="D84" s="108" t="str">
         <v>Return:
@@ -20413,7 +20881,9 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C85" s="107" t="str">
-        <v>status=MeetingStatus.InProgress</v>
+        <v>response = Write(f.Client(f.Seed(MeetingStatus.InProgress).Secretary), f.Seed(MeetingStatus.InProgress).Url + "/participants/assignments", HttpMethod.Put, object { changes = [{ participantId = f.Seed(MeetingSta…
+status = 409
+code = "MSG256"</v>
       </c>
       <c r="D85" s="108" t="str">
         <v>Return:
@@ -20473,7 +20943,7 @@
       <c r="S86" s="90"/>
       <c r="T86"/>
     </row>
-    <row r="87" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="87" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A87" s="105" t="str">
         <v>UTC045</v>
       </c>
@@ -20482,7 +20952,10 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C87" s="107" t="str">
-        <v>kind="Secretary"</v>
+        <v>response = Write(f.Client(f.Seed().Chair), f.Seed().Url + "/participants/assignments", HttpMethod.Put, object { changes = [{ participantId = f.Seed().ChairAssignment, role = "Member" }, { participantId = f.Seed…
+status = 400
+code = "MSG259"
+kind = "Secretary"</v>
       </c>
       <c r="D87" s="108" t="str">
         <v>Return: completes without error
@@ -20514,7 +20987,7 @@
       <c r="S87" s="94"/>
       <c r="T87"/>
     </row>
-    <row r="88" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="88" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A88" s="105" t="str">
         <v>UTC046</v>
       </c>
@@ -20523,7 +20996,10 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C88" s="107" t="str">
-        <v>kind="Inactive"</v>
+        <v>response = Write(f.Client(f.Seed().Chair), f.Seed().Url + "/participants/assignments", HttpMethod.Put, object { changes = [{ participantId = f.Seed().ChairAssignment, role = "Member" }, { participantId = f.Seed…
+status = 400
+code = "MSG259"
+kind = "Inactive"</v>
       </c>
       <c r="D88" s="108" t="str">
         <v>Return: completes without error
@@ -20555,7 +21031,7 @@
       <c r="S88" s="94"/>
       <c r="T88"/>
     </row>
-    <row r="89" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="89" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A89" s="105" t="str">
         <v>UTC047</v>
       </c>
@@ -20564,7 +21040,10 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C89" s="107" t="str">
-        <v>kind="Removed"</v>
+        <v>response = Write(f.Client(f.Seed().Chair), f.Seed().Url + "/participants/assignments", HttpMethod.Put, object { changes = [{ participantId = f.Seed().ChairAssignment, role = "Member" }, { participantId = f.Seed…
+status = 400
+code = "MSG259"
+kind = "Removed"</v>
       </c>
       <c r="D89" s="108" t="str">
         <v>Return: completes without error
@@ -20596,7 +21075,7 @@
       <c r="S89" s="94"/>
       <c r="T89"/>
     </row>
-    <row r="90" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="90" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A90" s="105" t="str">
         <v>UTC048</v>
       </c>
@@ -20605,7 +21084,10 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C90" s="107" t="str">
-        <v>kind="Missing"</v>
+        <v>response = Write(f.Client(f.Seed().Chair), f.Seed().Url + "/participants/assignments", HttpMethod.Put, object { changes = [{ participantId = f.Seed().ChairAssignment, role = "Member" }, { participantId = 019251…
+status = 400
+code = "MSG259"
+kind = "Missing"</v>
       </c>
       <c r="D90" s="108" t="str">
         <v>Return: completes without error
@@ -20670,7 +21152,7 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C92" s="107" t="str">
-        <v>status=MeetingStatus.Draft</v>
+        <v>id = f.Seed(MeetingStatus.Draft).Member</v>
       </c>
       <c r="D92" s="108" t="str">
         <v>Return:
@@ -20714,7 +21196,7 @@
 2. Test data is seeded (status).</v>
       </c>
       <c r="C93" s="107" t="str">
-        <v>status=MeetingStatus.WaitingApproval</v>
+        <v>id = f.Seed(MeetingStatus.WaitingApproval).Member</v>
       </c>
       <c r="D93" s="108" t="str">
         <v>Return:
@@ -20773,7 +21255,7 @@
       <c r="S94" s="90"/>
       <c r="T94"/>
     </row>
-    <row r="95" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="95" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A95" s="105" t="str">
         <v>UTC051</v>
       </c>
@@ -20782,7 +21264,9 @@
 2. Test data is seeded (MeetingStatus.Draft).</v>
       </c>
       <c r="C95" s="107" t="str">
-        <v>Write(chair, s.Url + "/participants", HttpMethod.Post, new { userIds…; 201; "MSG96"</v>
+        <v>response = Write(f.Client(f.Seed(MeetingStatus.Draft).Chair), f.Seed(MeetingStatus.Draft).Url + "/participants", HttpMethod.Post, { userIds = [f.Seed(MeetingStatus.Draft).Outsider], role = "Secretary" })
+status = 201
+code = "MSG96"</v>
       </c>
       <c r="D95" s="108" t="str">
         <v>Return: completes without error
@@ -20917,7 +21401,7 @@
 3. context = secretary.GetFromJsonAsync&lt;JsonElement&gt;(s.Url + "/participant-context").</v>
       </c>
       <c r="C99" s="107" t="str">
-        <v>s.Secretary</v>
+        <v>id = f.Seed().Secretary</v>
       </c>
       <c r="D99" s="108" t="str">
         <v>Return:
@@ -20989,7 +21473,9 @@
 2. Test data is seeded (meeting, users and agenda from the fixture).</v>
       </c>
       <c r="C101" s="107" t="str">
-        <v>Write(member, s.Url + "/invitation-response", HttpMethod.Put, new { r…; 200; "MSG105"</v>
+        <v>response = Write(f.Client(f.Seed().Member), f.Seed().Url + "/invitation-response", HttpMethod.Put, { response = "Accepted" })
+status = 200
+code = "MSG105"</v>
       </c>
       <c r="D101" s="108" t="str">
         <v>Return:
@@ -21062,7 +21548,8 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C103" s="107" t="str">
-        <v>kind="valid"</v>
+        <v>! = kind == "inactive"
+kind = "valid"</v>
       </c>
       <c r="D103" s="108" t="str">
         <v>Return:
@@ -21110,7 +21597,8 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C104" s="107" t="str">
-        <v>kind="missing"</v>
+        <v>! = kind == "inactive"
+kind = "missing"</v>
       </c>
       <c r="D104" s="108" t="str">
         <v>Return:
@@ -21158,7 +21646,8 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C105" s="107" t="str">
-        <v>kind="empty"</v>
+        <v>! = kind == "inactive"
+kind = "empty"</v>
       </c>
       <c r="D105" s="108" t="str">
         <v>Return:
@@ -21206,7 +21695,8 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C106" s="107" t="str">
-        <v>kind="no-chair"</v>
+        <v>! = kind == "inactive"
+kind = "no-chair"</v>
       </c>
       <c r="D106" s="108" t="str">
         <v>Return:
@@ -21254,7 +21744,8 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C107" s="107" t="str">
-        <v>kind="two-chairs"</v>
+        <v>! = kind == "inactive"
+kind = "two-chairs"</v>
       </c>
       <c r="D107" s="108" t="str">
         <v>Return:
@@ -21302,7 +21793,8 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C108" s="107" t="str">
-        <v>kind="duplicate"</v>
+        <v>! = kind == "inactive"
+kind = "duplicate"</v>
       </c>
       <c r="D108" s="108" t="str">
         <v>Return:
@@ -21350,7 +21842,7 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C109" s="107" t="str">
-        <v>kind="inactive"</v>
+        <v>! = kind == "inactive"</v>
       </c>
       <c r="D109" s="108" t="str">
         <v>Return:
@@ -21398,7 +21890,8 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C110" s="107" t="str">
-        <v>kind="unknown"</v>
+        <v>! = kind == "inactive"
+kind = "unknown"</v>
       </c>
       <c r="D110" s="108" t="str">
         <v>Return:
@@ -21446,7 +21939,8 @@
 3. service = new MeetingService(new MeetingRepository(db), NullLogger&lt;MeetingService&gt;.Instance, f.Cloc….</v>
       </c>
       <c r="C111" s="107" t="str">
-        <v>kind="bad-role"</v>
+        <v>! = kind == "inactive"
+kind = "bad-role"</v>
       </c>
       <c r="D111" s="108" t="str">
         <v>Return:
@@ -21698,7 +22192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -22113,7 +22607,8 @@
         <v>1. SpeakerMatcher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C13" s="107" t="str">
-        <v>[1, 2, 3]; [2, 4, 6]</v>
+        <v>a = [1, 2, 3]
+b = [2, 4, 6]</v>
       </c>
       <c r="D13" s="108" t="str">
         <v>Return:
@@ -22173,7 +22668,7 @@
       <c r="S14" s="90"/>
       <c r="T14"/>
     </row>
-    <row r="15" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="15" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A15" s="105" t="str">
         <v>UTC002</v>
       </c>
@@ -22181,7 +22676,8 @@
         <v>1. SpeakerMatcher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C15" s="107" t="str">
-        <v>[new("SPEAKER_00", 1000, [1f, 1f])]; C(Lan, [1f, -0.6f])</v>
+        <v>speakers = [{ "SPEAKER_00", 1000, [1f, 1f] }]
+candidates = SpeakerMatcher.Candidate { UserId = Guid.NewGuid(), Minh = Guid.NewGuid(), Embedding = [1f, -0.6f] }</v>
       </c>
       <c r="D15" s="108" t="str">
         <v>Return: empty
@@ -22237,7 +22733,7 @@
       <c r="S16" s="90"/>
       <c r="T16"/>
     </row>
-    <row r="17" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="17" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A17" s="105" t="str">
         <v>UTC003</v>
       </c>
@@ -22245,7 +22741,9 @@
         <v>1. SpeakerMatcher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C17" s="107" t="str">
-        <v>[new("SPEAKER_00", 1000, [1f, 1f])]; C(Lan, [1f, 0.9f]); C(Minh, [0.9f, 1f])</v>
+        <v>[{ "SPEAKER_00", 1000, [1f, 1f] }]
+SpeakerMatcher.Candidate { UserId = Guid.NewGuid(), Minh = Guid.NewGuid(), Embedding = [1f, 0.9f] }
+SpeakerMatcher.Candidate { UserId = Minh, Embedding = [0.9f, 1f] }</v>
       </c>
       <c r="D17" s="108" t="str">
         <v>Return: empty
@@ -22301,7 +22799,7 @@
       <c r="S18" s="90"/>
       <c r="T18"/>
     </row>
-    <row r="19" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="19" spans="1:20" s="93" customFormat="1" ht="269.0" outlineLevel="1" customHeight="1">
       <c r="A19" s="105" t="str">
         <v>UTC004</v>
       </c>
@@ -22309,7 +22807,10 @@
         <v>1. SpeakerMatcher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C19" s="107" t="str">
-        <v>[new("SPEAKER_00", 1000, [1f, 0.05f]), new("SPEAKER_01", 1000, [0.95f…; C(Lan, [0.6f, 0.8f]); C(Lan, [1f, 0f]); C(Minh, [0f, 1f])</v>
+        <v>[{ "SPEAKER_00", 1000, [1f, 0.05f] }, { "SPEAKER_01", 1000, [0.95f, 0.1f] }, { "SPEAKER_02", 1000, [0f, 1f] }]
+SpeakerMatcher.Candidate { UserId = Guid.NewGuid(), Minh = Guid.NewGuid(), Embedding = [0.6f, 0.8f] }
+SpeakerMatcher.Candidate { UserId = Guid.NewGuid(), Minh = Guid.NewGuid(), Embedding = [1f, 0f] }
+SpeakerMatcher.Candidate { UserId = Minh, Embedding = [0f, 1f] }</v>
       </c>
       <c r="D19" s="108" t="str">
         <v>Return:
@@ -22368,7 +22869,7 @@
       <c r="S20" s="90"/>
       <c r="T20"/>
     </row>
-    <row r="21" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="21" spans="1:20" s="93" customFormat="1" ht="211.0" outlineLevel="1" customHeight="1">
       <c r="A21" s="105" t="str">
         <v>UTC005</v>
       </c>
@@ -22376,7 +22877,9 @@
         <v>1. SpeakerMatcher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C21" s="107" t="str">
-        <v>[new("SPEAKER_00", 1000, [1f, 0f]), new("SPEAKER_01", 1000, [0.6f, 0.…; C(Lan, [1f, 0f]); C(Lan, [0.6f, 0.8f])</v>
+        <v>[{ "SPEAKER_00", 1000, [1f, 0f] }, { "SPEAKER_01", 1000, [0.6f, 0.8f] }]
+SpeakerMatcher.Candidate { UserId = Guid.NewGuid(), Minh = Guid.NewGuid(), Embedding = [1f, 0f] }
+SpeakerMatcher.Candidate { UserId = Guid.NewGuid(), Minh = Guid.NewGuid(), Embedding = [0.6f, 0.8f] }</v>
       </c>
       <c r="D21" s="108" t="str">
         <v>Return:
@@ -22442,7 +22945,7 @@
         <v>1. SpeakerMatcher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>[("SPEAKER_00", Lan, 0.70, null), ("SPEAKER_01", Lan, 0.82, null), ("…</v>
+        <v>voices = [("SPEAKER_00", Lan, 0.70, null), ("SPEAKER_01", Lan, 0.82, null), ("SPEAKER_02", Minh, 0.90, null)]</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return:
@@ -22494,7 +22997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -23100,7 +23603,7 @@
       <c r="S18" s="90"/>
       <c r="T18"/>
     </row>
-    <row r="19" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="19" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A19" s="105" t="str">
         <v>UTC004</v>
       </c>
@@ -23108,7 +23611,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C19" s="107" t="str">
-        <v>new NewUser("Trần Chủ Toạ", "chutoa@trustcabinet.local", ValidPasswor…; _actorId</v>
+        <v>request = NewUser { FullName = "Trần Chủ Toạ", Email = "chutoa@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7202-7945-be13-d2022cf25203 }
+actorId = 0196d335-4baa-70b9-87df-a6f0e3cdd694 (generated)</v>
       </c>
       <c r="D19" s="108" t="str">
         <v>Return:
@@ -23169,7 +23673,7 @@
       <c r="S20" s="90"/>
       <c r="T20"/>
     </row>
-    <row r="21" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="21" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A21" s="105" t="str">
         <v>UTC005</v>
       </c>
@@ -23179,7 +23683,8 @@
 3. service: a new UserService is prepared.</v>
       </c>
       <c r="C21" s="107" t="str">
-        <v>new NewUser("Trần Chủ Toạ", "chutoa@trustcabinet.local", ValidPasswor…; _actorId</v>
+        <v>request = NewUser { FullName = "Trần Chủ Toạ", Email = "chutoa@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7202-7945-be13-d2022cf25203 }
+actorId = 019a1e41-6dc8-7dcb-9d9b-0f946077fc39 (generated)</v>
       </c>
       <c r="D21" s="108" t="str">
         <v>Return:
@@ -23239,7 +23744,7 @@
       <c r="S22" s="90"/>
       <c r="T22"/>
     </row>
-    <row r="23" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="23" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A23" s="105" t="str">
         <v>UTC006</v>
       </c>
@@ -23247,7 +23752,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>new NewUser("Trần Chủ Toạ", "chutoa@trustcabinet.local", ValidPasswor…; _actorId</v>
+        <v>request = NewUser { FullName = "Trần Chủ Toạ", Email = "chutoa@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7202-7945-be13-d2022cf25203 }
+actorId = 019bd821-2754-75c8-a9d9-7c320ccf77ff (generated)</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return:
@@ -23306,7 +23812,7 @@
       <c r="S24" s="90"/>
       <c r="T24"/>
     </row>
-    <row r="25" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="25" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A25" s="105" t="str">
         <v>UTC007</v>
       </c>
@@ -23314,7 +23820,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C25" s="107" t="str">
-        <v>fullName=""; email="hople@trustcabinet.local"; field="fullName"</v>
+        <v>request = NewUser { FullName = "", Email = "hople@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 01975dae-bf4a-7a8c-8c87-9d64ac66bc91 (generated)</v>
       </c>
       <c r="D25" s="108" t="str">
         <v>Return:
@@ -23349,7 +23856,7 @@
       <c r="S25" s="94"/>
       <c r="T25"/>
     </row>
-    <row r="26" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="26" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A26" s="105" t="str">
         <v>UTC008</v>
       </c>
@@ -23357,7 +23864,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C26" s="107" t="str">
-        <v>fullName="   "; email="hople@trustcabinet.local"; field="fullName"</v>
+        <v>request = NewUser { FullName = "   ", Email = "hople@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 0196f7c8-4247-7415-a2b9-6cb6b632377e (generated)</v>
       </c>
       <c r="D26" s="108" t="str">
         <v>Return:
@@ -23392,7 +23900,7 @@
       <c r="S26" s="94"/>
       <c r="T26"/>
     </row>
-    <row r="27" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="27" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A27" s="105" t="str">
         <v>UTC009</v>
       </c>
@@ -23400,7 +23908,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C27" s="107" t="str">
-        <v>fullName="Tên hợp lệ"; email=""; field="email"</v>
+        <v>request = NewUser { FullName = "Tên hợp lệ", Email = "", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 0191d039-a7e7-7749-bd2b-4553c888684e (generated)</v>
       </c>
       <c r="D27" s="108" t="str">
         <v>Return:
@@ -23435,7 +23944,7 @@
       <c r="S27" s="94"/>
       <c r="T27"/>
     </row>
-    <row r="28" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="28" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A28" s="105" t="str">
         <v>UTC010</v>
       </c>
@@ -23443,7 +23952,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C28" s="107" t="str">
-        <v>fullName="Tên hợp lệ"; email="khong-phai-email"; field="email"</v>
+        <v>request = NewUser { FullName = "Tên hợp lệ", Email = "khong-phai-email", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 019aa22a-8a96-7c71-9fc5-7e8fb53783e7 (generated)</v>
       </c>
       <c r="D28" s="108" t="str">
         <v>Return:
@@ -23478,7 +23988,7 @@
       <c r="S28" s="94"/>
       <c r="T28"/>
     </row>
-    <row r="29" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="29" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A29" s="105" t="str">
         <v>UTC011</v>
       </c>
@@ -23486,7 +23996,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C29" s="107" t="str">
-        <v>fullName="Tên hợp lệ"; email="thieu@ten-mien"; field="email"</v>
+        <v>request = NewUser { FullName = "Tên hợp lệ", Email = "thieu@ten-mien", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 0193561b-e99f-7404-8932-c00841d8ae29 (generated)</v>
       </c>
       <c r="D29" s="108" t="str">
         <v>Return:
@@ -23521,7 +24032,7 @@
       <c r="S29" s="94"/>
       <c r="T29"/>
     </row>
-    <row r="30" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="30" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A30" s="105" t="str">
         <v>UTC012</v>
       </c>
@@ -23529,7 +24040,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C30" s="107" t="str">
-        <v>fullName="Tên hợp lệ"; email="co khoang trang@x.vn"; field="email"</v>
+        <v>request = NewUser { FullName = "Tên hợp lệ", Email = "co khoang trang@x.vn", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 019c0232-cb00-7bc7-9f40-40fb2141f2be (generated)</v>
       </c>
       <c r="D30" s="108" t="str">
         <v>Return:
@@ -23588,7 +24100,7 @@
       <c r="S31" s="90"/>
       <c r="T31"/>
     </row>
-    <row r="32" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="32" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A32" s="105" t="str">
         <v>UTC013</v>
       </c>
@@ -23596,7 +24108,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C32" s="107" t="str">
-        <v>new NewUser("Tên hợp lệ", "hople@trustcabinet.local", "ngan", BuiltIn…; _actorId</v>
+        <v>request = NewUser { FullName = "Tên hợp lệ", Email = "hople@trustcabinet.local", Password = "ngan", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 01991222-d8a7-7ba8-9fc7-999da2756f13 (generated)</v>
       </c>
       <c r="D32" s="108" t="str">
         <v>Return:
@@ -23654,7 +24167,7 @@
       <c r="S33" s="90"/>
       <c r="T33"/>
     </row>
-    <row r="34" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="34" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A34" s="105" t="str">
         <v>UTC014</v>
       </c>
@@ -23662,7 +24175,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C34" s="107" t="str">
-        <v>new NewUser("Tên hợp lệ", "hople@trustcabinet.local", ValidPassword,…; _actorId</v>
+        <v>request = NewUser { FullName = "Tên hợp lệ", Email = "hople@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 019426ee-0676-7fe5-841a-358769ce3a18 (generated) }
+actorId = 0196427b-0f95-7c52-8c2f-0b17a323f202 (generated)</v>
       </c>
       <c r="D34" s="108" t="str">
         <v>Return:
@@ -23720,7 +24234,7 @@
       <c r="S35" s="90"/>
       <c r="T35"/>
     </row>
-    <row r="36" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="36" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A36" s="105" t="str">
         <v>UTC015</v>
       </c>
@@ -23730,7 +24244,8 @@
 3. _users.WithRole(deputy, Capability.MinutesEditor).</v>
       </c>
       <c r="C36" s="107" t="str">
-        <v>new NewUser("Phó Thư Ký", "phothuky@trustcabinet.local", ValidPasswor…; _actorId</v>
+        <v>request = NewUser { FullName = "Phó Thư Ký", Email = "phothuky@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 019e7042-ad9a-7e7e-8a92-b5bdc56c163a (generated) }
+actorId = 019277e3-1b91-7349-8fc8-79209b766401 (generated)</v>
       </c>
       <c r="D36" s="108" t="str">
         <v>Return:
@@ -23789,7 +24304,7 @@
       <c r="S37" s="90"/>
       <c r="T37"/>
     </row>
-    <row r="38" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="38" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A38" s="105" t="str">
         <v>UTC016</v>
       </c>
@@ -23797,7 +24312,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C38" s="107" t="str">
-        <v>new NewUser("", "khong-phai-email", "ngan", BuiltInRoles.Member); _actorId</v>
+        <v>request = NewUser { FullName = "", Email = "khong-phai-email", Password = "ngan", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 0195f5f5-4473-790a-954b-6ee873ef57b3 (generated)</v>
       </c>
       <c r="D38" s="108" t="str">
         <v>Return: ["email", "fullName", "password"]
@@ -23853,7 +24369,7 @@
       <c r="S39" s="90"/>
       <c r="T39"/>
     </row>
-    <row r="40" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="40" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A40" s="105" t="str">
         <v>UTC017</v>
       </c>
@@ -23862,7 +24378,8 @@
 2. GivenUser(email: "trungnhau@trustcabinet.local").</v>
       </c>
       <c r="C40" s="107" t="str">
-        <v>new NewUser("Tên khác", "trungnhau@trustcabinet.local", ValidPassword…; _actorId</v>
+        <v>request = NewUser { FullName = "Tên khác", Email = "trungnhau@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 01991a69-e79c-7428-a1b2-cfaf7283e098 (generated)</v>
       </c>
       <c r="D40" s="108" t="str">
         <v>Return: UserOutcome.DuplicateEmail
@@ -23918,7 +24435,7 @@
       <c r="S41" s="90"/>
       <c r="T41"/>
     </row>
-    <row r="42" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="42" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A42" s="105" t="str">
         <v>UTC018</v>
       </c>
@@ -23927,7 +24444,8 @@
 2. GivenUser(email: "trungnhau@trustcabinet.local").</v>
       </c>
       <c r="C42" s="107" t="str">
-        <v>new NewUser("Tên khác", "TrungNhau@TrustCabinet.local", ValidPassword…; _actorId</v>
+        <v>request = NewUser { FullName = "Tên khác", Email = "TrungNhau@TrustCabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 01942b44-f9f3-73a4-afe1-8661722d6e10 (generated)</v>
       </c>
       <c r="D42" s="108" t="str">
         <v>Return: UserOutcome.DuplicateEmail
@@ -23983,7 +24501,7 @@
       <c r="S43" s="90"/>
       <c r="T43"/>
     </row>
-    <row r="44" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="44" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A44" s="105" t="str">
         <v>UTC019</v>
       </c>
@@ -23991,7 +24509,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C44" s="107" t="str">
-        <v>new NewUser(" Trần Chủ Toạ ", " chutoa@trustcabinet.local ", ValidPas…; _actorId</v>
+        <v>request = NewUser { FullName = "  Trần Chủ Toạ  ", Email = "  chutoa@trustcabinet.local  ", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7202-7945-be13-d2022cf25203 }
+actorId = 019d8664-65c0-717b-aa79-32f0fdfd7ec7 (generated)</v>
       </c>
       <c r="D44" s="108" t="str">
         <v>Return:
@@ -24050,7 +24569,7 @@
       <c r="S45" s="90"/>
       <c r="T45"/>
     </row>
-    <row r="46" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="46" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A46" s="105" t="str">
         <v>UTC020</v>
       </c>
@@ -24059,7 +24578,8 @@
 2. _users.NextSaveThrows = DuplicateEmailException().</v>
       </c>
       <c r="C46" s="107" t="str">
-        <v>new NewUser("Tên hợp lệ", "hople@trustcabinet.local", ValidPassword,…; _actorId</v>
+        <v>request = NewUser { FullName = "Tên hợp lệ", Email = "hople@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 0192dacf-9fad-7f79-ac50-d994c1bfc92c (generated)</v>
       </c>
       <c r="D46" s="108" t="str">
         <v>Return: UserOutcome.DuplicateEmail
@@ -24115,7 +24635,7 @@
       <c r="S47" s="90"/>
       <c r="T47"/>
     </row>
-    <row r="48" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="48" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A48" s="105" t="str">
         <v>UTC021</v>
       </c>
@@ -24124,7 +24644,8 @@
 2. _users.NextSaveThrows = new Microsoft.EntityFrameworkCore.DbUpdateException( "insert or update violates foreign k….</v>
       </c>
       <c r="C48" s="107" t="str">
-        <v>new NewUser("Tên hợp lệ", "hople@trustcabinet.local", ValidPassword,…; _actorId</v>
+        <v>request = NewUser { FullName = "Tên hợp lệ", Email = "hople@trustcabinet.local", Password = "MatKhauDaiVaAnToan@2026", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 0193d91c-9711-7a7e-80ce-be3046c02719 (generated)</v>
       </c>
       <c r="D48" s="108" t="str">
         <v>Return:
@@ -24191,7 +24712,7 @@
 2. user: a user with role Secretary exists ("Nguyễn Thư Ký", "thuky@trustcabinet.local", BuiltInRoles.Secretary).</v>
       </c>
       <c r="C50" s="107" t="str">
-        <v>user.Id</v>
+        <v>id = 019931ff-e226-723a-8401-52e391b00bba (generated)</v>
       </c>
       <c r="D50" s="108" t="str">
         <v>Return:
@@ -24258,7 +24779,7 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C52" s="107" t="str">
-        <v>Guid.CreateVersion7()</v>
+        <v>id = 019544dc-ebb7-700a-bbf1-ebeca6432682 (generated)</v>
       </c>
       <c r="D52" s="108" t="str">
         <v>Return:
@@ -24316,7 +24837,7 @@
       <c r="S53" s="90"/>
       <c r="T53"/>
     </row>
-    <row r="54" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="54" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A54" s="105" t="str">
         <v>UTC024</v>
       </c>
@@ -24325,7 +24846,9 @@
 2. user: a user with role Member exists ("Tên Cũ", "cu@trustcabinet.local", BuiltInRoles.Member).</v>
       </c>
       <c r="C54" s="107" t="str">
-        <v>user.Id; new UserEdit("Tên Mới", "moi@trustcabinet.local", BuiltInRoles.Secret…; _actorId</v>
+        <v>id = 0191438f-a027-758c-bc28-d014443f9d75 (generated)
+request = UserEdit { FullName = "Tên Mới", Email = "moi@trustcabinet.local", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }
+actorId = 019b1182-eb7a-7c72-8cb4-28f7ed9a3a4c (generated)</v>
       </c>
       <c r="D54" s="108" t="str">
         <v>Return:
@@ -24385,7 +24908,7 @@
       <c r="S55" s="90"/>
       <c r="T55"/>
     </row>
-    <row r="56" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="56" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A56" s="105" t="str">
         <v>UTC025</v>
       </c>
@@ -24394,7 +24917,9 @@
 2. user: a user with role Member exists (email: "giunguyen@trustcabinet.local").</v>
       </c>
       <c r="C56" s="107" t="str">
-        <v>user.Id; new UserEdit("Tên Mới", "giunguyen@trustcabinet.local", user.RoleId); _actorId</v>
+        <v>id = 019439cd-2d20-7e8b-b6f2-34f020293d92 (generated)
+request = UserEdit { FullName = "Tên Mới", Email = "giunguyen@trustcabinet.local", RoleId = GivenUser(email: "giunguyen@trustcabinet.local").RoleId }
+actorId = 019628e3-0151-7c3b-aec6-b3af0748d416 (generated)</v>
       </c>
       <c r="D56" s="108" t="str">
         <v>Return: true
@@ -24450,7 +24975,7 @@
       <c r="S57" s="90"/>
       <c r="T57"/>
     </row>
-    <row r="58" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
+    <row r="58" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A58" s="105" t="str">
         <v>UTC026</v>
       </c>
@@ -24460,7 +24985,9 @@
 3. GivenUser("Người Hai", "nguoi-hai@trustcabinet.local").</v>
       </c>
       <c r="C58" s="107" t="str">
-        <v>user.Id; new UserEdit(user.FullName, "nguoi-hai@trustcabinet.local", user.Role…; _actorId</v>
+        <v>id = 01941694-33e7-77ff-9ad5-42951244c092 (generated)
+request = UserEdit { FullName = GivenUser(email: "nguoi-mot@trustcabinet.local").FullName, Email = "nguoi-hai@trustcabinet.local", RoleId = GivenUser(email: "nguoi-mot@trustcabinet.local").RoleId }
+actorId = 019ae6e8-88d0-7a41-b81c-74d13d34b176 (generated)</v>
       </c>
       <c r="D58" s="108" t="str">
         <v>Return: UserOutcome.DuplicateEmail
@@ -24516,7 +25043,7 @@
       <c r="S59" s="90"/>
       <c r="T59"/>
     </row>
-    <row r="60" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="60" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A60" s="105" t="str">
         <v>UTC027</v>
       </c>
@@ -24525,7 +25052,9 @@
 2. user: a user with role Member exists ("Tên Cũ", "cu@trustcabinet.local").</v>
       </c>
       <c r="C60" s="107" t="str">
-        <v>user.Id; new UserEdit("", "khong-phai-email", BuiltInRoles.Member); _actorId</v>
+        <v>id = 0191fd6d-3565-7e9c-9c7c-ff08174d6ff8 (generated)
+request = UserEdit { FullName = "", Email = "khong-phai-email", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 01941d5b-223e-744b-8adb-ee1ab55343af (generated)</v>
       </c>
       <c r="D60" s="108" t="str">
         <v>Return: UserOutcome.InvalidInformation
@@ -24581,7 +25110,7 @@
       <c r="S61" s="90"/>
       <c r="T61"/>
     </row>
-    <row r="62" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="62" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A62" s="105" t="str">
         <v>UTC028</v>
       </c>
@@ -24589,7 +25118,9 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C62" s="107" t="str">
-        <v>Guid.CreateVersion7(); new UserEdit("Tên hợp lệ", "hople@trustcabinet.local", BuiltInRoles.M…; _actorId</v>
+        <v>id = 019bf3d5-6d71-7531-9b48-e5f518011d1a (generated)
+request = UserEdit { FullName = "Tên hợp lệ", Email = "hople@trustcabinet.local", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 019a63f2-9d19-76a6-b925-7abbfa2be7a3 (generated)</v>
       </c>
       <c r="D62" s="108" t="str">
         <v>Return: UserOutcome.NotFound
@@ -24654,7 +25185,9 @@
 2. user: a user with role Member exists (role: BuiltInRoles.Member).</v>
       </c>
       <c r="C64" s="107" t="str">
-        <v>"rt-cua-ho"; user.Id; TimeSpan.FromDays(7)</v>
+        <v>refreshToken = "rt-cua-ho"
+userId = 019be61b-bd6a-7e6e-9806-d297e3665485 (generated)
+lifetime = TimeSpan.FromDays(7)</v>
       </c>
       <c r="D64" s="108" t="str">
         <v>Return:
@@ -24712,7 +25245,7 @@
       <c r="S65" s="90"/>
       <c r="T65"/>
     </row>
-    <row r="66" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="66" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A66" s="105" t="str">
         <v>UTC030</v>
       </c>
@@ -24721,7 +25254,9 @@
 2. user: a user with role Member exists (role: BuiltInRoles.Member).</v>
       </c>
       <c r="C66" s="107" t="str">
-        <v>"rt-cua-ho"; user.Id; TimeSpan.FromDays(7)</v>
+        <v>refreshToken = "rt-cua-ho"
+userId = 0198a734-63fa-77fe-b412-7a6170d84cd6 (generated)
+lifetime = TimeSpan.FromDays(7)</v>
       </c>
       <c r="D66" s="108" t="str">
         <v>Return:
@@ -24779,7 +25314,7 @@
       <c r="S67" s="90"/>
       <c r="T67"/>
     </row>
-    <row r="68" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
+    <row r="68" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A68" s="105" t="str">
         <v>UTC031</v>
       </c>
@@ -24789,7 +25324,9 @@
 3. _capabilitiesChanged.OnPublish = () =&gt; throw new InvalidOperationException("Hub khong phan hoi").</v>
       </c>
       <c r="C68" s="107" t="str">
-        <v>user.Id; new UserEdit(user.FullName, user.Email, BuiltInRoles.Secretary); _actorId</v>
+        <v>id = 0197c474-0997-713a-85ed-8d3f6d3e282f (generated)
+request = UserEdit { FullName = GivenUser(role: BuiltInRoles.Member).FullName, Email = GivenUser(role: BuiltInRoles.Member).Email, RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }
+actorId = 019b8d03-9670-7be7-9514-b86d1751385a (generated)</v>
       </c>
       <c r="D68" s="108" t="str">
         <v>Return: true
@@ -24845,7 +25382,7 @@
       <c r="S69" s="90"/>
       <c r="T69"/>
     </row>
-    <row r="70" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="70" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A70" s="105" t="str">
         <v>UTC032</v>
       </c>
@@ -24854,7 +25391,9 @@
 2. user: a user with role Secretary exists (role: BuiltInRoles.Secretary).</v>
       </c>
       <c r="C70" s="107" t="str">
-        <v>"rt-cua-ho"; user.Id; TimeSpan.FromDays(7)</v>
+        <v>refreshToken = "rt-cua-ho"
+userId = 019630e5-7dc2-7309-8649-0dae2ce12760 (generated)
+lifetime = TimeSpan.FromDays(7)</v>
       </c>
       <c r="D70" s="108" t="str">
         <v>Return:
@@ -24912,7 +25451,7 @@
       <c r="S71" s="90"/>
       <c r="T71"/>
     </row>
-    <row r="72" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="72" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A72" s="105" t="str">
         <v>UTC033</v>
       </c>
@@ -24921,7 +25460,9 @@
 2. admin: a user with role Admin exists ("Phạm Quản Trị", "quantri@trustcabinet.local", BuiltInRoles.Admin).</v>
       </c>
       <c r="C72" s="107" t="str">
-        <v>admin.Id; new UserEdit(admin.FullName, admin.Email, BuiltInRoles.Member); admin.Id</v>
+        <v>id = 0192bc24-a135-7eb9-bb55-19eee040e427 (generated)
+request = UserEdit { FullName = GivenUser("Phạm Quản Trị", "quantri@trustcabinet.local", 01a0ce78-7205-7486-b976-d52d428d5451).FullName, Email = GivenUser("Phạm Quản Trị", "quantri@trustcabinet.local", 01a0ce7…
+actorId = 0192bc24-a135-7eb9-bb55-19eee040e427 (generated)</v>
       </c>
       <c r="D72" s="108" t="str">
         <v>Return: UserOutcome.StatusChangeNotAllowed
@@ -24977,7 +25518,7 @@
       <c r="S73" s="90"/>
       <c r="T73"/>
     </row>
-    <row r="74" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="74" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A74" s="105" t="str">
         <v>UTC034</v>
       </c>
@@ -24986,7 +25527,9 @@
 2. admin: a user with role Admin exists ("Phạm Quản Trị", "quantri@trustcabinet.local", BuiltInRoles.Admin).</v>
       </c>
       <c r="C74" s="107" t="str">
-        <v>admin.Id; new UserEdit("Phạm Quản Trị (mới)", admin.Email, BuiltInRoles.Admin); admin.Id</v>
+        <v>id = 0192b244-b5f3-761d-ac0c-29fa8e966810 (generated)
+request = UserEdit { FullName = "Phạm Quản Trị (mới)", Email = GivenUser("Phạm Quản Trị", "quantri@trustcabinet.local", 01a0ce78-7205-7486-b976-d52d428d5451).Email, RoleId = 01a0ce78-7205-7486-b976-d52d428d545…
+actorId = 0192b244-b5f3-761d-ac0c-29fa8e966810 (generated)</v>
       </c>
       <c r="D74" s="108" t="str">
         <v>Return: true
@@ -25042,7 +25585,7 @@
       <c r="S75" s="90"/>
       <c r="T75"/>
     </row>
-    <row r="76" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
+    <row r="76" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A76" s="105" t="str">
         <v>UTC035</v>
       </c>
@@ -25052,7 +25595,9 @@
 3. other: a user with role Admin exists ("Quản Trị Hai", "quantri2@trustcabinet.local", BuiltInRoles.Admin).</v>
       </c>
       <c r="C76" s="107" t="str">
-        <v>other.Id; new UserEdit(other.FullName, other.Email, BuiltInRoles.Member); _actorId</v>
+        <v>id = 019d1b77-d869-7dad-b334-aa7a77b798c2 (generated)
+request = UserEdit { FullName = GivenUser("Quản Trị Hai", "quantri2@trustcabinet.local", 01a0ce78-7205-7486-b976-d52d428d5451).FullName, Email = GivenUser("Quản Trị Hai", "quantri2@trustcabinet.local", 01a0ce7…
+actorId = 0199d124-6710-79c1-87e6-db549fcc4b47 (generated)</v>
       </c>
       <c r="D76" s="108" t="str">
         <v>Return: true
@@ -25108,7 +25653,7 @@
       <c r="S77" s="90"/>
       <c r="T77"/>
     </row>
-    <row r="78" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="78" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A78" s="105" t="str">
         <v>UTC036</v>
       </c>
@@ -25117,7 +25662,9 @@
 2. only: a user with role Admin exists ("Quản Trị Duy Nhất", "quantri@trustcabinet.local", BuiltInRoles.Admin).</v>
       </c>
       <c r="C78" s="107" t="str">
-        <v>only.Id; new UserEdit(only.FullName, only.Email, BuiltInRoles.Member); _actorId</v>
+        <v>id = 0194b140-ebeb-7d33-ab58-78ac99ae1c22 (generated)
+request = UserEdit { FullName = GivenUser("Quản Trị Duy Nhất", "quantri@trustcabinet.local", 01a0ce78-7205-7486-b976-d52d428d5451).FullName, Email = GivenUser("Quản Trị Duy Nhất", "quantri@trustcabinet.local",…
+actorId = 01999af1-0405-724e-b0bb-1eaf3bab513e (generated)</v>
       </c>
       <c r="D78" s="108" t="str">
         <v>Return: UserOutcome.StatusChangeNotAllowed
@@ -25173,7 +25720,7 @@
       <c r="S79" s="90"/>
       <c r="T79"/>
     </row>
-    <row r="80" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="80" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A80" s="105" t="str">
         <v>UTC037</v>
       </c>
@@ -25183,7 +25730,9 @@
 3. _users.WithCapabilities(BuiltInRoles.Chair, Capability.AdminUsers).</v>
       </c>
       <c r="C80" s="107" t="str">
-        <v>only.Id; new UserEdit(only.FullName, only.Email, BuiltInRoles.Chair); _actorId</v>
+        <v>id = 01981941-e911-7cee-b7df-66eb89cb660e (generated)
+request = UserEdit { FullName = GivenUser("Quản Trị Duy Nhất", "quantri@trustcabinet.local", 01a0ce78-7205-7486-b976-d52d428d5451).FullName, Email = GivenUser("Quản Trị Duy Nhất", "quantri@trustcabinet.local",…
+actorId = 019eb85a-d3da-7b80-bcca-e5077450ffd0 (generated)</v>
       </c>
       <c r="D80" s="108" t="str">
         <v>Return: true
@@ -25239,7 +25788,7 @@
       <c r="S81" s="90"/>
       <c r="T81"/>
     </row>
-    <row r="82" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="82" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A82" s="105" t="str">
         <v>UTC038</v>
       </c>
@@ -25248,7 +25797,9 @@
 2. retired: a user with role Admin exists ("Quản Trị Đã Nghỉ", "danghi@trustcabinet.local", BuiltInRoles.Admin,…).</v>
       </c>
       <c r="C82" s="107" t="str">
-        <v>retired.Id; new UserEdit(retired.FullName, retired.Email, BuiltInRoles.Member); _actorId</v>
+        <v>id = 01943d12-a95b-7853-bc47-08596c8fc957 (generated)
+request = UserEdit { FullName = GivenUser("Quản Trị Đã Nghỉ", "danghi@trustcabinet.local", 01a0ce78-7205-7486-b976-d52d428d5451, isActive: false).FullName, Email = GivenUser("Quản Trị Đã Nghỉ", "danghi@trustca…
+actorId = 0196ffc7-60e6-7285-9b6f-2b8944278ace (generated)</v>
       </c>
       <c r="D82" s="108" t="str">
         <v>Return: true
@@ -25313,7 +25864,9 @@
 2. user: a user with role Member exists ("Lê Thành Viên", "cu@trustcabinet.local").</v>
       </c>
       <c r="C84" s="107" t="str">
-        <v>"rt-cua-ho"; user.Id; TimeSpan.FromDays(7)</v>
+        <v>refreshToken = "rt-cua-ho"
+userId = 01976839-45f7-7f46-adb3-7c2c3724684b (generated)
+lifetime = TimeSpan.FromDays(7)</v>
       </c>
       <c r="D84" s="108" t="str">
         <v>Return: true
@@ -25378,7 +25931,9 @@
 2. user: a user with role Member exists ("Lê Thành Viên", "thanhvien@trustcabinet.local").</v>
       </c>
       <c r="C86" s="107" t="str">
-        <v>"rt-cua-ho"; user.Id; TimeSpan.FromDays(7)</v>
+        <v>refreshToken = "rt-cua-ho"
+userId = 019d618f-a7f5-72a3-975e-efeb3682232c (generated)
+lifetime = TimeSpan.FromDays(7)</v>
       </c>
       <c r="D86" s="108" t="str">
         <v>Return: true
@@ -25434,7 +25989,7 @@
       <c r="S87" s="90"/>
       <c r="T87"/>
     </row>
-    <row r="88" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="88" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A88" s="105" t="str">
         <v>UTC041</v>
       </c>
@@ -25443,7 +25998,9 @@
 2. target: a user with role Member exists ("Lê Thành Viên", "thanhvien@trustcabinet.local").</v>
       </c>
       <c r="C88" s="107" t="str">
-        <v>target.Id; new UserEdit(target.FullName, target.Email, BuiltInRoles.Chair); _actorId</v>
+        <v>id = 019efc61-12e0-7a8d-b32a-e73e9e788775 (generated)
+request = UserEdit { FullName = GivenUser("Lê Thành Viên", "thanhvien@trustcabinet.local").FullName, Email = GivenUser("Lê Thành Viên", "thanhvien@trustcabinet.local").Email, RoleId = 01a0ce78-7202-7945-be13-d…
+actorId = 0193fdfc-d7fe-7be2-bc21-69b597b332aa (generated)</v>
       </c>
       <c r="D88" s="108" t="str">
         <v>Return: 2
@@ -25508,7 +26065,9 @@
 2. user: a user with role Member exists ("Lê Thành Viên", "thanhvien@trustcabinet.local").</v>
       </c>
       <c r="C90" s="107" t="str">
-        <v>"rt-cua-ho"; user.Id; TimeSpan.FromDays(7)</v>
+        <v>refreshToken = "rt-cua-ho"
+userId = 019cccc3-2a3b-76f3-8c6b-e5dc42507356 (generated)
+lifetime = TimeSpan.FromDays(7)</v>
       </c>
       <c r="D90" s="108" t="str">
         <v>Return:
@@ -25634,7 +26193,7 @@
       <c r="S93" s="90"/>
       <c r="T93"/>
     </row>
-    <row r="94" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
+    <row r="94" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A94" s="105" t="str">
         <v>UTC044</v>
       </c>
@@ -25644,7 +26203,9 @@
 3. _refreshTokens.OnRevokeAll = () =&gt; throw new InvalidOperationException("Redis khong phan hoi").</v>
       </c>
       <c r="C94" s="107" t="str">
-        <v>user.Id; new UserEdit(user.FullName, "dia-chi-moi@trustcabinet.local", BuiltIn…; _actorId</v>
+        <v>id = 01959dd9-27ba-7595-8258-01db990d2c45 (generated)
+request = UserEdit { FullName = GivenUser("Lê Thành Viên", "thanhvien@trustcabinet.local").FullName, Email = "dia-chi-moi@trustcabinet.local", RoleId = 01a0ce78-7204-7558-b181-e908a08e83a3 }
+actorId = 0198f432-0a11-734d-b21d-c1bb4f2bac45 (generated)</v>
       </c>
       <c r="D94" s="108" t="str">
         <v>Return: true
@@ -25700,7 +26261,7 @@
       <c r="S95" s="90"/>
       <c r="T95"/>
     </row>
-    <row r="96" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="96" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A96" s="105" t="str">
         <v>UTC045</v>
       </c>
@@ -25709,7 +26270,9 @@
 2. user: a user with role Member exists (isActive: true).</v>
       </c>
       <c r="C96" s="107" t="str">
-        <v>"rt-cua-ho"; user.Id; TimeSpan.FromDays(7)</v>
+        <v>refreshToken = "rt-cua-ho"
+userId = 019da443-b8da-750e-b9d3-7f0580d83885 (generated)
+lifetime = TimeSpan.FromDays(7)</v>
       </c>
       <c r="D96" s="108" t="str">
         <v>Return:
@@ -25767,7 +26330,7 @@
       <c r="S97" s="90"/>
       <c r="T97"/>
     </row>
-    <row r="98" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="98" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A98" s="105" t="str">
         <v>UTC046</v>
       </c>
@@ -25776,7 +26339,9 @@
 2. user: a user with role Member exists.</v>
       </c>
       <c r="C98" s="107" t="str">
-        <v>user.Id; isActive: false; _actorId</v>
+        <v>id = 0191a9c6-f669-763a-9752-1bbc4c36e7df (generated)
+isActive = false
+isActive = 019d66f5-aa71-7605-87e7-08ad5ef7857c (generated)</v>
       </c>
       <c r="D98" s="108" t="str">
         <v>Return: contains _users.Users
@@ -25832,7 +26397,7 @@
       <c r="S99" s="90"/>
       <c r="T99"/>
     </row>
-    <row r="100" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="100" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A100" s="105" t="str">
         <v>UTC047</v>
       </c>
@@ -25841,7 +26406,9 @@
 2. user: a user with role Member exists (isActive: false).</v>
       </c>
       <c r="C100" s="107" t="str">
-        <v>"rt-nguoi-khac"; Guid.CreateVersion7(); TimeSpan.FromDays(7)</v>
+        <v>refreshToken = "rt-nguoi-khac"
+userId = 0195e45a-045b-7805-a060-7bf30dbe17f7 (generated)
+lifetime = TimeSpan.FromDays(7)</v>
       </c>
       <c r="D100" s="108" t="str">
         <v>Return:
@@ -25899,7 +26466,7 @@
       <c r="S101" s="90"/>
       <c r="T101"/>
     </row>
-    <row r="102" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="102" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A102" s="105" t="str">
         <v>UTC048</v>
       </c>
@@ -25908,7 +26475,9 @@
 2. user: a user with role Member exists (isActive: isActive).</v>
       </c>
       <c r="C102" s="107" t="str">
-        <v>isActive=true</v>
+        <v>id = 019fadd3-e248-7148-a730-61ab6ee76d6c (generated)
+isActive = true
+actorId = 0191cbb3-b8d9-792b-81c6-b5a26142ed36 (generated)</v>
       </c>
       <c r="D102" s="108" t="str">
         <v>Return: UserOutcome.StatusChangeNotAllowed
@@ -25940,7 +26509,7 @@
       <c r="S102" s="94"/>
       <c r="T102"/>
     </row>
-    <row r="103" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="103" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A103" s="105" t="str">
         <v>UTC049</v>
       </c>
@@ -25949,7 +26518,9 @@
 2. user: a user with role Member exists (isActive: isActive).</v>
       </c>
       <c r="C103" s="107" t="str">
-        <v>isActive=false</v>
+        <v>id = 0196197a-937b-7ca3-aa29-c232f5080016 (generated)
+isActive = false
+actorId = 019c43e4-f22b-781c-85f9-d4a5f3222582 (generated)</v>
       </c>
       <c r="D103" s="108" t="str">
         <v>Return: UserOutcome.StatusChangeNotAllowed
@@ -26014,7 +26585,9 @@
 2. admin: a user with role Admin exists ("Phạm Quản Trị", "quantri@trustcabinet.local", BuiltInRoles.Admin).</v>
       </c>
       <c r="C105" s="107" t="str">
-        <v>admin.Id; isActive: false; admin.Id</v>
+        <v>id = 0196a61f-1be8-75d4-8022-6236d81dc320 (generated)
+isActive = false
+isActive = 0196a61f-1be8-75d4-8022-6236d81dc320 (generated)</v>
       </c>
       <c r="D105" s="108" t="str">
         <v>Return: UserOutcome.StatusChangeNotAllowed
@@ -26080,7 +26653,9 @@
 3. b: a user with role Admin exists ("Quản Trị B", "b@trustcabinet.local", BuiltInRoles.Admin).</v>
       </c>
       <c r="C107" s="107" t="str">
-        <v>a.Id; isActive: false; b.Id</v>
+        <v>id = 0191add1-df76-7a27-a344-4340de15ea44 (generated)
+isActive = false
+isActive = 01964d44-3d47-7185-9a95-cc43590484a9 (generated)</v>
       </c>
       <c r="D107" s="108" t="str">
         <v>Return:
@@ -26147,7 +26722,9 @@
 2. only: a user with role Admin exists ("Quản Trị Duy Nhất", "quantri@trustcabinet.local", BuiltInRoles.Admin).</v>
       </c>
       <c r="C109" s="107" t="str">
-        <v>only.Id; isActive: false; _actorId</v>
+        <v>id = 0199e368-d5a9-7ee5-9c80-005d50ea6ed4 (generated)
+isActive = false
+isActive = 019d76e2-a50f-7ee2-bc61-d57461102641 (generated)</v>
       </c>
       <c r="D109" s="108" t="str">
         <v>Return: UserOutcome.StatusChangeNotAllowed
@@ -26215,7 +26792,9 @@
 5. newAdmin: a user with role Member exists ("Quản Trị Mới", "quantrimoi@trustcabinet.local", board.Id).</v>
       </c>
       <c r="C111" s="107" t="str">
-        <v>oldAdmin.Id; isActive: false; _actorId</v>
+        <v>id = 0191a7c5-a8cb-7db9-b081-f357b74eaf43 (generated)
+isActive = false
+isActive = 019d19a8-a29f-7e4b-bd70-55997d4fa699 (generated)</v>
       </c>
       <c r="D111" s="108" t="str">
         <v>Return: true
@@ -26271,7 +26850,7 @@
       <c r="S112" s="90"/>
       <c r="T112"/>
     </row>
-    <row r="113" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
+    <row r="113" spans="1:20" s="93" customFormat="1" ht="240.0" outlineLevel="1" customHeight="1">
       <c r="A113" s="105" t="str">
         <v>UTC054</v>
       </c>
@@ -26282,7 +26861,9 @@
 4. only: a user with role Admin exists ("Quản Trị Duy Nhất", "quantri@trustcabinet.local", BuiltInRoles.Admin).</v>
       </c>
       <c r="C113" s="107" t="str">
-        <v>only.Id; new UserEdit(only.FullName, only.Email, plain.Id); _actorId</v>
+        <v>id = 01960b45-f155-70b2-9769-4c7af65621aa (generated)
+request = UserEdit { FullName = GivenUser("Quản Trị Duy Nhất", "quantri@trustcabinet.local", 01a0ce78-7205-7486-b976-d52d428d5451).FullName, Email = GivenUser("Quản Trị Duy Nhất", "quantri@trustcabinet.local",…
+actorId = 0199dd8c-5d12-738d-bb35-a5145d88a5c1 (generated)</v>
       </c>
       <c r="D113" s="108" t="str">
         <v>Return: UserOutcome.StatusChangeNotAllowed
@@ -26338,7 +26919,7 @@
       <c r="S114" s="90"/>
       <c r="T114"/>
     </row>
-    <row r="115" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="115" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A115" s="105" t="str">
         <v>UTC055</v>
       </c>
@@ -26347,7 +26928,9 @@
 2. user: a user with role Member exists (role: BuiltInRoles.Member).</v>
       </c>
       <c r="C115" s="107" t="str">
-        <v>user.Id; new UserEdit(user.FullName, user.Email, BuiltInRoles.Secretary); _actorId</v>
+        <v>id = 019b469d-55de-7a8f-968a-7119378b7276 (generated)
+request = UserEdit { FullName = GivenUser(role: BuiltInRoles.Member).FullName, Email = GivenUser(role: BuiltInRoles.Member).Email, RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }
+actorId = 019ef451-d300-781e-8b06-0b846a5421c4 (generated)</v>
       </c>
       <c r="D115" s="108" t="str">
         <v>Return: "Thư ký"
@@ -26403,7 +26986,7 @@
       <c r="S116" s="90"/>
       <c r="T116"/>
     </row>
-    <row r="117" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="117" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A117" s="105" t="str">
         <v>UTC056</v>
       </c>
@@ -26412,7 +26995,9 @@
 2. user: a user with role Member exists.</v>
       </c>
       <c r="C117" s="107" t="str">
-        <v>user.Id; new UserEdit(user.FullName, user.Email, Guid.CreateVersion7()); _actorId</v>
+        <v>id = 01974a35-9654-7ad5-873e-803fff095476 (generated)
+request = UserEdit { FullName = GivenUser().FullName, Email = GivenUser().Email, RoleId = 01907a6d-489d-74e7-81eb-06698304a29a (generated) }
+actorId = 0197306a-8b9b-7523-8c80-46637ef98648 (generated)</v>
       </c>
       <c r="D117" s="108" t="str">
         <v>Return:
@@ -26470,7 +27055,7 @@
       <c r="S118" s="90"/>
       <c r="T118"/>
     </row>
-    <row r="119" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="119" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A119" s="105" t="str">
         <v>UTC057</v>
       </c>
@@ -26479,7 +27064,9 @@
 2. member: a user with role Member exists (role: BuiltInRoles.Member).</v>
       </c>
       <c r="C119" s="107" t="str">
-        <v>member.Id; isActive: false; _actorId</v>
+        <v>id = 0193f861-ddf1-707b-818e-782cb2051eb9 (generated)
+isActive = false
+isActive = 01984a47-5fcf-759d-9968-4e27f8cd6740 (generated)</v>
       </c>
       <c r="D119" s="108" t="str">
         <v>Return: true
@@ -26535,7 +27122,7 @@
       <c r="S120" s="90"/>
       <c r="T120"/>
     </row>
-    <row r="121" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="121" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A121" s="105" t="str">
         <v>UTC058</v>
       </c>
@@ -26543,7 +27130,9 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C121" s="107" t="str">
-        <v>Guid.CreateVersion7(); isActive: false; _actorId</v>
+        <v>id = 019aa193-3081-739e-b367-82804056dcca (generated)
+isActive = false
+isActive = 019e8802-350d-7a99-8912-9d1ce0ab148e (generated)</v>
       </c>
       <c r="D121" s="108" t="str">
         <v>Return: UserOutcome.NotFound
@@ -26599,7 +27188,7 @@
       <c r="S122" s="90"/>
       <c r="T122"/>
     </row>
-    <row r="123" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="123" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A123" s="105" t="str">
         <v>UTC059</v>
       </c>
@@ -26608,7 +27197,8 @@
 2. target: a user with role Member exists.</v>
       </c>
       <c r="C123" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 01923728-2da1-73e3-a7e1-0b1164f90014 (generated)
+actorId = 019b0f57-680c-79c0-b857-d5c33619690a (generated)</v>
       </c>
       <c r="D123" s="108" t="str">
         <v>Return: true
@@ -26674,7 +27264,8 @@
 3. before = target.PasswordHash.</v>
       </c>
       <c r="C125" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019bf632-4bf4-73a5-b605-a7ff193ac15b (generated)
+actorId = 0195b43c-41f2-78dd-ad96-2a47d4da37c4 (generated)</v>
       </c>
       <c r="D125" s="108" t="str">
         <v>Return:
@@ -26741,7 +27332,8 @@
 2. target: a user with role Member exists (isActive: false).</v>
       </c>
       <c r="C127" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 01978615-d2e9-753f-93bc-7ee944ee227c (generated)
+actorId = 019f5614-1ed6-7e1d-ad0c-4eb0e7781eb9 (generated)</v>
       </c>
       <c r="D127" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetNotAvailable
@@ -26808,7 +27400,9 @@
 4. target.GoogleSubjectId = "google-sub-123".</v>
       </c>
       <c r="C129" s="107" t="str">
-        <v>passwordHash=null</v>
+        <v>id = 019b559c-9e50-7cb9-a33c-72211b53886c (generated)
+actorId = 0199f18c-97ac-7982-a4ad-1e0a34e292ff (generated)
+passwordHash = null</v>
       </c>
       <c r="D129" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetNotAvailable
@@ -26851,7 +27445,9 @@
 4. target.GoogleSubjectId = "google-sub-123".</v>
       </c>
       <c r="C130" s="107" t="str">
-        <v>passwordHash=""</v>
+        <v>id = 0195e688-581f-72f0-a50f-f83113452228 (generated)
+actorId = 019411b6-b847-7fda-85f1-aeb6a40e145c (generated)
+passwordHash = ""</v>
       </c>
       <c r="D130" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetNotAvailable
@@ -26917,7 +27513,8 @@
 3. _resetEmail.Fails = true.</v>
       </c>
       <c r="C132" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019a09aa-abb5-78d5-b2ab-fe70c591adeb (generated)
+actorId = 0196701b-97b9-70b6-8512-c3c9990cd0cb (generated)</v>
       </c>
       <c r="D132" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetEmailFailed
@@ -26983,7 +27580,8 @@
 3. _resetEmail.Fails = true.</v>
       </c>
       <c r="C134" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 01922764-3373-7489-b2a9-49e8d84e5e86 (generated)
+actorId = 01956efa-5a1e-7934-8ff0-47e531a3c4d0 (generated)</v>
       </c>
       <c r="D134" s="108" t="str">
         <v>Return:
@@ -27051,7 +27649,8 @@
 3. _resetEmail.Fails = true.</v>
       </c>
       <c r="C136" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 0192147e-4552-7213-a7bd-56ed02c3d670 (generated)
+actorId = 019ed276-612f-7bac-88a6-077269b99038 (generated)</v>
       </c>
       <c r="D136" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27119,7 +27718,8 @@
 5. target.IsActive = true.</v>
       </c>
       <c r="C138" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019fcbae-7f3d-7b49-a620-3aca8a1ff855 (generated)
+actorId = 01901283-6a20-78e5-a005-5a0c2da26215 (generated)</v>
       </c>
       <c r="D138" s="108" t="str">
         <v>Return:
@@ -27187,7 +27787,8 @@
 3. _resetEmail.OnSend = async () =&gt; { target.Email = "dachinhsua@trustcabinet.local"; _resetTokens.RevokeAsync(ta….</v>
       </c>
       <c r="C140" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019fbef7-e574-730a-b1ee-a067c38a0a51 (generated)
+actorId = 019964d9-6690-73da-8f9c-2be157ddbb71 (generated)</v>
       </c>
       <c r="D140" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27253,7 +27854,8 @@
 3. _resetEmail.OnSend = () =&gt; { target.Email = "ThanhVien@TrustCabinet.local"; return Task.CompletedTask; }.</v>
       </c>
       <c r="C142" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019bc40f-8d1c-79a3-8638-67200309089a (generated)
+actorId = 01921065-8ec1-7c87-84a1-d68c468eb385 (generated)</v>
       </c>
       <c r="D142" s="108" t="str">
         <v>Return: true
@@ -27309,7 +27911,7 @@
       <c r="S143" s="90"/>
       <c r="T143"/>
     </row>
-    <row r="144" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="144" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A144" s="105" t="str">
         <v>UTC070</v>
       </c>
@@ -27317,7 +27919,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C144" s="107" t="str">
-        <v>Guid.CreateVersion7(); _actorId</v>
+        <v>id = 0192611f-2436-79b4-94d9-ab6bd95d7196 (generated)
+actorId = 019b33ea-7406-714e-bf4a-3fef3909965f (generated)</v>
       </c>
       <c r="D144" s="108" t="str">
         <v>Return: UserOutcome.NotFound
@@ -27373,7 +27976,7 @@
       <c r="S145" s="90"/>
       <c r="T145"/>
     </row>
-    <row r="146" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="146" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A146" s="105" t="str">
         <v>UTC071</v>
       </c>
@@ -27382,7 +27985,8 @@
 2. target: a user with role Member exists.</v>
       </c>
       <c r="C146" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 0197e86e-195f-709d-ba28-2b3e874089ba (generated)
+actorId = 0192b41e-f4eb-7f31-b90a-b57465691b34 (generated)</v>
       </c>
       <c r="D146" s="108" t="str">
         <v>Return: true
@@ -27448,7 +28052,8 @@
 3. token = _resetTokens.Created[0].</v>
       </c>
       <c r="C148" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019898b2-7960-7200-9188-0652ad5ff206 (generated)
+actorId = 01903de0-42b9-7f43-a788-75feb3dd54fb (generated)</v>
       </c>
       <c r="D148" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27513,7 +28118,8 @@
 2. target: a user with role Member exists.</v>
       </c>
       <c r="C150" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019bb6b7-8b52-742b-886e-cf6608a5ac90 (generated)
+actorId = 019c62f7-435d-7edc-a5ce-8ac89d5ecf55 (generated)</v>
       </c>
       <c r="D150" s="108" t="str">
         <v>Return:
@@ -27582,7 +28188,8 @@
 4. target.GoogleSubjectId = "google-sub-123".</v>
       </c>
       <c r="C152" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 01961ff2-86df-7a43-9073-dd2631b4f0ca (generated)
+actorId = 01918243-efe1-7b51-b63b-1c3bb20c2d30 (generated)</v>
       </c>
       <c r="D152" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27648,7 +28255,8 @@
 3. _resetTokens.Now += UserService.PasswordResetLinkLifetime.</v>
       </c>
       <c r="C154" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019155f6-1fa0-721d-a9e7-f11b19e34717 (generated)
+actorId = 019e8c10-9e39-7ca9-aa88-4b80e7fa4f3a (generated)</v>
       </c>
       <c r="D154" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27712,7 +28320,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C156" s="107" t="str">
-        <v>token=null</v>
+        <v>token = null
+newPassword = "MotMatKhauMoiRatDai@2026"</v>
       </c>
       <c r="D156" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27752,7 +28361,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C157" s="107" t="str">
-        <v>token=""</v>
+        <v>token = ""
+newPassword = "MotMatKhauMoiRatDai@2026"</v>
       </c>
       <c r="D157" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27792,7 +28402,8 @@
         <v>1. UserService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C158" s="107" t="str">
-        <v>token="khong-phai-token-nao-ca"</v>
+        <v>token = "khong-phai-token-nao-ca"
+newPassword = "MotMatKhauMoiRatDai@2026"</v>
       </c>
       <c r="D158" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27858,7 +28469,8 @@
 3. before = target.PasswordHash.</v>
       </c>
       <c r="C160" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019c9ef8-d43b-736f-9494-e3858000eb38 (generated)
+actorId = 01913bec-c9ee-7c6c-9324-f704d3045da8 (generated)</v>
       </c>
       <c r="D160" s="108" t="str">
         <v>Return:
@@ -27927,7 +28539,8 @@
 4. target.IsActive = false.</v>
       </c>
       <c r="C162" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 0197cbc8-4f53-7ead-9007-6ff69faf0baf (generated)
+actorId = 0191e78b-3ebe-7efe-b242-e4233142002e (generated)</v>
       </c>
       <c r="D162" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -27994,7 +28607,8 @@
 4. _refreshTokens.OnRevokeAll = () =&gt; { if (++revokes == 1) { _refreshTokens.StoreAsync("dang-nhap-chen-giua", target.Id,….</v>
       </c>
       <c r="C164" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 0196d6ea-8721-7121-9394-d2fcdc319386 (generated)
+actorId = 0197686a-f5df-7719-b6db-8fc14aea4540 (generated)</v>
       </c>
       <c r="D164" s="108" t="str">
         <v>Return: null
@@ -28061,7 +28675,8 @@
 4. _refreshTokens.OnRevokeAll = () =&gt; { if (++revokes == 2) { throw new InvalidOperationException("Redis down"); } }.</v>
       </c>
       <c r="C166" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019939f6-3571-76c8-af20-ad16d9cb1f14 (generated)
+actorId = 0192c9bd-2695-70ba-a388-99a6b1c042be (generated)</v>
       </c>
       <c r="D166" s="108" t="str">
         <v>Return: true
@@ -28117,7 +28732,7 @@
       <c r="S167" s="90"/>
       <c r="T167"/>
     </row>
-    <row r="168" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="168" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A168" s="105" t="str">
         <v>UTC083</v>
       </c>
@@ -28126,7 +28741,8 @@
 2. target: a user with role Member exists.</v>
       </c>
       <c r="C168" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 01960f2a-6d6f-78e3-8b3e-c50c216b091b (generated)
+actorId = 01996070-2365-7c3b-8af3-b7e833f82a61 (generated)</v>
       </c>
       <c r="D168" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -28182,7 +28798,7 @@
       <c r="S169" s="90"/>
       <c r="T169"/>
     </row>
-    <row r="170" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="170" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A170" s="105" t="str">
         <v>UTC084</v>
       </c>
@@ -28191,7 +28807,8 @@
 2. target: a user with role Member exists.</v>
       </c>
       <c r="C170" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 0191bd37-0b42-7594-b3b4-a32e3b3dc342 (generated)
+actorId = 019d2e2f-90cc-7061-bd3b-ce7e296839c5 (generated)</v>
       </c>
       <c r="D170" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -28257,7 +28874,9 @@
 3. _resetTokens.RevokeThrows = new InvalidOperationException("Redis down").</v>
       </c>
       <c r="C172" s="107" t="str">
-        <v>target.Id; isActive: false; _actorId</v>
+        <v>id = 019b3c1b-6c29-7b7f-8428-a5aae82949a7 (generated)
+isActive = false
+isActive = 0193f4ff-5580-755c-bfe3-ac90028432db (generated)</v>
       </c>
       <c r="D172" s="108" t="str">
         <v>Return: true
@@ -28324,7 +28943,8 @@
 4. _refreshTokens.OnRevokeAll = null.</v>
       </c>
       <c r="C174" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 01917084-928e-750f-8367-9e16a1635624 (generated)
+actorId = 01978ef0-388d-725d-8492-3d95002c3a63 (generated)</v>
       </c>
       <c r="D174" s="108" t="str">
         <v>Return: UserOutcome.PasswordResetLinkInvalid
@@ -28380,7 +29000,7 @@
       <c r="S175" s="90"/>
       <c r="T175"/>
     </row>
-    <row r="176" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="176" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A176" s="105" t="str">
         <v>UTC087</v>
       </c>
@@ -28389,7 +29009,8 @@
 2. target: a user with role Member exists.</v>
       </c>
       <c r="C176" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 019f2bb2-0ab3-7d35-a4d8-666f6964381c (generated)
+actorId = 019d56c2-fe96-7b16-9be0-dab24fc3d10a (generated)</v>
       </c>
       <c r="D176" s="108" t="str">
         <v>Return: true
@@ -28456,7 +29077,8 @@
 4. _refreshTokens.OnRevokeAll = () =&gt; throw new InvalidOperationException("Redis down").</v>
       </c>
       <c r="C178" s="107" t="str">
-        <v>target.Id; _actorId</v>
+        <v>id = 0198d5a2-c183-7412-a98f-7904661a691e (generated)
+actorId = 0195524b-f0b5-73c2-8542-ab0848a22cf3 (generated)</v>
       </c>
       <c r="D178" s="108" t="str">
         <v>Return: before
@@ -28506,7 +29128,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3578CB4C-E828-4B28-945C-3E0FCA1FE4AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C410E055-B778-4748-989A-3C52FF046FC7}">
   <dimension ref="B1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -28856,7 +29478,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822EAD2B-75B1-41DD-B57A-CC25CC6C5230}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F85459-3690-4BA5-92E3-3D0DF56699A9}">
   <dimension ref="A2:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -29314,7 +29936,7 @@
       </c>
       <c r="F19" s="42" t="n">
         <f>'Meetings'!B9</f>
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="G19" s="41" t="n">
         <f>'Meetings'!C9</f>
@@ -29322,7 +29944,7 @@
       </c>
       <c r="H19" s="41" t="n">
         <f>'Meetings'!D9</f>
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I19" s="41" t="n">
         <f>'Meetings'!B3</f>
@@ -29514,7 +30136,7 @@
       </c>
       <c r="F26" s="44" t="n">
         <f>SUM(F12:F25)</f>
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="G26" s="44" t="n">
         <f>SUM(G12:G25)</f>
@@ -29522,7 +30144,7 @@
       </c>
       <c r="H26" s="44" t="n">
         <f>SUM(H12:H25)</f>
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="I26" s="44" t="n">
         <f>SUM(I12:I25)</f>
@@ -29584,7 +30206,7 @@
       <c r="C30" s="34"/>
       <c r="D30" s="61" t="n">
         <f>IFERROR(F26*100/I26,0)</f>
-        <v>50.84</v>
+        <v>47.63</v>
       </c>
       <c r="E30" s="34" t="str">
         <v>%</v>
@@ -29620,7 +30242,7 @@
       <c r="C32"/>
       <c r="D32" s="61" t="n">
         <f>IFERROR(H26*100/I26,0)</f>
-        <v>6.28</v>
+        <v>9.49</v>
       </c>
       <c r="E32" s="34" t="str">
         <v>%</v>
@@ -29669,7 +30291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -30085,7 +30707,7 @@
 2. hub = new NotificationWorkerTests.FakeHubContext().</v>
       </c>
       <c r="C13" s="107" t="str">
-        <v>[first, second]</v>
+        <v>userIds = [0195fc88-1831-718d-8860-389f726a9900 (generated), 01973253-22dc-79d3-bab2-44ecd902d2a6 (generated)]</v>
       </c>
       <c r="D13" s="108" t="str">
         <v>Return:
@@ -30154,7 +30776,7 @@
 2. hub = new NotificationWorkerTests.FakeHubContext().</v>
       </c>
       <c r="C15" s="107" t="str">
-        <v>[]</v>
+        <v>userIds = []</v>
       </c>
       <c r="D15" s="108" t="str">
         <v>Return: empty
@@ -30603,7 +31225,7 @@
       <c r="S28" s="90"/>
       <c r="T28"/>
     </row>
-    <row r="29" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="29" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A29" s="105" t="str">
         <v>UTC009</v>
       </c>
@@ -30611,7 +31233,9 @@
         <v>1. RolePermissionService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C29" s="107" t="str">
-        <v>BuiltInRoles.Member; [Capability.MeetingCreator]; _actorId</v>
+        <v>roleId = 01a0ce78-7204-7558-b181-e908a08e83a3
+capabilities = [Capability.MeetingCreator]
+actorId = 01997784-0591-7c4b-897d-1d5cc35c3fd4 (generated)</v>
       </c>
       <c r="D29" s="108" t="str">
         <v>Return: true
@@ -30667,7 +31291,7 @@
       <c r="S30" s="90"/>
       <c r="T30"/>
     </row>
-    <row r="31" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="31" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A31" s="105" t="str">
         <v>UTC010</v>
       </c>
@@ -30675,7 +31299,9 @@
         <v>1. RolePermissionService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C31" s="107" t="str">
-        <v>BuiltInRoles.Secretary; []; _actorId</v>
+        <v>roleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22
+capabilities = []
+actorId = 01983d7b-43d7-7ed8-a264-350357aed332 (generated)</v>
       </c>
       <c r="D31" s="108" t="str">
         <v>Return: true
@@ -30739,7 +31365,9 @@
         <v>1. RolePermissionService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C33" s="107" t="str">
-        <v>BuiltInRoles.Member; [Capability.MeetingCreator]; _actorId</v>
+        <v>roleId = 01a0ce78-7204-7558-b181-e908a08e83a3
+capabilities = [Capability.MeetingCreator]
+actorId = 01978d1f-b141-722f-b4dc-70649bb051e1 (generated)</v>
       </c>
       <c r="D33" s="108" t="str">
         <v>Return:
@@ -30812,7 +31440,9 @@
 3. _roles.WithActiveUser(BuiltInRoles.Chair, untouched).</v>
       </c>
       <c r="C35" s="107" t="str">
-        <v>BuiltInRoles.Member; [Capability.MeetingCreator]; _actorId</v>
+        <v>roleId = 01a0ce78-7204-7558-b181-e908a08e83a3
+capabilities = [Capability.MeetingCreator]
+actorId = 019935f0-cb6f-7865-9cfc-ea6cd1b4c507 (generated)</v>
       </c>
       <c r="D35" s="108" t="str">
         <v>Return:
@@ -30879,7 +31509,9 @@
 2. _roles.WithActiveUser(BuiltInRoles.Secretary, secretary).</v>
       </c>
       <c r="C37" s="107" t="str">
-        <v>BuiltInRoles.Secretary; []; _actorId</v>
+        <v>roleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22
+capabilities = []
+actorId = 0197be3b-a0e6-7541-b9bc-6dc2a132b994 (generated)</v>
       </c>
       <c r="D37" s="108" t="str">
         <v>Return: [secretary]
@@ -31012,7 +31644,9 @@
 3. _publisher.OnPublish = () =&gt; throw new InvalidOperationException("Hub khong phan hoi").</v>
       </c>
       <c r="C41" s="107" t="str">
-        <v>BuiltInRoles.Member; [Capability.MeetingCreator]; _actorId</v>
+        <v>roleId = 01a0ce78-7204-7558-b181-e908a08e83a3
+capabilities = [Capability.MeetingCreator]
+actorId = 019fa9a9-6599-783c-9fa4-d07de6140ba4 (generated)</v>
       </c>
       <c r="D41" s="108" t="str">
         <v>Return: true
@@ -31068,7 +31702,7 @@
       <c r="S42" s="90"/>
       <c r="T42"/>
     </row>
-    <row r="43" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="43" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A43" s="105" t="str">
         <v>UTC016</v>
       </c>
@@ -31076,7 +31710,9 @@
         <v>1. RolePermissionService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C43" s="107" t="str">
-        <v>BuiltInRoles.Member; [Capability.MeetingCreator]; _actorId</v>
+        <v>roleId = 01a0ce78-7204-7558-b181-e908a08e83a3
+capabilities = [Capability.MeetingCreator]
+actorId = 0192f9c5-f61c-7d5b-bcee-52abc0c6eaa1 (generated)</v>
       </c>
       <c r="D43" s="108" t="str">
         <v>Return: 1
@@ -31132,7 +31768,7 @@
       <c r="S44" s="90"/>
       <c r="T44"/>
     </row>
-    <row r="45" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="45" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A45" s="105" t="str">
         <v>UTC017</v>
       </c>
@@ -31141,7 +31777,9 @@
 2. _roles.WithActiveUser(BuiltInRoles.Admin, member).</v>
       </c>
       <c r="C45" s="107" t="str">
-        <v>BuiltInRoles.Admin; [Capability.AdminUsers]; _actorId</v>
+        <v>roleId = 01a0ce78-7205-7486-b976-d52d428d5451
+capabilities = [Capability.AdminUsers]
+actorId = 01917ca5-6bd1-73b7-9b3e-bd3d3cd75aba (generated)</v>
       </c>
       <c r="D45" s="108" t="str">
         <v>Return: true
@@ -31197,7 +31835,7 @@
       <c r="S46" s="90"/>
       <c r="T46"/>
     </row>
-    <row r="47" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="47" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A47" s="105" t="str">
         <v>UTC018</v>
       </c>
@@ -31205,7 +31843,9 @@
         <v>1. RolePermissionService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C47" s="107" t="str">
-        <v>BuiltInRoles.Member; [Capability.MeetingCreator, Capability.MeetingCreator]; _actorId</v>
+        <v>roleId = 01a0ce78-7204-7558-b181-e908a08e83a3
+capabilities = [Capability.MeetingCreator, Capability.MeetingCreator]
+actorId = 0190483d-0293-768b-bdb7-08346075a76c (generated)</v>
       </c>
       <c r="D47" s="108" t="str">
         <v>Return: true
@@ -31261,7 +31901,7 @@
       <c r="S48" s="90"/>
       <c r="T48"/>
     </row>
-    <row r="49" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="49" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A49" s="105" t="str">
         <v>UTC019</v>
       </c>
@@ -31269,7 +31909,9 @@
         <v>1. RolePermissionService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C49" s="107" t="str">
-        <v>BuiltInRoles.Admin; []; _actorId</v>
+        <v>roleId = 01a0ce78-7205-7486-b976-d52d428d5451
+capabilities = []
+actorId = 019744cb-00ee-7965-a468-cee5f9015a69 (generated)</v>
       </c>
       <c r="D49" s="108" t="str">
         <v>Return:
@@ -31337,7 +31979,9 @@
 3. _roles.WithActiveUser(BuiltInRoles.Secretary, Guid.CreateVersion7()).</v>
       </c>
       <c r="C51" s="107" t="str">
-        <v>BuiltInRoles.Admin; []; _actorId</v>
+        <v>roleId = 01a0ce78-7205-7486-b976-d52d428d5451
+capabilities = []
+actorId = 019c533f-300f-7cc5-98f8-646f2ff59be7 (generated)</v>
       </c>
       <c r="D51" s="108" t="str">
         <v>Return: true
@@ -31402,7 +32046,9 @@
 2. _roles.WithCapabilities(BuiltInRoles.Member, Capability.AdminUsers).</v>
       </c>
       <c r="C53" s="107" t="str">
-        <v>BuiltInRoles.Admin; []; _actorId</v>
+        <v>roleId = 01a0ce78-7205-7486-b976-d52d428d5451
+capabilities = []
+actorId = 0195d3e9-7a45-7c37-83cd-f1cd8752ddb4 (generated)</v>
       </c>
       <c r="D53" s="108" t="str">
         <v>Return:
@@ -31460,7 +32106,7 @@
       <c r="S54" s="90"/>
       <c r="T54"/>
     </row>
-    <row r="55" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="55" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A55" s="105" t="str">
         <v>UTC022</v>
       </c>
@@ -31469,7 +32115,9 @@
 2. _roles.WithNoUsers().</v>
       </c>
       <c r="C55" s="107" t="str">
-        <v>BuiltInRoles.Secretary; [Capability.MinutesEditor]; _actorId</v>
+        <v>roleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22
+capabilities = [Capability.MinutesEditor]
+actorId = 019a0ba2-6782-7cb1-8a43-4391b85bbd5d (generated)</v>
       </c>
       <c r="D55" s="108" t="str">
         <v>Return:
@@ -31527,7 +32175,7 @@
       <c r="S56" s="90"/>
       <c r="T56"/>
     </row>
-    <row r="57" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="57" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A57" s="105" t="str">
         <v>UTC023</v>
       </c>
@@ -31536,7 +32184,9 @@
 2. _roles.WithActiveUser(BuiltInRoles.Secretary, Guid.CreateVersion7()).</v>
       </c>
       <c r="C57" s="107" t="str">
-        <v>BuiltInRoles.Secretary; [Capability.AdminUsers]; _actorId</v>
+        <v>roleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22
+capabilities = [Capability.AdminUsers]
+actorId = 019f8d24-11d2-7518-8238-40ed7c878b7b (generated)</v>
       </c>
       <c r="D57" s="108" t="str">
         <v>Return: true
@@ -31592,7 +32242,7 @@
       <c r="S58" s="90"/>
       <c r="T58"/>
     </row>
-    <row r="59" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="59" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A59" s="105" t="str">
         <v>UTC024</v>
       </c>
@@ -31600,7 +32250,9 @@
         <v>1. RolePermissionService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C59" s="107" t="str">
-        <v>Guid.CreateVersion7(); [Capability.MeetingCreator]; _actorId</v>
+        <v>roleId = 01914e22-a4e3-7ccf-abbc-13952ec98ba5 (generated)
+capabilities = [Capability.MeetingCreator]
+actorId = 0190eca6-90de-79f5-bc53-2e044b308eec (generated)</v>
       </c>
       <c r="D59" s="108" t="str">
         <v>Return:
@@ -31668,7 +32320,9 @@
 3. _roles.WithRole(deputy).</v>
       </c>
       <c r="C61" s="107" t="str">
-        <v>deputy.Id; [Capability.MinutesEditor]; _actorId</v>
+        <v>roleId = 019a6ccc-483d-7549-954f-18f77af229d1 (generated)
+capabilities = [Capability.MinutesEditor]
+actorId = 0194cb58-f1b1-7d11-a7b0-51cbfe915ef5 (generated)</v>
       </c>
       <c r="D61" s="108" t="str">
         <v>Return: true
@@ -31733,7 +32387,9 @@
 2. board = new Role { Name = "Ban quản trị" }.</v>
       </c>
       <c r="C63" s="107" t="str">
-        <v>board.Id; [Capability.AdminUsers]; _actorId</v>
+        <v>roleId = 019e38dc-ebfc-7496-828a-e25fd219b55e (generated)
+capabilities = [Capability.AdminUsers]
+actorId = 0199856e-0b67-73f6-8ff0-f950bbc1b65d (generated)</v>
       </c>
       <c r="D63" s="108" t="str">
         <v>Return:
@@ -31792,7 +32448,7 @@
       <c r="S64" s="90"/>
       <c r="T64"/>
     </row>
-    <row r="65" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="65" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A65" s="105" t="str">
         <v>UTC027</v>
       </c>
@@ -31800,7 +32456,9 @@
         <v>1. RolePermissionService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C65" s="107" t="str">
-        <v>BuiltInRoles.Member; [(Capability)(-1)]; _actorId</v>
+        <v>roleId = 01a0ce78-7204-7558-b181-e908a08e83a3
+capabilities = [(Capability)(-1)]
+actorId = 019c2de4-a46d-7a14-8d8a-33646c29cfca (generated)</v>
       </c>
       <c r="D65" s="108" t="str">
         <v>Return:
@@ -31858,7 +32516,7 @@
       <c r="S66" s="90"/>
       <c r="T66"/>
     </row>
-    <row r="67" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="67" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A67" s="105" t="str">
         <v>UTC028</v>
       </c>
@@ -31867,7 +32525,9 @@
 2. _roles.NextSaveThrows = new DbUpdateException("the database said no").</v>
       </c>
       <c r="C67" s="107" t="str">
-        <v>BuiltInRoles.Member; [Capability.MeetingCreator]; _actorId</v>
+        <v>roleId = 01a0ce78-7204-7558-b181-e908a08e83a3
+capabilities = [Capability.MeetingCreator]
+actorId = 019ac558-21ac-793c-a1a6-3dc1865ef2e8 (generated)</v>
       </c>
       <c r="D67" s="108" t="str">
         <v>Return:
@@ -31995,7 +32655,7 @@
       <c r="S70" s="90"/>
       <c r="T70"/>
     </row>
-    <row r="71" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="71" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A71" s="105" t="str">
         <v>UTC030</v>
       </c>
@@ -32003,7 +32663,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C71" s="107" t="str">
-        <v>new NewRole("Thư ký phó", "Hỗ trợ thư ký soạn biên bản.", ["MinutesEd…; _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = "Hỗ trợ thư ký soạn biên bản.", Capabilities = ["MinutesEditor"] }
+actorId = 0190c038-79bb-7811-bb8e-c8497efb9f3d (generated)</v>
       </c>
       <c r="D71" s="108" t="str">
         <v>Return: true
@@ -32067,7 +32728,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C73" s="107" t="str">
-        <v>new NewRole("Thư ký phó", "Hỗ trợ.", ["MinutesEditor", "MeetingCreato…; _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = "Hỗ trợ.", Capabilities = ["MinutesEditor", "MeetingCreator"] }
+actorId = 019e1539-1ce6-79fe-b8eb-cecb55658953 (generated)</v>
       </c>
       <c r="D73" s="108" t="str">
         <v>Return:
@@ -32130,7 +32792,7 @@
       <c r="S74" s="90"/>
       <c r="T74"/>
     </row>
-    <row r="75" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="75" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A75" s="105" t="str">
         <v>UTC032</v>
       </c>
@@ -32138,7 +32800,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C75" s="107" t="str">
-        <v>new NewRole("Thư ký phó", null, ["AdminUsers"]); _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = ["AdminUsers"] }
+actorId = 0194016e-ad4c-7871-935d-1c2b4a87d2ca (generated)</v>
       </c>
       <c r="D75" s="108" t="str">
         <v>Return: 1
@@ -32194,7 +32857,7 @@
       <c r="S76" s="90"/>
       <c r="T76"/>
     </row>
-    <row r="77" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="77" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A77" s="105" t="str">
         <v>UTC033</v>
       </c>
@@ -32202,7 +32865,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C77" s="107" t="str">
-        <v>new NewRole("Khách mời thường trực", null, null); _actorId</v>
+        <v>request = NewRole { Name = "Khách mời thường trực", Description = null, Capabilities = null }
+actorId = 019227a4-6a7f-7dc0-b878-07f4a5fb64b1 (generated)</v>
       </c>
       <c r="D77" s="108" t="str">
         <v>Return: true
@@ -32258,7 +32922,7 @@
       <c r="S78" s="90"/>
       <c r="T78"/>
     </row>
-    <row r="79" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="79" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A79" s="105" t="str">
         <v>UTC034</v>
       </c>
@@ -32266,7 +32930,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C79" s="107" t="str">
-        <v>new NewRole(" Thư ký \t phó ", " Mô tả ", []); _actorId</v>
+        <v>request = NewRole { Name = "   Thư   ký \t phó  ", Description = "  Mô tả  ", Capabilities = [] }
+actorId = 0195a6ba-aea7-7058-9ec7-4e75c82901d4 (generated)</v>
       </c>
       <c r="D79" s="108" t="str">
         <v>Return:
@@ -32324,7 +32989,7 @@
       <c r="S80" s="90"/>
       <c r="T80"/>
     </row>
-    <row r="81" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="81" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A81" s="105" t="str">
         <v>UTC035</v>
       </c>
@@ -32332,7 +32997,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C81" s="107" t="str">
-        <v>description=null</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = [] }
+actorId = 0197ce63-bf59-720c-9b0a-bc553de96f55 (generated)</v>
       </c>
       <c r="D81" s="108" t="str">
         <v>Return: null
@@ -32364,7 +33030,7 @@
       <c r="S81" s="94"/>
       <c r="T81"/>
     </row>
-    <row r="82" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="82" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A82" s="105" t="str">
         <v>UTC036</v>
       </c>
@@ -32372,7 +33038,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C82" s="107" t="str">
-        <v>description=""</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = "", Capabilities = [] }
+actorId = 01930315-df19-7172-b284-2c318488cae9 (generated)</v>
       </c>
       <c r="D82" s="108" t="str">
         <v>Return: null
@@ -32404,7 +33071,7 @@
       <c r="S82" s="94"/>
       <c r="T82"/>
     </row>
-    <row r="83" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="83" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A83" s="105" t="str">
         <v>UTC037</v>
       </c>
@@ -32412,7 +33079,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C83" s="107" t="str">
-        <v>description="   "</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = "   ", Capabilities = [] }
+actorId = 019cc2f1-104d-75dc-8e4c-241feccca3bf (generated)</v>
       </c>
       <c r="D83" s="108" t="str">
         <v>Return: null
@@ -32476,7 +33144,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C85" s="107" t="str">
-        <v>name=null</v>
+        <v>request = NewRole { Name = null, Description = null, Capabilities = [] }
+actorId = 019cd122-df36-7f56-b439-f8de0e8177ec (generated)</v>
       </c>
       <c r="D85" s="108" t="str">
         <v>Return:
@@ -32518,7 +33187,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C86" s="107" t="str">
-        <v>name=""</v>
+        <v>request = NewRole { Name = "", Description = null, Capabilities = [] }
+actorId = 019e5958-f80c-71b6-abb4-3082a8b32685 (generated)</v>
       </c>
       <c r="D86" s="108" t="str">
         <v>Return:
@@ -32560,7 +33230,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C87" s="107" t="str">
-        <v>name="  \t "</v>
+        <v>request = NewRole { Name = "  \t ", Description = null, Capabilities = [] }
+actorId = 0196ae12-7845-7039-a8ac-5111d0bb54e3 (generated)</v>
       </c>
       <c r="D87" s="108" t="str">
         <v>Return:
@@ -32626,7 +33297,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C89" s="107" t="str">
-        <v>new NewRole(new string('a', 64), null, []); _actorId</v>
+        <v>request = NewRole { Name = 'a' × 64, Description = null, Capabilities = [] }
+actorId = 0196cc69-84ec-7bce-a520-4a439737ff27 (generated)</v>
       </c>
       <c r="D89" s="108" t="str">
         <v>Return:
@@ -32685,7 +33357,7 @@
       <c r="S90" s="90"/>
       <c r="T90"/>
     </row>
-    <row r="91" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="91" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A91" s="105" t="str">
         <v>UTC042</v>
       </c>
@@ -32693,7 +33365,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C91" s="107" t="str">
-        <v>new NewRole(padded, null, []); _actorId</v>
+        <v>request = NewRole { Name = "  " + 'a' × 32 + "     " + 'b' × 31 + "  ", Description = null, Capabilities = [] }
+actorId = 01977e72-2204-775c-a348-03698950f3f7 (generated)</v>
       </c>
       <c r="D91" s="108" t="str">
         <v>Return:
@@ -32751,7 +33424,7 @@
       <c r="S92" s="90"/>
       <c r="T92"/>
     </row>
-    <row r="93" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="93" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A93" s="105" t="str">
         <v>UTC043</v>
       </c>
@@ -32759,7 +33432,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C93" s="107" t="str">
-        <v>new NewRole("Thư ký phó", new string('m', 257), []); _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = 'm' × 257, Capabilities = [] }
+actorId = 0198ce6e-b572-7e5d-8a43-ff591635087c (generated)</v>
       </c>
       <c r="D93" s="108" t="str">
         <v>Return:
@@ -32817,7 +33491,7 @@
       <c r="S94" s="90"/>
       <c r="T94"/>
     </row>
-    <row r="95" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="95" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A95" s="105" t="str">
         <v>UTC044</v>
       </c>
@@ -32825,7 +33499,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C95" s="107" t="str">
-        <v>new NewRole("Thư ký phó", null, ["MinutesEditor", "DeleteEverything",…; _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = ["MinutesEditor", "DeleteEverything", "AlsoWrong"] }
+actorId = 0196d948-d0a8-79b2-bdd4-1ed9e0a8564b (generated)</v>
       </c>
       <c r="D95" s="108" t="str">
         <v>Return: RoleOutcome.InvalidInformation
@@ -32881,7 +33556,7 @@
       <c r="S96" s="90"/>
       <c r="T96"/>
     </row>
-    <row r="97" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="97" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A97" s="105" t="str">
         <v>UTC045</v>
       </c>
@@ -32889,7 +33564,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C97" s="107" t="str">
-        <v>capability="1"</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = ["1"] }
+actorId = 019f96cf-bccc-75f4-8c99-3443ee2d9e6d (generated)</v>
       </c>
       <c r="D97" s="108" t="str">
         <v>Return:
@@ -32923,7 +33599,7 @@
       <c r="S97" s="94"/>
       <c r="T97"/>
     </row>
-    <row r="98" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="98" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A98" s="105" t="str">
         <v>UTC046</v>
       </c>
@@ -32931,7 +33607,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C98" s="107" t="str">
-        <v>capability="99"</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = ["99"] }
+actorId = 019ad577-285d-7ba1-b938-bfe24f3f9bac (generated)</v>
       </c>
       <c r="D98" s="108" t="str">
         <v>Return:
@@ -32965,7 +33642,7 @@
       <c r="S98" s="94"/>
       <c r="T98"/>
     </row>
-    <row r="99" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="99" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A99" s="105" t="str">
         <v>UTC047</v>
       </c>
@@ -32973,7 +33650,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C99" s="107" t="str">
-        <v>capability="-1"</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = ["-1"] }
+actorId = 0191242c-d60e-7bda-9740-e0b1d39c3d41 (generated)</v>
       </c>
       <c r="D99" s="108" t="str">
         <v>Return:
@@ -33031,7 +33709,7 @@
       <c r="S100" s="90"/>
       <c r="T100"/>
     </row>
-    <row r="101" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="101" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A101" s="105" t="str">
         <v>UTC048</v>
       </c>
@@ -33039,7 +33717,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C101" s="107" t="str">
-        <v>new NewRole("Thư ký phó", null, ["MinutesEditor", null]); _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = ["MinutesEditor", null] }
+actorId = 0198ad12-087a-7f17-befa-54087a24d837 (generated)</v>
       </c>
       <c r="D101" s="108" t="str">
         <v>Return: "Quyền không hợp lệ: null."
@@ -33095,7 +33774,7 @@
       <c r="S102" s="90"/>
       <c r="T102"/>
     </row>
-    <row r="103" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="103" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A103" s="105" t="str">
         <v>UTC049</v>
       </c>
@@ -33103,7 +33782,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C103" s="107" t="str">
-        <v>new NewRole("", new string('m', 257), ["Nonsense"]); _actorId</v>
+        <v>request = NewRole { Name = "", Description = 'm' × 257, Capabilities = ["Nonsense"] }
+actorId = 019737a4-4a80-7457-8921-3af518201184 (generated)</v>
       </c>
       <c r="D103" s="108" t="str">
         <v>Return: ["capabilities", "description", "name"]
@@ -33159,7 +33839,7 @@
       <c r="S104" s="90"/>
       <c r="T104"/>
     </row>
-    <row r="105" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="105" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A105" s="105" t="str">
         <v>UTC050</v>
       </c>
@@ -33167,7 +33847,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C105" s="107" t="str">
-        <v>new NewRole("Thư ký phó", null, ["minuteseditor", "MinutesEditor", "M…; _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = ["minuteseditor", "MinutesEditor", "MEETINGCREATOR"] }
+actorId = 019c0dc4-4074-7a84-aec6-c6c2c57027ef (generated)</v>
       </c>
       <c r="D105" s="108" t="str">
         <v>Return: true
@@ -33223,7 +33904,7 @@
       <c r="S106" s="90"/>
       <c r="T106"/>
     </row>
-    <row r="107" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="107" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A107" s="105" t="str">
         <v>UTC051</v>
       </c>
@@ -33232,7 +33913,8 @@
 2. GivenCustomRole("Thư ký phó").</v>
       </c>
       <c r="C107" s="107" t="str">
-        <v>name="thư ký phó"</v>
+        <v>request = NewRole { Name = "thư ký phó", Description = null, Capabilities = [] }
+actorId = 01978990-c18e-7f37-86a7-31e5301bf9dc (generated)</v>
       </c>
       <c r="D107" s="108" t="str">
         <v>Return: RoleOutcome.DuplicateName
@@ -33264,7 +33946,7 @@
       <c r="S107" s="94"/>
       <c r="T107"/>
     </row>
-    <row r="108" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="108" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A108" s="105" t="str">
         <v>UTC052</v>
       </c>
@@ -33273,7 +33955,8 @@
 2. GivenCustomRole("Thư ký phó").</v>
       </c>
       <c r="C108" s="107" t="str">
-        <v>name="THƯ KÝ PHÓ"</v>
+        <v>request = NewRole { Name = "THƯ KÝ PHÓ", Description = null, Capabilities = [] }
+actorId = 019e5188-1f8b-7aa6-8f5d-bfbd8400a999 (generated)</v>
       </c>
       <c r="D108" s="108" t="str">
         <v>Return: RoleOutcome.DuplicateName
@@ -33305,7 +33988,7 @@
       <c r="S108" s="94"/>
       <c r="T108"/>
     </row>
-    <row r="109" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="109" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A109" s="105" t="str">
         <v>UTC053</v>
       </c>
@@ -33314,7 +33997,8 @@
 2. GivenCustomRole("Thư ký phó").</v>
       </c>
       <c r="C109" s="107" t="str">
-        <v>name="  Thư   ký phó "</v>
+        <v>request = NewRole { Name = "  Thư   ký phó ", Description = null, Capabilities = [] }
+actorId = 019e312f-3237-791e-9547-36fac1f3d4e8 (generated)</v>
       </c>
       <c r="D109" s="108" t="str">
         <v>Return: RoleOutcome.DuplicateName
@@ -33370,7 +34054,7 @@
       <c r="S110" s="90"/>
       <c r="T110"/>
     </row>
-    <row r="111" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="111" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A111" s="105" t="str">
         <v>UTC054</v>
       </c>
@@ -33379,7 +34063,8 @@
 2. GivenCustomRole("Thư ký phó").</v>
       </c>
       <c r="C111" s="107" t="str">
-        <v>new NewRole(decomposed, null, []); _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó".Normalize(System.Text.NormalizationForm.FormD), Description = null, Capabilities = [] }
+actorId = 019b9a97-acba-7028-b799-7c042fe189ce (generated)</v>
       </c>
       <c r="D111" s="108" t="str">
         <v>Return: RoleOutcome.DuplicateName
@@ -33435,7 +34120,7 @@
       <c r="S112" s="90"/>
       <c r="T112"/>
     </row>
-    <row r="113" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="113" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A113" s="105" t="str">
         <v>UTC055</v>
       </c>
@@ -33444,7 +34129,8 @@
 2. name = new string('ế', 64).Normalize(System.Text.NormalizationForm.FormD).</v>
       </c>
       <c r="C113" s="107" t="str">
-        <v>new NewRole(name, null, []); _actorId</v>
+        <v>request = NewRole { Name = 'ế' × 64).Normalize(System.Text.NormalizationForm.FormD, Description = null, Capabilities = [] }
+actorId = 0193005a-506d-73b9-905c-6f9ba01f97e7 (generated)</v>
       </c>
       <c r="D113" s="108" t="str">
         <v>Return:
@@ -33502,7 +34188,7 @@
       <c r="S114" s="90"/>
       <c r="T114"/>
     </row>
-    <row r="115" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="115" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A115" s="105" t="str">
         <v>UTC056</v>
       </c>
@@ -33510,7 +34196,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C115" s="107" t="str">
-        <v>new NewRole("thành viên", null, []); _actorId</v>
+        <v>request = NewRole { Name = "thành viên", Description = null, Capabilities = [] }
+actorId = 01908f20-1adb-77a6-8c6b-1843fa9bfc03 (generated)</v>
       </c>
       <c r="D115" s="108" t="str">
         <v>Return: RoleOutcome.DuplicateName
@@ -33575,7 +34262,8 @@
 2. _roles.NextSaveThrows = FakeRoleRepository.Refused(PostgresErrorCodes.UniqueViolation).</v>
       </c>
       <c r="C117" s="107" t="str">
-        <v>new NewRole("Thư ký phó", null, []); _actorId</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = [] }
+actorId = 0193c0ec-e7c1-73c8-9211-d976b75db22c (generated)</v>
       </c>
       <c r="D117" s="108" t="str">
         <v>Return: RoleOutcome.DuplicateName
@@ -33640,7 +34328,9 @@
 2. _roles.NextSaveThrows = fromTheDriver ? new NpgsqlException("connection lost") : new DbUpdateException("the datab….</v>
       </c>
       <c r="C119" s="107" t="str">
-        <v>fromTheDriver=true</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = [] }
+actorId = 019b0fc9-c3dc-73ce-9c68-458bfd0d0f1a (generated)
+fromTheDriver = true</v>
       </c>
       <c r="D119" s="108" t="str">
         <v>Return:
@@ -33683,7 +34373,9 @@
 2. _roles.NextSaveThrows = fromTheDriver ? new NpgsqlException("connection lost") : new DbUpdateException("the datab….</v>
       </c>
       <c r="C120" s="107" t="str">
-        <v>fromTheDriver=false</v>
+        <v>request = NewRole { Name = "Thư ký phó", Description = null, Capabilities = [] }
+actorId = 019db843-4675-7de5-8471-f31733d88943 (generated)
+fromTheDriver = false</v>
       </c>
       <c r="D120" s="108" t="str">
         <v>Return:
@@ -33741,7 +34433,7 @@
       <c r="S121" s="90"/>
       <c r="T121"/>
     </row>
-    <row r="122" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="122" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A122" s="105" t="str">
         <v>UTC060</v>
       </c>
@@ -33751,7 +34443,9 @@
 3. _roles.WithUsers(role.Id, 2).</v>
       </c>
       <c r="C122" s="107" t="str">
-        <v>role.Id; new RoleEdit("Phó thư ký", "Mô tả mới"); _actorId</v>
+        <v>id = 0199818e-ad5d-70c2-9429-a65a21e7a68b (generated)
+request = RoleEdit { Name = "Phó thư ký", Description = "Mô tả mới" }
+actorId = 0190767d-4238-77f6-85d3-ed50edc24da0 (generated)</v>
       </c>
       <c r="D122" s="108" t="str">
         <v>Return:
@@ -33820,7 +34514,9 @@
 2. role: prepared by GivenCustomRole ("Thư ký phó").</v>
       </c>
       <c r="C124" s="107" t="str">
-        <v>role.Id; new RoleEdit("Phó thư ký", null); _actorId</v>
+        <v>id = 019f6390-1a11-7406-9fbd-f69472c2fb07 (generated)
+request = RoleEdit { Name = "Phó thư ký", Description = null }
+actorId = 019b960b-5df9-7ca4-856f-0b9e7d36b728 (generated)</v>
       </c>
       <c r="D124" s="108" t="str">
         <v>Return:
@@ -33883,7 +34579,7 @@
       <c r="S125" s="90"/>
       <c r="T125"/>
     </row>
-    <row r="126" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="126" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A126" s="105" t="str">
         <v>UTC062</v>
       </c>
@@ -33892,7 +34588,9 @@
 2. role: prepared by GivenCustomRole.</v>
       </c>
       <c r="C126" s="107" t="str">
-        <v>role.Id; new RoleEdit("Phó thư ký", null); _actorId</v>
+        <v>id = 019a2e0b-7a44-7feb-b62d-e13b76042a0a (generated)
+request = RoleEdit { Name = "Phó thư ký", Description = null }
+actorId = 0192522b-eac2-7770-a2f8-2ba57f1ff999 (generated)</v>
       </c>
       <c r="D126" s="108" t="str">
         <v>Return: 0
@@ -33948,7 +34646,7 @@
       <c r="S127" s="90"/>
       <c r="T127"/>
     </row>
-    <row r="128" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="128" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A128" s="105" t="str">
         <v>UTC063</v>
       </c>
@@ -33956,7 +34654,9 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C128" s="107" t="str">
-        <v>Guid.CreateVersion7(); new RoleEdit("Tên", null); _actorId</v>
+        <v>id = 019fbd8f-2c94-799d-8f09-159ed09ad20a (generated)
+request = RoleEdit { Name = "Tên", Description = null }
+actorId = 019491e3-e360-7915-ab7f-83f03a76863a (generated)</v>
       </c>
       <c r="D128" s="108" t="str">
         <v>Return: RoleOutcome.NotFound
@@ -34080,7 +34780,7 @@
       <c r="S131" s="90"/>
       <c r="T131"/>
     </row>
-    <row r="132" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="132" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
       <c r="A132" s="105" t="str">
         <v>UTC065</v>
       </c>
@@ -34088,7 +34788,9 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C132" s="107" t="str">
-        <v>BuiltInRoles.Member; new RoleEdit("", null); _actorId</v>
+        <v>id = 01a0ce78-7204-7558-b181-e908a08e83a3
+request = RoleEdit { Name = "", Description = null }
+actorId = 0190438f-987d-71de-bb9b-ddfc2dd97f03 (generated)</v>
       </c>
       <c r="D132" s="108" t="str">
         <v>Return: RoleOutcome.BuiltInRole
@@ -34144,7 +34846,7 @@
       <c r="S133" s="90"/>
       <c r="T133"/>
     </row>
-    <row r="134" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="134" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A134" s="105" t="str">
         <v>UTC066</v>
       </c>
@@ -34153,7 +34855,9 @@
 2. role: prepared by GivenCustomRole.</v>
       </c>
       <c r="C134" s="107" t="str">
-        <v>role.Id; new RoleEdit(" ", new string('m', 257)); _actorId</v>
+        <v>id = 0198b34a-fb80-7bfa-a591-b4e1afbc3146 (generated)
+request = RoleEdit { Name = "   ", Description = 'm' × 257 }
+actorId = 019454a5-01b5-7d9f-8b65-46ec604f619c (generated)</v>
       </c>
       <c r="D134" s="108" t="str">
         <v>Return:
@@ -34211,7 +34915,7 @@
       <c r="S135" s="90"/>
       <c r="T135"/>
     </row>
-    <row r="136" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="136" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A136" s="105" t="str">
         <v>UTC067</v>
       </c>
@@ -34221,7 +34925,9 @@
 3. role: prepared by GivenCustomRole ("Thư ký phó").</v>
       </c>
       <c r="C136" s="107" t="str">
-        <v>role.Id; new RoleEdit("uỷ viên THƯỜNG trực", null); _actorId</v>
+        <v>id = 019edbac-5b3e-7064-9528-a4040d827382 (generated)
+request = RoleEdit { Name = "uỷ viên THƯỜNG trực", Description = null }
+actorId = 01982927-41a7-77fd-8400-835c9196c76b (generated)</v>
       </c>
       <c r="D136" s="108" t="str">
         <v>Return: RoleOutcome.DuplicateName
@@ -34277,7 +34983,7 @@
       <c r="S137" s="90"/>
       <c r="T137"/>
     </row>
-    <row r="138" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="138" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A138" s="105" t="str">
         <v>UTC068</v>
       </c>
@@ -34286,7 +34992,9 @@
 2. role: prepared by GivenCustomRole ("thư ký phó").</v>
       </c>
       <c r="C138" s="107" t="str">
-        <v>role.Id; new RoleEdit("Thư Ký Phó", "Hỗ trợ thư ký."); _actorId</v>
+        <v>id = 019dd468-df08-7013-bf5c-55289fca5871 (generated)
+request = RoleEdit { Name = "Thư Ký Phó", Description = "Hỗ trợ thư ký." }
+actorId = 019d1cd5-3238-75e3-9935-36b929cf9344 (generated)</v>
       </c>
       <c r="D138" s="108" t="str">
         <v>Return: true
@@ -34342,7 +35050,7 @@
       <c r="S139" s="90"/>
       <c r="T139"/>
     </row>
-    <row r="140" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="140" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A140" s="105" t="str">
         <v>UTC069</v>
       </c>
@@ -34351,7 +35059,9 @@
 2. role: prepared by GivenCustomRole ("Thư ký phó").</v>
       </c>
       <c r="C140" s="107" t="str">
-        <v>role.Id; new RoleEdit(" Thư ký phó ", " Hỗ trợ thư ký. "); _actorId</v>
+        <v>id = 019c3c91-8029-7c77-aea3-fa57724256d3 (generated)
+request = RoleEdit { Name = "  Thư ký  phó ", Description = " Hỗ trợ thư ký. " }
+actorId = 019b9b9d-791d-72db-9fbe-474f7809d551 (generated)</v>
       </c>
       <c r="D140" s="108" t="str">
         <v>Return:
@@ -34419,7 +35129,9 @@
 3. _roles.NextSaveThrows = FakeRoleRepository.Refused(PostgresErrorCodes.UniqueViolation).</v>
       </c>
       <c r="C142" s="107" t="str">
-        <v>role.Id; new RoleEdit("Phó thư ký", null); _actorId</v>
+        <v>id = 019e0ddd-d64b-74a4-8ad2-1af7be86ba8b (generated)
+request = RoleEdit { Name = "Phó thư ký", Description = null }
+actorId = 0190f7eb-4a4b-7df6-b166-9dae793595ba (generated)</v>
       </c>
       <c r="D142" s="108" t="str">
         <v>Return: RoleOutcome.DuplicateName
@@ -34485,7 +35197,9 @@
 3. _roles.NextSaveThrows = new DbUpdateConcurrencyException("0 rows affected").</v>
       </c>
       <c r="C144" s="107" t="str">
-        <v>role.Id; new RoleEdit("Phó thư ký", null); _actorId</v>
+        <v>id = 019274c8-0386-7f4a-850b-f7f9c7036c0a (generated)
+request = RoleEdit { Name = "Phó thư ký", Description = null }
+actorId = 019a64b3-3dc1-75d0-9e4d-ac39928b42cc (generated)</v>
       </c>
       <c r="D144" s="108" t="str">
         <v>Return: RoleOutcome.NotFound
@@ -34541,7 +35255,7 @@
       <c r="S145" s="90"/>
       <c r="T145"/>
     </row>
-    <row r="146" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="146" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A146" s="105" t="str">
         <v>UTC072</v>
       </c>
@@ -34551,7 +35265,9 @@
 3. _roles.NextSaveThrows = new DbUpdateException("the database said no").</v>
       </c>
       <c r="C146" s="107" t="str">
-        <v>role.Id; new RoleEdit("Phó thư ký", null); _actorId</v>
+        <v>id = 019c9525-2c4f-769e-9b2b-d624e30221da (generated)
+request = RoleEdit { Name = "Phó thư ký", Description = null }
+actorId = 0190001c-f8b6-77c6-8d75-28cd25e7a4ff (generated)</v>
       </c>
       <c r="D146" s="108" t="str">
         <v>Return: RoleOutcome.SaveFailed
@@ -34616,7 +35332,8 @@
 2. role: prepared by GivenCustomRole ("Thư ký phó", Capability.MinutesEditor).</v>
       </c>
       <c r="C148" s="107" t="str">
-        <v>role.Id; _actorId</v>
+        <v>id = 019556b4-e618-7583-a4a2-5cc57acd3a3c (generated)
+actorId = 019a9489-c973-79b5-946e-0f4ccf0db13d (generated)</v>
       </c>
       <c r="D148" s="108" t="str">
         <v>Return: true
@@ -34681,7 +35398,8 @@
 2. role: prepared by GivenCustomRole ("Thư ký phó", Capability.MinutesEditor, Capability.MeetingCreator).</v>
       </c>
       <c r="C150" s="107" t="str">
-        <v>role.Id; _actorId</v>
+        <v>id = 019372b2-36ea-7e13-a4a8-b9770cebfba1 (generated)
+actorId = 0191b79a-fe17-7ca0-882f-9663bec134fd (generated)</v>
       </c>
       <c r="D150" s="108" t="str">
         <v>Return:
@@ -34743,7 +35461,7 @@
       <c r="S151" s="90"/>
       <c r="T151"/>
     </row>
-    <row r="152" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="152" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A152" s="105" t="str">
         <v>UTC075</v>
       </c>
@@ -34752,7 +35470,8 @@
 2. role: prepared by GivenCustomRole.</v>
       </c>
       <c r="C152" s="107" t="str">
-        <v>role.Id; _actorId</v>
+        <v>id = 019c5e0c-65f1-7d01-8825-8b9cc5dd1415 (generated)
+actorId = 019d4aa6-906e-72c4-903c-57e2123b9e62 (generated)</v>
       </c>
       <c r="D152" s="108" t="str">
         <v>Return: 1
@@ -34808,7 +35527,7 @@
       <c r="S153" s="90"/>
       <c r="T153"/>
     </row>
-    <row r="154" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="154" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A154" s="105" t="str">
         <v>UTC076</v>
       </c>
@@ -34816,7 +35535,8 @@
         <v>1. RoleService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C154" s="107" t="str">
-        <v>Guid.CreateVersion7(); _actorId</v>
+        <v>id = 0194dcc0-1600-7c88-8120-4dc61d6831b6 (generated)
+actorId = 01902408-66b4-748a-9221-c19f7166f78e (generated)</v>
       </c>
       <c r="D154" s="108" t="str">
         <v>Return: RoleOutcome.NotFound
@@ -34950,7 +35670,8 @@
 3. _roles.WithUsers(role.Id, 3).</v>
       </c>
       <c r="C158" s="107" t="str">
-        <v>role.Id; _actorId</v>
+        <v>id = 0191599f-b888-7318-8aef-3115b1e8f362 (generated)
+actorId = 019d6e1a-f80c-728d-8d2d-0266243c8d52 (generated)</v>
       </c>
       <c r="D158" s="108" t="str">
         <v>Return:
@@ -35019,7 +35740,8 @@
 4. _roles.NextSaveThrows = FakeRoleRepository.Refused(PostgresErrorCodes.ForeignKeyViolation).</v>
       </c>
       <c r="C160" s="107" t="str">
-        <v>role.Id; _actorId</v>
+        <v>id = 0193fb2c-dce0-7829-80f0-2ab6759ff519 (generated)
+actorId = 01969d90-1ef9-7da0-81f3-df0d15818a56 (generated)</v>
       </c>
       <c r="D160" s="108" t="str">
         <v>Return:
@@ -35087,7 +35809,8 @@
 3. _roles.NextSaveThrows = new DbUpdateException("the database said no").</v>
       </c>
       <c r="C162" s="107" t="str">
-        <v>role.Id; _actorId</v>
+        <v>id = 019196be-f9d1-740c-99f0-a191d4a3d805 (generated)
+actorId = 019eb011-4320-738c-ab25-eb6259cc9ae8 (generated)</v>
       </c>
       <c r="D162" s="108" t="str">
         <v>Return: RoleOutcome.SaveFailed
@@ -35137,7 +35860,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -35544,7 +36267,7 @@
       <c r="S12" s="90"/>
       <c r="T12"/>
     </row>
-    <row r="13" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="13" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A13" s="105" t="str">
         <v>UTC001</v>
       </c>
@@ -35553,12 +36276,14 @@
 2. start = new DateTimeOffset(2026, 10, 12, 0, 0, 0, TimeSpan.Zero).</v>
       </c>
       <c r="C13" s="107" t="str">
-        <v>seconds=0</v>
+        <v>seconds = 0</v>
       </c>
       <c r="D13" s="108" t="str">
         <v>Return:
-1. ActualStartedAt: start
-2. Status: AgendaItemStatus.Done
+1. AgendaExecution.TryComplete(item, start.AddSeconds(seconds).AddTicks(7)): true
+2. (item.ActualEndedAt.Value - item.ActualStartedAt.Value).TotalSeconds: seconds
+3. item.ActualStartedAt: start
+4. item.Status: AgendaItemStatus.Done
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -35587,7 +36312,7 @@
       <c r="S13" s="94"/>
       <c r="T13"/>
     </row>
-    <row r="14" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="14" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A14" s="105" t="str">
         <v>UTC002</v>
       </c>
@@ -35596,12 +36321,14 @@
 2. start = new DateTimeOffset(2026, 10, 12, 0, 0, 0, TimeSpan.Zero).</v>
       </c>
       <c r="C14" s="107" t="str">
-        <v>seconds=1</v>
+        <v>seconds = 1</v>
       </c>
       <c r="D14" s="108" t="str">
         <v>Return:
-1. ActualStartedAt: start
-2. Status: AgendaItemStatus.Done
+1. AgendaExecution.TryComplete(item, start.AddSeconds(seconds).AddTicks(7)): true
+2. (item.ActualEndedAt.Value - item.ActualStartedAt.Value).TotalSeconds: seconds
+3. item.ActualStartedAt: start
+4. item.Status: AgendaItemStatus.Done
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -35630,7 +36357,7 @@
       <c r="S14" s="94"/>
       <c r="T14"/>
     </row>
-    <row r="15" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="15" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A15" s="105" t="str">
         <v>UTC003</v>
       </c>
@@ -35639,12 +36366,14 @@
 2. start = new DateTimeOffset(2026, 10, 12, 0, 0, 0, TimeSpan.Zero).</v>
       </c>
       <c r="C15" s="107" t="str">
-        <v>seconds=1200</v>
+        <v>seconds = 1200</v>
       </c>
       <c r="D15" s="108" t="str">
         <v>Return:
-1. ActualStartedAt: start
-2. Status: AgendaItemStatus.Done
+1. AgendaExecution.TryComplete(item, start.AddSeconds(seconds).AddTicks(7)): true
+2. (item.ActualEndedAt.Value - item.ActualStartedAt.Value).TotalSeconds: seconds
+3. item.ActualStartedAt: start
+4. item.Status: AgendaItemStatus.Done
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -35673,7 +36402,7 @@
       <c r="S15" s="94"/>
       <c r="T15"/>
     </row>
-    <row r="16" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="16" spans="1:20" s="93" customFormat="1" ht="167.5" outlineLevel="1" customHeight="1">
       <c r="A16" s="105" t="str">
         <v>UTC004</v>
       </c>
@@ -35682,12 +36411,14 @@
 2. start = new DateTimeOffset(2026, 10, 12, 0, 0, 0, TimeSpan.Zero).</v>
       </c>
       <c r="C16" s="107" t="str">
-        <v>seconds=1201</v>
+        <v>seconds = 1201</v>
       </c>
       <c r="D16" s="108" t="str">
         <v>Return:
-1. ActualStartedAt: start
-2. Status: AgendaItemStatus.Done
+1. AgendaExecution.TryComplete(item, start.AddSeconds(seconds).AddTicks(7)): true
+2. (item.ActualEndedAt.Value - item.ActualStartedAt.Value).TotalSeconds: seconds
+3. item.ActualStartedAt: start
+4. item.Status: AgendaItemStatus.Done
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -35740,7 +36471,7 @@
       <c r="S17" s="90"/>
       <c r="T17"/>
     </row>
-    <row r="18" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="18" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A18" s="105" t="str">
         <v>UTC005</v>
       </c>
@@ -35752,8 +36483,10 @@
       </c>
       <c r="D18" s="108" t="str">
         <v>Return:
-1. Status: AgendaItemStatus.InProgress
-2. ActualEndedAt: null
+1. AgendaExecution.TryComplete(item, DateTimeOffset.UtcNow): false
+2. AgendaExecution.TryComplete(item, DateTimeOffset.UtcNow): false
+3. item.Status: AgendaItemStatus.InProgress
+4. item.ActualEndedAt: null
 Exception: N/A
 Log Message: N/A</v>
       </c>
@@ -35816,7 +36549,7 @@
 3. b = new AgendaItem { Title = "B", Position = 8 }.</v>
       </c>
       <c r="C20" s="107" t="str">
-        <v>[a, b]</v>
+        <v>items = [AgendaItem { Title = "A", Position = 1 }, AgendaItem { Title = "B", Position = 8 }]</v>
       </c>
       <c r="D20" s="108" t="str">
         <v>Return:
@@ -35876,7 +36609,7 @@
       <c r="S21" s="90"/>
       <c r="T21"/>
     </row>
-    <row r="22" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="22" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A22" s="105" t="str">
         <v>UTC007</v>
       </c>
@@ -35884,7 +36617,7 @@
         <v>1. AgendaRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C22" s="107" t="str">
-        <v>new(" X ", "A\nB")</v>
+        <v>input = AgendaInput { Title = "  X  ", Description = "A\nB", PresenterId = null, PresenterGuestInvitationId = null, DocumentIds = null, OrderVersion = null, OrderedItemIds = null, Conclusion = null, ParseFai…</v>
       </c>
       <c r="D22" s="108" t="str">
         <v>Return:
@@ -35937,7 +36670,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -36353,7 +37086,7 @@
 2. Test data is seeded (MeetingStatus.InProgress).</v>
       </c>
       <c r="C13" s="107" t="str">
-        <v>differentTargets=false</v>
+        <v>differentTargets = false</v>
       </c>
       <c r="D13" s="108" t="str">
         <v>Return:
@@ -36396,7 +37129,7 @@
 2. Test data is seeded (MeetingStatus.InProgress).</v>
       </c>
       <c r="C14" s="107" t="str">
-        <v>differentTargets=true</v>
+        <v>differentTargets = true</v>
       </c>
       <c r="D14" s="108" t="str">
         <v>Return:
@@ -36464,7 +37197,7 @@
 3. switch (change) { case "ended": meeting.Status = MeetingStatus.Ended; break; case "secretary": (db.MeetingParticipants.FindAsync(s.Secretar….</v>
       </c>
       <c r="C16" s="107" t="str">
-        <v>change="ended"; expected=409</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D16" s="108" t="str">
         <v>Return:
@@ -36509,7 +37242,7 @@
 3. switch (change) { case "ended": meeting.Status = MeetingStatus.Ended; break; case "secretary": (db.MeetingParticipants.FindAsync(s.Secretar….</v>
       </c>
       <c r="C17" s="107" t="str">
-        <v>change="secretary"; expected=403</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D17" s="108" t="str">
         <v>Return:
@@ -36554,7 +37287,7 @@
 3. switch (change) { case "ended": meeting.Status = MeetingStatus.Ended; break; case "secretary": (db.MeetingParticipants.FindAsync(s.Secretar….</v>
       </c>
       <c r="C18" s="107" t="str">
-        <v>change="inactive"; expected=403</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D18" s="108" t="str">
         <v>Return:
@@ -36599,7 +37332,7 @@
 3. switch (change) { case "ended": meeting.Status = MeetingStatus.Ended; break; case "secretary": (db.MeetingParticipants.FindAsync(s.Secretar….</v>
       </c>
       <c r="C19" s="107" t="str">
-        <v>change="removed"; expected=409</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D19" s="108" t="str">
         <v>Return:
@@ -36644,7 +37377,7 @@
 3. switch (change) { case "ended": meeting.Status = MeetingStatus.Ended; break; case "secretary": (db.MeetingParticipants.FindAsync(s.Secretar….</v>
       </c>
       <c r="C20" s="107" t="str">
-        <v>change="revoked"; expected=409</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D20" s="108" t="str">
         <v>Return:
@@ -36689,7 +37422,7 @@
 3. switch (change) { case "ended": meeting.Status = MeetingStatus.Ended; break; case "secretary": (db.MeetingParticipants.FindAsync(s.Secretar….</v>
       </c>
       <c r="C21" s="107" t="str">
-        <v>change="newParticipant"; expected=200</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D21" s="108" t="str">
         <v>Return:
@@ -36734,7 +37467,7 @@
 3. switch (change) { case "ended": meeting.Status = MeetingStatus.Ended; break; case "secretary": (db.MeetingParticipants.FindAsync(s.Secretar….</v>
       </c>
       <c r="C22" s="107" t="str">
-        <v>change="response"; expected=200</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D22" s="108" t="str">
         <v>Return:
@@ -36779,7 +37512,7 @@
 3. switch (change) { case "ended": meeting.Status = MeetingStatus.Ended; break; case "secretary": (db.MeetingParticipants.FindAsync(s.Secretar….</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>change="targetRole"; expected=200</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return:
@@ -36916,7 +37649,7 @@
 2. Test data is seeded (MeetingStatus.InProgress).</v>
       </c>
       <c r="C27" s="107" t="str">
-        <v>f; s</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D27" s="108" t="str">
         <v>Return:
@@ -36974,7 +37707,7 @@
       <c r="S28" s="90"/>
       <c r="T28"/>
     </row>
-    <row r="29" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="29" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A29" s="105" t="str">
         <v>UTC013</v>
       </c>
@@ -36983,7 +37716,9 @@
 2. Test data is seeded (MeetingStatus.InProgress).</v>
       </c>
       <c r="C29" s="107" t="str">
-        <v>Save(client, s, Entry(s.MeetingId, s.MemberAssignment)); 200; "MSG147"</v>
+        <v>response = f.Client(f.Seed(MeetingStatus.InProgress).Secretary).PostAsJsonAsync(f.Seed(MeetingStatus.InProgress).Url + "/attendance", { object { f.Seed(MeetingStatus.InProgress).MemberAssignment, "Internal", at…
+status = 200
+code = "MSG147"</v>
       </c>
       <c r="D29" s="108" t="str">
         <v>Return:
@@ -37186,7 +37921,7 @@
 4. denied = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C35" s="107" t="str">
-        <v>secretary</v>
+        <v>actor = f.Client(f.Seed(MeetingStatus.InProgress).Secretary)</v>
       </c>
       <c r="D35" s="108" t="str">
         <v>Return:
@@ -37254,7 +37989,8 @@
 3. events = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C37" s="107" t="str">
-        <v>owner=true</v>
+        <v>actor = f.Client(f.Seed(MeetingStatus.InProgress).Organizer)
+owner = true</v>
       </c>
       <c r="D37" s="108" t="str">
         <v>Return:
@@ -37298,7 +38034,8 @@
 3. events = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C38" s="107" t="str">
-        <v>owner=false</v>
+        <v>actor = f.Client(f.Seed(MeetingStatus.InProgress).Member)
+owner = false</v>
       </c>
       <c r="D38" s="108" t="str">
         <v>Return:
@@ -37366,7 +38103,7 @@
 3. events = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C40" s="107" t="str">
-        <v>reason="inactive"</v>
+        <v>actor = f.Client(f.Seed(MeetingStatus.InProgress).Member)</v>
       </c>
       <c r="D40" s="108" t="str">
         <v>Return: completes without error
@@ -37408,7 +38145,7 @@
 3. events = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C41" s="107" t="str">
-        <v>reason="removed"</v>
+        <v>actor = f.Client(f.Seed(MeetingStatus.InProgress).Member)</v>
       </c>
       <c r="D41" s="108" t="str">
         <v>Return: completes without error
@@ -37475,7 +38212,7 @@
 4. eventsB = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C43" s="107" t="str">
-        <v>change="sessionRevoked"</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D43" s="108" t="str">
         <v>Return: completes without error
@@ -37518,7 +38255,7 @@
 4. eventsB = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C44" s="107" t="str">
-        <v>change="expired"</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D44" s="108" t="str">
         <v>Return: completes without error
@@ -37561,7 +38298,7 @@
 4. eventsB = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C45" s="107" t="str">
-        <v>change="unverified"</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D45" s="108" t="str">
         <v>Return: completes without error
@@ -37604,7 +38341,7 @@
 4. eventsB = Channel.CreateUnbounded&lt;AttendanceChange&gt;().</v>
       </c>
       <c r="C46" s="107" t="str">
-        <v>change="invitationRevoked"</v>
+        <v>s = f.Seed(MeetingStatus.InProgress)</v>
       </c>
       <c r="D46" s="108" t="str">
         <v>Return: completes without error
@@ -37660,7 +38397,7 @@
       <c r="S47" s="90"/>
       <c r="T47"/>
     </row>
-    <row r="48" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="48" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A48" s="105" t="str">
         <v>UTC025</v>
       </c>
@@ -37668,7 +38405,7 @@
         <v>1. AttendanceHub runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C48" s="107" t="str">
-        <v>new(Guid.CreateVersion7(), Guid.CreateVersion7(), Guid.CreateVersion7…; default</v>
+        <v>session = MeetingGuestSession { MeetingId = 0194f0e8-85a5-7621-9a9f-9b4c1713bc3a (generated), InvitationId = 019c0b61-a379-7ec2-89bc-ebaf6189b56f (generated), SessionId = 019b12ac-2ef6-7d0a-8aac-90fd44d22f63 (…</v>
       </c>
       <c r="D48" s="108" t="str">
         <v>Return:
@@ -37799,7 +38536,7 @@
       <c r="S51" s="90"/>
       <c r="T51"/>
     </row>
-    <row r="52" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="52" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A52" s="105" t="str">
         <v>UTC027</v>
       </c>
@@ -37808,7 +38545,10 @@
 2. original = CultureInfo.CurrentCulture.</v>
       </c>
       <c r="C52" s="107" t="str">
-        <v>meeting; "Internal"; entry; long.MaxValue</v>
+        <v>meetingId = 019eb376-8b7e-70dc-8e54-5f6366127710 (generated)
+kind = "Internal"
+entryId = 0196b956-e681-71c7-a85a-2ee89b7e4a5c (generated)
+version = long.MaxValue</v>
       </c>
       <c r="D52" s="108" t="str">
         <v>Return: matches "^[a-f0-9]{64}$"
@@ -37925,7 +38665,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -38341,7 +39081,8 @@
 2. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator, Capability.MinutesEditor).</v>
       </c>
       <c r="C13" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D13" s="108" t="str">
         <v>Return:
@@ -38410,7 +39151,8 @@
 2. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator).</v>
       </c>
       <c r="C15" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D15" s="108" t="str">
         <v>Return:
@@ -38479,7 +39221,8 @@
 3. _users.WithUser(user).WithCapabilities(BuiltInRoles.Chair, Capability.AdminUsers).</v>
       </c>
       <c r="C17" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D17" s="108" t="str">
         <v>Return: [Capability.AdminUsers]
@@ -38545,7 +39288,8 @@
 3. _users.WithUser(user).</v>
       </c>
       <c r="C19" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D19" s="108" t="str">
         <v>Return:
@@ -38613,7 +39357,8 @@
 3. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator).</v>
       </c>
       <c r="C21" s="107" t="str">
-        <v>" ThuKy@TrustCabinet.Local "; Password</v>
+        <v>email = "  ThuKy@TrustCabinet.Local  "
+password = "MatKhau@2026"</v>
       </c>
       <c r="D21" s="108" t="str">
         <v>Return: SignInOutcome.Success
@@ -38677,7 +39422,8 @@
         <v>1. AuthenticationService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>"khong-ton-tai@trustcabinet.local"; Password</v>
+        <v>email = "khong-ton-tai@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -38742,7 +39488,8 @@
 2. _users.WithUser(user).</v>
       </c>
       <c r="C25" s="107" t="str">
-        <v>user.Email; "SaiMatKhau@2026"</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "SaiMatKhau@2026"</v>
       </c>
       <c r="D25" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -38807,7 +39554,8 @@
 2. _users.WithUser(NewUser()).</v>
       </c>
       <c r="C27" s="107" t="str">
-        <v>"nobody@trustcabinet.local"; Password</v>
+        <v>email = "nobody@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D27" s="108" t="str">
         <v>Return:
@@ -38874,7 +39622,8 @@
         <v>1. AuthenticationService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C29" s="107" t="str">
-        <v>"nobody@trustcabinet.local"; Password</v>
+        <v>email = "nobody@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D29" s="108" t="str">
         <v>Return: 1
@@ -38938,7 +39687,8 @@
         <v>1. AuthenticationService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C31" s="107" t="str">
-        <v>"nobody@trustcabinet.local"; Password</v>
+        <v>email = "nobody@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D31" s="108" t="str">
         <v>Return:
@@ -39004,7 +39754,8 @@
         <v>1. AuthenticationService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C33" s="107" t="str">
-        <v>"nobody@trustcabinet.local"; Password</v>
+        <v>email = "nobody@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D33" s="108" t="str">
         <v>Return:
@@ -39073,7 +39824,8 @@
 4. afterUnknownEmail = _passwordHasher.VerifyCount - afterKnownEmail.</v>
       </c>
       <c r="C35" s="107" t="str">
-        <v>"thuky@trustcabinet.local"; "SaiMatKhau@2026"</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "SaiMatKhau@2026"</v>
       </c>
       <c r="D35" s="108" t="str">
         <v>Return: afterKnownEmail
@@ -39138,7 +39890,9 @@
 2. _users.WithUser(NewUser()).</v>
       </c>
       <c r="C37" s="107" t="str">
-        <v>email=""; password=Password</v>
+        <v>email = ""
+password = "MatKhau@2026"
+password = Password</v>
       </c>
       <c r="D37" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -39179,7 +39933,9 @@
 2. _users.WithUser(NewUser()).</v>
       </c>
       <c r="C38" s="107" t="str">
-        <v>email="   "; password=Password</v>
+        <v>email = "   "
+password = "MatKhau@2026"
+password = Password</v>
       </c>
       <c r="D38" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -39220,7 +39976,8 @@
 2. _users.WithUser(NewUser()).</v>
       </c>
       <c r="C39" s="107" t="str">
-        <v>email="thuky@trustcabinet.local"; password=""</v>
+        <v>email = "thuky@trustcabinet.local"
+password = ""</v>
       </c>
       <c r="D39" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -39261,7 +40018,8 @@
 2. _users.WithUser(NewUser()).</v>
       </c>
       <c r="C40" s="107" t="str">
-        <v>email="thuky@trustcabinet.local"; password="   "</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "   "</v>
       </c>
       <c r="D40" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -39326,7 +40084,8 @@
 2. _users.WithUser(NewUser()).</v>
       </c>
       <c r="C42" s="107" t="str">
-        <v>"thuky@trustcabinet.local"; "SaiMatKhau@2026"</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "SaiMatKhau@2026"</v>
       </c>
       <c r="D42" s="108" t="str">
         <v>Return:
@@ -39395,7 +40154,8 @@
 4. service: a new AuthenticationService is prepared.</v>
       </c>
       <c r="C44" s="107" t="str">
-        <v>user.Email; "SET-BY-SCRUM-11"</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "SET-BY-SCRUM-11"</v>
       </c>
       <c r="D44" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -39461,7 +40221,8 @@
 3. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator).</v>
       </c>
       <c r="C46" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D46" s="108" t="str">
         <v>Return: SignInOutcome.AccountDeactivated
@@ -39527,7 +40288,8 @@
 3. _users.WithUser(user).</v>
       </c>
       <c r="C48" s="107" t="str">
-        <v>user.Email; "SaiMatKhau@2026"</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "SaiMatKhau@2026"</v>
       </c>
       <c r="D48" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -39593,7 +40355,8 @@
 3. _users.WithUser(user).</v>
       </c>
       <c r="C50" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D50" s="108" t="str">
         <v>Return:
@@ -39663,7 +40426,8 @@
 5. _users.WithUser(user).</v>
       </c>
       <c r="C52" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D52" s="108" t="str">
         <v>Return:
@@ -39731,7 +40495,8 @@
 2. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator).</v>
       </c>
       <c r="C54" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D54" s="108" t="str">
         <v>Return:
@@ -39800,7 +40565,8 @@
 3. _users.WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor, Capability.AdminUsers).</v>
       </c>
       <c r="C56" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D56" s="108" t="str">
         <v>Return:
@@ -39867,7 +40633,8 @@
 2. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator).</v>
       </c>
       <c r="C58" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D58" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -39933,7 +40700,8 @@
 3. _users.OnFindById = () =&gt; throw new InvalidOperationException("database unavailable").</v>
       </c>
       <c r="C60" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D60" s="108" t="str">
         <v>Return: SignInOutcome.Success
@@ -39999,7 +40767,8 @@
 3. _refreshTokens.Now = DateTimeOffset.UtcNow.Add(_tokenIssuer.RefreshTokenLifetime).AddSeconds(1).</v>
       </c>
       <c r="C62" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D62" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -40063,7 +40832,7 @@
         <v>1. AuthenticationService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C64" s="107" t="str">
-        <v>token=""</v>
+        <v>refreshToken = ""</v>
       </c>
       <c r="D64" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -40103,7 +40872,7 @@
         <v>1. AuthenticationService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C65" s="107" t="str">
-        <v>token="   "</v>
+        <v>refreshToken = "   "</v>
       </c>
       <c r="D65" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -40143,7 +40912,7 @@
         <v>1. AuthenticationService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C66" s="107" t="str">
-        <v>token="khong-phai-token"</v>
+        <v>refreshToken = "khong-phai-token"</v>
       </c>
       <c r="D66" s="108" t="str">
         <v>Return: SignInOutcome.InvalidCredentials
@@ -40209,7 +40978,8 @@
 3. user.IsActive = false.</v>
       </c>
       <c r="C68" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D68" s="108" t="str">
         <v>Return: SignInOutcome.AccountDeactivated
@@ -40275,7 +41045,8 @@
 3. _users.WithCapabilities(BuiltInRoles.Secretary).</v>
       </c>
       <c r="C70" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D70" s="108" t="str">
         <v>Return:
@@ -40343,7 +41114,8 @@
 3. _users.WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator, Capability.MinutesEditor).</v>
       </c>
       <c r="C72" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D72" s="108" t="str">
         <v>Return: [Capability.MeetingCreator, Capability.MinutesEditor]
@@ -40408,7 +41180,8 @@
 2. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator).</v>
       </c>
       <c r="C74" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D74" s="108" t="str">
         <v>Return:
@@ -40475,7 +41248,8 @@
 2. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator).</v>
       </c>
       <c r="C76" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D76" s="108" t="str">
         <v>Return: completes without error
@@ -40540,7 +41314,8 @@
 2. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MeetingCreator).</v>
       </c>
       <c r="C78" s="107" t="str">
-        <v>user.Email; Password</v>
+        <v>email = "thuky@trustcabinet.local"
+password = "MatKhau@2026"</v>
       </c>
       <c r="D78" s="108" t="str">
         <v>Return: [phone.RefreshToken]
@@ -40606,7 +41381,7 @@
 3. _users.WithUser(NewGoogleUser()).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C80" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D80" s="108" t="str">
         <v>Return:
@@ -40675,7 +41450,7 @@
 3. _users.WithUser(NewGoogleUser()).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C82" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D82" s="108" t="str">
         <v>Return:
@@ -40745,7 +41520,7 @@
 4. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C84" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D84" s="108" t="str">
         <v>Return:
@@ -40813,7 +41588,7 @@
 3. _users.WithUser(NewGoogleUser(role: BuiltInRoles.Member)).</v>
       </c>
       <c r="C86" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D86" s="108" t="str">
         <v>Return:
@@ -40881,7 +41656,7 @@
 3. _users.WithUser(NewGoogleUser()).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C88" s="107" t="str">
-        <v>idToken=""</v>
+        <v>idToken = ""</v>
       </c>
       <c r="D88" s="108" t="str">
         <v>Return:
@@ -40925,7 +41700,7 @@
 3. _users.WithUser(NewGoogleUser()).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C89" s="107" t="str">
-        <v>idToken="   "</v>
+        <v>idToken = "   "</v>
       </c>
       <c r="D89" s="108" t="str">
         <v>Return:
@@ -40969,7 +41744,7 @@
 3. _users.WithUser(NewGoogleUser()).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C90" s="107" t="str">
-        <v>idToken="khong-phai-id-token"</v>
+        <v>idToken = "khong-phai-id-token"</v>
       </c>
       <c r="D90" s="108" t="str">
         <v>Return:
@@ -41035,7 +41810,7 @@
         <v>1. GoogleSignInService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C92" s="107" t="str">
-        <v>"khong-phai-id-token"</v>
+        <v>idToken = "khong-phai-id-token"</v>
       </c>
       <c r="D92" s="108" t="str">
         <v>Return: GoogleSignInOutcome.InvalidGoogleToken
@@ -41100,7 +41875,7 @@
 2. _google.WithValidToken(IdToken, "mot-sub-chua-ai-lien-ket", "nguoi.la@gmail.com").</v>
       </c>
       <c r="C94" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D94" s="108" t="str">
         <v>Return: GoogleSignInOutcome.NotLinked
@@ -41167,7 +41942,7 @@
 4. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C96" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D96" s="108" t="str">
         <v>Return: GoogleSignInOutcome.Success
@@ -41233,7 +42008,7 @@
 3. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C98" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D98" s="108" t="str">
         <v>Return: GoogleSignInOutcome.NotLinked
@@ -41300,7 +42075,7 @@
 4. _users.WithUser(user).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C100" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D100" s="108" t="str">
         <v>Return: GoogleSignInOutcome.AccountDeactivated
@@ -41366,7 +42141,7 @@
 3. _users.WithUser(NewGoogleUser(isActive: false)) .WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C102" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D102" s="108" t="str">
         <v>Return: GoogleSignInOutcome.NotLinked
@@ -41432,7 +42207,7 @@
 3. _users.WithUser(NewGoogleUser(isActive: false)) .WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C104" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D104" s="108" t="str">
         <v>Return: GoogleSignInOutcome.AccountDeactivated
@@ -41498,7 +42273,7 @@
 3. _users.WithUser(NewGoogleUser()).</v>
       </c>
       <c r="C106" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D106" s="108" t="str">
         <v>Return:
@@ -41630,7 +42405,7 @@
 3. _users.WithUser(NewGoogleUser()).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C110" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D110" s="108" t="str">
         <v>Return:
@@ -41698,7 +42473,7 @@
 3. _users.WithUser(NewGoogleUser()).WithCapabilities(BuiltInRoles.Secretary, Capability.MinutesEditor).</v>
       </c>
       <c r="C112" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D112" s="108" t="str">
         <v>Return:
@@ -41767,7 +42542,7 @@
 4. user.IsActive = false.</v>
       </c>
       <c r="C114" s="107" t="str">
-        <v>IdToken</v>
+        <v>idToken = "id-token-hop-le"</v>
       </c>
       <c r="D114" s="108" t="str">
         <v>Return: SignInOutcome.AccountDeactivated
@@ -41823,7 +42598,7 @@
       <c r="S115" s="90"/>
       <c r="T115"/>
     </row>
-    <row r="116" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="116" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A116" s="105" t="str">
         <v>UTC056</v>
       </c>
@@ -41831,7 +42606,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C116" s="107" t="str">
-        <v>new GoogleJsonWebSignature.Payload { Subject = "115742000000000000000…</v>
+        <v>payload = GoogleJsonWebSignature.Payload { Subject = "115742000000000000000", Email = "thuky@trustcabinet.local", EmailVerified = true }</v>
       </c>
       <c r="D116" s="108" t="str">
         <v>Return:
@@ -41890,7 +42665,7 @@
       <c r="S117" s="90"/>
       <c r="T117"/>
     </row>
-    <row r="118" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="118" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A118" s="105" t="str">
         <v>UTC057</v>
       </c>
@@ -41898,7 +42673,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C118" s="107" t="str">
-        <v>new GoogleJsonWebSignature.Payload { Subject = "115742000000000000000…</v>
+        <v>payload = GoogleJsonWebSignature.Payload { Subject = "115742000000000000000", Email = "thuky@trustcabinet.local", EmailVerified = false }</v>
       </c>
       <c r="D118" s="108" t="str">
         <v>Return: null
@@ -41954,7 +42729,7 @@
       <c r="S119" s="90"/>
       <c r="T119"/>
     </row>
-    <row r="120" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="120" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A120" s="105" t="str">
         <v>UTC058</v>
       </c>
@@ -41962,7 +42737,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C120" s="107" t="str">
-        <v>subject=null</v>
+        <v>payload = GoogleJsonWebSignature.Payload { Subject = null, Email = "thuky@trustcabinet.local", EmailVerified = true }</v>
       </c>
       <c r="D120" s="108" t="str">
         <v>Return: null
@@ -41994,7 +42769,7 @@
       <c r="S120" s="94"/>
       <c r="T120"/>
     </row>
-    <row r="121" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="121" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A121" s="105" t="str">
         <v>UTC059</v>
       </c>
@@ -42002,7 +42777,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C121" s="107" t="str">
-        <v>subject=""</v>
+        <v>payload = GoogleJsonWebSignature.Payload { Subject = "", Email = "thuky@trustcabinet.local", EmailVerified = true }</v>
       </c>
       <c r="D121" s="108" t="str">
         <v>Return: null
@@ -42034,7 +42809,7 @@
       <c r="S121" s="94"/>
       <c r="T121"/>
     </row>
-    <row r="122" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="122" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A122" s="105" t="str">
         <v>UTC060</v>
       </c>
@@ -42042,7 +42817,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C122" s="107" t="str">
-        <v>subject="   "</v>
+        <v>payload = GoogleJsonWebSignature.Payload { Subject = "   ", Email = "thuky@trustcabinet.local", EmailVerified = true }</v>
       </c>
       <c r="D122" s="108" t="str">
         <v>Return: null
@@ -42106,7 +42881,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C124" s="107" t="str">
-        <v>idToken=""</v>
+        <v>idToken = ""</v>
       </c>
       <c r="D124" s="108" t="str">
         <v>Return: null
@@ -42146,7 +42921,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C125" s="107" t="str">
-        <v>idToken="   "</v>
+        <v>idToken = "   "</v>
       </c>
       <c r="D125" s="108" t="str">
         <v>Return: null
@@ -42210,7 +42985,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C127" s="107" t="str">
-        <v>idToken="notajwt"</v>
+        <v>idToken = "notajwt"</v>
       </c>
       <c r="D127" s="108" t="str">
         <v>Return: null
@@ -42250,7 +43025,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C128" s="107" t="str">
-        <v>idToken="a.b"</v>
+        <v>idToken = "a.b"</v>
       </c>
       <c r="D128" s="108" t="str">
         <v>Return: null
@@ -42290,7 +43065,7 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C129" s="107" t="str">
-        <v>idToken="a.b.c"</v>
+        <v>idToken = "a.b.c"</v>
       </c>
       <c r="D129" s="108" t="str">
         <v>Return: null
@@ -42330,7 +43105,8 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C130" s="107" t="str">
-        <v>idToken="!!!.???.###"</v>
+        <v>idToken = "!!.???.###"
+idToken = "!!!.???.###"</v>
       </c>
       <c r="D130" s="108" t="str">
         <v>Return: null
@@ -42386,7 +43162,7 @@
       <c r="S131" s="90"/>
       <c r="T131"/>
     </row>
-    <row r="132" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="132" spans="1:20" s="93" customFormat="1" ht="225.5" outlineLevel="1" customHeight="1">
       <c r="A132" s="105" t="str">
         <v>UTC067</v>
       </c>
@@ -42394,7 +43170,10 @@
         <v>1. GoogleTokenVerifier runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C132" s="107" t="str">
-        <v>'.'; Base64Url("""{"alg":"RS256","kid":"forged"}"""); Base64Url($$""" {"iss":"accounts.google.com","sub":"11574200000000000…; Base64Url("chu-ky-gia")</v>
+        <v>'.'
+Base64Url("""{"alg":"RS256","kid":"forged"}""")
+Base64Url($$""" {"iss":"accounts.google.com","sub":"115742000000000000000", "email":"attacker@gmail.com","email_verified":true, "aud":"{{ClientId}}","exp":9999999999,"iat":1600000000} """)
+Base64Url("chu-ky-gia")</v>
       </c>
       <c r="D132" s="108" t="str">
         <v>Return: null
@@ -42450,7 +43229,7 @@
       <c r="S133" s="90"/>
       <c r="T133"/>
     </row>
-    <row r="134" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="134" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A134" s="105" t="str">
         <v>UTC068</v>
       </c>
@@ -42458,7 +43237,7 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C134" s="107" t="str">
-        <v>NewIssuer().CreateAccessToken(Secretary, [])</v>
+        <v>token = CreateAccessToken(User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }, [])</v>
       </c>
       <c r="D134" s="108" t="str">
         <v>Return:
@@ -42516,7 +43295,7 @@
       <c r="S135" s="90"/>
       <c r="T135"/>
     </row>
-    <row r="136" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="136" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A136" s="105" t="str">
         <v>UTC069</v>
       </c>
@@ -42524,7 +43303,7 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C136" s="107" t="str">
-        <v>NewIssuer().CreateAccessToken( Secretary, [Capability.MeetingCreator,…</v>
+        <v>token = CreateAccessToken(User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }, [Capability.MeetingCreator,…</v>
       </c>
       <c r="D136" s="108" t="str">
         <v>Return: ["MeetingCreator", "MinutesEditor"]
@@ -42580,7 +43359,7 @@
       <c r="S137" s="90"/>
       <c r="T137"/>
     </row>
-    <row r="138" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="138" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A138" s="105" t="str">
         <v>UTC070</v>
       </c>
@@ -42588,7 +43367,7 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C138" s="107" t="str">
-        <v>NewIssuer().CreateAccessToken(Secretary, [])</v>
+        <v>token = CreateAccessToken(User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }, [])</v>
       </c>
       <c r="D138" s="108" t="str">
         <v>Return: does not contain token.Claims
@@ -42644,7 +43423,7 @@
       <c r="S139" s="90"/>
       <c r="T139"/>
     </row>
-    <row r="140" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="140" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A140" s="105" t="str">
         <v>UTC071</v>
       </c>
@@ -42652,7 +43431,8 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C140" s="107" t="str">
-        <v>Secretary; []</v>
+        <v>user = User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }
+capabilities = []</v>
       </c>
       <c r="D140" s="108" t="str">
         <v>Return: does not contain "khong-lien-quan"
@@ -42708,7 +43488,7 @@
       <c r="S141" s="90"/>
       <c r="T141"/>
     </row>
-    <row r="142" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="142" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A142" s="105" t="str">
         <v>UTC072</v>
       </c>
@@ -42716,7 +43496,7 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C142" s="107" t="str">
-        <v>issuer.CreateAccessToken(Secretary, [])</v>
+        <v>token = CreateAccessToken(User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }, [])</v>
       </c>
       <c r="D142" s="108" t="str">
         <v>Return: not first
@@ -42772,7 +43552,7 @@
       <c r="S143" s="90"/>
       <c r="T143"/>
     </row>
-    <row r="144" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="144" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A144" s="105" t="str">
         <v>UTC073</v>
       </c>
@@ -42781,7 +43561,7 @@
 2. issuer = NewIssuer(new AuthenticationOptions { SigningKey = SigningKey, AccessTokenMinutes = 5 }).</v>
       </c>
       <c r="C144" s="107" t="str">
-        <v>issuer.CreateAccessToken(Secretary, [])</v>
+        <v>token = CreateAccessToken(User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }, [])</v>
       </c>
       <c r="D144" s="108" t="str">
         <v>Return: between DateTime.UtcNow.AddMinutes(4) and DateTime.UtcNow.AddMinutes(6)
@@ -42837,7 +43617,7 @@
       <c r="S145" s="90"/>
       <c r="T145"/>
     </row>
-    <row r="146" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="146" spans="1:20" s="93" customFormat="1" ht="298.0" outlineLevel="1" customHeight="1">
       <c r="A146" s="105" t="str">
         <v>UTC074</v>
       </c>
@@ -42845,7 +43625,8 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C146" s="107" t="str">
-        <v>raw; Parameters(SigningKey); out _</v>
+        <v>CreateAccessToken(User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }, [Capability.MeetingCreator])
+TokenValidationParameters { ValidateIssuer = true, ValidIssuer = "TrustCabinet", ValidateAudience = true, ValidAudience = "TrustCabinet", ValidateLifetime = true, ValidateIssuerSigningKey = true, Iss…</v>
       </c>
       <c r="D146" s="108" t="str">
         <v>Return: Secretary.Id
@@ -42901,7 +43682,7 @@
       <c r="S147" s="90"/>
       <c r="T147"/>
     </row>
-    <row r="148" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="148" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A148" s="105" t="str">
         <v>UTC075</v>
       </c>
@@ -42909,7 +43690,8 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C148" s="107" t="str">
-        <v>Secretary; []</v>
+        <v>user = User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }
+capabilities = []</v>
       </c>
       <c r="D148" s="108" t="str">
         <v>Return: N/A
@@ -42965,7 +43747,7 @@
       <c r="S149" s="90"/>
       <c r="T149"/>
     </row>
-    <row r="150" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="150" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A150" s="105" t="str">
         <v>UTC076</v>
       </c>
@@ -42974,7 +43756,8 @@
 2. tampered = raw[..^1] + (raw[^1] == 'A' ? 'B' : 'A').</v>
       </c>
       <c r="C150" s="107" t="str">
-        <v>Secretary; []</v>
+        <v>user = User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }
+capabilities = []</v>
       </c>
       <c r="D150" s="108" t="str">
         <v>Return: N/A
@@ -43030,7 +43813,7 @@
       <c r="S151" s="90"/>
       <c r="T151"/>
     </row>
-    <row r="152" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="152" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A152" s="105" t="str">
         <v>UTC077</v>
       </c>
@@ -43039,7 +43822,8 @@
 2. foreign = NewIssuer(new AuthenticationOptions { SigningKey = SigningKey, Issuer = "SomethingElse",….</v>
       </c>
       <c r="C152" s="107" t="str">
-        <v>Secretary; []</v>
+        <v>user = User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }
+capabilities = []</v>
       </c>
       <c r="D152" s="108" t="str">
         <v>Return: N/A
@@ -43095,7 +43879,7 @@
       <c r="S153" s="90"/>
       <c r="T153"/>
     </row>
-    <row r="154" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="154" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A154" s="105" t="str">
         <v>UTC078</v>
       </c>
@@ -43103,7 +43887,7 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C154" s="107" t="str">
-        <v>NewIssuer().CreateAccessToken(Secretary, [])</v>
+        <v>token = CreateAccessToken(User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }, [])</v>
       </c>
       <c r="D154" s="108" t="str">
         <v>Return: does not contain token.Claims
@@ -43159,7 +43943,7 @@
       <c r="S155" s="90"/>
       <c r="T155"/>
     </row>
-    <row r="156" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="156" spans="1:20" s="93" customFormat="1" ht="283.5" outlineLevel="1" customHeight="1">
       <c r="A156" s="105" t="str">
         <v>UTC079</v>
       </c>
@@ -43168,7 +43952,8 @@
 2. laggingClock.LifetimeValidator = (notBefore, expires, _, _) =&gt; { var theirNow = DateTime.UtcNow.AddSeconds(-30); return (n….</v>
       </c>
       <c r="C156" s="107" t="str">
-        <v>raw; laggingClock; out _</v>
+        <v>CreateAccessToken(User { FullName = "Nguyễn Thư Ký", Email = "thuky@trustcabinet.local", PasswordHash = "khong-lien-quan", RoleId = 01a0ce78-7203-7c7f-8326-7a0baebf4c22 }, [Capability.AdminUsers])
+TokenValidationParameters { ValidateIssuer = true, ValidIssuer = "TrustCabinet", ValidateAudience = true, ValidAudience = "TrustCabinet", ValidateLifetime = true, ValidateIssuerSigningKey = true, Iss…</v>
       </c>
       <c r="D156" s="108" t="str">
         <v>Return: Secretary.Id
@@ -43232,7 +44017,8 @@
         <v>1. JwtTokenIssuer runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C158" s="107" t="str">
-        <v>0; 100</v>
+        <v>0
+100</v>
       </c>
       <c r="D158" s="108" t="str">
         <v>Return: 100
@@ -43360,7 +44146,7 @@
         <v>1. PasswordHasher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C162" s="107" t="str">
-        <v>"MatKhau@2026"</v>
+        <v>password = "MatKhau@2026"</v>
       </c>
       <c r="D162" s="108" t="str">
         <v>Return: true
@@ -43424,7 +44210,7 @@
         <v>1. PasswordHasher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C164" s="107" t="str">
-        <v>"MatKhau@2026"</v>
+        <v>password = "MatKhau@2026"</v>
       </c>
       <c r="D164" s="108" t="str">
         <v>Return: false
@@ -43488,7 +44274,7 @@
         <v>1. PasswordHasher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C166" s="107" t="str">
-        <v>"MatKhau@2026"</v>
+        <v>password = "MatKhau@2026"</v>
       </c>
       <c r="D166" s="108" t="str">
         <v>Return: false
@@ -43552,7 +44338,7 @@
         <v>1. PasswordHasher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C168" s="107" t="str">
-        <v>"MatKhau@2026"</v>
+        <v>password = "MatKhau@2026"</v>
       </c>
       <c r="D168" s="108" t="str">
         <v>Return: does not contain "MatKhau"
@@ -43616,7 +44402,7 @@
         <v>1. PasswordHasher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C170" s="107" t="str">
-        <v>"MatKhau@2026"</v>
+        <v>password = "MatKhau@2026"</v>
       </c>
       <c r="D170" s="108" t="str">
         <v>Return: not first
@@ -43744,7 +44530,7 @@
         <v>1. PasswordHasher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C174" s="107" t="str">
-        <v>storedHash=""</v>
+        <v>storedHash = ""</v>
       </c>
       <c r="D174" s="108" t="str">
         <v>Return: false
@@ -43784,7 +44570,7 @@
         <v>1. PasswordHasher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C175" s="107" t="str">
-        <v>storedHash="khong-phai-hash"</v>
+        <v>storedHash = "khong-phai-hash"</v>
       </c>
       <c r="D175" s="108" t="str">
         <v>Return: false
@@ -43824,7 +44610,7 @@
         <v>1. PasswordHasher runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C176" s="107" t="str">
-        <v>storedHash="SET-BY-SCRUM-11"</v>
+        <v>storedHash = "SET-BY-SCRUM-11"</v>
       </c>
       <c r="D176" s="108" t="str">
         <v>Return: false
@@ -43938,7 +44724,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -44414,7 +45200,7 @@
       <c r="S14" s="90"/>
       <c r="T14"/>
     </row>
-    <row r="15" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="15" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A15" s="105" t="str">
         <v>UTC002</v>
       </c>
@@ -44422,7 +45208,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C15" s="107" t="str">
-        <v>status=MeetingStatus.InProgress; mode=MeetingMode.Online; expected=CallRoomStatus.Open</v>
+        <v>status = MeetingStatus.InProgress
+mode = MeetingMode.Online
+expected = CallRoomStatus.Open</v>
       </c>
       <c r="D15" s="108" t="str">
         <v>Return: expected
@@ -44454,7 +45242,7 @@
       <c r="S15" s="94"/>
       <c r="T15"/>
     </row>
-    <row r="16" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="16" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A16" s="105" t="str">
         <v>UTC003</v>
       </c>
@@ -44462,7 +45250,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C16" s="107" t="str">
-        <v>status=MeetingStatus.InProgress; mode=MeetingMode.Hybrid; expected=CallRoomStatus.Open</v>
+        <v>status = MeetingStatus.InProgress
+mode = MeetingMode.Hybrid
+expected = CallRoomStatus.Open</v>
       </c>
       <c r="D16" s="108" t="str">
         <v>Return: expected
@@ -44494,7 +45284,7 @@
       <c r="S16" s="94"/>
       <c r="T16"/>
     </row>
-    <row r="17" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="17" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A17" s="105" t="str">
         <v>UTC004</v>
       </c>
@@ -44502,7 +45292,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C17" s="107" t="str">
-        <v>status=MeetingStatus.InProgress; mode=MeetingMode.InPerson; expected=CallRoomStatus.InPersonOnly</v>
+        <v>status = MeetingStatus.InProgress
+mode = MeetingMode.InPerson
+expected = CallRoomStatus.InPersonOnly</v>
       </c>
       <c r="D17" s="108" t="str">
         <v>Return: expected
@@ -44534,7 +45326,7 @@
       <c r="S17" s="94"/>
       <c r="T17"/>
     </row>
-    <row r="18" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="18" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A18" s="105" t="str">
         <v>UTC005</v>
       </c>
@@ -44542,7 +45334,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C18" s="107" t="str">
-        <v>status=MeetingStatus.Published; mode=MeetingMode.Online; expected=CallRoomStatus.NotStarted</v>
+        <v>status = MeetingStatus.Published
+mode = MeetingMode.Online
+expected = CallRoomStatus.NotStarted</v>
       </c>
       <c r="D18" s="108" t="str">
         <v>Return: expected
@@ -44574,7 +45368,7 @@
       <c r="S18" s="94"/>
       <c r="T18"/>
     </row>
-    <row r="19" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="19" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A19" s="105" t="str">
         <v>UTC006</v>
       </c>
@@ -44582,7 +45376,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C19" s="107" t="str">
-        <v>status=MeetingStatus.Ended; mode=MeetingMode.Online; expected=CallRoomStatus.Ended</v>
+        <v>status = MeetingStatus.Ended
+mode = MeetingMode.Online
+expected = CallRoomStatus.Ended</v>
       </c>
       <c r="D19" s="108" t="str">
         <v>Return: expected
@@ -44614,7 +45410,7 @@
       <c r="S19" s="94"/>
       <c r="T19"/>
     </row>
-    <row r="20" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="20" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A20" s="105" t="str">
         <v>UTC007</v>
       </c>
@@ -44622,7 +45418,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C20" s="107" t="str">
-        <v>status=MeetingStatus.Cancelled; mode=MeetingMode.Online; expected=CallRoomStatus.Cancelled</v>
+        <v>status = MeetingStatus.Cancelled
+mode = MeetingMode.Online
+expected = CallRoomStatus.Cancelled</v>
       </c>
       <c r="D20" s="108" t="str">
         <v>Return: expected
@@ -44654,7 +45452,7 @@
       <c r="S20" s="94"/>
       <c r="T20"/>
     </row>
-    <row r="21" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="21" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A21" s="105" t="str">
         <v>UTC008</v>
       </c>
@@ -44662,7 +45460,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C21" s="107" t="str">
-        <v>status=MeetingStatus.Cancelled; mode=MeetingMode.InPerson; expected=CallRoomStatus.InPersonOnly</v>
+        <v>status = MeetingStatus.Cancelled
+mode = MeetingMode.InPerson
+expected = CallRoomStatus.InPersonOnly</v>
       </c>
       <c r="D21" s="108" t="str">
         <v>Return: expected
@@ -44718,7 +45518,7 @@
       <c r="S22" s="90"/>
       <c r="T22"/>
     </row>
-    <row r="23" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="23" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A23" s="105" t="str">
         <v>UTC009</v>
       </c>
@@ -44726,7 +45526,8 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>_meetingId; _chair</v>
+        <v>meetingId = 01979efe-62f3-77f4-99d4-821f61a30999 (generated)
+actorId = 0194259f-2099-7b09-b1ca-2edeea60b423 (generated)</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return: CallOutcome.Success
@@ -44790,7 +45591,8 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C25" s="107" t="str">
-        <v>_meetingId; _member</v>
+        <v>meetingId = 0195987e-ad71-784a-9e92-70b1ee0cbf03 (generated)
+actorId = 019e12d5-947e-78a2-842e-916b513d0f92 (generated)</v>
       </c>
       <c r="D25" s="108" t="str">
         <v>Return:
@@ -44851,7 +45653,7 @@
       <c r="S26" s="90"/>
       <c r="T26"/>
     </row>
-    <row r="27" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="27" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A27" s="105" t="str">
         <v>UTC011</v>
       </c>
@@ -44859,7 +45661,8 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C27" s="107" t="str">
-        <v>_meetingId; _member</v>
+        <v>meetingId = 01957621-6701-7c5d-90cf-37760364ea84 (generated)
+actorId = 01919a24-7bcc-7f10-84ac-e17081603ee9 (generated)</v>
       </c>
       <c r="D27" s="108" t="str">
         <v>Return: CallOutcome.ReadFailed
@@ -44915,7 +45718,7 @@
       <c r="S28" s="90"/>
       <c r="T28"/>
     </row>
-    <row r="29" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="29" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
       <c r="A29" s="105" t="str">
         <v>UTC012</v>
       </c>
@@ -44923,7 +45726,8 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C29" s="107" t="str">
-        <v>Room; _chair</v>
+        <v>room = CallRoomNames.ForMeeting(0195c93a-a5b6-7087-9d79-cbb1fc2202fd (generated))
+participant = 01981e98-fab9-7601-a713-d0a97f2c5772 (generated)</v>
       </c>
       <c r="D29" s="108" t="str">
         <v>Return:
@@ -44981,7 +45785,7 @@
       <c r="S30" s="90"/>
       <c r="T30"/>
     </row>
-    <row r="31" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
+    <row r="31" spans="1:20" s="93" customFormat="1" ht="182.0" outlineLevel="1" customHeight="1">
       <c r="A31" s="105" t="str">
         <v>UTC013</v>
       </c>
@@ -44989,7 +45793,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C31" s="107" t="str">
-        <v>Room; _member; new RoomTrack("TR_mic", CallTrackSource.Microphone, Muted: false)</v>
+        <v>room = CallRoomNames.ForMeeting(019a1704-d808-71c0-8072-a1e8a601cc22 (generated))
+userId = 019dc508-a276-763f-97c2-1440caf3249d (generated)
+tracks = RoomTrack { Sid = "TR_mic", Source = CallTrackSource.Microphone, Muted = false }</v>
       </c>
       <c r="D31" s="108" t="str">
         <v>Return:
@@ -45057,7 +45863,9 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C33" s="107" t="str">
-        <v>_meetingId; _chair; MeetingRole.Chair</v>
+        <v>meetingId = 0191ff28-399d-79ad-9720-f4b2cb2d675b (generated)
+userId = 0197038e-b611-743b-a3c3-e98736fb0bdd (generated)
+role = MeetingRole.Chair</v>
       </c>
       <c r="D33" s="108" t="str">
         <v>Return:
@@ -45117,7 +45925,7 @@
       <c r="S34" s="90"/>
       <c r="T34"/>
     </row>
-    <row r="35" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="35" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A35" s="105" t="str">
         <v>UTC015</v>
       </c>
@@ -45126,7 +45934,8 @@
 2. joinedAt = DateTimeOffset.UtcNow.AddMinutes(-3).</v>
       </c>
       <c r="C35" s="107" t="str">
-        <v>joined</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 01979a88-7fe6-70ef-afc8-9f39f716fab9 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(0191a268-85bc-7c41-b14e-1b6bb7490d3b…
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D35" s="108" t="str">
         <v>Return:
@@ -45188,7 +45997,7 @@
       <c r="S36" s="90"/>
       <c r="T36"/>
     </row>
-    <row r="37" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="37" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A37" s="105" t="str">
         <v>UTC016</v>
       </c>
@@ -45196,7 +46005,10 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C37" s="107" t="str">
-        <v>status=MeetingStatus.Ended; mode=MeetingMode.Online</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 019686e5-b231-7211-a6f8-f46aee776882 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(0195a308-fab2-7751-b554-678afe222328…
+status = MeetingStatus.Ended
+mode = MeetingMode.Online
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D37" s="108" t="str">
         <v>Return:
@@ -45231,7 +46043,7 @@
       <c r="S37" s="94"/>
       <c r="T37"/>
     </row>
-    <row r="38" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="38" spans="1:20" s="93" customFormat="1" ht="254.5" outlineLevel="1" customHeight="1">
       <c r="A38" s="105" t="str">
         <v>UTC017</v>
       </c>
@@ -45239,7 +46051,10 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C38" s="107" t="str">
-        <v>status=MeetingStatus.InProgress; mode=MeetingMode.InPerson</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 019fe97c-7da7-7d66-9824-20e027e03fee (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(01957524-7104-7fca-ac89-dbd1e87bbc7d…
+status = MeetingStatus.InProgress
+mode = MeetingMode.InPerson
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D38" s="108" t="str">
         <v>Return:
@@ -45298,7 +46113,7 @@
       <c r="S39" s="90"/>
       <c r="T39"/>
     </row>
-    <row r="40" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
+    <row r="40" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A40" s="105" t="str">
         <v>UTC018</v>
       </c>
@@ -45306,7 +46121,8 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C40" s="107" t="str">
-        <v>Webhook("participant_joined", _member)</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 0198237c-5cfe-7301-a845-7f63ed59c498 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(019fca7f-9364-7ed1-8eef-3042b092fc3a…
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D40" s="108" t="str">
         <v>Return:
@@ -45364,7 +46180,7 @@
       <c r="S41" s="90"/>
       <c r="T41"/>
     </row>
-    <row r="42" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="42" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A42" s="105" t="str">
         <v>UTC019</v>
       </c>
@@ -45372,7 +46188,8 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C42" s="107" t="str">
-        <v>Webhook("participant_joined", _member) with { RoomName = "direct-x" }</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 019ab214-69d5-777c-96cf-2ec3f84e0df7 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(0196948b-e368-77e4-ab2b-889622bc30b1…
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D42" s="108" t="str">
         <v>Return: empty
@@ -45428,7 +46245,7 @@
       <c r="S43" s="90"/>
       <c r="T43"/>
     </row>
-    <row r="44" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
+    <row r="44" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A44" s="105" t="str">
         <v>UTC020</v>
       </c>
@@ -45436,7 +46253,8 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C44" s="107" t="str">
-        <v>Webhook("track_published", _member) with { TrackSource = CallTrackSou…</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 01931cfb-bc4a-7aeb-969b-5a179935a1cc (generated).ToString("N"), Event = "track_published", RoomName = CallRoomNames.ForMeeting(01970584-aa5a-7126-a6c3-c32a3755e6da (ge…
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D44" s="108" t="str">
         <v>Return: (Room, _chair.ToString("D"), "TR_old")
@@ -45492,7 +46310,7 @@
       <c r="S45" s="90"/>
       <c r="T45"/>
     </row>
-    <row r="46" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="46" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A46" s="105" t="str">
         <v>UTC021</v>
       </c>
@@ -45501,7 +46319,8 @@
 2. _calls.MeetingStatusOverride[_meetingId] = MeetingStatus.Ended.</v>
       </c>
       <c r="C46" s="107" t="str">
-        <v>Webhook("participant_joined", _member)</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 0191e55e-e6dc-7547-a6a1-9b911a650f43 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(019acbd9-5a99-7ffe-aacd-af2a6b1a87cc…
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D46" s="108" t="str">
         <v>Return:
@@ -45560,7 +46379,7 @@
       <c r="S47" s="90"/>
       <c r="T47"/>
     </row>
-    <row r="48" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
+    <row r="48" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A48" s="105" t="str">
         <v>UTC022</v>
       </c>
@@ -45568,7 +46387,8 @@
         <v>1. CallRoomService runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C48" s="107" t="str">
-        <v>Webhook("participant_joined", _chair)</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 0192df99-b016-7aa7-9bcc-147b985e253c (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(01924a95-010b-7a65-89aa-927490e30321…
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D48" s="108" t="str">
         <v>Return:
@@ -45627,7 +46447,7 @@
       <c r="S49" s="90"/>
       <c r="T49"/>
     </row>
-    <row r="50" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="50" spans="1:20" s="93" customFormat="1" ht="196.5" outlineLevel="1" customHeight="1">
       <c r="A50" s="105" t="str">
         <v>UTC023</v>
       </c>
@@ -45636,7 +46456,8 @@
 2. _options.EnforceRoster = false.</v>
       </c>
       <c r="C50" s="107" t="str">
-        <v>Webhook("participant_joined", _member)</v>
+        <v>webhook = CallWebhookEvent { Id = "EV_" + 0197f548-b518-70f0-8f68-da1041a0c0af (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(0199a7da-a6e4-75ba-84dd-9642895b0c71…
+(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
       </c>
       <c r="D50" s="108" t="str">
         <v>Return: empty
@@ -45767,7 +46588,8 @@
         <v>1. LiveKitWebhookParsing runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C54" s="107" t="str">
-        <v>body; Sign(body)</v>
+        <v>body = Encoding.UTF8.GetBytes(RoomFinished)
+authorizationHeader = Sign(Encoding.UTF8.GetBytes(RoomFinished))</v>
       </c>
       <c r="D54" s="108" t="str">
         <v>Return:
@@ -45835,7 +46657,8 @@
         <v>1. LiveKitWebhookParsing runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C56" s="107" t="str">
-        <v>body; Sign(body)</v>
+        <v>body = Encoding.UTF8.GetBytes(TrackPublished)
+authorizationHeader = Sign(Encoding.UTF8.GetBytes(TrackPublished))</v>
       </c>
       <c r="D56" s="108" t="str">
         <v>Return:
@@ -45904,7 +46727,7 @@
 2. body[10] ^= 1.</v>
       </c>
       <c r="C58" s="107" t="str">
-        <v>body</v>
+        <v>body = Encoding.UTF8.GetBytes(RoomFinished)</v>
       </c>
       <c r="D58" s="108" t="str">
         <v>Return: null
@@ -45968,7 +46791,7 @@
         <v>1. LiveKitWebhookParsing runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C60" s="107" t="str">
-        <v>RoomFinished</v>
+        <v>"""{"event":"room_finished","room":{"sid":"RM_X5eULkqkUoEu","name":"meeting-0192f5c4-8a4e-7d2b-9c1a-3f6e5d4c3b2a","emptyTimeout":300,"departureTimeout":20,"creationTime":"1790732775","creationTimeMs"…</v>
       </c>
       <c r="D60" s="108" t="str">
         <v>Return:
@@ -46027,7 +46850,7 @@
       <c r="S61" s="90"/>
       <c r="T61"/>
     </row>
-    <row r="62" spans="1:20" s="93" customFormat="1" ht="124.0" outlineLevel="1" customHeight="1">
+    <row r="62" spans="1:20" s="93" customFormat="1" ht="153.0" outlineLevel="1" customHeight="1">
       <c r="A62" s="105" t="str">
         <v>UTC029</v>
       </c>
@@ -46036,7 +46859,7 @@
 2. gateway = new LiveKitGateway(Options.Create(new LiveKitOptions()), new NoHttp()).</v>
       </c>
       <c r="C62" s="107" t="str">
-        <v>RoomFinished</v>
+        <v>"""{"event":"room_finished","room":{"sid":"RM_X5eULkqkUoEu","name":"meeting-0192f5c4-8a4e-7d2b-9c1a-3f6e5d4c3b2a","emptyTimeout":300,"departureTimeout":20,"creationTime":"1790732775","creationTimeMs"…</v>
       </c>
       <c r="D62" s="108" t="str">
         <v>Return:
@@ -46088,7 +46911,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC373AC-D315-4E8F-9B4E-BFF882E3FF09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -46702,7 +47525,7 @@
       <c r="S18" s="90"/>
       <c r="T18"/>
     </row>
-    <row r="19" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="19" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
       <c r="A19" s="105" t="str">
         <v>UTC004</v>
       </c>
@@ -46710,7 +47533,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C19" s="107" t="str">
-        <v>input="C:\\Users\\me\\Báo cáo.pdf"; expected="Báo cáo.pdf"</v>
+        <v>fileName = "C:\\Users\\me\\Báo cáo.pdf"
+expected = "Báo cáo.pdf"</v>
       </c>
       <c r="D19" s="108" t="str">
         <v>Return: expected
@@ -46742,7 +47566,7 @@
       <c r="S19" s="94"/>
       <c r="T19"/>
     </row>
-    <row r="20" spans="1:20" s="93" customFormat="1" ht="51.5" outlineLevel="1" customHeight="1">
+    <row r="20" spans="1:20" s="93" customFormat="1" ht="66.0" outlineLevel="1" customHeight="1">
       <c r="A20" s="105" t="str">
         <v>UTC005</v>
       </c>
@@ -46750,7 +47574,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C20" s="107" t="str">
-        <v>input="  thư mục/tờ trình.docx "; expected="tờ trình.docx"</v>
+        <v>fileName = "  thư mục/tờ trình.docx "
+expected = "tờ trình.docx"</v>
       </c>
       <c r="D20" s="108" t="str">
         <v>Return: expected
@@ -46790,7 +47615,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C21" s="107" t="str">
-        <v>input=""; expected=null</v>
+        <v>fileName = ""
+expected = null</v>
       </c>
       <c r="D21" s="108" t="str">
         <v>Return: expected
@@ -46830,7 +47656,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C22" s="107" t="str">
-        <v>input="a/"; expected=null</v>
+        <v>fileName = "a/"
+expected = null</v>
       </c>
       <c r="D22" s="108" t="str">
         <v>Return: expected
@@ -46870,7 +47697,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C23" s="107" t="str">
-        <v>input="tab\there.pdf"; expected=null</v>
+        <v>fileName = "tab\there.pdf"
+expected = null</v>
       </c>
       <c r="D23" s="108" t="str">
         <v>Return: expected
@@ -46910,7 +47738,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C24" s="107" t="str">
-        <v>input="Bao cao‮xcod.pdf"; expected=null</v>
+        <v>fileName = "Bao cao‮xcod.pdf"
+expected = null</v>
       </c>
       <c r="D24" s="108" t="str">
         <v>Return: expected
@@ -46950,7 +47779,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C25" s="107" t="str">
-        <v>input="a​b.pdf"; expected=null</v>
+        <v>fileName = "a​b.pdf"
+expected = null</v>
       </c>
       <c r="D25" s="108" t="str">
         <v>Return: expected
@@ -47014,7 +47844,7 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C27" s="107" t="str">
-        <v>new string('a', 251) + ".pdf"</v>
+        <v>fileName = 'a' × 251 + ".pdf"</v>
       </c>
       <c r="D27" s="108" t="str">
         <v>Return:
@@ -47080,7 +47910,7 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C29" s="107" t="str">
-        <v>meeting</v>
+        <v>meeting = Meeting { Title = "Họp", PlannedStartTime = 2026-10-23T17:00:00Z }</v>
       </c>
       <c r="D29" s="108" t="str">
         <v>Return:
@@ -47138,7 +47968,7 @@
       <c r="S30" s="90"/>
       <c r="T30"/>
     </row>
-    <row r="31" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="31" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A31" s="105" t="str">
         <v>UTC013</v>
       </c>
@@ -47146,7 +47976,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C31" s="107" t="str">
-        <v>name="poly.html"; pdfBytes=true</v>
+        <v>candidates = [{ "poly.html", SampleFiles.Pdf().Length, () =&gt; new MemoryStream(bytes), null }]
+pdfBytes = true</v>
       </c>
       <c r="D31" s="108" t="str">
         <v>Return: name == "BAO-CAO.PDF" ? DocumentUploadFailure.None : DocumentUploadFailure.Invalid
@@ -47178,7 +48009,7 @@
       <c r="S31" s="94"/>
       <c r="T31"/>
     </row>
-    <row r="32" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="32" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A32" s="105" t="str">
         <v>UTC014</v>
       </c>
@@ -47186,7 +48017,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C32" s="107" t="str">
-        <v>name="x.pdf.exe"; pdfBytes=true</v>
+        <v>candidates = [{ "x.pdf.exe", SampleFiles.Pdf().Length, () =&gt; new MemoryStream(bytes), null }]
+pdfBytes = true</v>
       </c>
       <c r="D32" s="108" t="str">
         <v>Return: name == "BAO-CAO.PDF" ? DocumentUploadFailure.None : DocumentUploadFailure.Invalid
@@ -47226,7 +48058,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C33" s="107" t="str">
-        <v>name=".."; pdfBytes=true</v>
+        <v>candidates = [{ "..", SampleFiles.Pdf().Length, () =&gt; new MemoryStream(bytes), null }]
+pdfBytes = true</v>
       </c>
       <c r="D33" s="108" t="str">
         <v>Return: name == "BAO-CAO.PDF" ? DocumentUploadFailure.None : DocumentUploadFailure.Invalid
@@ -47258,7 +48091,7 @@
       <c r="S33" s="94"/>
       <c r="T33"/>
     </row>
-    <row r="34" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="34" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A34" s="105" t="str">
         <v>UTC016</v>
       </c>
@@ -47266,7 +48099,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C34" s="107" t="str">
-        <v>name="du-thao.pdf"; pdfBytes=false</v>
+        <v>candidates = [{ "du-thao.pdf", SampleFiles.Docx().Length, () =&gt; new MemoryStream(bytes), null }]
+pdfBytes = false</v>
       </c>
       <c r="D34" s="108" t="str">
         <v>Return: name == "BAO-CAO.PDF" ? DocumentUploadFailure.None : DocumentUploadFailure.Invalid
@@ -47298,7 +48132,7 @@
       <c r="S34" s="94"/>
       <c r="T34"/>
     </row>
-    <row r="35" spans="1:20" s="93" customFormat="1" ht="80.5" outlineLevel="1" customHeight="1">
+    <row r="35" spans="1:20" s="93" customFormat="1" ht="95.0" outlineLevel="1" customHeight="1">
       <c r="A35" s="105" t="str">
         <v>UTC017</v>
       </c>
@@ -47306,7 +48140,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C35" s="107" t="str">
-        <v>name="BAO-CAO.PDF"; pdfBytes=true</v>
+        <v>candidates = [{ "BAO-CAO.PDF", SampleFiles.Pdf().Length, () =&gt; new MemoryStream(bytes), null }]
+pdfBytes = true</v>
       </c>
       <c r="D35" s="108" t="str">
         <v>Return: name == "BAO-CAO.PDF" ? DocumentUploadFailure.None : DocumentUploadFailure.Invalid
@@ -47370,7 +48205,8 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C37" s="107" t="str">
-        <v>0; 5</v>
+        <v>0
+5</v>
       </c>
       <c r="D37" s="108" t="str">
         <v>Return:
@@ -47428,7 +48264,7 @@
       <c r="S38" s="90"/>
       <c r="T38"/>
     </row>
-    <row r="39" spans="1:20" s="93" customFormat="1" ht="109.5" outlineLevel="1" customHeight="1">
+    <row r="39" spans="1:20" s="93" customFormat="1" ht="138.5" outlineLevel="1" customHeight="1">
       <c r="A39" s="105" t="str">
         <v>UTC019</v>
       </c>
@@ -47436,7 +48272,7 @@
         <v>1. DocumentFileRules runs in process; its dependencies are fakes or stubs.</v>
       </c>
       <c r="C39" s="107" t="str">
-        <v>[ new("ok.pdf", 10, () =&gt; new MemoryStream(SampleFiles.Pdf()), "4"),…; default</v>
+        <v>candidates = [{ "ok.pdf", 10, () =&gt; new MemoryStream(SampleFiles.Pdf()), "4" }, { "rong.pdf", 0, () =&gt; new MemoryStream(), null }, { "anh.pdf", 16, () =&gt; new MemoryStream(SampleFiles.Png()), null }]</v>
       </c>
       <c r="D39" s="108" t="str">
         <v>Return:

--- a/docs/08-reports/test-reports/Report5.1_Unit_Test.xlsx
+++ b/docs/08-reports/test-reports/Report5.1_Unit_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\TrustCabinet\artifacts\test-report-build\template-edition\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18EDBB6E-31EF-438D-9DB4-7DFD237EED1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F5BD32F-D8E0-4F03-97FC-5A7790A6E3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="641" xr2:uid="{F2F39266-E81B-480E-9EC2-6124A2D61A65}" activeTab="0" firstSheet="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="641" xr2:uid="{AB2F6659-BE8F-4379-ABDF-41AA593B86FC}" activeTab="0" firstSheet="0"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="sheet1"/>
@@ -41,290 +41,286 @@
   <fonts count="44">
     <font>
       <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="20"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="52"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color indexed="23"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="17"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color indexed="12"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="62"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="52"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="60"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="63"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color indexed="56"/>
-      <name val="Cambria"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="ＭＳ ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="26"/>
       <color indexed="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color indexed="8"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="60"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color indexed="17"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="9"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color indexed="12"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="9"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="10"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color indexed="8"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
       <color indexed="12"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="30">
@@ -1579,15 +1575,15 @@
     <cellStyle name="Linked Cell" xfId="36" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="37" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_Functional Test Case v1.0" xfId="38" xr:uid="{0849A3DE-A885-4038-9296-9ECD047E5C24}"/>
-    <cellStyle name="Normal_Sheet1" xfId="39" xr:uid="{7D176B20-EBBC-4670-AF06-B407D855B490}"/>
-    <cellStyle name="Normal_Template_UnitTest Case_v0.9" xfId="40" xr:uid="{9D6BCDA0-0344-403C-8DCF-85EC4131754A}"/>
+    <cellStyle name="Normal_Functional Test Case v1.0" xfId="38" xr:uid="{4E346C50-61F1-4AA2-881F-EC4E9242EE33}"/>
+    <cellStyle name="Normal_Sheet1" xfId="39" xr:uid="{5A8D3F87-8528-4A37-9442-28870C25DFD2}"/>
+    <cellStyle name="Normal_Template_UnitTest Case_v0.9" xfId="40" xr:uid="{C2DAFCC6-8239-4E5C-B498-14C5542EE239}"/>
     <cellStyle name="Note" xfId="41" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="42" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="43" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="44" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="45" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="46" xr:uid="{60842961-AA5C-4BD0-8437-AF46D55B8D6C}"/>
+    <cellStyle name="標準_結合試験(AllOvertheWorld)" xfId="46" xr:uid="{30122DEA-AF32-48DA-99A7-CAAD2E9DBB07}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1627,9 +1623,9 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="ＭＳ Ｐゴシック"/>
-                <a:ea typeface="ＭＳ Ｐゴシック"/>
-                <a:cs typeface="ＭＳ Ｐゴシック"/>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1689,7 +1685,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-8817-445C-9A95-6D9F73656B3C}"/>
+                <c16:uniqueId val="{00000000-3DB0-4F76-922D-A0FFDBFF694D}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1709,7 +1705,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-8817-445C-9A95-6D9F73656B3C}"/>
+                <c16:uniqueId val="{00000001-3DB0-4F76-922D-A0FFDBFF694D}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1729,7 +1725,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-8817-445C-9A95-6D9F73656B3C}"/>
+                <c16:uniqueId val="{00000002-3DB0-4F76-922D-A0FFDBFF694D}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1752,9 +1748,9 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="ＭＳ Ｐゴシック"/>
-                    <a:ea typeface="ＭＳ Ｐゴシック"/>
-                    <a:cs typeface="ＭＳ Ｐゴシック"/>
+                    <a:latin typeface="Times New Roman"/>
+                    <a:ea typeface="Times New Roman"/>
+                    <a:cs typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -1808,7 +1804,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-8817-445C-9A95-6D9F73656B3C}"/>
+              <c16:uniqueId val="{00000003-3DB0-4F76-922D-A0FFDBFF694D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1863,9 +1859,9 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="ＭＳ Ｐゴシック"/>
-              <a:ea typeface="ＭＳ Ｐゴシック"/>
-              <a:cs typeface="ＭＳ Ｐゴシック"/>
+              <a:latin typeface="Times New Roman"/>
+              <a:ea typeface="Times New Roman"/>
+              <a:cs typeface="Times New Roman"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -1896,9 +1892,9 @@
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
-          <a:latin typeface="ＭＳ Ｐゴシック"/>
-          <a:ea typeface="ＭＳ Ｐゴシック"/>
-          <a:cs typeface="ＭＳ Ｐゴシック"/>
+          <a:latin typeface="Times New Roman"/>
+          <a:ea typeface="Times New Roman"/>
+          <a:cs typeface="Times New Roman"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -1937,9 +1933,9 @@
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="ＭＳ Ｐゴシック"/>
-                <a:ea typeface="ＭＳ Ｐゴシック"/>
-                <a:cs typeface="ＭＳ Ｐゴシック"/>
+                <a:latin typeface="Times New Roman"/>
+                <a:ea typeface="Times New Roman"/>
+                <a:cs typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -1999,7 +1995,7 @@
             <c:bubble3D val="0"/>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000000-10F8-41BB-A90B-FBED645AB6CB}"/>
+                <c16:uniqueId val="{00000000-12E0-41BD-8532-25C43E0B509B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2019,7 +2015,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-10F8-41BB-A90B-FBED645AB6CB}"/>
+                <c16:uniqueId val="{00000001-12E0-41BD-8532-25C43E0B509B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2039,7 +2035,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-10F8-41BB-A90B-FBED645AB6CB}"/>
+                <c16:uniqueId val="{00000002-12E0-41BD-8532-25C43E0B509B}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2062,9 +2058,9 @@
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="ＭＳ Ｐゴシック"/>
-                    <a:ea typeface="ＭＳ Ｐゴシック"/>
-                    <a:cs typeface="ＭＳ Ｐゴシック"/>
+                    <a:latin typeface="Times New Roman"/>
+                    <a:ea typeface="Times New Roman"/>
+                    <a:cs typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -2118,7 +2114,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-10F8-41BB-A90B-FBED645AB6CB}"/>
+              <c16:uniqueId val="{00000003-12E0-41BD-8532-25C43E0B509B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2173,9 +2169,9 @@
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:latin typeface="ＭＳ Ｐゴシック"/>
-              <a:ea typeface="ＭＳ Ｐゴシック"/>
-              <a:cs typeface="ＭＳ Ｐゴシック"/>
+              <a:latin typeface="Times New Roman"/>
+              <a:ea typeface="Times New Roman"/>
+              <a:cs typeface="Times New Roman"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -2206,9 +2202,9 @@
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
-          <a:latin typeface="ＭＳ Ｐゴシック"/>
-          <a:ea typeface="ＭＳ Ｐゴシック"/>
-          <a:cs typeface="ＭＳ Ｐゴシック"/>
+          <a:latin typeface="Times New Roman"/>
+          <a:ea typeface="Times New Roman"/>
+          <a:cs typeface="Times New Roman"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -2242,7 +2238,7 @@
         <xdr:cNvPr id="1143" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF795424-E923-7B34-A3A1-2D35F6424194}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1259D24-47FC-DB6A-8345-40025742BEDC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2321,7 +2317,7 @@
         <xdr:cNvPr id="2283" name="Chart 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{211708ED-54E1-C89E-95AE-8C77B31176D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A43FC3EB-17A1-7815-9880-C20B13CFA650}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2359,7 +2355,7 @@
         <xdr:cNvPr id="2284" name="Chart 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB5D027F-9D77-14D6-346B-0BA80D7FC922}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{076DFB8F-916D-299D-8D58-5EF57AB6FA25}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2425,74 +2421,74 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
+        <a:font script="Jpan" typeface="Times New Roman"/>
+        <a:font script="Hang" typeface="Times New Roman"/>
+        <a:font script="Hans" typeface="Times New Roman"/>
+        <a:font script="Hant" typeface="Times New Roman"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Thai" typeface="Times New Roman"/>
+        <a:font script="Ethi" typeface="Times New Roman"/>
+        <a:font script="Beng" typeface="Times New Roman"/>
+        <a:font script="Gujr" typeface="Times New Roman"/>
+        <a:font script="Khmr" typeface="Times New Roman"/>
+        <a:font script="Knda" typeface="Times New Roman"/>
+        <a:font script="Guru" typeface="Times New Roman"/>
+        <a:font script="Cans" typeface="Times New Roman"/>
+        <a:font script="Cher" typeface="Times New Roman"/>
+        <a:font script="Yiii" typeface="Times New Roman"/>
+        <a:font script="Tibt" typeface="Times New Roman"/>
+        <a:font script="Thaa" typeface="Times New Roman"/>
+        <a:font script="Deva" typeface="Times New Roman"/>
+        <a:font script="Telu" typeface="Times New Roman"/>
+        <a:font script="Taml" typeface="Times New Roman"/>
+        <a:font script="Syrc" typeface="Times New Roman"/>
+        <a:font script="Orya" typeface="Times New Roman"/>
+        <a:font script="Mlym" typeface="Times New Roman"/>
+        <a:font script="Laoo" typeface="Times New Roman"/>
+        <a:font script="Sinh" typeface="Times New Roman"/>
+        <a:font script="Mong" typeface="Times New Roman"/>
         <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Uigh" typeface="Times New Roman"/>
+        <a:font script="Geor" typeface="Times New Roman"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
+        <a:font script="Jpan" typeface="Times New Roman"/>
+        <a:font script="Hang" typeface="Times New Roman"/>
+        <a:font script="Hans" typeface="Times New Roman"/>
+        <a:font script="Hant" typeface="Times New Roman"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Times New Roman"/>
+        <a:font script="Ethi" typeface="Times New Roman"/>
+        <a:font script="Beng" typeface="Times New Roman"/>
+        <a:font script="Gujr" typeface="Times New Roman"/>
+        <a:font script="Khmr" typeface="Times New Roman"/>
+        <a:font script="Knda" typeface="Times New Roman"/>
+        <a:font script="Guru" typeface="Times New Roman"/>
+        <a:font script="Cans" typeface="Times New Roman"/>
+        <a:font script="Cher" typeface="Times New Roman"/>
+        <a:font script="Yiii" typeface="Times New Roman"/>
+        <a:font script="Tibt" typeface="Times New Roman"/>
+        <a:font script="Thaa" typeface="Times New Roman"/>
+        <a:font script="Deva" typeface="Times New Roman"/>
+        <a:font script="Telu" typeface="Times New Roman"/>
+        <a:font script="Taml" typeface="Times New Roman"/>
+        <a:font script="Syrc" typeface="Times New Roman"/>
+        <a:font script="Orya" typeface="Times New Roman"/>
+        <a:font script="Mlym" typeface="Times New Roman"/>
+        <a:font script="Laoo" typeface="Times New Roman"/>
+        <a:font script="Sinh" typeface="Times New Roman"/>
+        <a:font script="Mong" typeface="Times New Roman"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Times New Roman"/>
+        <a:font script="Geor" typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office 2007 - 2010">
@@ -2668,7 +2664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAFEEBDD-2240-420E-9655-FD684C8C98FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424C54E1-1486-420B-9A33-4AC742E0EA7E}">
   <dimension ref="A2:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -2898,7 +2894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5280,7 +5276,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9865,7 +9861,7 @@
         <v>input = MeetingInput { Title = null, PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Interna…
 actorId = 0199fb77-7481-77ef-b77b-790118cfa525 (generated)
 participants = [{ 0199fb77-7481-77ef-b77b-790118cfa525 (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D121" s="108" t="str">
         <v>Return:
@@ -9911,7 +9907,7 @@
         <v>input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
 actorId = 019cea92-687d-73ba-a726-f6593c7179a0 (generated)
 participants = [{ 019cea92-687d-73ba-a726-f6593c7179a0 (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D122" s="108" t="str">
         <v>Return:
@@ -9957,7 +9953,7 @@
         <v>input = MeetingInput { Title = "   ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Intern…
 actorId = 01976757-af95-7799-8365-077991d5fc68 (generated)
 participants = [{ 01976757-af95-7799-8365-077991d5fc68 (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D123" s="108" t="str">
         <v>Return:
@@ -10026,7 +10022,7 @@
         <v>input = MeetingInput { Title = 'a' × 301, PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "0", Location = 'b' × 301, OnlineLink = null, Sensitivity = "not-a-sensiti…
 actorId = 019049de-1aca-7bbf-a58c-305fab06f061 (generated)
 participants = [{ 019049de-1aca-7bbf-a58c-305fab06f061 (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D125" s="108" t="str">
         <v>Return:
@@ -10101,7 +10097,7 @@
 actorId = 0197b94d-22a4-7d7b-b9ad-d75c8b202db9 (generated)
 participants = [{ 0197b94d-22a4-7d7b-b9ad-d75c8b202db9 (generated), "Chair" }]
 sensitivity = "Normal"
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D127" s="108" t="str">
         <v>Return: true
@@ -10145,7 +10141,7 @@
 actorId = 01929d09-b91b-7157-8ebd-2632ac549172 (generated)
 participants = [{ 01929d09-b91b-7157-8ebd-2632ac549172 (generated), "Chair" }]
 sensitivity = "Internal"
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D128" s="108" t="str">
         <v>Return: true
@@ -10189,7 +10185,7 @@
 actorId = 019e0e26-f60e-7773-9116-2114e62e252f (generated)
 participants = [{ 019e0e26-f60e-7773-9116-2114e62e252f (generated), "Chair" }]
 sensitivity = "Confidential"
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D129" s="108" t="str">
         <v>Return: true
@@ -10233,7 +10229,7 @@
 actorId = 019bbcf5-c494-7324-9ee1-8ad955624709 (generated)
 participants = [{ 019bbcf5-c494-7324-9ee1-8ad955624709 (generated), "Chair" }]
 sensitivity = "Secret"
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D130" s="108" t="str">
         <v>Return: true
@@ -10300,7 +10296,7 @@
         <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = null, Location = "Phòng họp A", OnlineLink = null, Sensitivity = nul…
 actorId = 019b13dd-1bc1-75ab-8534-8e1db8f99bbb (generated)
 participants = [{ 019b13dd-1bc1-75ab-8534-8e1db8f99bbb (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D132" s="108" t="str">
         <v>Return: true
@@ -10367,7 +10363,7 @@
         <v>input = MeetingInput { Title = 't' × 300, PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = 'l' × 300, OnlineLink = null, Sensitivity = "Intern…
 actorId = 0195f162-780f-71d1-abd2-1f366d7dcc10 (generated)
 participants = [{ 0195f162-780f-71d1-abd2-1f366d7dcc10 (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D134" s="108" t="str">
         <v>Return: true
@@ -10435,7 +10431,7 @@
         <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
 actorId = 0194eb83-f9fd-7a63-bc92-785e67769e15 (generated)
 participants = [{ 0194eb83-f9fd-7a63-bc92-785e67769e15 (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D136" s="108" t="str">
         <v>Return: true
@@ -10503,7 +10499,7 @@
 actorId = 0193bf77-06e0-712f-8b39-a2d01ebc9412 (generated)
 participants = [{ 0193bf77-06e0-712f-8b39-a2d01ebc9412 (generated), "Chair" }]
 start = "2099-03-01 09:00"
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D138" s="108" t="str">
         <v>Return:
@@ -10549,7 +10545,7 @@
 actorId = 0196214b-4db7-7293-8741-96108c4565ea (generated)
 participants = [{ 0196214b-4db7-7293-8741-96108c4565ea (generated), "Chair" }]
 start = "2099-03-01T09:00:00"
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D139" s="108" t="str">
         <v>Return:
@@ -10595,7 +10591,7 @@
 actorId = 019698e2-7ee3-72b5-8897-ad9e4a27a9d2 (generated)
 participants = [{ 019698e2-7ee3-72b5-8897-ad9e4a27a9d2 (generated), "Chair" }]
 start = "not a time"
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D140" s="108" t="str">
         <v>Return:
@@ -10664,9 +10660,9 @@
       </c>
       <c r="C142" s="107" t="str">
         <v>id = 0192a02c-63da-75da-89f1-db0df08a10a7 (generated)
-input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-10-29T10:36:00Z", PlannedEndTime = "2026-10-29T11:36:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
+input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-10-29T11:09:00Z", PlannedEndTime = "2026-10-29T12:09:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
 actorId = 01949f21-1e1c-7f93-8304-f75982c46284 (generated)
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D142" s="108" t="str">
         <v>Return:
@@ -10736,7 +10732,7 @@
         <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = null, Location = null, OnlineLink = null, Sensitivity = null, Descri…
 actorId = 019790b3-0863-75a5-a3f4-ef6e0cd6798d (generated)
 participants = [{ 019790b3-0863-75a5-a3f4-ef6e0cd6798d (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D144" s="108" t="str">
         <v>Return: true
@@ -10804,7 +10800,7 @@
         <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
 actorId = 019b6f85-c758-702f-84b5-1216ab8bebc2 (generated)
 participants = [{ 019b6f85-c758-702f-84b5-1216ab8bebc2 (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D146" s="108" t="str">
         <v>Return: true
@@ -10873,7 +10869,7 @@
         <v>id = 0199af92-7f91-736d-ad5a-e0f3232c883e (generated)
 input = MeetingInput { Title = "  Giao ban mới  ", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "Hybrid", Location = "Phòng họp A", OnlineLink = null, Sensitivit…
 actorId = 01979603-74ea-72ae-aae3-5bee674a3ccd (generated)
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D148" s="108" t="str">
         <v>Return: true
@@ -10941,7 +10937,7 @@
         <v>id = 019a87bf-4b02-772c-a349-acb8bd59b26c (generated)
 input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = null, Location = "Phòng họp A", OnlineLink = null, Sensitivity = nul…
 actorId = 0196d460-b2cb-70cc-99cc-61405816c2b8 (generated)
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D150" s="108" t="str">
         <v>Return: true
@@ -11082,7 +11078,7 @@
 input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
 actorId = 0197b236-4cfc-7391-a435-4f25fc0b4a5e (generated)
 status = MeetingStatus.Draft
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D154" s="108" t="str">
         <v>Return:
@@ -11130,7 +11126,7 @@
 input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
 actorId = 01971dce-2360-7688-8843-bbf68bef3bee (generated)
 status = MeetingStatus.Rejected
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D155" s="108" t="str">
         <v>Return:
@@ -11202,7 +11198,7 @@
 input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
 actorId = 019f9591-9920-7285-89f6-56ccbdeee38d (generated)
 status = MeetingStatus.WaitingApproval
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D157" s="108" t="str">
         <v>Return: MeetingOutcome.NotEditable
@@ -11248,7 +11244,7 @@
 input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
 actorId = 0197b73c-cf30-7079-b7f7-dcfb49e98a2f (generated)
 status = MeetingStatus.Approved
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D158" s="108" t="str">
         <v>Return: MeetingOutcome.NotEditable
@@ -11294,7 +11290,7 @@
 input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
 actorId = 019408ef-c78b-7fed-b50c-a34eb3c586d3 (generated)
 status = MeetingStatus.InProgress
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D159" s="108" t="str">
         <v>Return: MeetingOutcome.NotEditable
@@ -11340,7 +11336,7 @@
 input = MeetingInput { Title = "", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity = "Internal"…
 actorId = 019fb61b-b24f-7fce-8747-79c00bb8f589 (generated)
 status = MeetingStatus.Ended
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D160" s="108" t="str">
         <v>Return: MeetingOutcome.NotEditable
@@ -11413,7 +11409,7 @@
 actorId = 01962d9f-cbf2-7092-a9b4-0194c3d2cb8a (generated)
 status = MeetingStatus.Draft
 assigned = false
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D162" s="108" t="str">
         <v>Return: true
@@ -11462,7 +11458,7 @@
 actorId = 01963e47-2edc-7642-bad3-14a361d5a7a8 (generated)
 status = MeetingStatus.Rejected
 assigned = false
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D163" s="108" t="str">
         <v>Return: true
@@ -11511,7 +11507,7 @@
 actorId = 0190fe14-7826-7f0b-9eeb-4ca5ecc59e15 (generated)
 status = MeetingStatus.Rejected
 assigned = true
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D164" s="108" t="str">
         <v>Return: true
@@ -11580,7 +11576,7 @@
         <v>id = 01934659-304b-76d9-95e9-5fad5915d2ee (generated)
 input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
 actorId = 019c7d63-bdda-72f9-867e-061f32104143 (generated)
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D166" s="108" t="str">
         <v>Return: true
@@ -12318,7 +12314,7 @@
         <v>input = MeetingInput { Title = "Giao ban tuần", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivity…
 actorId = 01986f74-094e-7e5e-9cae-749fb93b0257 (generated)
 participants = [{ 01986f74-094e-7e5e-9cae-749fb93b0257 (generated), "Chair" }]
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D187" s="108" t="str">
         <v>Return: MeetingOutcome.SaveFailed
@@ -12387,7 +12383,7 @@
         <v>id = 01953d41-8f50-7d90-9c36-58985e7b34cb (generated)
 input = MeetingInput { Title = "Không được lưu", PlannedStartTime = "2026-11-06T02:00:00Z", PlannedEndTime = "2026-11-06T03:00:00Z", Mode = "InPerson", Location = "Phòng họp A", OnlineLink = null, Sensitivit…
 actorId = 0196513e-dd0f-7203-9cd6-70022cd14f5d (generated)
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D189" s="108" t="str">
         <v>Return: MeetingOutcome.SaveFailed
@@ -17339,7 +17335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17807,7 +17803,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -22192,7 +22188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -22997,7 +22993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -29128,7 +29124,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C410E055-B778-4748-989A-3C52FF046FC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA96116-0634-4107-9A3C-AAED46A8D9E4}">
   <dimension ref="B1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -29478,7 +29474,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F85459-3690-4BA5-92E3-3D0DF56699A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07B50A3E-0E72-45C1-991B-3121E7775B09}">
   <dimension ref="A2:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
@@ -30291,7 +30287,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -35860,7 +35856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -36670,7 +36666,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -38665,7 +38661,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -44724,7 +44720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -45935,7 +45931,7 @@
       </c>
       <c r="C35" s="107" t="str">
         <v>webhook = CallWebhookEvent { Id = "EV_" + 01979a88-7fe6-70ef-afc8-9f39f716fab9 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(0191a268-85bc-7c41-b14e-1b6bb7490d3b…
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D35" s="108" t="str">
         <v>Return:
@@ -46008,7 +46004,7 @@
         <v>webhook = CallWebhookEvent { Id = "EV_" + 019686e5-b231-7211-a6f8-f46aee776882 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(0195a308-fab2-7751-b554-678afe222328…
 status = MeetingStatus.Ended
 mode = MeetingMode.Online
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D37" s="108" t="str">
         <v>Return:
@@ -46054,7 +46050,7 @@
         <v>webhook = CallWebhookEvent { Id = "EV_" + 019fe97c-7da7-7d66-9824-20e027e03fee (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(01957524-7104-7fca-ac89-dbd1e87bbc7d…
 status = MeetingStatus.InProgress
 mode = MeetingMode.InPerson
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D38" s="108" t="str">
         <v>Return:
@@ -46122,7 +46118,7 @@
       </c>
       <c r="C40" s="107" t="str">
         <v>webhook = CallWebhookEvent { Id = "EV_" + 0198237c-5cfe-7301-a845-7f63ed59c498 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(019fca7f-9364-7ed1-8eef-3042b092fc3a…
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D40" s="108" t="str">
         <v>Return:
@@ -46189,7 +46185,7 @@
       </c>
       <c r="C42" s="107" t="str">
         <v>webhook = CallWebhookEvent { Id = "EV_" + 019ab214-69d5-777c-96cf-2ec3f84e0df7 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(0196948b-e368-77e4-ab2b-889622bc30b1…
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D42" s="108" t="str">
         <v>Return: empty
@@ -46254,7 +46250,7 @@
       </c>
       <c r="C44" s="107" t="str">
         <v>webhook = CallWebhookEvent { Id = "EV_" + 01931cfb-bc4a-7aeb-969b-5a179935a1cc (generated).ToString("N"), Event = "track_published", RoomName = CallRoomNames.ForMeeting(01970584-aa5a-7126-a6c3-c32a3755e6da (ge…
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D44" s="108" t="str">
         <v>Return: (Room, _chair.ToString("D"), "TR_old")
@@ -46320,7 +46316,7 @@
       </c>
       <c r="C46" s="107" t="str">
         <v>webhook = CallWebhookEvent { Id = "EV_" + 0191e55e-e6dc-7547-a6a1-9b911a650f43 (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(019acbd9-5a99-7ffe-aacd-af2a6b1a87cc…
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D46" s="108" t="str">
         <v>Return:
@@ -46388,7 +46384,7 @@
       </c>
       <c r="C48" s="107" t="str">
         <v>webhook = CallWebhookEvent { Id = "EV_" + 0192df99-b016-7aa7-9bcc-147b985e253c (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(01924a95-010b-7a65-89aa-927490e30321…
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D48" s="108" t="str">
         <v>Return:
@@ -46457,7 +46453,7 @@
       </c>
       <c r="C50" s="107" t="str">
         <v>webhook = CallWebhookEvent { Id = "EV_" + 0197f548-b518-70f0-8f68-da1041a0c0af (generated).ToString("N"), Event = "participant_joined", RoomName = CallRoomNames.ForMeeting(0199a7da-a6e4-75ba-84dd-9642895b0c71…
-(times counted from the run date, here 30/10/2026 10:36 UTC)</v>
+(times counted from the run date, here 30/10/2026 11:09 UTC)</v>
       </c>
       <c r="D50" s="108" t="str">
         <v>Return: empty
@@ -46911,7 +46907,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32029CD-BB41-4075-8060-21D08861851D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5340C85-7128-46DD-8EF0-462B949D9F63}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
